--- a/Financial Analysis/AMZN.xlsx
+++ b/Financial Analysis/AMZN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E979305E-CCA4-4C17-9AFD-9A85A3195A36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4275EE7-5152-4AFA-900E-5DDB5F7E34D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EA1D195A-C8DC-4C80-AD05-94F317AC85A7}"/>
   </bookViews>
@@ -877,14 +877,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>189.98</v>
+        <v>204.88</v>
       </c>
       <c r="E3" s="2">
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45781</v>
+        <v>45804</v>
       </c>
       <c r="G3" s="2">
         <v>45869</v>
@@ -930,7 +930,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>2016903.6719999998</v>
+        <v>2175088.0319999997</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>1968324.6719999998</v>
+        <v>2126509.0319999997</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -3434,7 +3434,7 @@
         <v>3071.41</v>
       </c>
       <c r="AK11" s="4">
-        <f t="shared" ref="AJ11:AL11" si="42">AG11*1.04</f>
+        <f t="shared" ref="AK11:AL11" si="42">AG11*1.04</f>
         <v>2821.52</v>
       </c>
       <c r="AL11" s="4">
@@ -5348,7 +5348,7 @@
         <v>-1</v>
       </c>
       <c r="AJ20" s="4">
-        <f t="shared" ref="AI20:AL20" si="113">AJ18*0.001</f>
+        <f t="shared" ref="AJ20:AL20" si="113">AJ18*0.001</f>
         <v>17.079328749999995</v>
       </c>
       <c r="AK20" s="4">
@@ -6201,47 +6201,47 @@
         <v>10515</v>
       </c>
       <c r="AY22" s="4">
-        <f>10616.4</f>
+        <f t="shared" ref="AY22:BI22" si="133">10616.4</f>
         <v>10616.4</v>
       </c>
       <c r="AZ22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BA22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BB22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BC22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BD22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BE22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BF22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BG22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BH22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
       <c r="BI22" s="4">
-        <f>10616.4</f>
+        <f t="shared" si="133"/>
         <v>10616.4</v>
       </c>
     </row>
@@ -6250,235 +6250,235 @@
         <v>50</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23:R23" si="133">C21/C22</f>
+        <f t="shared" ref="C23:R23" si="134">C21/C22</f>
         <v>1.437648927720413</v>
       </c>
       <c r="D23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.39118347895154881</v>
       </c>
       <c r="E23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>0.50833995234312945</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.6854646544876886</v>
       </c>
       <c r="G23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>3.2347100873709294</v>
       </c>
       <c r="H23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>5.0317712470214451</v>
       </c>
       <c r="I23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>5.7247815726767275</v>
       </c>
       <c r="J23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>6.0107227958697376</v>
       </c>
       <c r="K23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>7.071088165210484</v>
       </c>
       <c r="L23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>5.2124702144559167</v>
       </c>
       <c r="M23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>4.2374900714853059</v>
       </c>
       <c r="N23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>6.4892772041302615</v>
       </c>
       <c r="O23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>5.0337569499602859</v>
       </c>
       <c r="P23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>10.411040508339951</v>
       </c>
       <c r="Q23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>12.571485305798252</v>
       </c>
       <c r="R23" s="6">
-        <f t="shared" si="133"/>
+        <f t="shared" si="134"/>
         <v>14.340746624305003</v>
       </c>
       <c r="S23" s="6">
-        <f t="shared" ref="S23:V23" si="134">S21/S22</f>
+        <f t="shared" ref="S23:V23" si="135">S21/S22</f>
         <v>16.098093725178714</v>
       </c>
       <c r="T23" s="6">
-        <f t="shared" ref="T23:U23" si="135">T21/T22</f>
+        <f t="shared" ref="T23:U23" si="136">T21/T22</f>
         <v>15.401980198019801</v>
       </c>
       <c r="U23" s="6">
+        <f t="shared" si="136"/>
+        <v>6.21259842519685</v>
+      </c>
+      <c r="V23" s="6">
         <f t="shared" si="135"/>
-        <v>6.21259842519685</v>
-      </c>
-      <c r="V23" s="6">
-        <f t="shared" si="134"/>
         <v>28.194881889763778</v>
       </c>
       <c r="W23" s="6">
-        <f t="shared" ref="W23:X23" si="136">W21/W22</f>
+        <f t="shared" ref="W23:X23" si="137">W21/W22</f>
         <v>-7.5520628683693518</v>
       </c>
       <c r="X23" s="6">
-        <f t="shared" si="136"/>
+        <f t="shared" si="137"/>
         <v>-0.19931203931203931</v>
       </c>
       <c r="Y23" s="6">
-        <f t="shared" ref="Y23" si="137">Y21/Y22</f>
+        <f t="shared" ref="Y23" si="138">Y21/Y22</f>
         <v>0.28181728976547932</v>
       </c>
       <c r="Z23" s="6">
-        <f t="shared" ref="Z23" si="138">Z21/Z22</f>
+        <f t="shared" ref="Z23" si="139">Z21/Z22</f>
         <v>2.7201565557729943E-2</v>
       </c>
       <c r="AA23" s="6">
-        <f t="shared" ref="AA23:AB23" si="139">AA21/AA22</f>
+        <f t="shared" ref="AA23:AB23" si="140">AA21/AA22</f>
         <v>0.30946341463414634</v>
       </c>
       <c r="AB23" s="6">
-        <f t="shared" si="139"/>
+        <f t="shared" si="140"/>
         <v>0.65629557608167233</v>
       </c>
       <c r="AC23" s="6">
-        <f t="shared" ref="AC23" si="140">AC21/AC22</f>
+        <f t="shared" ref="AC23" si="141">AC21/AC22</f>
         <v>0.9570819608602984</v>
       </c>
       <c r="AD23" s="6">
-        <f t="shared" ref="AD23" si="141">AD21/AD22</f>
+        <f t="shared" ref="AD23" si="142">AD21/AD22</f>
         <v>1.0258787176516029</v>
       </c>
       <c r="AE23" s="6">
-        <f t="shared" ref="AE23:AF23" si="142">AE21/AE22</f>
+        <f t="shared" ref="AE23:AF23" si="143">AE21/AE22</f>
         <v>1.0036563071297988</v>
       </c>
       <c r="AF23" s="6">
-        <f t="shared" si="142"/>
+        <f t="shared" si="143"/>
         <v>1.2975079380352159</v>
       </c>
       <c r="AG23" s="6">
-        <f t="shared" ref="AG23:AH23" si="143">AG21/AG22</f>
+        <f t="shared" ref="AG23:AH23" si="144">AG21/AG22</f>
         <v>1.4577270565858298</v>
       </c>
       <c r="AH23" s="6">
-        <f t="shared" si="143"/>
+        <f t="shared" si="144"/>
         <v>1.8957543593631538</v>
       </c>
       <c r="AI23" s="6">
-        <f t="shared" ref="AI23:AL23" si="144">AI21/AI22</f>
+        <f t="shared" ref="AI23:AL23" si="145">AI21/AI22</f>
         <v>1.6132587317734826</v>
       </c>
       <c r="AJ23" s="6">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>1.3819320481754638</v>
       </c>
       <c r="AK23" s="6">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>1.6615170522964469</v>
       </c>
       <c r="AL23" s="6">
-        <f t="shared" si="144"/>
+        <f t="shared" si="145"/>
         <v>2.1470732429354586</v>
       </c>
       <c r="AN23" s="6">
-        <f t="shared" ref="AN23:AV23" si="145">AN21/AN22</f>
+        <f t="shared" ref="AN23:AV23" si="146">AN21/AN22</f>
         <v>-0.4785544082605242</v>
       </c>
       <c r="AO23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>1.1834789515488482</v>
       </c>
       <c r="AP23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>4.7081016679904684</v>
       </c>
       <c r="AQ23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>6.0226370135027798</v>
       </c>
       <c r="AR23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>20.001985702938839</v>
       </c>
       <c r="AS23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>23.010325655281967</v>
       </c>
       <c r="AT23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>42.35702938840349</v>
       </c>
       <c r="AU23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>66.25099285146942</v>
       </c>
       <c r="AV23" s="6">
-        <f t="shared" si="145"/>
+        <f t="shared" si="146"/>
         <v>-0.26634050880626225</v>
       </c>
       <c r="AW23" s="6">
-        <f t="shared" ref="AW23:BE23" si="146">AW21/AW22</f>
+        <f t="shared" ref="AW23:BE23" si="147">AW21/AW22</f>
         <v>2.9379103901120125</v>
       </c>
       <c r="AX23" s="6">
-        <f t="shared" ref="AX23" si="147">AX21/AX22</f>
+        <f t="shared" ref="AX23" si="148">AX21/AX22</f>
         <v>5.6346172135045176</v>
       </c>
       <c r="AY23" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>6.8037810751808498</v>
       </c>
       <c r="AZ23" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>8.5127027461413523</v>
       </c>
       <c r="BA23" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>9.3630550820978371</v>
       </c>
       <c r="BB23" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>10.074121523173281</v>
       </c>
       <c r="BC23" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>10.521224056004034</v>
       </c>
       <c r="BD23" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>10.875842442324762</v>
       </c>
       <c r="BE23" s="6">
-        <f t="shared" si="146"/>
+        <f t="shared" si="147"/>
         <v>11.116970421638808</v>
       </c>
       <c r="BF23" s="6">
-        <f t="shared" ref="BF23:BI23" si="148">BF21/BF22</f>
+        <f t="shared" ref="BF23:BI23" si="149">BF21/BF22</f>
         <v>11.37518421876597</v>
       </c>
       <c r="BG23" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>11.509476458646466</v>
       </c>
       <c r="BH23" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>11.646172016177049</v>
       </c>
       <c r="BI23" s="6">
-        <f t="shared" si="148"/>
+        <f t="shared" si="149"/>
         <v>11.785348945557789</v>
       </c>
     </row>
@@ -6495,127 +6495,127 @@
         <v>0.33163394286677339</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" ref="H25:V25" si="149">H3/D3-1</f>
+        <f t="shared" ref="H25:V25" si="150">H3/D3-1</f>
         <v>0.28769448373408779</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.17303948832035587</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>8.166969147005454E-2</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>8.4733428255022947E-2</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.12528245041426067</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.17720618739998817</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.13069351230425053</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.22045911968030807</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.40127175368139234</v>
       </c>
       <c r="Q25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.32844988168957356</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.40588025800324479</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.37403503740350375</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>0.15444630204601539</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>3.9830219426232549E-2</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="149"/>
+        <f t="shared" si="150"/>
         <v>5.0664264805224679E-3</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" ref="W25:W27" si="150">W3/S3-1</f>
+        <f t="shared" ref="W25:W27" si="151">W3/S3-1</f>
         <v>-1.8020211859247515E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" ref="X25:X27" si="151">X3/T3-1</f>
+        <f t="shared" ref="X25:X27" si="152">X3/T3-1</f>
         <v>-2.4636231984001111E-2</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" ref="Y25:Y27" si="152">Y3/U3-1</f>
+        <f t="shared" ref="Y25:Y27" si="153">Y3/U3-1</f>
         <v>8.1347036956046281E-2</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" ref="Z25:Z27" si="153">Z3/V3-1</f>
+        <f t="shared" ref="Z25:Z27" si="154">Z3/V3-1</f>
         <v>-1.2392181023860194E-2</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" ref="AA25:AA27" si="154">AA3/W3-1</f>
+        <f t="shared" ref="AA25:AA27" si="155">AA3/W3-1</f>
         <v>9.317155256398868E-3</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" ref="AB25:AB27" si="155">AB3/X3-1</f>
+        <f t="shared" ref="AB25:AB27" si="156">AB3/X3-1</f>
         <v>4.342907644719407E-2</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" ref="AC25:AC27" si="156">AC3/Y3-1</f>
+        <f t="shared" ref="AC25:AC27" si="157">AC3/Y3-1</f>
         <v>6.4560161779575242E-2</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" ref="AD25:AD27" si="157">AD3/Z3-1</f>
+        <f t="shared" ref="AD25:AD27" si="158">AD3/Z3-1</f>
         <v>8.7507620762501626E-2</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AE27" si="158">AE3/AA3-1</f>
+        <f t="shared" ref="AE25:AE27" si="159">AE3/AA3-1</f>
         <v>6.9040557378775347E-2</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" ref="AF25:AF27" si="159">AF3/AB3-1</f>
+        <f t="shared" ref="AF25:AF27" si="160">AF3/AB3-1</f>
         <v>4.2976690608483636E-2</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" ref="AG25:AG27" si="160">AG3/AC3-1</f>
+        <f t="shared" ref="AG25:AG27" si="161">AG3/AC3-1</f>
         <v>7.0127115290243847E-2</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" ref="AH25:AH27" si="161">AH3/AD3-1</f>
+        <f t="shared" ref="AH25:AH27" si="162">AH3/AD3-1</f>
         <v>7.200500632309037E-2</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" ref="AI25:AI27" si="162">AI3/AE3-1</f>
+        <f t="shared" ref="AI25:AI27" si="163">AI3/AE3-1</f>
         <v>5.0151850939834208E-2</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" ref="AJ25:AJ27" si="163">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ25:AJ27" si="164">AJ3/AF3-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" ref="AK25:AK27" si="164">AK3/AG3-1</f>
+        <f t="shared" ref="AK25:AK27" si="165">AK3/AG3-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" ref="AL25:AL27" si="165">AL3/AH3-1</f>
+        <f t="shared" ref="AL25:AL27" si="166">AL3/AH3-1</f>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN25" s="10"/>
@@ -6624,83 +6624,83 @@
         <v>0.131107305936073</v>
       </c>
       <c r="AP25" s="10">
-        <f t="shared" ref="AP25:BE25" si="166">AP3/AO3-1</f>
+        <f t="shared" ref="AP25:BE25" si="167">AP3/AO3-1</f>
         <v>0.19423979411616288</v>
       </c>
       <c r="AQ25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0.25254317857708752</v>
       </c>
       <c r="AR25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0.19686772593867019</v>
       </c>
       <c r="AS25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0.13030335059718845</v>
       </c>
       <c r="AT25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0.34604474867056934</v>
       </c>
       <c r="AU25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>0.11982493110714865</v>
       </c>
       <c r="AV25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>4.6073610243726471E-3</v>
       </c>
       <c r="AW25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>5.3462110077768354E-2</v>
       </c>
       <c r="AX25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>6.4184581475416946E-2</v>
       </c>
       <c r="AY25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>4.151235168612355E-2</v>
       </c>
       <c r="AZ25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BA25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BB25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BC25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE25" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="167"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF25" s="10">
-        <f t="shared" ref="BF25:BF27" si="167">BF3/BE3-1</f>
+        <f t="shared" ref="BF25:BF27" si="168">BF3/BE3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG25" s="10">
-        <f t="shared" ref="BG25:BG27" si="168">BG3/BF3-1</f>
+        <f t="shared" ref="BG25:BG27" si="169">BG3/BF3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH25" s="10">
-        <f t="shared" ref="BH25:BH27" si="169">BH3/BG3-1</f>
+        <f t="shared" ref="BH25:BH27" si="170">BH3/BG3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI25" s="10">
-        <f t="shared" ref="BI25:BI27" si="170">BI3/BH3-1</f>
+        <f t="shared" ref="BI25:BI27" si="171">BI3/BH3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -6717,212 +6717,212 @@
         <v>0.62245409015025044</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" ref="H26:V26" si="171">H4/D4-1</f>
+        <f t="shared" ref="H26:V26" si="172">H4/D4-1</f>
         <v>0.5913701741105224</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.52443910256410264</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.44725010455876202</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.30766064721922115</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.3104366853772238</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.32522996057818654</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.33276740237691005</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.32238265727662596</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.40365906780891536</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.43351512146752613</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.47713782355332701</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.5181636964089138</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.42433019551049966</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.28970971386410271</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="172"/>
         <v>0.21095799922934355</v>
       </c>
       <c r="W26" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>0.17563250827993016</v>
       </c>
       <c r="X26" s="10">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>0.17399593289273008</v>
       </c>
       <c r="Y26" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.21140231693363853</v>
       </c>
       <c r="Z26" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>0.19208739923631746</v>
       </c>
       <c r="AA26" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>0.17316508026471511</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>0.16535981069920669</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0.179321438585617</v>
       </c>
       <c r="AD26" s="10">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>0.1853876170986235</v>
       </c>
       <c r="AE26" s="10">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.17080864486977276</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>0.14673992382317413</v>
       </c>
       <c r="AG26" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.14220642706977671</v>
       </c>
       <c r="AH26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0.13197795363400466</v>
       </c>
       <c r="AI26" s="10">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>0.11285468093885775</v>
       </c>
       <c r="AJ26" s="10">
-        <f t="shared" si="163"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AK26" s="10">
         <f t="shared" si="164"/>
         <v>0.10000000000000009</v>
       </c>
-      <c r="AL26" s="10">
+      <c r="AK26" s="10">
         <f t="shared" si="165"/>
         <v>0.10000000000000009</v>
       </c>
+      <c r="AL26" s="10">
+        <f t="shared" si="166"/>
+        <v>0.10000000000000009</v>
+      </c>
       <c r="AN26" s="10"/>
       <c r="AO26" s="10">
-        <f t="shared" ref="AO26:BE26" si="172">AO4/AN4-1</f>
+        <f t="shared" ref="AO26:BE26" si="173">AO4/AN4-1</f>
         <v>0.46699809604400255</v>
       </c>
       <c r="AP26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.48972528661042602</v>
       </c>
       <c r="AQ26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.43492570543536124</v>
       </c>
       <c r="AR26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.53425304415286545</v>
       </c>
       <c r="AS26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.3203513168887131</v>
       </c>
       <c r="AT26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.41655080547808354</v>
       </c>
       <c r="AU26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.34020770030972858</v>
       </c>
       <c r="AV26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.18877365316727701</v>
       </c>
       <c r="AW26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.17638943197999124</v>
       </c>
       <c r="AX26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.14659859892504823</v>
       </c>
       <c r="AY26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>0.10289677504047612</v>
       </c>
       <c r="AZ26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="BA26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="BB26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BC26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BD26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="173"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF26" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG26" s="10">
-        <f t="shared" si="168"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BH26" s="10">
         <f t="shared" si="169"/>
         <v>1.0000000000000009E-2</v>
       </c>
+      <c r="BH26" s="10">
+        <f t="shared" si="170"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="BI26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -6939,212 +6939,212 @@
         <v>0.42918743349946809</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" ref="H27:V27" si="173">H5/D5-1</f>
+        <f t="shared" ref="H27:V27" si="174">H5/D5-1</f>
         <v>0.39338690554604128</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.29334308705193846</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.19734339073329688</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.16962501469378166</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.1988806111258179</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.23693792420814486</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.20797701117665746</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.26385259631490787</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.40230900258658764</v>
       </c>
       <c r="Q27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.37387290836084075</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.43594816839553041</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.43823888034777081</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.27181932697498645</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>0.15255083467679031</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="174"/>
         <v>9.4436701047349692E-2</v>
       </c>
       <c r="W27" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="151"/>
         <v>7.3038574245747334E-2</v>
       </c>
       <c r="X27" s="10">
-        <f t="shared" si="151"/>
+        <f t="shared" si="152"/>
         <v>7.2108241952600016E-2</v>
       </c>
       <c r="Y27" s="10">
-        <f t="shared" si="152"/>
+        <f t="shared" si="153"/>
         <v>0.14699671515720314</v>
       </c>
       <c r="Z27" s="10">
-        <f t="shared" si="153"/>
+        <f t="shared" si="154"/>
         <v>8.5814921549791867E-2</v>
       </c>
       <c r="AA27" s="10">
-        <f t="shared" si="154"/>
+        <f t="shared" si="155"/>
         <v>9.3727456975026602E-2</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="155"/>
+        <f t="shared" si="156"/>
         <v>0.10845967302901816</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="156"/>
+        <f t="shared" si="157"/>
         <v>0.125742519728405</v>
       </c>
       <c r="AD27" s="10">
-        <f t="shared" si="157"/>
+        <f t="shared" si="158"/>
         <v>0.13911825420230017</v>
       </c>
       <c r="AE27" s="10">
-        <f t="shared" si="158"/>
+        <f t="shared" si="159"/>
         <v>0.12527677884388888</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="159"/>
+        <f t="shared" si="160"/>
         <v>0.10115862869559389</v>
       </c>
       <c r="AG27" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="161"/>
         <v>0.11038348371225104</v>
       </c>
       <c r="AH27" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="162"/>
         <v>0.10491230341078239</v>
       </c>
       <c r="AI27" s="10">
-        <f t="shared" si="162"/>
+        <f t="shared" si="163"/>
         <v>8.6202926461660834E-2</v>
       </c>
       <c r="AJ27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="164"/>
         <v>7.9196429174804184E-2</v>
       </c>
       <c r="AK27" s="10">
-        <f t="shared" si="164"/>
+        <f t="shared" si="165"/>
         <v>7.4470439396514321E-2</v>
       </c>
       <c r="AL27" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="166"/>
         <v>6.9350025560194206E-2</v>
       </c>
       <c r="AN27" s="10"/>
       <c r="AO27" s="10">
-        <f t="shared" ref="AO27:BE27" si="174">AO5/AN5-1</f>
+        <f t="shared" ref="AO27:BE27" si="175">AO5/AN5-1</f>
         <v>0.20247673843664304</v>
       </c>
       <c r="AP27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.27083528026465808</v>
       </c>
       <c r="AQ27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.30796326119408479</v>
       </c>
       <c r="AR27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.3093396152159491</v>
       </c>
       <c r="AS27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.20454125820676983</v>
       </c>
       <c r="AT27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.37623430604373276</v>
       </c>
       <c r="AU27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.21695366571345676</v>
       </c>
       <c r="AV27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>9.399517263985091E-2</v>
       </c>
       <c r="AW27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.1182957412988368</v>
       </c>
       <c r="AX27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>0.1099089224666614</v>
       </c>
       <c r="AY27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>7.6695007045907371E-2</v>
       </c>
       <c r="AZ27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>7.348402817248334E-2</v>
       </c>
       <c r="BA27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>6.3845339135212287E-2</v>
       </c>
       <c r="BB27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>4.8155575805053141E-2</v>
       </c>
       <c r="BC27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>3.2240492281612632E-2</v>
       </c>
       <c r="BD27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>2.6166252955616587E-2</v>
       </c>
       <c r="BE27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="175"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF27" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="168"/>
         <v>1.6189290016107805E-2</v>
       </c>
       <c r="BG27" s="10">
-        <f t="shared" si="168"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BH27" s="10">
         <f t="shared" si="169"/>
         <v>1.0000000000000009E-2</v>
       </c>
+      <c r="BH27" s="10">
+        <f t="shared" si="170"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="BI27" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -7153,19 +7153,19 @@
         <v>52</v>
       </c>
       <c r="C28" s="10">
-        <f t="shared" ref="C28:F28" si="175">C7/C5</f>
+        <f t="shared" ref="C28:F28" si="176">C7/C5</f>
         <v>0.37167497339978722</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.38213674087735477</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.37022220190197513</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="176"/>
         <v>0.36324086480406265</v>
       </c>
       <c r="G28" s="10">
@@ -7173,215 +7173,215 @@
         <v>0.39784883037498531</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" ref="H28:V28" si="176">H7/H5</f>
+        <f t="shared" ref="H28:V28" si="177">H7/H5</f>
         <v>0.4207918919941005</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.4166607748868778</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.38126355635991876</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.4318257956448911</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.42689735663365086</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.40981123447792972</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.38267552637899288</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.41344165827280921</v>
       </c>
       <c r="P28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.40772899046247973</v>
       </c>
       <c r="Q28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.40604295595194756</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.36853171916689897</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.42495254243535635</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.43247258577997877</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.43210121647475003</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="177"/>
         <v>0.39717783017494834</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" ref="W28:AE28" si="177">W7/W5</f>
+        <f t="shared" ref="W28:AE28" si="178">W7/W5</f>
         <v>0.42891862182680085</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.4521008957883102</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.44714833085498934</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.42602075011393797</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.46771306082067871</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.48376654785203488</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.47567495789157344</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.45544566106342044</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="178"/>
         <v>0.49318624269954575</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" ref="AF28:AH28" si="178">AF7/AF5</f>
+        <f t="shared" ref="AF28:AH28" si="179">AF7/AF5</f>
         <v>0.50137521371564497</v>
       </c>
       <c r="AG28" s="10">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0.49031640829069029</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" si="178"/>
+        <f t="shared" si="179"/>
         <v>0.47339077276987307</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" ref="AI28:AL28" si="179">AI7/AI5</f>
+        <f t="shared" ref="AI28:AL28" si="180">AI7/AI5</f>
         <v>0.50550855351487467</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="179"/>
-        <v>0.5</v>
-      </c>
-      <c r="AK28" s="10">
-        <f t="shared" si="179"/>
-        <v>0.5</v>
-      </c>
-      <c r="AL28" s="10">
-        <f t="shared" si="179"/>
-        <v>0.48</v>
-      </c>
-      <c r="AN28" s="10">
-        <f t="shared" ref="AN28:BE28" si="180">AN7/AN5</f>
-        <v>0.29482626871038792</v>
-      </c>
-      <c r="AO28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.33040203353083003</v>
-      </c>
-      <c r="AP28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.35093060366064405</v>
-      </c>
-      <c r="AQ28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.3706835482891615</v>
-      </c>
-      <c r="AR28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.40247416128852193</v>
-      </c>
-      <c r="AS28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.40990011478600608</v>
-      </c>
-      <c r="AT28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.3956779186870571</v>
-      </c>
-      <c r="AU28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.42032514441639601</v>
-      </c>
-      <c r="AV28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.43805339865326287</v>
-      </c>
-      <c r="AW28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.46982088955000567</v>
-      </c>
-      <c r="AX28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.48854393464156787</v>
-      </c>
-      <c r="AY28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.49540127217672852</v>
-      </c>
-      <c r="AZ28" s="10">
         <f t="shared" si="180"/>
         <v>0.5</v>
       </c>
-      <c r="BA28" s="10">
+      <c r="AK28" s="10">
         <f t="shared" si="180"/>
         <v>0.5</v>
       </c>
-      <c r="BB28" s="10">
+      <c r="AL28" s="10">
         <f t="shared" si="180"/>
-        <v>0.5</v>
-      </c>
-      <c r="BC28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.5</v>
-      </c>
-      <c r="BD28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.5</v>
-      </c>
-      <c r="BE28" s="10">
-        <f t="shared" si="180"/>
-        <v>0.5</v>
-      </c>
-      <c r="BF28" s="10">
-        <f t="shared" ref="BF28:BI28" si="181">BF7/BF5</f>
-        <v>0.5</v>
-      </c>
-      <c r="BG28" s="10">
+        <v>0.48</v>
+      </c>
+      <c r="AN28" s="10">
+        <f t="shared" ref="AN28:BE28" si="181">AN7/AN5</f>
+        <v>0.29482626871038792</v>
+      </c>
+      <c r="AO28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.33040203353083003</v>
+      </c>
+      <c r="AP28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.35093060366064405</v>
+      </c>
+      <c r="AQ28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.3706835482891615</v>
+      </c>
+      <c r="AR28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.40247416128852193</v>
+      </c>
+      <c r="AS28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.40990011478600608</v>
+      </c>
+      <c r="AT28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.3956779186870571</v>
+      </c>
+      <c r="AU28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.42032514441639601</v>
+      </c>
+      <c r="AV28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.43805339865326287</v>
+      </c>
+      <c r="AW28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.46982088955000567</v>
+      </c>
+      <c r="AX28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.48854393464156787</v>
+      </c>
+      <c r="AY28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.49540127217672852</v>
+      </c>
+      <c r="AZ28" s="10">
         <f t="shared" si="181"/>
         <v>0.5</v>
       </c>
-      <c r="BH28" s="10">
+      <c r="BA28" s="10">
         <f t="shared" si="181"/>
         <v>0.5</v>
       </c>
+      <c r="BB28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.5</v>
+      </c>
+      <c r="BC28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.5</v>
+      </c>
+      <c r="BD28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.5</v>
+      </c>
+      <c r="BE28" s="10">
+        <f t="shared" si="181"/>
+        <v>0.5</v>
+      </c>
+      <c r="BF28" s="10">
+        <f t="shared" ref="BF28:BI28" si="182">BF7/BF5</f>
+        <v>0.5</v>
+      </c>
+      <c r="BG28" s="10">
+        <f t="shared" si="182"/>
+        <v>0.5</v>
+      </c>
+      <c r="BH28" s="10">
+        <f t="shared" si="182"/>
+        <v>0.5</v>
+      </c>
       <c r="BI28" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="182"/>
         <v>0.5</v>
       </c>
     </row>
@@ -7390,19 +7390,19 @@
         <v>53</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:F29" si="182">C14/C5</f>
+        <f t="shared" ref="C29:F29" si="183">C14/C5</f>
         <v>2.8140225121800973E-2</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>1.6545909629824794E-2</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>7.932516459400147E-3</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="183"/>
         <v>3.5184358096372388E-2</v>
       </c>
       <c r="G29" s="10">
@@ -7410,215 +7410,215 @@
         <v>3.7753222836095765E-2</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" ref="H29:V29" si="183">H14/H5</f>
+        <f t="shared" ref="H29:V29" si="184">H14/H5</f>
         <v>5.6404341413606625E-2</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>6.5822963800904979E-2</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>5.230509926363925E-2</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>7.4036850921273031E-2</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>4.8640464324017411E-2</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>4.5112244752147014E-2</v>
       </c>
       <c r="N29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>4.4363370197971111E-2</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>5.2868048560674334E-2</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>6.5716663667446468E-2</v>
       </c>
       <c r="Q29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>6.4423526964480726E-2</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>5.4740950181195493E-2</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>8.1691516614755155E-2</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>6.8111071807569867E-2</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>4.3785871566256365E-2</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="184"/>
         <v>2.5179751404535267E-2</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" ref="W29:AE29" si="184">W14/W5</f>
+        <f t="shared" ref="W29:AE29" si="185">W14/W5</f>
         <v>3.1508708048504003E-2</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>2.7360311463780786E-2</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>1.986609074672898E-2</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>1.8344012224873328E-2</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>3.7484885126964934E-2</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>5.7157527365812637E-2</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>7.8192377850618167E-2</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>7.771782938438819E-2</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="185"/>
         <v>0.10680817511321374</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" ref="AF29:AH29" si="185">AF14/AF5</f>
+        <f t="shared" ref="AF29:AH29" si="186">AF14/AF5</f>
         <v>9.9150543665569649E-2</v>
       </c>
       <c r="AG29" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.1095879202150091</v>
       </c>
       <c r="AH29" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="186"/>
         <v>0.1129068330919315</v>
       </c>
       <c r="AI29" s="10">
-        <f t="shared" ref="AI29:AL29" si="186">AI14/AI5</f>
+        <f t="shared" ref="AI29:AL29" si="187">AI14/AI5</f>
         <v>0.11823315153500742</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0.10291868938688288</v>
       </c>
       <c r="AK29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0.11618706586848795</v>
       </c>
       <c r="AL29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="187"/>
         <v>0.12604236637651955</v>
       </c>
       <c r="AN29" s="10">
-        <f t="shared" ref="AN29:BE29" si="187">AN14/AN5</f>
+        <f t="shared" ref="AN29:BE29" si="188">AN14/AN5</f>
         <v>2.000269699285297E-3</v>
       </c>
       <c r="AO29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>2.0867988710913405E-2</v>
       </c>
       <c r="AP29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>3.0782354195621642E-2</v>
       </c>
       <c r="AQ29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>2.3090416380870993E-2</v>
       </c>
       <c r="AR29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>5.3330585219441187E-2</v>
       </c>
       <c r="AS29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>5.1831941879781268E-2</v>
       </c>
       <c r="AT29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>5.9313999751336569E-2</v>
       </c>
       <c r="AU29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>5.2954097509269465E-2</v>
       </c>
       <c r="AV29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>2.3829581912242232E-2</v>
       </c>
       <c r="AW29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>6.4114407996033296E-2</v>
       </c>
       <c r="AX29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.1075194487420038</v>
       </c>
       <c r="AY29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.11644721622224849</v>
       </c>
       <c r="AZ29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.13609238614352212</v>
       </c>
       <c r="BA29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.14113833995967062</v>
       </c>
       <c r="BB29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.14512611859442434</v>
       </c>
       <c r="BC29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.14683313651576702</v>
       </c>
       <c r="BD29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.14782537355703679</v>
       </c>
       <c r="BE29" s="10">
-        <f t="shared" si="187"/>
+        <f t="shared" si="188"/>
         <v>0.14795580959312712</v>
       </c>
       <c r="BF29" s="10">
-        <f t="shared" ref="BF29:BI29" si="188">BF14/BF5</f>
+        <f t="shared" ref="BF29:BI29" si="189">BF14/BF5</f>
         <v>0.14879851375279768</v>
       </c>
       <c r="BG29" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.14877562692746168</v>
       </c>
       <c r="BH29" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.14875228689766357</v>
       </c>
       <c r="BI29" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="189"/>
         <v>0.14872848468905753</v>
       </c>
       <c r="BK29" t="s">
@@ -7633,19 +7633,19 @@
         <v>54</v>
       </c>
       <c r="C30" s="10">
-        <f t="shared" ref="C30:F30" si="189">C8/C5</f>
+        <f t="shared" ref="C30:F30" si="190">C8/C5</f>
         <v>0.1315170521364171</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.13589777367935713</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.1467629846378932</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="190"/>
         <v>0.14844590012075495</v>
       </c>
       <c r="G30" s="10">
@@ -7653,215 +7653,215 @@
         <v>0.15265859488264566</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" ref="H30:V30" si="190">H8/H5</f>
+        <f t="shared" ref="H30:V30" si="191">H8/H5</f>
         <v>0.1499829822637371</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.14626343325791855</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.13854081759529172</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.14407035175879396</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.14622105860828971</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.14528229090753206</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.13943753788441965</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.15282563749138525</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.15527712794673384</v>
       </c>
       <c r="Q30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.15294607103853555</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.1471387041535582</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.15232495991448422</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.15597806862398303</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.16693137927300292</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="191"/>
         <v>0.16334090181352429</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" ref="W30:AE30" si="191">W8/W5</f>
+        <f t="shared" ref="W30:AE30" si="192">W8/W5</f>
         <v>0.17408367970870117</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.1677912136859297</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.16194207756036538</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.15484169325219163</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.16414359521977417</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.15853939858464242</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.15595144077213924</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.15353522278640394</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="192"/>
         <v>0.15572209080823093</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" ref="AF30:AH30" si="192">AF8/AF5</f>
+        <f t="shared" ref="AF30:AH30" si="193">AF8/AF5</f>
         <v>0.1592544787365604</v>
       </c>
       <c r="AG30" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0.15521441114824674</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="193"/>
         <v>0.14889878163074038</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" ref="AI30:AL30" si="193">AI8/AI5</f>
+        <f t="shared" ref="AI30:AL30" si="194">AI8/AI5</f>
         <v>0.15798467240969505</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>0.16</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="194"/>
         <v>0.16</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="193"/>
-        <v>0.15</v>
-      </c>
-      <c r="AN30" s="10">
-        <f t="shared" ref="AN30:BE30" si="194">AN8/AN5</f>
-        <v>0.12098260439609836</v>
-      </c>
-      <c r="AO30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.1253200755097845</v>
-      </c>
-      <c r="AP30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.12956385536852788</v>
-      </c>
-      <c r="AQ30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.14195517974205302</v>
-      </c>
-      <c r="AR30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.14610948657503425</v>
-      </c>
-      <c r="AS30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.14341477673765338</v>
-      </c>
-      <c r="AT30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15157072402503211</v>
-      </c>
-      <c r="AU30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15987118525739535</v>
-      </c>
-      <c r="AV30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.16401126107283703</v>
-      </c>
-      <c r="AW30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.1576572109571405</v>
-      </c>
-      <c r="AX30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15440647439725749</v>
-      </c>
-      <c r="AY30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15661971636190025</v>
-      </c>
-      <c r="AZ30" s="10">
         <f t="shared" si="194"/>
         <v>0.15</v>
       </c>
-      <c r="BA30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15</v>
-      </c>
-      <c r="BB30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15</v>
-      </c>
-      <c r="BC30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15</v>
-      </c>
-      <c r="BD30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.15</v>
-      </c>
-      <c r="BE30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.14999999999999997</v>
-      </c>
-      <c r="BF30" s="10">
-        <f t="shared" ref="BF30:BI30" si="195">BF8/BF5</f>
-        <v>0.15</v>
-      </c>
-      <c r="BG30" s="10">
+      <c r="AN30" s="10">
+        <f t="shared" ref="AN30:BE30" si="195">AN8/AN5</f>
+        <v>0.12098260439609836</v>
+      </c>
+      <c r="AO30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.1253200755097845</v>
+      </c>
+      <c r="AP30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.12956385536852788</v>
+      </c>
+      <c r="AQ30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.14195517974205302</v>
+      </c>
+      <c r="AR30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.14610948657503425</v>
+      </c>
+      <c r="AS30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.14341477673765338</v>
+      </c>
+      <c r="AT30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.15157072402503211</v>
+      </c>
+      <c r="AU30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.15987118525739535</v>
+      </c>
+      <c r="AV30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.16401126107283703</v>
+      </c>
+      <c r="AW30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.1576572109571405</v>
+      </c>
+      <c r="AX30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.15440647439725749</v>
+      </c>
+      <c r="AY30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.15661971636190025</v>
+      </c>
+      <c r="AZ30" s="10">
         <f t="shared" si="195"/>
         <v>0.15</v>
       </c>
-      <c r="BH30" s="10">
+      <c r="BA30" s="10">
         <f t="shared" si="195"/>
         <v>0.15</v>
       </c>
+      <c r="BB30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.15</v>
+      </c>
+      <c r="BC30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.15</v>
+      </c>
+      <c r="BD30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.15</v>
+      </c>
+      <c r="BE30" s="10">
+        <f t="shared" si="195"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="BF30" s="10">
+        <f t="shared" ref="BF30:BI30" si="196">BF8/BF5</f>
+        <v>0.15</v>
+      </c>
+      <c r="BG30" s="10">
+        <f t="shared" si="196"/>
+        <v>0.15</v>
+      </c>
+      <c r="BH30" s="10">
+        <f t="shared" si="196"/>
+        <v>0.15</v>
+      </c>
       <c r="BI30" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="196"/>
         <v>0.15</v>
       </c>
       <c r="BK30" t="s">
@@ -7884,212 +7884,212 @@
         <v>0.4057291666666667</v>
       </c>
       <c r="H31" s="10">
-        <f t="shared" ref="H31:V31" si="196">H9/D9-1</f>
+        <f t="shared" ref="H31:V31" si="197">H9/D9-1</f>
         <v>0.30148048452220721</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.33239209358612354</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.42761627906976751</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>1.9370137087810302</v>
       </c>
       <c r="L31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>2.1247845570492934</v>
       </c>
       <c r="M31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>1.7853466545564638</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.98330278965587459</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.17635927841554189</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.14594594594594601</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.19304347826086965</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.23706365503080074</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.33919571045576413</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.33529072006160954</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.310131195335277</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="197"/>
         <v>0.27089385011204259</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" ref="W31" si="197">W9/S9-1</f>
+        <f t="shared" ref="W31" si="198">W9/S9-1</f>
         <v>0.18850096092248569</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" ref="X31" si="198">X9/T9-1</f>
+        <f t="shared" ref="X31" si="199">X9/T9-1</f>
         <v>0.3028620863672411</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" ref="Y31" si="199">Y9/U9-1</f>
+        <f t="shared" ref="Y31" si="200">Y9/U9-1</f>
         <v>0.35500695410292082</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" ref="Z31" si="200">Z9/V9-1</f>
+        <f t="shared" ref="Z31" si="201">Z9/V9-1</f>
         <v>0.35923724939593815</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" ref="AA31" si="201">AA9/W9-1</f>
+        <f t="shared" ref="AA31" si="202">AA9/W9-1</f>
         <v>0.37784665139469076</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" ref="AB31" si="202">AB9/X9-1</f>
+        <f t="shared" ref="AB31" si="203">AB9/X9-1</f>
         <v>0.21353474988933163</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" ref="AC31" si="203">AC9/Y9-1</f>
+        <f t="shared" ref="AC31" si="204">AC9/Y9-1</f>
         <v>8.8170387477546797E-2</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" ref="AD31" si="204">AD9/Z9-1</f>
+        <f t="shared" ref="AD31" si="205">AD9/Z9-1</f>
         <v>5.880657249927923E-2</v>
       </c>
       <c r="AE31" s="10">
-        <f t="shared" ref="AE31" si="205">AE9/AA9-1</f>
+        <f t="shared" ref="AE31" si="206">AE9/AA9-1</f>
         <v>-1.2713936430317485E-3</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" ref="AF31" si="206">AF9/AB9-1</f>
+        <f t="shared" ref="AF31" si="207">AF9/AB9-1</f>
         <v>1.7007888377182923E-2</v>
       </c>
       <c r="AG31" s="10">
-        <f t="shared" ref="AG31" si="207">AG9/AC9-1</f>
+        <f t="shared" ref="AG31" si="208">AG9/AC9-1</f>
         <v>4.9143989058152204E-2</v>
       </c>
       <c r="AH31" s="10">
-        <f t="shared" ref="AH31" si="208">AH9/AD9-1</f>
+        <f t="shared" ref="AH31" si="209">AH9/AD9-1</f>
         <v>6.9561666212905049E-2</v>
       </c>
       <c r="AI31" s="10">
-        <f t="shared" ref="AI31" si="209">AI9/AE9-1</f>
+        <f t="shared" ref="AI31" si="210">AI9/AE9-1</f>
         <v>0.12583235409322358</v>
       </c>
       <c r="AJ31" s="10">
-        <f t="shared" ref="AJ31" si="210">AJ9/AF9-1</f>
+        <f t="shared" ref="AJ31" si="211">AJ9/AF9-1</f>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" ref="AK31" si="211">AK9/AG9-1</f>
+        <f t="shared" ref="AK31" si="212">AK9/AG9-1</f>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="AL31" s="10">
-        <f t="shared" ref="AL31" si="212">AL9/AH9-1</f>
+        <f t="shared" ref="AL31" si="213">AL9/AH9-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN31" s="10"/>
       <c r="AO31" s="10">
-        <f t="shared" ref="AO31:BE31" si="213">AO9/AN9-1</f>
+        <f t="shared" ref="AO31:BE31" si="214">AO9/AN9-1</f>
         <v>0.21283471837488466</v>
       </c>
       <c r="AP31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.37666539779215835</v>
       </c>
       <c r="AQ31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.3919535462463708</v>
       </c>
       <c r="AR31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.37206992451330945</v>
       </c>
       <c r="AS31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>1.6011292891269728</v>
       </c>
       <c r="AT31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.18941333630190349</v>
       </c>
       <c r="AU31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.31152604239786608</v>
       </c>
       <c r="AV31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.3061621351602084</v>
       </c>
       <c r="AW31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>0.16949175692841445</v>
       </c>
       <c r="AX31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>3.4126743126766446E-2</v>
       </c>
       <c r="AY31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>8.510469371160112E-2</v>
       </c>
       <c r="AZ31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BA31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BB31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE31" s="10">
-        <f t="shared" si="213"/>
+        <f t="shared" si="214"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF31" s="10">
-        <f t="shared" ref="BF31" si="214">BF9/BE9-1</f>
+        <f t="shared" ref="BF31" si="215">BF9/BE9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG31" s="10">
-        <f t="shared" ref="BG31" si="215">BG9/BF9-1</f>
+        <f t="shared" ref="BG31" si="216">BG9/BF9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH31" s="10">
-        <f t="shared" ref="BH31" si="216">BH9/BG9-1</f>
+        <f t="shared" ref="BH31" si="217">BH9/BG9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI31" s="10">
-        <f t="shared" ref="BI31" si="217">BI9/BH9-1</f>
+        <f t="shared" ref="BI31" si="218">BI9/BH9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK31" t="s">
@@ -8105,19 +8105,19 @@
         <v>56</v>
       </c>
       <c r="C32" s="10">
-        <f t="shared" ref="C32:F32" si="218">C10/C5</f>
+        <f t="shared" ref="C32:F32" si="219">C10/C5</f>
         <v>0.13476507812062496</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0.14619944671321303</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0.13588149231894661</v>
       </c>
       <c r="F32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="219"/>
         <v>0.10444477527996957</v>
       </c>
       <c r="G32" s="10">
@@ -8125,215 +8125,215 @@
         <v>0.13242035970377336</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:V32" si="219">H10/H5</f>
+        <f t="shared" ref="H32:V32" si="220">H10/H5</f>
         <v>0.13703059410808152</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>0.12659078054298642</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>0.10595029219568131</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>6.137353433835846E-2</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>6.767711816289193E-2</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>6.7904145410897246E-2</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>7.0587966192801679E-2</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>6.3987700789906163E-2</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>4.8868544178513586E-2</v>
       </c>
       <c r="Q32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>5.6518799729575124E-2</v>
       </c>
       <c r="R32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>5.8962207797379637E-2</v>
       </c>
       <c r="S32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>5.7197884221972389E-2</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>6.6536964980544747E-2</v>
       </c>
       <c r="U32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>7.2284590116593869E-2</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="220"/>
         <v>7.8668529677175206E-2</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" ref="W32:AE32" si="220">W10/W5</f>
+        <f t="shared" ref="W32:AE32" si="221">W10/W5</f>
         <v>7.1450654391810656E-2</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>8.3194483395747074E-2</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>8.6655494449296225E-2</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>8.5909224953754595E-2</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>7.9869344681920251E-2</v>
       </c>
       <c r="AB32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>7.9958030405631667E-2</v>
       </c>
       <c r="AC32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>7.3740416401668965E-2</v>
       </c>
       <c r="AD32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>7.5911532645724603E-2</v>
       </c>
       <c r="AE32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="221"/>
         <v>6.7418866397326138E-2</v>
       </c>
       <c r="AF32" s="10">
-        <f t="shared" ref="AF32:AH32" si="221">AF10/AF5</f>
+        <f t="shared" ref="AF32:AH32" si="222">AF10/AF5</f>
         <v>7.1038066726585886E-2</v>
       </c>
       <c r="AG32" s="10">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>6.6774926515480532E-2</v>
       </c>
       <c r="AH32" s="10">
-        <f t="shared" si="221"/>
+        <f t="shared" si="222"/>
         <v>6.9885831132316611E-2</v>
       </c>
       <c r="AI32" s="10">
-        <f t="shared" ref="AI32:AL32" si="222">AI10/AI5</f>
+        <f t="shared" ref="AI32:AL32" si="223">AI10/AI5</f>
         <v>6.2717210455652123E-2</v>
       </c>
       <c r="AJ32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AK32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AL32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="223"/>
         <v>6.5000000000000002E-2</v>
       </c>
       <c r="AN32" s="10">
-        <f t="shared" ref="AN32:BE32" si="223">AN10/AN5</f>
+        <f t="shared" ref="AN32:BE32" si="224">AN10/AN5</f>
         <v>0.10422753629702881</v>
       </c>
       <c r="AO32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.11718969029774032</v>
       </c>
       <c r="AP32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.11828336532168517</v>
       </c>
       <c r="AQ32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.12717438970910686</v>
       </c>
       <c r="AR32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>0.12382400048091993</v>
       </c>
       <c r="AS32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>6.7299534439366607E-2</v>
       </c>
       <c r="AT32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>5.7011272742343237E-2</v>
       </c>
       <c r="AU32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>6.9283686161993263E-2</v>
       </c>
       <c r="AV32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>8.2177815219569517E-2</v>
       </c>
       <c r="AW32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>7.7194081265168718E-2</v>
       </c>
       <c r="AX32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>6.8824172086293947E-2</v>
       </c>
       <c r="AY32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="224"/>
         <v>6.4482658923057337E-2</v>
       </c>
       <c r="AZ32" s="10">
-        <f t="shared" si="223"/>
-        <v>0.06</v>
-      </c>
-      <c r="BA32" s="10">
-        <f t="shared" si="223"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="BB32" s="10">
-        <f t="shared" si="223"/>
-        <v>0.06</v>
-      </c>
-      <c r="BC32" s="10">
-        <f t="shared" si="223"/>
-        <v>0.06</v>
-      </c>
-      <c r="BD32" s="10">
-        <f t="shared" si="223"/>
-        <v>0.06</v>
-      </c>
-      <c r="BE32" s="10">
-        <f t="shared" si="223"/>
-        <v>0.06</v>
-      </c>
-      <c r="BF32" s="10">
-        <f t="shared" ref="BF32:BI32" si="224">BF10/BF5</f>
-        <v>0.06</v>
-      </c>
-      <c r="BG32" s="10">
         <f t="shared" si="224"/>
         <v>0.06</v>
       </c>
-      <c r="BH32" s="10">
+      <c r="BA32" s="10">
+        <f t="shared" si="224"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="BB32" s="10">
         <f t="shared" si="224"/>
         <v>0.06</v>
       </c>
+      <c r="BC32" s="10">
+        <f t="shared" si="224"/>
+        <v>0.06</v>
+      </c>
+      <c r="BD32" s="10">
+        <f t="shared" si="224"/>
+        <v>0.06</v>
+      </c>
+      <c r="BE32" s="10">
+        <f t="shared" si="224"/>
+        <v>0.06</v>
+      </c>
+      <c r="BF32" s="10">
+        <f t="shared" ref="BF32:BI32" si="225">BF10/BF5</f>
+        <v>0.06</v>
+      </c>
+      <c r="BG32" s="10">
+        <f t="shared" si="225"/>
+        <v>0.06</v>
+      </c>
+      <c r="BH32" s="10">
+        <f t="shared" si="225"/>
+        <v>0.06</v>
+      </c>
       <c r="BI32" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="225"/>
         <v>0.06</v>
       </c>
       <c r="BK32" t="s">
@@ -8357,212 +8357,212 @@
         <v>0.34213836477987414</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" ref="H33:V33" si="225">H11/D11-1</f>
+        <f t="shared" ref="H33:V33" si="226">H11/D11-1</f>
         <v>0.27116704805491998</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>8.4375000000000089E-2</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>6.9923371647509613E-2</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>9.9343955014058016E-2</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.14311431143114306</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.29490874159462055</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.26410026857654434</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.23785166240409206</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.24409448818897639</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.23738872403560829</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.39376770538243622</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.36845730027548207</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.36582278481012653</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.29076738609112707</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="225"/>
+        <f t="shared" si="226"/>
         <v>0.28302845528455278</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" ref="W33" si="226">W11/S11-1</f>
+        <f t="shared" ref="W33" si="227">W11/S11-1</f>
         <v>0.30548565676899853</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" ref="X33" si="227">X11/T11-1</f>
+        <f t="shared" ref="X33" si="228">X11/T11-1</f>
         <v>0.34522706209453191</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33" si="228">Y11/U11-1</f>
+        <f t="shared" ref="Y33" si="229">Y11/U11-1</f>
         <v>0.42173711100789602</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" ref="Z33" si="229">Z11/V11-1</f>
+        <f t="shared" ref="Z33" si="230">Z11/V11-1</f>
         <v>0.32000000000000006</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" ref="AA33" si="230">AA11/W11-1</f>
+        <f t="shared" ref="AA33" si="231">AA11/W11-1</f>
         <v>0.17309175019275247</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" ref="AB33" si="231">AB11/X11-1</f>
+        <f t="shared" ref="AB33" si="232">AB11/X11-1</f>
         <v>0.10299689975887016</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" ref="AC33" si="232">AC11/Y11-1</f>
+        <f t="shared" ref="AC33" si="233">AC11/Y11-1</f>
         <v>-0.16334531198954594</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" ref="AD33" si="233">AD11/Z11-1</f>
+        <f t="shared" ref="AD33" si="234">AD11/Z11-1</f>
         <v>-9.6909690969096962E-2</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" ref="AE33" si="234">AE11/AA11-1</f>
+        <f t="shared" ref="AE33" si="235">AE11/AA11-1</f>
         <v>-9.8915543871179734E-2</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" ref="AF33" si="235">AF11/AB11-1</f>
+        <f t="shared" ref="AF33" si="236">AF11/AB11-1</f>
         <v>-5.0281074328544673E-2</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" ref="AG33" si="236">AG11/AC11-1</f>
+        <f t="shared" ref="AG33" si="237">AG11/AC11-1</f>
         <v>5.9351815696993437E-2</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" ref="AH33" si="237">AH11/AD11-1</f>
+        <f t="shared" ref="AH33" si="238">AH11/AD11-1</f>
         <v>-4.8837209302325602E-2</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" ref="AI33" si="238">AI11/AE11-1</f>
+        <f t="shared" ref="AI33" si="239">AI11/AE11-1</f>
         <v>-4.1575492341356712E-2</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" ref="AJ33" si="239">AJ11/AF11-1</f>
+        <f t="shared" ref="AJ33" si="240">AJ11/AF11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" ref="AK33" si="240">AK11/AG11-1</f>
+        <f t="shared" ref="AK33" si="241">AK11/AG11-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" ref="AL33" si="241">AL11/AH11-1</f>
+        <f t="shared" ref="AL33" si="242">AL11/AH11-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AN33" s="10"/>
       <c r="AO33" s="10">
-        <f t="shared" ref="AO33:BE33" si="242">AO11/AN11-1</f>
+        <f t="shared" ref="AO33:BE33" si="243">AO11/AN11-1</f>
         <v>0.12564432989690721</v>
       </c>
       <c r="AP33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.39210074413279905</v>
       </c>
       <c r="AQ33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.51027960526315796</v>
       </c>
       <c r="AR33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.18050639803974944</v>
       </c>
       <c r="AS33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.19995387453874547</v>
       </c>
       <c r="AT33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.28156832596578907</v>
       </c>
       <c r="AU33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.32318536292741462</v>
       </c>
       <c r="AV33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>0.34772753031848569</v>
       </c>
       <c r="AW33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>-6.3072912286603611E-3</v>
       </c>
       <c r="AX33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>-3.8676371022342559E-2</v>
       </c>
       <c r="AY33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>1.2276608856413462E-2</v>
       </c>
       <c r="AZ33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE33" s="10">
-        <f t="shared" si="242"/>
+        <f t="shared" si="243"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF33" s="10">
-        <f t="shared" ref="BF33" si="243">BF11/BE11-1</f>
+        <f t="shared" ref="BF33" si="244">BF11/BE11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG33" s="10">
-        <f t="shared" ref="BG33" si="244">BG11/BF11-1</f>
+        <f t="shared" ref="BG33" si="245">BG11/BF11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH33" s="10">
-        <f t="shared" ref="BH33" si="245">BH11/BG11-1</f>
+        <f t="shared" ref="BH33" si="246">BH11/BG11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI33" s="10">
-        <f t="shared" ref="BI33" si="246">BI11/BH11-1</f>
+        <f t="shared" ref="BI33" si="247">BI11/BH11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK33" t="s">
@@ -8578,235 +8578,235 @@
         <v>47</v>
       </c>
       <c r="C34" s="10">
-        <f t="shared" ref="C34:V34" si="247">C19/C18</f>
+        <f t="shared" ref="C34:V34" si="248">C19/C18</f>
         <v>0.2402938090241343</v>
       </c>
       <c r="D34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.70120120120120122</v>
       </c>
       <c r="E34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.18354430379746836</v>
       </c>
       <c r="F34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>8.5470085470085479E-3</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.14979123173277661</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>2.8406909788867563E-2</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.14985250737463127</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>9.7611940298507463E-2</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.18995682799363781</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>8.8958116995500172E-2</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.18768996960486323</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.19393042190969653</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.21992314513745195</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.1581739270213792</v>
       </c>
       <c r="Q34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>8.3565868703186955E-2</v>
       </c>
       <c r="R34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>7.2891178364455897E-2</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.20997273081417997</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.1005327773917072</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>0.26767091541135574</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="248"/>
         <v>4.0980313378867012E-2</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" ref="W34:AE34" si="248">W19/W18</f>
+        <f t="shared" ref="W34:AE34" si="249">W19/W18</f>
         <v>0.27008547008547007</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>0.24010554089709762</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>2.34375E-2</v>
       </c>
       <c r="Z34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>1.2754677754677755</v>
       </c>
       <c r="AA34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>0.23015294974508377</v>
       </c>
       <c r="AB34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>0.10630702102340341</v>
       </c>
       <c r="AC34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>0.18918697185987365</v>
       </c>
       <c r="AD34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>0.22373228116323249</v>
       </c>
       <c r="AE34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="249"/>
         <v>0.1900177154740815</v>
       </c>
       <c r="AF34" s="10">
-        <f t="shared" ref="AF34:AH34" si="249">AF19/AF18</f>
+        <f t="shared" ref="AF34:AH34" si="250">AF19/AF18</f>
         <v>0.11590685470646113</v>
       </c>
       <c r="AG34" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v>0.15002494871652713</v>
       </c>
       <c r="AH34" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="250"/>
         <v>0.10403150029084075</v>
       </c>
       <c r="AI34" s="10">
-        <f t="shared" ref="AI34:AL34" si="250">AI19/AI18</f>
+        <f t="shared" ref="AI34:AL34" si="251">AI19/AI18</f>
         <v>0.21001891231145348</v>
       </c>
       <c r="AJ34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AK34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AL34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="251"/>
         <v>0.14000000000000001</v>
       </c>
       <c r="AN34" s="10">
-        <f t="shared" ref="AN34:BE34" si="251">AN19/AN18</f>
+        <f t="shared" ref="AN34:BE34" si="252">AN19/AN18</f>
         <v>-1.5045045045045045</v>
       </c>
       <c r="AO34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.60586734693877553</v>
       </c>
       <c r="AP34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.36613566289825283</v>
       </c>
       <c r="AQ34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.20225899658523772</v>
       </c>
       <c r="AR34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.106207264008525</v>
       </c>
       <c r="AS34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.16980322003577816</v>
       </c>
       <c r="AT34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.1184134337000579</v>
       </c>
       <c r="AU34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.12557993237398757</v>
       </c>
       <c r="AV34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.54194743935309975</v>
       </c>
       <c r="AW34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.18957850733551668</v>
       </c>
       <c r="AX34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.13503075174162707</v>
       </c>
       <c r="AY34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="252"/>
         <v>0.15768567597071112</v>
       </c>
       <c r="AZ34" s="10">
-        <f t="shared" si="251"/>
-        <v>0.15</v>
-      </c>
-      <c r="BA34" s="10">
-        <f t="shared" si="251"/>
-        <v>0.15</v>
-      </c>
-      <c r="BB34" s="10">
-        <f t="shared" si="251"/>
-        <v>0.15</v>
-      </c>
-      <c r="BC34" s="10">
-        <f t="shared" si="251"/>
-        <v>0.15</v>
-      </c>
-      <c r="BD34" s="10">
-        <f t="shared" si="251"/>
-        <v>0.15</v>
-      </c>
-      <c r="BE34" s="10">
-        <f t="shared" si="251"/>
-        <v>0.15</v>
-      </c>
-      <c r="BF34" s="10">
-        <f t="shared" ref="BF34:BI34" si="252">BF19/BF18</f>
-        <v>0.15</v>
-      </c>
-      <c r="BG34" s="10">
         <f t="shared" si="252"/>
         <v>0.15</v>
       </c>
-      <c r="BH34" s="10">
+      <c r="BA34" s="10">
         <f t="shared" si="252"/>
         <v>0.15</v>
       </c>
+      <c r="BB34" s="10">
+        <f t="shared" si="252"/>
+        <v>0.15</v>
+      </c>
+      <c r="BC34" s="10">
+        <f t="shared" si="252"/>
+        <v>0.15</v>
+      </c>
+      <c r="BD34" s="10">
+        <f t="shared" si="252"/>
+        <v>0.15</v>
+      </c>
+      <c r="BE34" s="10">
+        <f t="shared" si="252"/>
+        <v>0.15</v>
+      </c>
+      <c r="BF34" s="10">
+        <f t="shared" ref="BF34:BI34" si="253">BF19/BF18</f>
+        <v>0.15</v>
+      </c>
+      <c r="BG34" s="10">
+        <f t="shared" si="253"/>
+        <v>0.15</v>
+      </c>
+      <c r="BH34" s="10">
+        <f t="shared" si="253"/>
+        <v>0.15</v>
+      </c>
       <c r="BI34" s="10">
-        <f t="shared" si="252"/>
+        <f t="shared" si="253"/>
         <v>0.15</v>
       </c>
       <c r="BK34" t="s">
@@ -8822,19 +8822,19 @@
         <v>58</v>
       </c>
       <c r="C35" s="10">
-        <f t="shared" ref="C35:F35" si="253">C21/C5</f>
+        <f t="shared" ref="C35:F35" si="254">C21/C5</f>
         <v>2.027216217729742E-2</v>
       </c>
       <c r="D35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>5.1903570017125542E-3</v>
       </c>
       <c r="E35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>5.8522311631309439E-3</v>
       </c>
       <c r="F35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="254"/>
         <v>3.0701536731014178E-2</v>
       </c>
       <c r="G35" s="10">
@@ -8842,199 +8842,199 @@
         <v>3.1914893617021274E-2</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" ref="H35:V35" si="254">H21/H5</f>
+        <f t="shared" ref="H35:V35" si="255">H21/H5</f>
         <v>4.791438187800174E-2</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>5.0958003393665158E-2</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>4.1819211693353411E-2</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>5.9648241206030149E-2</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>4.1401173427544007E-2</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>3.0493991226189964E-2</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>3.7375481775449755E-2</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>3.3597518952446587E-2</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>5.896841821126507E-2</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>6.5848458058141351E-2</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>5.7520608498267692E-2</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>7.470650030409702E-2</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>6.8783162362928904E-2</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>2.8480669963541854E-2</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="255"/>
         <v>0.1042339824760574</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" ref="W35:AE35" si="255">W21/W5</f>
+        <f t="shared" ref="W35:AE35" si="256">W21/W5</f>
         <v>-3.3011576380062517E-2</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>-1.6727980599501788E-2</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>2.2596203019645794E-2</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>1.8632208251789495E-3</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>2.4906170008951147E-2</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>5.0229567728060844E-2</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>6.9043841686293975E-2</v>
       </c>
       <c r="AD35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>6.2508457822676972E-2</v>
       </c>
       <c r="AE35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="256"/>
         <v>7.2784743882271671E-2</v>
       </c>
       <c r="AF35" s="10">
-        <f t="shared" ref="AF35:AH35" si="256">AF21/AF5</f>
+        <f t="shared" ref="AF35:AH35" si="257">AF21/AF5</f>
         <v>9.1129026808220201E-2</v>
       </c>
       <c r="AG35" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>9.6477148989469838E-2</v>
       </c>
       <c r="AH35" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="257"/>
         <v>0.10652210956803272</v>
       </c>
       <c r="AI35" s="10">
-        <f t="shared" ref="AI35:AL35" si="257">AI21/AI5</f>
+        <f t="shared" ref="AI35:AL35" si="258">AI21/AI5</f>
         <v>0.1100233190078822</v>
       </c>
       <c r="AJ35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="258"/>
         <v>9.1869053883544508E-2</v>
       </c>
       <c r="AK35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="258"/>
         <v>0.10333003434389727</v>
       </c>
       <c r="AL35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="258"/>
         <v>0.11350818038090509</v>
       </c>
       <c r="AN35" s="10">
-        <f t="shared" ref="AN35:BE35" si="258">AN21/AN5</f>
+        <f t="shared" ref="AN35:BE35" si="259">AN21/AN5</f>
         <v>-2.7082303231896437E-3</v>
       </c>
       <c r="AO35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>5.5697811337681999E-3</v>
       </c>
       <c r="AP35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>1.7435490157147373E-2</v>
       </c>
       <c r="AQ35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>1.7052162864178651E-2</v>
       </c>
       <c r="AR35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>4.3252736305590261E-2</v>
       </c>
       <c r="AS35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>4.1308703060722513E-2</v>
       </c>
       <c r="AT35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>5.5252496995316841E-2</v>
       </c>
       <c r="AU35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>7.1014128755145567E-2</v>
       </c>
       <c r="AV35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>-5.2958950004183018E-3</v>
       </c>
       <c r="AW35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>5.2932835755978319E-2</v>
       </c>
       <c r="AX35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>9.2871171971866534E-2</v>
       </c>
       <c r="AY35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.10515795613237959</v>
       </c>
       <c r="AZ35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.12256421472412569</v>
       </c>
       <c r="BA35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.12671712225239701</v>
       </c>
       <c r="BB35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.13007659491982979</v>
       </c>
       <c r="BC35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.13160650384000341</v>
       </c>
       <c r="BD35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.13257335961263461</v>
       </c>
       <c r="BE35" s="10">
-        <f t="shared" si="258"/>
+        <f t="shared" si="259"/>
         <v>0.13285552904465028</v>
       </c>
       <c r="BF35" s="10">
@@ -9042,15 +9042,15 @@
         <v>0.13721330021770192</v>
       </c>
       <c r="BG35" s="10">
-        <f t="shared" ref="BG35:BI35" si="259">BG21/BG5</f>
+        <f t="shared" ref="BG35:BI35" si="260">BG21/BG5</f>
         <v>0.13401480067190805</v>
       </c>
       <c r="BH35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="260"/>
         <v>0.13426382714395338</v>
       </c>
       <c r="BI35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="260"/>
         <v>0.13452310844034301</v>
       </c>
       <c r="BK35" t="s">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="BL35" s="3">
         <f>Main!D3</f>
-        <v>189.98</v>
+        <v>204.88</v>
       </c>
     </row>
     <row r="36" spans="2:64" x14ac:dyDescent="0.3">
@@ -9067,7 +9067,7 @@
       </c>
       <c r="BL36" s="13">
         <f>BL34/BL35-1</f>
-        <v>4.0562329874762826E-2</v>
+        <v>-3.5113083611834073E-2</v>
       </c>
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.3">

--- a/Financial Analysis/AMZN.xlsx
+++ b/Financial Analysis/AMZN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4275EE7-5152-4AFA-900E-5DDB5F7E34D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1628EEFC-1879-4B65-9E09-C78E9BE743B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EA1D195A-C8DC-4C80-AD05-94F317AC85A7}"/>
   </bookViews>
@@ -402,14 +402,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
@@ -426,7 +426,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22235160" y="0"/>
+          <a:off x="22837140" y="0"/>
           <a:ext cx="0" cy="6743700"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -877,17 +877,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>204.88</v>
+        <v>229.8</v>
       </c>
       <c r="E3" s="2">
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45804</v>
+        <v>45887</v>
       </c>
       <c r="G3" s="2">
-        <v>45869</v>
+        <v>45961</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -906,11 +906,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>10616.4</f>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -930,7 +929,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>2175088.0319999997</v>
+        <v>2444382.6</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -1017,7 +1016,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>2126509.0319999997</v>
+        <v>2395803.6</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1750,16 +1749,15 @@
         <v>63970</v>
       </c>
       <c r="AJ3" s="4">
-        <f>AF3*1.05</f>
-        <v>64647.450000000004</v>
+        <v>68246</v>
       </c>
       <c r="AK3" s="4">
-        <f>AG3*1.04</f>
-        <v>70305.040000000008</v>
+        <f>AG3*1.05</f>
+        <v>70981.05</v>
       </c>
       <c r="AL3" s="4">
-        <f>AH3*1.03</f>
-        <v>84692.78</v>
+        <f>AH3*1.04</f>
+        <v>85515.040000000008</v>
       </c>
       <c r="AN3" s="4">
         <v>70080</v>
@@ -1804,47 +1802,47 @@
       </c>
       <c r="AY3" s="4">
         <f>SUM(AI3:AL3)</f>
-        <v>283615.27</v>
+        <v>288712.08999999997</v>
       </c>
       <c r="AZ3" s="4">
         <f>AY3*1.05</f>
-        <v>297796.03350000002</v>
+        <v>303147.69449999998</v>
       </c>
       <c r="BA3" s="4">
         <f>AZ3*1.04</f>
-        <v>309707.87484</v>
+        <v>315273.60227999999</v>
       </c>
       <c r="BB3" s="4">
         <f>BA3*1.03</f>
-        <v>318999.11108519998</v>
+        <v>324731.81034839997</v>
       </c>
       <c r="BC3" s="4">
         <f t="shared" ref="BC3:BD3" si="0">BB3*1.02</f>
-        <v>325379.09330690396</v>
+        <v>331226.44655536796</v>
       </c>
       <c r="BD3" s="4">
         <f t="shared" si="0"/>
-        <v>331886.67517304205</v>
+        <v>337850.97548647533</v>
       </c>
       <c r="BE3" s="4">
         <f>BD3*1.02</f>
-        <v>338524.40867650288</v>
+        <v>344607.99499620486</v>
       </c>
       <c r="BF3" s="4">
         <f>BE3*1.01</f>
-        <v>341909.65276326792</v>
+        <v>348054.07494616689</v>
       </c>
       <c r="BG3" s="4">
         <f t="shared" ref="BG3:BI3" si="1">BF3*1.01</f>
-        <v>345328.7492909006</v>
+        <v>351534.61569562857</v>
       </c>
       <c r="BH3" s="4">
         <f t="shared" si="1"/>
-        <v>348782.0367838096</v>
+        <v>355049.96185258485</v>
       </c>
       <c r="BI3" s="4">
         <f t="shared" si="1"/>
-        <v>352269.85715164768</v>
+        <v>358600.4614711107</v>
       </c>
     </row>
     <row r="4" spans="2:61" x14ac:dyDescent="0.3">
@@ -1951,16 +1949,15 @@
         <v>91697</v>
       </c>
       <c r="AJ4" s="4">
-        <f>AF4*1.1</f>
-        <v>95048.8</v>
+        <v>99456</v>
       </c>
       <c r="AK4" s="4">
-        <f>AG4*1.1</f>
-        <v>100403.6</v>
+        <f>AG4*1.14</f>
+        <v>104054.63999999998</v>
       </c>
       <c r="AL4" s="4">
-        <f>AH4*1.1</f>
-        <v>116122.6</v>
+        <f>AH4*1.13</f>
+        <v>119289.57999999999</v>
       </c>
       <c r="AN4" s="4">
         <v>18908</v>
@@ -2005,47 +2002,47 @@
       </c>
       <c r="AY4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>403272</v>
+        <v>414497.22</v>
       </c>
       <c r="AZ4" s="4">
         <f>AY4*1.09</f>
-        <v>439566.48000000004</v>
+        <v>451801.96980000002</v>
       </c>
       <c r="BA4" s="4">
         <f>AZ4*1.08</f>
-        <v>474731.79840000009</v>
+        <v>487946.12738400005</v>
       </c>
       <c r="BB4" s="4">
         <f>BA4*1.06</f>
-        <v>503215.70630400011</v>
+        <v>517222.8950270401</v>
       </c>
       <c r="BC4" s="4">
         <f>BB4*1.04</f>
-        <v>523344.33455616015</v>
+        <v>537911.81082812173</v>
       </c>
       <c r="BD4" s="4">
         <f t="shared" ref="BD4" si="2">BC4*1.03</f>
-        <v>539044.66459284502</v>
+        <v>554049.16515296535</v>
       </c>
       <c r="BE4" s="4">
         <f>BD4*1.02</f>
-        <v>549825.55788470188</v>
+        <v>565130.1484560247</v>
       </c>
       <c r="BF4" s="4">
         <f t="shared" ref="BF4" si="3">BE4*1.02</f>
-        <v>560822.06904239592</v>
+        <v>576432.75142514519</v>
       </c>
       <c r="BG4" s="4">
         <f>BF4*1.01</f>
-        <v>566430.28973281989</v>
+        <v>582197.07893939666</v>
       </c>
       <c r="BH4" s="4">
         <f t="shared" ref="BH4:BI4" si="4">BG4*1.01</f>
-        <v>572094.59263014805</v>
+        <v>588019.04972879065</v>
       </c>
       <c r="BI4" s="4">
         <f t="shared" si="4"/>
-        <v>577815.53855644958</v>
+        <v>593899.24022607855</v>
       </c>
     </row>
     <row r="5" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2186,15 +2183,15 @@
       </c>
       <c r="AJ5" s="8">
         <f t="shared" si="14"/>
-        <v>159696.25</v>
+        <v>167702</v>
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="14"/>
-        <v>170708.64</v>
+        <v>175035.69</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="14"/>
-        <v>200815.38</v>
+        <v>204804.62</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" ref="AN5:AU5" si="15">AN3+AN4</f>
@@ -2242,47 +2239,47 @@
       </c>
       <c r="AY5" s="8">
         <f t="shared" si="16"/>
-        <v>686887.27</v>
+        <v>703209.30999999994</v>
       </c>
       <c r="AZ5" s="8">
         <f t="shared" si="16"/>
-        <v>737362.51350000012</v>
+        <v>754949.66430000006</v>
       </c>
       <c r="BA5" s="8">
         <f t="shared" si="16"/>
-        <v>784439.67324000015</v>
+        <v>803219.72966399998</v>
       </c>
       <c r="BB5" s="8">
         <f t="shared" si="16"/>
-        <v>822214.81738920009</v>
+        <v>841954.70537544007</v>
       </c>
       <c r="BC5" s="8">
         <f t="shared" si="16"/>
-        <v>848723.42786306411</v>
+        <v>869138.25738348975</v>
       </c>
       <c r="BD5" s="8">
         <f t="shared" si="16"/>
-        <v>870931.33976588701</v>
+        <v>891900.14063944062</v>
       </c>
       <c r="BE5" s="8">
         <f t="shared" si="16"/>
-        <v>888349.96656120475</v>
+        <v>909738.14345222956</v>
       </c>
       <c r="BF5" s="8">
         <f t="shared" ref="BF5:BI5" si="18">BF3+BF4</f>
-        <v>902731.72180566378</v>
+        <v>924486.82637131214</v>
       </c>
       <c r="BG5" s="8">
         <f t="shared" si="18"/>
-        <v>911759.03902372043</v>
+        <v>933731.69463502523</v>
       </c>
       <c r="BH5" s="8">
         <f t="shared" si="18"/>
-        <v>920876.62941395771</v>
+        <v>943069.0115813755</v>
       </c>
       <c r="BI5" s="8">
         <f t="shared" si="18"/>
-        <v>930085.39570809726</v>
+        <v>952499.70169718924</v>
       </c>
     </row>
     <row r="6" spans="2:61" x14ac:dyDescent="0.3">
@@ -2389,16 +2386,15 @@
         <v>76976</v>
       </c>
       <c r="AJ6" s="4">
-        <f t="shared" ref="AJ6:AK6" si="19">AJ5-AJ7</f>
-        <v>79848.125</v>
+        <v>80809</v>
       </c>
       <c r="AK6" s="4">
-        <f t="shared" si="19"/>
-        <v>85354.32</v>
+        <f t="shared" ref="AK6" si="19">AK5-AK7</f>
+        <v>87517.845000000001</v>
       </c>
       <c r="AL6" s="4">
         <f>AL5-AL7</f>
-        <v>104423.9976</v>
+        <v>104450.35619999999</v>
       </c>
       <c r="AN6" s="4">
         <v>62752</v>
@@ -2443,47 +2439,47 @@
       </c>
       <c r="AY6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>346602.44260000001</v>
+        <v>349753.20120000001</v>
       </c>
       <c r="AZ6" s="4">
         <f t="shared" ref="AZ6:BE6" si="20">AZ5-AZ7</f>
-        <v>368681.25675000006</v>
+        <v>369925.33550700004</v>
       </c>
       <c r="BA6" s="4">
         <f t="shared" si="20"/>
-        <v>392219.83662000007</v>
+        <v>385545.47023871995</v>
       </c>
       <c r="BB6" s="4">
         <f t="shared" si="20"/>
-        <v>411107.40869460005</v>
+        <v>395718.71152645681</v>
       </c>
       <c r="BC6" s="4">
         <f t="shared" si="20"/>
-        <v>424361.71393153205</v>
+        <v>408494.98097024014</v>
       </c>
       <c r="BD6" s="4">
         <f t="shared" si="20"/>
-        <v>435465.6698829435</v>
+        <v>419193.06610053708</v>
       </c>
       <c r="BE6" s="4">
         <f t="shared" si="20"/>
-        <v>444174.98328060238</v>
+        <v>427576.92742254789</v>
       </c>
       <c r="BF6" s="4">
         <f t="shared" ref="BF6:BI6" si="21">BF5-BF7</f>
-        <v>451365.86090283189</v>
+        <v>434508.8083945167</v>
       </c>
       <c r="BG6" s="4">
         <f t="shared" si="21"/>
-        <v>455879.51951186021</v>
+        <v>438853.89647846186</v>
       </c>
       <c r="BH6" s="4">
         <f t="shared" si="21"/>
-        <v>460438.31470697885</v>
+        <v>443242.43544324645</v>
       </c>
       <c r="BI6" s="4">
         <f t="shared" si="21"/>
-        <v>465042.69785404863</v>
+        <v>447674.85979767895</v>
       </c>
     </row>
     <row r="7" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2603,7 +2599,7 @@
         <v>77408</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" ref="AE7:AI7" si="30">AE5-AE6</f>
+        <f t="shared" ref="AE7:AJ7" si="30">AE5-AE6</f>
         <v>70680</v>
       </c>
       <c r="AF7" s="8">
@@ -2623,16 +2619,16 @@
         <v>78691</v>
       </c>
       <c r="AJ7" s="8">
-        <f t="shared" ref="AJ7:AK7" si="31">AJ5*0.5</f>
-        <v>79848.125</v>
+        <f t="shared" si="30"/>
+        <v>86893</v>
       </c>
       <c r="AK7" s="8">
-        <f t="shared" si="31"/>
-        <v>85354.32</v>
+        <f t="shared" ref="AK7" si="31">AK5*0.5</f>
+        <v>87517.845000000001</v>
       </c>
       <c r="AL7" s="8">
-        <f>AL5*0.48</f>
-        <v>96391.382400000002</v>
+        <f>AL5*0.49</f>
+        <v>100354.2638</v>
       </c>
       <c r="AN7" s="8">
         <f t="shared" ref="AN7:AW7" si="32">AN5-AN6</f>
@@ -2680,47 +2676,47 @@
       </c>
       <c r="AY7" s="8">
         <f t="shared" si="33"/>
-        <v>340284.82740000001</v>
+        <v>353456.10879999993</v>
       </c>
       <c r="AZ7" s="8">
-        <f>AZ5*0.5</f>
-        <v>368681.25675000006</v>
+        <f>AZ5*0.51</f>
+        <v>385024.32879300002</v>
       </c>
       <c r="BA7" s="8">
-        <f t="shared" ref="BA7" si="34">BA5*0.5</f>
-        <v>392219.83662000007</v>
+        <f>BA5*0.52</f>
+        <v>417674.25942528003</v>
       </c>
       <c r="BB7" s="8">
-        <f>BB5*0.5</f>
-        <v>411107.40869460005</v>
+        <f>BB5*0.53</f>
+        <v>446235.99384898326</v>
       </c>
       <c r="BC7" s="8">
-        <f t="shared" ref="BC7:BI7" si="35">BC5*0.5</f>
-        <v>424361.71393153205</v>
+        <f t="shared" ref="BC7:BI7" si="34">BC5*0.53</f>
+        <v>460643.27641324961</v>
       </c>
       <c r="BD7" s="8">
-        <f t="shared" si="35"/>
-        <v>435465.6698829435</v>
+        <f t="shared" si="34"/>
+        <v>472707.07453890354</v>
       </c>
       <c r="BE7" s="8">
-        <f t="shared" si="35"/>
-        <v>444174.98328060238</v>
+        <f t="shared" si="34"/>
+        <v>482161.21602968167</v>
       </c>
       <c r="BF7" s="8">
-        <f t="shared" si="35"/>
-        <v>451365.86090283189</v>
+        <f t="shared" si="34"/>
+        <v>489978.01797679544</v>
       </c>
       <c r="BG7" s="8">
-        <f t="shared" si="35"/>
-        <v>455879.51951186021</v>
+        <f t="shared" si="34"/>
+        <v>494877.79815656337</v>
       </c>
       <c r="BH7" s="8">
-        <f t="shared" si="35"/>
-        <v>460438.31470697885</v>
+        <f t="shared" si="34"/>
+        <v>499826.57613812905</v>
       </c>
       <c r="BI7" s="8">
-        <f t="shared" si="35"/>
-        <v>465042.69785404863</v>
+        <f t="shared" si="34"/>
+        <v>504824.8418995103</v>
       </c>
     </row>
     <row r="8" spans="2:61" x14ac:dyDescent="0.3">
@@ -2827,16 +2823,15 @@
         <v>24593</v>
       </c>
       <c r="AJ8" s="4">
-        <f t="shared" ref="AJ8:AK8" si="36">AJ5*0.16</f>
-        <v>25551.4</v>
+        <v>25976</v>
       </c>
       <c r="AK8" s="4">
-        <f t="shared" si="36"/>
-        <v>27313.382400000002</v>
+        <f t="shared" ref="AK8" si="35">AK5*0.16</f>
+        <v>28005.7104</v>
       </c>
       <c r="AL8" s="4">
         <f>AL5*0.15</f>
-        <v>30122.307000000001</v>
+        <v>30720.692999999999</v>
       </c>
       <c r="AN8" s="4">
         <v>10766</v>
@@ -2881,47 +2876,47 @@
       </c>
       <c r="AY8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>107580.0894</v>
+        <v>109295.4034</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" ref="AZ8:BE8" si="37">AZ5*0.15</f>
-        <v>110604.37702500001</v>
+        <f t="shared" ref="AZ8:BE8" si="36">AZ5*0.15</f>
+        <v>113242.449645</v>
       </c>
       <c r="BA8" s="4">
+        <f t="shared" si="36"/>
+        <v>120482.95944959999</v>
+      </c>
+      <c r="BB8" s="4">
+        <f t="shared" si="36"/>
+        <v>126293.20580631601</v>
+      </c>
+      <c r="BC8" s="4">
+        <f t="shared" si="36"/>
+        <v>130370.73860752345</v>
+      </c>
+      <c r="BD8" s="4">
+        <f t="shared" si="36"/>
+        <v>133785.02109591608</v>
+      </c>
+      <c r="BE8" s="4">
+        <f t="shared" si="36"/>
+        <v>136460.72151783443</v>
+      </c>
+      <c r="BF8" s="4">
+        <f t="shared" ref="BF8:BI8" si="37">BF5*0.15</f>
+        <v>138673.02395569682</v>
+      </c>
+      <c r="BG8" s="4">
         <f t="shared" si="37"/>
-        <v>117665.95098600003</v>
-      </c>
-      <c r="BB8" s="4">
+        <v>140059.75419525377</v>
+      </c>
+      <c r="BH8" s="4">
         <f t="shared" si="37"/>
-        <v>123332.22260838001</v>
-      </c>
-      <c r="BC8" s="4">
+        <v>141460.35173720631</v>
+      </c>
+      <c r="BI8" s="4">
         <f t="shared" si="37"/>
-        <v>127308.51417945961</v>
-      </c>
-      <c r="BD8" s="4">
-        <f t="shared" si="37"/>
-        <v>130639.70096488304</v>
-      </c>
-      <c r="BE8" s="4">
-        <f t="shared" si="37"/>
-        <v>133252.4949841807</v>
-      </c>
-      <c r="BF8" s="4">
-        <f t="shared" ref="BF8:BI8" si="38">BF5*0.15</f>
-        <v>135409.75827084956</v>
-      </c>
-      <c r="BG8" s="4">
-        <f t="shared" si="38"/>
-        <v>136763.85585355805</v>
-      </c>
-      <c r="BH8" s="4">
-        <f t="shared" si="38"/>
-        <v>138131.49441209366</v>
-      </c>
-      <c r="BI8" s="4">
-        <f t="shared" si="38"/>
-        <v>139512.8093562146</v>
+        <v>142874.95525457838</v>
       </c>
     </row>
     <row r="9" spans="2:61" x14ac:dyDescent="0.3">
@@ -3028,16 +3023,15 @@
         <v>22994</v>
       </c>
       <c r="AJ9" s="4">
-        <f>AF9*1.09</f>
-        <v>24311.360000000001</v>
+        <v>27166</v>
       </c>
       <c r="AK9" s="4">
-        <f>AG9*1.08</f>
-        <v>24024.600000000002</v>
+        <f>AG9*1.24</f>
+        <v>27583.8</v>
       </c>
       <c r="AL9" s="4">
-        <f>AH9*1.05</f>
-        <v>24749.55</v>
+        <f>AH9*1.2</f>
+        <v>28285.200000000001</v>
       </c>
       <c r="AN9" s="4">
         <v>4332</v>
@@ -3082,47 +3076,47 @@
       </c>
       <c r="AY9" s="4">
         <f>SUM(AI9:AL9)</f>
-        <v>96079.510000000009</v>
+        <v>106029</v>
       </c>
       <c r="AZ9" s="4">
-        <f>AY9*1.05</f>
-        <v>100883.48550000001</v>
+        <f>AY9*1.08</f>
+        <v>114511.32</v>
       </c>
       <c r="BA9" s="4">
-        <f>AZ9*1.03</f>
-        <v>103909.99006500002</v>
+        <f>AZ9*1.04</f>
+        <v>119091.77280000001</v>
       </c>
       <c r="BB9" s="4">
-        <f t="shared" ref="BB9:BE9" si="39">BA9*1.02</f>
-        <v>105988.18986630002</v>
+        <f>BA9*1.03</f>
+        <v>122664.52598400001</v>
       </c>
       <c r="BC9" s="4">
-        <f t="shared" si="39"/>
-        <v>108107.95366362602</v>
+        <f t="shared" ref="BC9:BE9" si="38">BB9*1.02</f>
+        <v>125117.81650368001</v>
       </c>
       <c r="BD9" s="4">
-        <f t="shared" si="39"/>
-        <v>110270.11273689853</v>
+        <f t="shared" si="38"/>
+        <v>127620.1728337536</v>
       </c>
       <c r="BE9" s="4">
-        <f t="shared" si="39"/>
-        <v>112475.5149916365</v>
+        <f t="shared" si="38"/>
+        <v>130172.57629042868</v>
       </c>
       <c r="BF9" s="4">
         <f>BE9*1.01</f>
-        <v>113600.27014155287</v>
+        <v>131474.30205333297</v>
       </c>
       <c r="BG9" s="4">
-        <f t="shared" ref="BG9:BI9" si="40">BF9*1.01</f>
-        <v>114736.27284296841</v>
+        <f t="shared" ref="BG9:BI9" si="39">BF9*1.01</f>
+        <v>132789.04507386629</v>
       </c>
       <c r="BH9" s="4">
-        <f t="shared" si="40"/>
-        <v>115883.63557139809</v>
+        <f t="shared" si="39"/>
+        <v>134116.93552460495</v>
       </c>
       <c r="BI9" s="4">
-        <f t="shared" si="40"/>
-        <v>117042.47192711207</v>
+        <f t="shared" si="39"/>
+        <v>135458.10487985102</v>
       </c>
     </row>
     <row r="10" spans="2:61" x14ac:dyDescent="0.3">
@@ -3229,16 +3223,15 @@
         <v>9763</v>
       </c>
       <c r="AJ10" s="4">
-        <f>AJ5*0.065</f>
-        <v>10380.25625</v>
+        <v>11416</v>
       </c>
       <c r="AK10" s="4">
         <f>AK5*0.065</f>
-        <v>11096.061600000001</v>
+        <v>11377.31985</v>
       </c>
       <c r="AL10" s="4">
         <f>AL5*0.065</f>
-        <v>13052.9997</v>
+        <v>13312.300300000001</v>
       </c>
       <c r="AN10" s="4">
         <v>9275</v>
@@ -3283,47 +3276,47 @@
       </c>
       <c r="AY10" s="4">
         <f>SUM(AI10:AL10)</f>
-        <v>44292.31755</v>
+        <v>45868.620150000002</v>
       </c>
       <c r="AZ10" s="4">
         <f>AZ5*0.06</f>
-        <v>44241.750810000005</v>
+        <v>45296.979857999999</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" ref="BA10:BI10" si="41">BA5*0.06</f>
-        <v>47066.38039440001</v>
+        <f t="shared" ref="BA10:BI10" si="40">BA5*0.06</f>
+        <v>48193.183779839994</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" si="41"/>
-        <v>49332.889043352006</v>
+        <f t="shared" si="40"/>
+        <v>50517.2823225264</v>
       </c>
       <c r="BC10" s="4">
-        <f t="shared" si="41"/>
-        <v>50923.405671783847</v>
+        <f t="shared" si="40"/>
+        <v>52148.295443009381</v>
       </c>
       <c r="BD10" s="4">
-        <f t="shared" si="41"/>
-        <v>52255.88038595322</v>
+        <f t="shared" si="40"/>
+        <v>53514.008438366436</v>
       </c>
       <c r="BE10" s="4">
-        <f t="shared" si="41"/>
-        <v>53300.997993672281</v>
+        <f t="shared" si="40"/>
+        <v>54584.288607133771</v>
       </c>
       <c r="BF10" s="4">
-        <f t="shared" si="41"/>
-        <v>54163.903308339824</v>
+        <f t="shared" si="40"/>
+        <v>55469.209582278723</v>
       </c>
       <c r="BG10" s="4">
-        <f t="shared" si="41"/>
-        <v>54705.542341423221</v>
+        <f t="shared" si="40"/>
+        <v>56023.901678101509</v>
       </c>
       <c r="BH10" s="4">
-        <f t="shared" si="41"/>
-        <v>55252.597764837461</v>
+        <f t="shared" si="40"/>
+        <v>56584.140694882524</v>
       </c>
       <c r="BI10" s="4">
-        <f t="shared" si="41"/>
-        <v>55805.123742485834</v>
+        <f t="shared" si="40"/>
+        <v>57149.982101831352</v>
       </c>
     </row>
     <row r="11" spans="2:61" x14ac:dyDescent="0.3">
@@ -3430,15 +3423,14 @@
         <v>2628</v>
       </c>
       <c r="AJ11" s="4">
-        <f>AF11*1.01</f>
-        <v>3071.41</v>
+        <v>2965</v>
       </c>
       <c r="AK11" s="4">
-        <f t="shared" ref="AK11:AL11" si="42">AG11*1.04</f>
+        <f t="shared" ref="AK11:AL11" si="41">AG11*1.04</f>
         <v>2821.52</v>
       </c>
       <c r="AL11" s="4">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>2977.52</v>
       </c>
       <c r="AN11" s="4">
@@ -3484,47 +3476,47 @@
       </c>
       <c r="AY11" s="4">
         <f>SUM(AI11:AL11)</f>
-        <v>11498.45</v>
+        <v>11392.04</v>
       </c>
       <c r="AZ11" s="4">
         <f>AY11*1.02</f>
-        <v>11728.419000000002</v>
+        <v>11619.880800000001</v>
       </c>
       <c r="BA11" s="4">
         <f>AZ11*1.02</f>
-        <v>11962.987380000002</v>
+        <v>11852.278416000001</v>
       </c>
       <c r="BB11" s="4">
         <f>BA11*1.02</f>
-        <v>12202.247127600003</v>
+        <v>12089.323984320001</v>
       </c>
       <c r="BC11" s="4">
         <f>BB11*1.02</f>
-        <v>12446.292070152003</v>
+        <v>12331.1104640064</v>
       </c>
       <c r="BD11" s="4">
-        <f t="shared" ref="BD11:BE11" si="43">BC11*1.01</f>
-        <v>12570.754990853524</v>
+        <f t="shared" ref="BD11:BE11" si="42">BC11*1.01</f>
+        <v>12454.421568646465</v>
       </c>
       <c r="BE11" s="4">
-        <f t="shared" si="43"/>
-        <v>12696.462540762059</v>
+        <f t="shared" si="42"/>
+        <v>12578.96578433293</v>
       </c>
       <c r="BF11" s="4">
-        <f t="shared" ref="BF11" si="44">BE11*1.01</f>
-        <v>12823.42716616968</v>
+        <f t="shared" ref="BF11" si="43">BE11*1.01</f>
+        <v>12704.75544217626</v>
       </c>
       <c r="BG11" s="4">
-        <f t="shared" ref="BG11" si="45">BF11*1.01</f>
-        <v>12951.661437831377</v>
+        <f t="shared" ref="BG11" si="44">BF11*1.01</f>
+        <v>12831.802996598022</v>
       </c>
       <c r="BH11" s="4">
-        <f t="shared" ref="BH11" si="46">BG11*1.01</f>
-        <v>13081.178052209691</v>
+        <f t="shared" ref="BH11" si="45">BG11*1.01</f>
+        <v>12960.121026564002</v>
       </c>
       <c r="BI11" s="4">
-        <f t="shared" ref="BI11" si="47">BH11*1.01</f>
-        <v>13211.989832731788</v>
+        <f t="shared" ref="BI11" si="46">BH11*1.01</f>
+        <v>13089.722236829642</v>
       </c>
     </row>
     <row r="12" spans="2:61" x14ac:dyDescent="0.3">
@@ -3631,15 +3623,14 @@
         <v>308</v>
       </c>
       <c r="AJ12" s="4">
-        <f t="shared" ref="AJ12:AL12" si="48">AF12*1.01</f>
-        <v>97.97</v>
+        <v>199</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" ref="AK12:AL12" si="47">AG12*1.01</f>
         <v>264.62</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>177.76</v>
       </c>
       <c r="AN12" s="4">
@@ -3685,47 +3676,47 @@
       </c>
       <c r="AY12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>848.35</v>
+        <v>949.38</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" ref="AZ12:BE12" si="49">AY12*1.03</f>
-        <v>873.80050000000006</v>
+        <f t="shared" ref="AZ12:BE12" si="48">AY12*1.03</f>
+        <v>977.8614</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" si="49"/>
-        <v>900.01451500000007</v>
+        <f t="shared" si="48"/>
+        <v>1007.1972420000001</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" si="49"/>
-        <v>927.01495045000013</v>
+        <f t="shared" si="48"/>
+        <v>1037.4131592600002</v>
       </c>
       <c r="BC12" s="4">
-        <f t="shared" si="49"/>
-        <v>954.82539896350011</v>
+        <f t="shared" si="48"/>
+        <v>1068.5355540378002</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="49"/>
-        <v>983.47016093240518</v>
+        <f t="shared" si="48"/>
+        <v>1100.5916206589343</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="49"/>
-        <v>1012.9742657603773</v>
+        <f t="shared" si="48"/>
+        <v>1133.6093692787024</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" ref="BF12" si="50">BE12*1.03</f>
-        <v>1043.3634937331888</v>
+        <f t="shared" ref="BF12" si="49">BE12*1.03</f>
+        <v>1167.6176503570634</v>
       </c>
       <c r="BG12" s="4">
-        <f t="shared" ref="BG12" si="51">BF12*1.03</f>
-        <v>1074.6643985451844</v>
+        <f t="shared" ref="BG12" si="50">BF12*1.03</f>
+        <v>1202.6461798677753</v>
       </c>
       <c r="BH12" s="4">
-        <f t="shared" ref="BH12" si="52">BG12*1.03</f>
-        <v>1106.90433050154</v>
+        <f t="shared" ref="BH12" si="51">BG12*1.03</f>
+        <v>1238.7255652638087</v>
       </c>
       <c r="BI12" s="4">
-        <f t="shared" ref="BI12" si="53">BH12*1.03</f>
-        <v>1140.1114604165862</v>
+        <f t="shared" ref="BI12" si="52">BH12*1.03</f>
+        <v>1275.887332221723</v>
       </c>
     </row>
     <row r="13" spans="2:61" x14ac:dyDescent="0.3">
@@ -3733,237 +3724,237 @@
         <v>40</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:R13" si="54">SUM(C8:C12)</f>
+        <f t="shared" ref="C13:R13" si="53">SUM(C8:C12)</f>
         <v>12269</v>
       </c>
       <c r="D13" s="4">
+        <f t="shared" si="53"/>
+        <v>13876</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="53"/>
+        <v>15848</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="53"/>
+        <v>19832</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="53"/>
+        <v>18380</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" si="53"/>
+        <v>19271</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="53"/>
+        <v>19849</v>
+      </c>
+      <c r="J13" s="4">
+        <f t="shared" si="53"/>
+        <v>23811</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="53"/>
+        <v>21360</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="53"/>
+        <v>23983</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="53"/>
+        <v>25522</v>
+      </c>
+      <c r="N13" s="4">
+        <f t="shared" si="53"/>
+        <v>29581</v>
+      </c>
+      <c r="O13" s="4">
+        <f t="shared" si="53"/>
+        <v>27206</v>
+      </c>
+      <c r="P13" s="4">
+        <f t="shared" si="53"/>
+        <v>30409</v>
+      </c>
+      <c r="Q13" s="4">
+        <f t="shared" si="53"/>
+        <v>32845</v>
+      </c>
+      <c r="R13" s="4">
+        <f t="shared" si="53"/>
+        <v>39398</v>
+      </c>
+      <c r="S13" s="4">
+        <f t="shared" ref="S13:V13" si="54">SUM(S8:S12)</f>
+        <v>37250</v>
+      </c>
+      <c r="T13" s="4">
+        <f t="shared" ref="T13:U13" si="55">SUM(T8:T12)</f>
+        <v>41202</v>
+      </c>
+      <c r="U13" s="4">
+        <f t="shared" si="55"/>
+        <v>43030</v>
+      </c>
+      <c r="V13" s="4">
         <f t="shared" si="54"/>
-        <v>13876</v>
-      </c>
-      <c r="E13" s="4">
-        <f t="shared" si="54"/>
-        <v>15848</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="54"/>
-        <v>19832</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="54"/>
-        <v>18380</v>
-      </c>
-      <c r="H13" s="4">
-        <f t="shared" si="54"/>
-        <v>19271</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="54"/>
-        <v>19849</v>
-      </c>
-      <c r="J13" s="4">
-        <f t="shared" si="54"/>
-        <v>23811</v>
-      </c>
-      <c r="K13" s="4">
-        <f t="shared" si="54"/>
-        <v>21360</v>
-      </c>
-      <c r="L13" s="4">
-        <f t="shared" si="54"/>
-        <v>23983</v>
-      </c>
-      <c r="M13" s="4">
-        <f t="shared" si="54"/>
-        <v>25522</v>
-      </c>
-      <c r="N13" s="4">
-        <f t="shared" si="54"/>
-        <v>29581</v>
-      </c>
-      <c r="O13" s="4">
-        <f t="shared" si="54"/>
-        <v>27206</v>
-      </c>
-      <c r="P13" s="4">
-        <f t="shared" si="54"/>
-        <v>30409</v>
-      </c>
-      <c r="Q13" s="4">
-        <f t="shared" si="54"/>
-        <v>32845</v>
-      </c>
-      <c r="R13" s="4">
-        <f t="shared" si="54"/>
-        <v>39398</v>
-      </c>
-      <c r="S13" s="4">
-        <f t="shared" ref="S13:V13" si="55">SUM(S8:S12)</f>
-        <v>37250</v>
-      </c>
-      <c r="T13" s="4">
-        <f t="shared" ref="T13:U13" si="56">SUM(T8:T12)</f>
-        <v>41202</v>
-      </c>
-      <c r="U13" s="4">
+        <v>51117</v>
+      </c>
+      <c r="W13" s="4">
+        <f t="shared" ref="W13:X13" si="56">SUM(W8:W12)</f>
+        <v>46276</v>
+      </c>
+      <c r="X13" s="4">
         <f t="shared" si="56"/>
-        <v>43030</v>
-      </c>
-      <c r="V13" s="4">
-        <f t="shared" si="55"/>
-        <v>51117</v>
-      </c>
-      <c r="W13" s="4">
-        <f t="shared" ref="W13:X13" si="57">SUM(W8:W12)</f>
-        <v>46276</v>
-      </c>
-      <c r="X13" s="4">
-        <f t="shared" si="57"/>
         <v>51493</v>
       </c>
       <c r="Y13" s="4">
-        <f t="shared" ref="Y13" si="58">SUM(Y8:Y12)</f>
+        <f t="shared" ref="Y13" si="57">SUM(Y8:Y12)</f>
         <v>54308</v>
       </c>
       <c r="Z13" s="4">
-        <f t="shared" ref="Z13" si="59">SUM(Z8:Z12)</f>
+        <f t="shared" ref="Z13" si="58">SUM(Z8:Z12)</f>
         <v>60827</v>
       </c>
       <c r="AA13" s="4">
-        <f t="shared" ref="AA13:AB13" si="60">SUM(AA8:AA12)</f>
+        <f t="shared" ref="AA13:AB13" si="59">SUM(AA8:AA12)</f>
         <v>54793</v>
       </c>
       <c r="AB13" s="4">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>57329</v>
       </c>
       <c r="AC13" s="4">
-        <f t="shared" ref="AC13" si="61">SUM(AC8:AC12)</f>
+        <f t="shared" ref="AC13" si="60">SUM(AC8:AC12)</f>
         <v>56873</v>
       </c>
       <c r="AD13" s="4">
-        <f t="shared" ref="AD13" si="62">SUM(AD8:AD12)</f>
+        <f t="shared" ref="AD13" si="61">SUM(AD8:AD12)</f>
         <v>64199</v>
       </c>
       <c r="AE13" s="4">
-        <f t="shared" ref="AE13:AF13" si="63">SUM(AE8:AE12)</f>
+        <f t="shared" ref="AE13:AF13" si="62">SUM(AE8:AE12)</f>
         <v>55373</v>
       </c>
       <c r="AF13" s="4">
+        <f t="shared" si="62"/>
+        <v>59520</v>
+      </c>
+      <c r="AG13" s="4">
+        <f t="shared" ref="AG13:AH13" si="63">SUM(AG8:AG12)</f>
+        <v>60489</v>
+      </c>
+      <c r="AH13" s="4">
         <f t="shared" si="63"/>
-        <v>59520</v>
-      </c>
-      <c r="AG13" s="4">
-        <f t="shared" ref="AG13:AH13" si="64">SUM(AG8:AG12)</f>
-        <v>60489</v>
-      </c>
-      <c r="AH13" s="4">
+        <v>67696</v>
+      </c>
+      <c r="AI13" s="4">
+        <f t="shared" ref="AI13:AL13" si="64">SUM(AI8:AI12)</f>
+        <v>60286</v>
+      </c>
+      <c r="AJ13" s="4">
         <f t="shared" si="64"/>
-        <v>67696</v>
-      </c>
-      <c r="AI13" s="4">
-        <f t="shared" ref="AI13:AL13" si="65">SUM(AI8:AI12)</f>
-        <v>60286</v>
-      </c>
-      <c r="AJ13" s="4">
-        <f t="shared" si="65"/>
-        <v>63412.396250000005</v>
+        <v>67722</v>
       </c>
       <c r="AK13" s="4">
-        <f t="shared" si="65"/>
-        <v>65520.184000000008</v>
+        <f t="shared" si="64"/>
+        <v>70052.970249999998</v>
       </c>
       <c r="AL13" s="4">
-        <f t="shared" si="65"/>
-        <v>71080.136700000003</v>
+        <f t="shared" si="64"/>
+        <v>75473.473299999998</v>
       </c>
       <c r="AM13" s="4"/>
       <c r="AN13" s="4">
-        <f t="shared" ref="AN13:AU13" si="66">SUM(AN8:AN12)</f>
+        <f t="shared" ref="AN13:AU13" si="65">SUM(AN8:AN12)</f>
         <v>26058</v>
       </c>
       <c r="AO13" s="4">
+        <f t="shared" si="65"/>
+        <v>33122</v>
+      </c>
+      <c r="AP13" s="4">
+        <f t="shared" si="65"/>
+        <v>43536</v>
+      </c>
+      <c r="AQ13" s="4">
+        <f t="shared" si="65"/>
+        <v>61825</v>
+      </c>
+      <c r="AR13" s="4">
+        <f t="shared" si="65"/>
+        <v>81311</v>
+      </c>
+      <c r="AS13" s="4">
+        <f t="shared" si="65"/>
+        <v>100446</v>
+      </c>
+      <c r="AT13" s="4">
+        <f t="shared" si="65"/>
+        <v>129858</v>
+      </c>
+      <c r="AU13" s="4">
+        <f t="shared" si="65"/>
+        <v>172599</v>
+      </c>
+      <c r="AV13" s="4">
+        <f t="shared" ref="AV13:BE13" si="66">SUM(AV8:AV12)</f>
+        <v>212904</v>
+      </c>
+      <c r="AW13" s="4">
         <f t="shared" si="66"/>
-        <v>33122</v>
-      </c>
-      <c r="AP13" s="4">
+        <v>233194</v>
+      </c>
+      <c r="AX13" s="4">
+        <f t="shared" ref="AX13" si="67">SUM(AX8:AX12)</f>
+        <v>243078</v>
+      </c>
+      <c r="AY13" s="4">
         <f t="shared" si="66"/>
-        <v>43536</v>
-      </c>
-      <c r="AQ13" s="4">
+        <v>273534.44355000003</v>
+      </c>
+      <c r="AZ13" s="4">
         <f t="shared" si="66"/>
-        <v>61825</v>
-      </c>
-      <c r="AR13" s="4">
+        <v>285648.49170299998</v>
+      </c>
+      <c r="BA13" s="4">
         <f t="shared" si="66"/>
-        <v>81311</v>
-      </c>
-      <c r="AS13" s="4">
+        <v>300627.39168744005</v>
+      </c>
+      <c r="BB13" s="4">
         <f t="shared" si="66"/>
-        <v>100446</v>
-      </c>
-      <c r="AT13" s="4">
+        <v>312601.75125642237</v>
+      </c>
+      <c r="BC13" s="4">
         <f t="shared" si="66"/>
-        <v>129858</v>
-      </c>
-      <c r="AU13" s="4">
+        <v>321036.49657225702</v>
+      </c>
+      <c r="BD13" s="4">
         <f t="shared" si="66"/>
-        <v>172599</v>
-      </c>
-      <c r="AV13" s="4">
-        <f t="shared" ref="AV13:BE13" si="67">SUM(AV8:AV12)</f>
-        <v>212904</v>
-      </c>
-      <c r="AW13" s="4">
-        <f t="shared" si="67"/>
-        <v>233194</v>
-      </c>
-      <c r="AX13" s="4">
-        <f t="shared" ref="AX13" si="68">SUM(AX8:AX12)</f>
-        <v>243078</v>
-      </c>
-      <c r="AY13" s="4">
-        <f t="shared" si="67"/>
-        <v>260298.71695000003</v>
-      </c>
-      <c r="AZ13" s="4">
-        <f t="shared" si="67"/>
-        <v>268331.83283500001</v>
-      </c>
-      <c r="BA13" s="4">
-        <f t="shared" si="67"/>
-        <v>281505.32334040001</v>
-      </c>
-      <c r="BB13" s="4">
-        <f t="shared" si="67"/>
-        <v>291782.56359608204</v>
-      </c>
-      <c r="BC13" s="4">
-        <f t="shared" si="67"/>
-        <v>299740.99098398502</v>
-      </c>
-      <c r="BD13" s="4">
-        <f t="shared" si="67"/>
-        <v>306719.91923952074</v>
+        <v>328474.21555734152</v>
       </c>
       <c r="BE13" s="4">
-        <f t="shared" si="67"/>
-        <v>312738.44477601192</v>
+        <f t="shared" si="66"/>
+        <v>334930.16156900855</v>
       </c>
       <c r="BF13" s="4">
-        <f t="shared" ref="BF13:BI13" si="69">SUM(BF8:BF12)</f>
-        <v>317040.72238064511</v>
+        <f t="shared" ref="BF13:BI13" si="68">SUM(BF8:BF12)</f>
+        <v>339488.90868384182</v>
       </c>
       <c r="BG13" s="4">
-        <f t="shared" si="69"/>
-        <v>320231.9968743262</v>
+        <f t="shared" si="68"/>
+        <v>342907.1501236874</v>
       </c>
       <c r="BH13" s="4">
-        <f t="shared" si="69"/>
-        <v>323455.8101310404</v>
+        <f t="shared" si="68"/>
+        <v>346360.27454852161</v>
       </c>
       <c r="BI13" s="4">
-        <f t="shared" si="69"/>
-        <v>326712.50631896086</v>
+        <f t="shared" si="68"/>
+        <v>349848.65180531208</v>
       </c>
     </row>
     <row r="14" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3971,236 +3962,236 @@
         <v>42</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:R14" si="70">C7-C13</f>
+        <f t="shared" ref="C14:R14" si="69">C7-C13</f>
         <v>1005</v>
       </c>
       <c r="D14" s="8">
+        <f t="shared" si="69"/>
+        <v>628</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="69"/>
+        <v>347</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="69"/>
+        <v>2127</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="69"/>
+        <v>1927</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="69"/>
+        <v>2983</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="69"/>
+        <v>3724</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="69"/>
+        <v>3786</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="69"/>
+        <v>4420</v>
+      </c>
+      <c r="L14" s="8">
+        <f t="shared" si="69"/>
+        <v>3084</v>
+      </c>
+      <c r="M14" s="8">
+        <f t="shared" si="69"/>
+        <v>3157</v>
+      </c>
+      <c r="N14" s="8">
+        <f t="shared" si="69"/>
+        <v>3879</v>
+      </c>
+      <c r="O14" s="8">
+        <f t="shared" si="69"/>
+        <v>3989</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" si="69"/>
+        <v>5843</v>
+      </c>
+      <c r="Q14" s="8">
+        <f t="shared" si="69"/>
+        <v>6194</v>
+      </c>
+      <c r="R14" s="8">
+        <f t="shared" si="69"/>
+        <v>6873</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" ref="S14:V14" si="70">S7-S13</f>
+        <v>8865</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" ref="T14:U14" si="71">T7-T13</f>
+        <v>7702</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" si="71"/>
+        <v>4852</v>
+      </c>
+      <c r="V14" s="8">
         <f t="shared" si="70"/>
-        <v>628</v>
-      </c>
-      <c r="E14" s="8">
-        <f t="shared" si="70"/>
-        <v>347</v>
-      </c>
-      <c r="F14" s="8">
-        <f t="shared" si="70"/>
-        <v>2127</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="70"/>
-        <v>1927</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="70"/>
-        <v>2983</v>
-      </c>
-      <c r="I14" s="8">
-        <f t="shared" si="70"/>
-        <v>3724</v>
-      </c>
-      <c r="J14" s="8">
-        <f t="shared" si="70"/>
-        <v>3786</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="70"/>
-        <v>4420</v>
-      </c>
-      <c r="L14" s="8">
-        <f t="shared" si="70"/>
-        <v>3084</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" si="70"/>
-        <v>3157</v>
-      </c>
-      <c r="N14" s="8">
-        <f t="shared" si="70"/>
-        <v>3879</v>
-      </c>
-      <c r="O14" s="8">
-        <f t="shared" si="70"/>
-        <v>3989</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" si="70"/>
-        <v>5843</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="70"/>
-        <v>6194</v>
-      </c>
-      <c r="R14" s="8">
-        <f t="shared" si="70"/>
-        <v>6873</v>
-      </c>
-      <c r="S14" s="8">
-        <f t="shared" ref="S14:V14" si="71">S7-S13</f>
-        <v>8865</v>
-      </c>
-      <c r="T14" s="8">
-        <f t="shared" ref="T14:U14" si="72">T7-T13</f>
-        <v>7702</v>
-      </c>
-      <c r="U14" s="8">
+        <v>3460</v>
+      </c>
+      <c r="W14" s="8">
+        <f t="shared" ref="W14:X14" si="72">W7-W13</f>
+        <v>3669</v>
+      </c>
+      <c r="X14" s="8">
         <f t="shared" si="72"/>
-        <v>4852</v>
-      </c>
-      <c r="V14" s="8">
-        <f t="shared" si="71"/>
-        <v>3460</v>
-      </c>
-      <c r="W14" s="8">
-        <f t="shared" ref="W14:X14" si="73">W7-W13</f>
-        <v>3669</v>
-      </c>
-      <c r="X14" s="8">
-        <f t="shared" si="73"/>
         <v>3317</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" ref="Y14" si="74">Y7-Y13</f>
+        <f t="shared" ref="Y14" si="73">Y7-Y13</f>
         <v>2525</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" ref="Z14" si="75">Z7-Z13</f>
+        <f t="shared" ref="Z14" si="74">Z7-Z13</f>
         <v>2737</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" ref="AA14:AB14" si="76">AA7-AA13</f>
+        <f t="shared" ref="AA14:AB14" si="75">AA7-AA13</f>
         <v>4774</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>7681</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" ref="AC14" si="77">AC7-AC13</f>
+        <f t="shared" ref="AC14" si="76">AC7-AC13</f>
         <v>11188</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" ref="AD14" si="78">AD7-AD13</f>
+        <f t="shared" ref="AD14" si="77">AD7-AD13</f>
         <v>13209</v>
       </c>
       <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AF14" si="79">AE7-AE13</f>
+        <f t="shared" ref="AE14:AF14" si="78">AE7-AE13</f>
         <v>15307</v>
       </c>
       <c r="AF14" s="8">
+        <f t="shared" si="78"/>
+        <v>14672</v>
+      </c>
+      <c r="AG14" s="8">
+        <f t="shared" ref="AG14:AH14" si="79">AG7-AG13</f>
+        <v>17411</v>
+      </c>
+      <c r="AH14" s="8">
         <f t="shared" si="79"/>
-        <v>14672</v>
-      </c>
-      <c r="AG14" s="8">
-        <f t="shared" ref="AG14:AH14" si="80">AG7-AG13</f>
-        <v>17411</v>
-      </c>
-      <c r="AH14" s="8">
+        <v>21203</v>
+      </c>
+      <c r="AI14" s="8">
+        <f t="shared" ref="AI14:AL14" si="80">AI7-AI13</f>
+        <v>18405</v>
+      </c>
+      <c r="AJ14" s="8">
         <f t="shared" si="80"/>
-        <v>21203</v>
-      </c>
-      <c r="AI14" s="8">
-        <f t="shared" ref="AI14:AL14" si="81">AI7-AI13</f>
-        <v>18405</v>
-      </c>
-      <c r="AJ14" s="8">
+        <v>19171</v>
+      </c>
+      <c r="AK14" s="8">
+        <f t="shared" si="80"/>
+        <v>17464.874750000003</v>
+      </c>
+      <c r="AL14" s="8">
+        <f t="shared" si="80"/>
+        <v>24880.790500000003</v>
+      </c>
+      <c r="AN14" s="8">
+        <f t="shared" ref="AN14:AU14" si="81">AN7-AN13</f>
+        <v>178</v>
+      </c>
+      <c r="AO14" s="8">
         <f t="shared" si="81"/>
-        <v>16435.728749999995</v>
-      </c>
-      <c r="AK14" s="8">
+        <v>2233</v>
+      </c>
+      <c r="AP14" s="8">
         <f t="shared" si="81"/>
-        <v>19834.135999999999</v>
-      </c>
-      <c r="AL14" s="8">
+        <v>4186</v>
+      </c>
+      <c r="AQ14" s="8">
         <f t="shared" si="81"/>
-        <v>25311.245699999999</v>
-      </c>
-      <c r="AN14" s="8">
-        <f t="shared" ref="AN14:AU14" si="82">AN7-AN13</f>
-        <v>178</v>
-      </c>
-      <c r="AO14" s="8">
+        <v>4107</v>
+      </c>
+      <c r="AR14" s="8">
+        <f t="shared" si="81"/>
+        <v>12420</v>
+      </c>
+      <c r="AS14" s="8">
+        <f t="shared" si="81"/>
+        <v>14540</v>
+      </c>
+      <c r="AT14" s="8">
+        <f t="shared" si="81"/>
+        <v>22899</v>
+      </c>
+      <c r="AU14" s="8">
+        <f t="shared" si="81"/>
+        <v>24879</v>
+      </c>
+      <c r="AV14" s="8">
+        <f t="shared" ref="AV14:BE14" si="82">AV7-AV13</f>
+        <v>12248</v>
+      </c>
+      <c r="AW14" s="8">
         <f t="shared" si="82"/>
-        <v>2233</v>
-      </c>
-      <c r="AP14" s="8">
+        <v>36852</v>
+      </c>
+      <c r="AX14" s="8">
+        <f t="shared" ref="AX14" si="83">AX7-AX13</f>
+        <v>68593</v>
+      </c>
+      <c r="AY14" s="8">
         <f t="shared" si="82"/>
-        <v>4186</v>
-      </c>
-      <c r="AQ14" s="8">
+        <v>79921.665249999904</v>
+      </c>
+      <c r="AZ14" s="8">
         <f t="shared" si="82"/>
-        <v>4107</v>
-      </c>
-      <c r="AR14" s="8">
+        <v>99375.837090000045</v>
+      </c>
+      <c r="BA14" s="8">
         <f t="shared" si="82"/>
-        <v>12420</v>
-      </c>
-      <c r="AS14" s="8">
+        <v>117046.86773783999</v>
+      </c>
+      <c r="BB14" s="8">
         <f t="shared" si="82"/>
-        <v>14540</v>
-      </c>
-      <c r="AT14" s="8">
+        <v>133634.24259256088</v>
+      </c>
+      <c r="BC14" s="8">
         <f t="shared" si="82"/>
-        <v>22899</v>
-      </c>
-      <c r="AU14" s="8">
+        <v>139606.77984099259</v>
+      </c>
+      <c r="BD14" s="8">
         <f t="shared" si="82"/>
-        <v>24879</v>
-      </c>
-      <c r="AV14" s="8">
-        <f t="shared" ref="AV14:BE14" si="83">AV7-AV13</f>
-        <v>12248</v>
-      </c>
-      <c r="AW14" s="8">
-        <f t="shared" si="83"/>
-        <v>36852</v>
-      </c>
-      <c r="AX14" s="8">
-        <f t="shared" ref="AX14" si="84">AX7-AX13</f>
-        <v>68593</v>
-      </c>
-      <c r="AY14" s="8">
-        <f t="shared" si="83"/>
-        <v>79986.110449999978</v>
-      </c>
-      <c r="AZ14" s="8">
-        <f t="shared" si="83"/>
-        <v>100349.42391500005</v>
-      </c>
-      <c r="BA14" s="8">
-        <f t="shared" si="83"/>
-        <v>110714.51327960007</v>
-      </c>
-      <c r="BB14" s="8">
-        <f t="shared" si="83"/>
-        <v>119324.84509851801</v>
-      </c>
-      <c r="BC14" s="8">
-        <f t="shared" si="83"/>
-        <v>124620.72294754704</v>
-      </c>
-      <c r="BD14" s="8">
-        <f t="shared" si="83"/>
-        <v>128745.75064342277</v>
+        <v>144232.85898156202</v>
       </c>
       <c r="BE14" s="8">
-        <f t="shared" si="83"/>
-        <v>131436.53850459045</v>
+        <f t="shared" si="82"/>
+        <v>147231.05446067313</v>
       </c>
       <c r="BF14" s="8">
-        <f t="shared" ref="BF14:BI14" si="85">BF7-BF13</f>
-        <v>134325.13852218678</v>
+        <f t="shared" ref="BF14:BI14" si="84">BF7-BF13</f>
+        <v>150489.10929295362</v>
       </c>
       <c r="BG14" s="8">
-        <f t="shared" si="85"/>
-        <v>135647.52263753401</v>
+        <f t="shared" si="84"/>
+        <v>151970.64803287596</v>
       </c>
       <c r="BH14" s="8">
-        <f t="shared" si="85"/>
-        <v>136982.50457593845</v>
+        <f t="shared" si="84"/>
+        <v>153466.30158960744</v>
       </c>
       <c r="BI14" s="8">
-        <f t="shared" si="85"/>
-        <v>138330.19153508777</v>
+        <f t="shared" si="84"/>
+        <v>154976.19009419822</v>
       </c>
     </row>
     <row r="15" spans="2:61" x14ac:dyDescent="0.3">
@@ -4307,15 +4298,14 @@
         <v>-1066</v>
       </c>
       <c r="AJ15" s="4">
-        <f t="shared" ref="AJ15:AL15" si="86">AF15*1.05</f>
-        <v>-1239</v>
+        <v>-1085</v>
       </c>
       <c r="AK15" s="4">
-        <f t="shared" si="86"/>
+        <f t="shared" ref="AK15:AL15" si="85">AG15*1.05</f>
         <v>-1318.8</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" si="86"/>
+        <f t="shared" si="85"/>
         <v>-1310.4000000000001</v>
       </c>
       <c r="AN15" s="4">
@@ -4361,47 +4351,47 @@
       </c>
       <c r="AY15" s="4">
         <f>SUM(AI15:AL15)</f>
-        <v>-4934.2000000000007</v>
+        <v>-4780.2000000000007</v>
       </c>
       <c r="AZ15" s="4">
         <f>AY15*1.05</f>
-        <v>-5180.9100000000008</v>
+        <v>-5019.2100000000009</v>
       </c>
       <c r="BA15" s="4">
-        <f t="shared" ref="BA15:BI15" si="87">AZ15*1.05</f>
-        <v>-5439.9555000000009</v>
+        <f t="shared" ref="BA15:BI15" si="86">AZ15*1.05</f>
+        <v>-5270.1705000000011</v>
       </c>
       <c r="BB15" s="4">
-        <f t="shared" si="87"/>
-        <v>-5711.9532750000017</v>
+        <f t="shared" si="86"/>
+        <v>-5533.6790250000013</v>
       </c>
       <c r="BC15" s="4">
-        <f t="shared" si="87"/>
-        <v>-5997.5509387500024</v>
+        <f t="shared" si="86"/>
+        <v>-5810.3629762500013</v>
       </c>
       <c r="BD15" s="4">
-        <f t="shared" si="87"/>
-        <v>-6297.4284856875029</v>
+        <f t="shared" si="86"/>
+        <v>-6100.8811250625013</v>
       </c>
       <c r="BE15" s="4">
-        <f t="shared" si="87"/>
-        <v>-6612.2999099718782</v>
+        <f t="shared" si="86"/>
+        <v>-6405.925181315627</v>
       </c>
       <c r="BF15" s="4">
-        <f t="shared" si="87"/>
-        <v>-6942.9149054704721</v>
+        <f t="shared" si="86"/>
+        <v>-6726.2214403814087</v>
       </c>
       <c r="BG15" s="4">
-        <f t="shared" si="87"/>
-        <v>-7290.0606507439961</v>
+        <f t="shared" si="86"/>
+        <v>-7062.5325124004794</v>
       </c>
       <c r="BH15" s="4">
-        <f t="shared" si="87"/>
-        <v>-7654.5636832811961</v>
+        <f t="shared" si="86"/>
+        <v>-7415.6591380205036</v>
       </c>
       <c r="BI15" s="4">
-        <f t="shared" si="87"/>
-        <v>-8037.2918674452558</v>
+        <f t="shared" si="86"/>
+        <v>-7786.4420949215291</v>
       </c>
     </row>
     <row r="16" spans="2:61" x14ac:dyDescent="0.3">
@@ -4508,15 +4498,14 @@
         <v>541</v>
       </c>
       <c r="AJ16" s="4">
-        <f t="shared" ref="AJ16:AL16" si="88">AF16*0.98</f>
-        <v>577.22</v>
+        <v>516</v>
       </c>
       <c r="AK16" s="4">
-        <f t="shared" si="88"/>
+        <f t="shared" ref="AK16:AL16" si="87">AG16*0.98</f>
         <v>590.93999999999994</v>
       </c>
       <c r="AL16" s="4">
-        <f t="shared" si="88"/>
+        <f t="shared" si="87"/>
         <v>558.6</v>
       </c>
       <c r="AN16" s="4">
@@ -4562,47 +4551,47 @@
       </c>
       <c r="AY16" s="4">
         <f>SUM(AI16:AL16)</f>
-        <v>2267.7599999999998</v>
+        <v>2206.54</v>
       </c>
       <c r="AZ16" s="4">
-        <f t="shared" ref="AZ16:BI16" si="89">AY16*1.01</f>
-        <v>2290.4375999999997</v>
+        <f t="shared" ref="AZ16:BI16" si="88">AY16*1.01</f>
+        <v>2228.6053999999999</v>
       </c>
       <c r="BA16" s="4">
-        <f t="shared" si="89"/>
-        <v>2313.3419759999997</v>
+        <f t="shared" si="88"/>
+        <v>2250.8914540000001</v>
       </c>
       <c r="BB16" s="4">
-        <f t="shared" si="89"/>
-        <v>2336.4753957599996</v>
+        <f t="shared" si="88"/>
+        <v>2273.4003685400003</v>
       </c>
       <c r="BC16" s="4">
-        <f t="shared" si="89"/>
-        <v>2359.8401497175996</v>
+        <f t="shared" si="88"/>
+        <v>2296.1343722254005</v>
       </c>
       <c r="BD16" s="4">
-        <f t="shared" si="89"/>
-        <v>2383.4385512147755</v>
+        <f t="shared" si="88"/>
+        <v>2319.0957159476548</v>
       </c>
       <c r="BE16" s="4">
-        <f t="shared" si="89"/>
-        <v>2407.2729367269235</v>
+        <f t="shared" si="88"/>
+        <v>2342.2866731071313</v>
       </c>
       <c r="BF16" s="4">
-        <f t="shared" si="89"/>
-        <v>2431.3456660941929</v>
+        <f t="shared" si="88"/>
+        <v>2365.7095398382025</v>
       </c>
       <c r="BG16" s="4">
-        <f t="shared" si="89"/>
-        <v>2455.6591227551348</v>
+        <f t="shared" si="88"/>
+        <v>2389.3666352365844</v>
       </c>
       <c r="BH16" s="4">
-        <f t="shared" si="89"/>
-        <v>2480.2157139826863</v>
+        <f t="shared" si="88"/>
+        <v>2413.2603015889504</v>
       </c>
       <c r="BI16" s="4">
-        <f t="shared" si="89"/>
-        <v>2505.017871122513</v>
+        <f t="shared" si="88"/>
+        <v>2437.3929046048397</v>
       </c>
     </row>
     <row r="17" spans="2:153" x14ac:dyDescent="0.3">
@@ -4709,15 +4698,14 @@
         <v>-2749</v>
       </c>
       <c r="AJ17" s="4">
-        <f t="shared" ref="AJ17:AL17" si="90">AF17*1.01</f>
-        <v>18.18</v>
+        <v>-1117</v>
       </c>
       <c r="AK17" s="4">
-        <f t="shared" si="90"/>
+        <f t="shared" ref="AK17:AL17" si="89">AG17*1.01</f>
         <v>27.27</v>
       </c>
       <c r="AL17" s="4">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>-472.68</v>
       </c>
       <c r="AN17" s="4">
@@ -4763,47 +4751,47 @@
       </c>
       <c r="AY17" s="4">
         <f>SUM(AI17:AL17)</f>
-        <v>-3176.23</v>
+        <v>-4311.41</v>
       </c>
       <c r="AZ17" s="4">
-        <f t="shared" ref="AZ17:BE17" si="91">AY17*1.01</f>
-        <v>-3207.9922999999999</v>
+        <f t="shared" ref="AZ17:BE17" si="90">AY17*1.01</f>
+        <v>-4354.5240999999996</v>
       </c>
       <c r="BA17" s="4">
-        <f t="shared" si="91"/>
-        <v>-3240.0722230000001</v>
+        <f t="shared" si="90"/>
+        <v>-4398.0693409999994</v>
       </c>
       <c r="BB17" s="4">
-        <f t="shared" si="91"/>
-        <v>-3272.4729452300003</v>
+        <f t="shared" si="90"/>
+        <v>-4442.0500344099992</v>
       </c>
       <c r="BC17" s="4">
-        <f t="shared" si="91"/>
-        <v>-3305.1976746823002</v>
+        <f t="shared" si="90"/>
+        <v>-4486.4705347540994</v>
       </c>
       <c r="BD17" s="4">
-        <f t="shared" si="91"/>
-        <v>-3338.2496514291233</v>
+        <f t="shared" si="90"/>
+        <v>-4531.33524010164</v>
       </c>
       <c r="BE17" s="4">
-        <f t="shared" si="91"/>
-        <v>-3371.6321479434146</v>
+        <f t="shared" si="90"/>
+        <v>-4576.6485925026564</v>
       </c>
       <c r="BF17" s="4">
-        <f t="shared" ref="BF17" si="92">BE17*1.01</f>
-        <v>-3405.3484694228487</v>
+        <f t="shared" ref="BF17" si="91">BE17*1.01</f>
+        <v>-4622.4150784276826</v>
       </c>
       <c r="BG17" s="4">
-        <f t="shared" ref="BG17" si="93">BF17*1.01</f>
-        <v>-3439.4019541170774</v>
+        <f t="shared" ref="BG17" si="92">BF17*1.01</f>
+        <v>-4668.6392292119599</v>
       </c>
       <c r="BH17" s="4">
-        <f t="shared" ref="BH17" si="94">BG17*1.01</f>
-        <v>-3473.7959736582484</v>
+        <f t="shared" ref="BH17" si="93">BG17*1.01</f>
+        <v>-4715.3256215040792</v>
       </c>
       <c r="BI17" s="4">
-        <f t="shared" ref="BI17" si="95">BH17*1.01</f>
-        <v>-3508.5339333948309</v>
+        <f t="shared" ref="BI17" si="94">BH17*1.01</f>
+        <v>-4762.4788777191197</v>
       </c>
     </row>
     <row r="18" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4811,236 +4799,236 @@
         <v>46</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:R18" si="96">C14-C15-C16-C17</f>
+        <f t="shared" ref="C18:R18" si="95">C14-C15-C16-C17</f>
         <v>953</v>
       </c>
       <c r="D18" s="8">
+        <f t="shared" si="95"/>
+        <v>666</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" si="95"/>
+        <v>316</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="95"/>
+        <v>1872</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="95"/>
+        <v>1916</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="95"/>
+        <v>2605</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="95"/>
+        <v>3390</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="95"/>
+        <v>3350</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="95"/>
+        <v>4401</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="95"/>
+        <v>2889</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="95"/>
+        <v>2632</v>
+      </c>
+      <c r="N18" s="8">
+        <f t="shared" si="95"/>
+        <v>4053</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="95"/>
+        <v>3383</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="95"/>
+        <v>6221</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="95"/>
+        <v>6809</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="95"/>
+        <v>7765</v>
+      </c>
+      <c r="S18" s="8">
+        <f t="shared" ref="S18:V18" si="96">S14-S15-S16-S17</f>
+        <v>10268</v>
+      </c>
+      <c r="T18" s="8">
+        <f t="shared" ref="T18:U18" si="97">T14-T15-T16-T17</f>
+        <v>8634</v>
+      </c>
+      <c r="U18" s="8">
+        <f t="shared" si="97"/>
+        <v>4315</v>
+      </c>
+      <c r="V18" s="8">
         <f t="shared" si="96"/>
-        <v>666</v>
-      </c>
-      <c r="E18" s="8">
-        <f t="shared" si="96"/>
-        <v>316</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="96"/>
-        <v>1872</v>
-      </c>
-      <c r="G18" s="8">
-        <f t="shared" si="96"/>
-        <v>1916</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="96"/>
-        <v>2605</v>
-      </c>
-      <c r="I18" s="8">
-        <f t="shared" si="96"/>
-        <v>3390</v>
-      </c>
-      <c r="J18" s="8">
-        <f t="shared" si="96"/>
-        <v>3350</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="96"/>
-        <v>4401</v>
-      </c>
-      <c r="L18" s="8">
-        <f t="shared" si="96"/>
-        <v>2889</v>
-      </c>
-      <c r="M18" s="8">
-        <f t="shared" si="96"/>
-        <v>2632</v>
-      </c>
-      <c r="N18" s="8">
-        <f t="shared" si="96"/>
-        <v>4053</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" si="96"/>
-        <v>3383</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" si="96"/>
-        <v>6221</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="96"/>
-        <v>6809</v>
-      </c>
-      <c r="R18" s="8">
-        <f t="shared" si="96"/>
-        <v>7765</v>
-      </c>
-      <c r="S18" s="8">
-        <f t="shared" ref="S18:V18" si="97">S14-S15-S16-S17</f>
-        <v>10268</v>
-      </c>
-      <c r="T18" s="8">
-        <f t="shared" ref="T18:U18" si="98">T14-T15-T16-T17</f>
-        <v>8634</v>
-      </c>
-      <c r="U18" s="8">
+        <v>14934</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" ref="W18:X18" si="98">W14-W15-W16-W17</f>
+        <v>-5265</v>
+      </c>
+      <c r="X18" s="8">
         <f t="shared" si="98"/>
-        <v>4315</v>
-      </c>
-      <c r="V18" s="8">
-        <f t="shared" si="97"/>
-        <v>14934</v>
-      </c>
-      <c r="W18" s="8">
-        <f t="shared" ref="W18:X18" si="99">W14-W15-W16-W17</f>
-        <v>-5265</v>
-      </c>
-      <c r="X18" s="8">
-        <f t="shared" si="99"/>
         <v>-2653</v>
       </c>
       <c r="Y18" s="8">
-        <f t="shared" ref="Y18" si="100">Y14-Y15-Y16-Y17</f>
+        <f t="shared" ref="Y18" si="99">Y14-Y15-Y16-Y17</f>
         <v>2944</v>
       </c>
       <c r="Z18" s="8">
-        <f t="shared" ref="Z18" si="101">Z14-Z15-Z16-Z17</f>
+        <f t="shared" ref="Z18" si="100">Z14-Z15-Z16-Z17</f>
         <v>-962</v>
       </c>
       <c r="AA18" s="8">
-        <f t="shared" ref="AA18:AB18" si="102">AA14-AA15-AA16-AA17</f>
+        <f t="shared" ref="AA18:AB18" si="101">AA14-AA15-AA16-AA17</f>
         <v>4119</v>
       </c>
       <c r="AB18" s="8">
-        <f t="shared" si="102"/>
+        <f t="shared" si="101"/>
         <v>7563</v>
       </c>
       <c r="AC18" s="8">
-        <f t="shared" ref="AC18" si="103">AC14-AC15-AC16-AC17</f>
+        <f t="shared" ref="AC18" si="102">AC14-AC15-AC16-AC17</f>
         <v>12189</v>
       </c>
       <c r="AD18" s="8">
-        <f t="shared" ref="AD18" si="104">AD14-AD15-AD16-AD17</f>
+        <f t="shared" ref="AD18" si="103">AD14-AD15-AD16-AD17</f>
         <v>13686</v>
       </c>
       <c r="AE18" s="8">
-        <f t="shared" ref="AE18:AF18" si="105">AE14-AE15-AE16-AE17</f>
+        <f t="shared" ref="AE18:AF18" si="104">AE14-AE15-AE16-AE17</f>
         <v>12983</v>
       </c>
       <c r="AF18" s="8">
+        <f t="shared" si="104"/>
+        <v>15245</v>
+      </c>
+      <c r="AG18" s="8">
+        <f t="shared" ref="AG18:AL18" si="105">AG14-AG15-AG16-AG17</f>
+        <v>18037</v>
+      </c>
+      <c r="AH18" s="8">
         <f t="shared" si="105"/>
-        <v>15245</v>
-      </c>
-      <c r="AG18" s="8">
-        <f t="shared" ref="AG18:AL18" si="106">AG14-AG15-AG16-AG17</f>
-        <v>18037</v>
-      </c>
-      <c r="AH18" s="8">
+        <v>22349</v>
+      </c>
+      <c r="AI18" s="8">
+        <f t="shared" si="105"/>
+        <v>21679</v>
+      </c>
+      <c r="AJ18" s="8">
+        <f t="shared" si="105"/>
+        <v>20857</v>
+      </c>
+      <c r="AK18" s="8">
+        <f t="shared" si="105"/>
+        <v>18165.464750000003</v>
+      </c>
+      <c r="AL18" s="8">
+        <f t="shared" si="105"/>
+        <v>26105.270500000006</v>
+      </c>
+      <c r="AN18" s="8">
+        <f t="shared" ref="AN18:AU18" si="106">AN14-AN15-AN16-AN17</f>
+        <v>-111</v>
+      </c>
+      <c r="AO18" s="8">
         <f t="shared" si="106"/>
-        <v>22349</v>
-      </c>
-      <c r="AI18" s="8">
+        <v>1568</v>
+      </c>
+      <c r="AP18" s="8">
         <f t="shared" si="106"/>
-        <v>21679</v>
-      </c>
-      <c r="AJ18" s="8">
+        <v>3892</v>
+      </c>
+      <c r="AQ18" s="8">
         <f t="shared" si="106"/>
-        <v>17079.328749999993</v>
-      </c>
-      <c r="AK18" s="8">
+        <v>3807</v>
+      </c>
+      <c r="AR18" s="8">
         <f t="shared" si="106"/>
-        <v>20534.725999999999</v>
-      </c>
-      <c r="AL18" s="8">
+        <v>11261</v>
+      </c>
+      <c r="AS18" s="8">
         <f t="shared" si="106"/>
-        <v>26535.725700000003</v>
-      </c>
-      <c r="AN18" s="8">
-        <f t="shared" ref="AN18:AU18" si="107">AN14-AN15-AN16-AN17</f>
-        <v>-111</v>
-      </c>
-      <c r="AO18" s="8">
+        <v>13975</v>
+      </c>
+      <c r="AT18" s="8">
+        <f t="shared" si="106"/>
+        <v>24178</v>
+      </c>
+      <c r="AU18" s="8">
+        <f t="shared" si="106"/>
+        <v>38151</v>
+      </c>
+      <c r="AV18" s="8">
+        <f t="shared" ref="AV18:BE18" si="107">AV14-AV15-AV16-AV17</f>
+        <v>-5936</v>
+      </c>
+      <c r="AW18" s="8">
         <f t="shared" si="107"/>
-        <v>1568</v>
-      </c>
-      <c r="AP18" s="8">
+        <v>37557</v>
+      </c>
+      <c r="AX18" s="8">
+        <f t="shared" ref="AX18" si="108">AX14-AX15-AX16-AX17</f>
+        <v>68614</v>
+      </c>
+      <c r="AY18" s="8">
         <f t="shared" si="107"/>
-        <v>3892</v>
-      </c>
-      <c r="AQ18" s="8">
+        <v>86806.735249999911</v>
+      </c>
+      <c r="AZ18" s="8">
         <f t="shared" si="107"/>
-        <v>3807</v>
-      </c>
-      <c r="AR18" s="8">
+        <v>106520.96579000005</v>
+      </c>
+      <c r="BA18" s="8">
         <f t="shared" si="107"/>
-        <v>11261</v>
-      </c>
-      <c r="AS18" s="8">
+        <v>124464.21612483999</v>
+      </c>
+      <c r="BB18" s="8">
         <f t="shared" si="107"/>
-        <v>13975</v>
-      </c>
-      <c r="AT18" s="8">
+        <v>141336.57128343088</v>
+      </c>
+      <c r="BC18" s="8">
         <f t="shared" si="107"/>
-        <v>24178</v>
-      </c>
-      <c r="AU18" s="8">
+        <v>147607.47897977129</v>
+      </c>
+      <c r="BD18" s="8">
         <f t="shared" si="107"/>
-        <v>38151</v>
-      </c>
-      <c r="AV18" s="8">
-        <f t="shared" ref="AV18:BE18" si="108">AV14-AV15-AV16-AV17</f>
-        <v>-5936</v>
-      </c>
-      <c r="AW18" s="8">
-        <f t="shared" si="108"/>
-        <v>37557</v>
-      </c>
-      <c r="AX18" s="8">
-        <f t="shared" ref="AX18" si="109">AX14-AX15-AX16-AX17</f>
-        <v>68614</v>
-      </c>
-      <c r="AY18" s="8">
-        <f t="shared" si="108"/>
-        <v>85828.780449999977</v>
-      </c>
-      <c r="AZ18" s="8">
-        <f t="shared" si="108"/>
-        <v>106447.88861500005</v>
-      </c>
-      <c r="BA18" s="8">
-        <f t="shared" si="108"/>
-        <v>117081.19902660006</v>
-      </c>
-      <c r="BB18" s="8">
-        <f t="shared" si="108"/>
-        <v>125972.79592298801</v>
-      </c>
-      <c r="BC18" s="8">
-        <f t="shared" si="108"/>
-        <v>131563.63141126174</v>
-      </c>
-      <c r="BD18" s="8">
-        <f t="shared" si="108"/>
-        <v>135997.99022932461</v>
+        <v>152545.97963077851</v>
       </c>
       <c r="BE18" s="8">
-        <f t="shared" si="108"/>
-        <v>139013.19762577885</v>
+        <f t="shared" si="107"/>
+        <v>155871.3415613843</v>
       </c>
       <c r="BF18" s="8">
-        <f t="shared" ref="BF18:BI18" si="110">BF14-BF15-BF16-BF17</f>
-        <v>142242.05623098591</v>
+        <f t="shared" ref="BF18:BI18" si="109">BF14-BF15-BF16-BF17</f>
+        <v>159472.0362719245</v>
       </c>
       <c r="BG18" s="8">
-        <f t="shared" si="110"/>
-        <v>143921.32611963997</v>
+        <f t="shared" si="109"/>
+        <v>161312.4531392518</v>
       </c>
       <c r="BH18" s="8">
-        <f t="shared" si="110"/>
-        <v>145630.64851889521</v>
+        <f t="shared" si="109"/>
+        <v>163184.02604754307</v>
       </c>
       <c r="BI18" s="8">
-        <f t="shared" si="110"/>
-        <v>147370.99946480533</v>
+        <f t="shared" si="109"/>
+        <v>165087.71816223403</v>
       </c>
     </row>
     <row r="19" spans="2:153" x14ac:dyDescent="0.3">
@@ -5147,16 +5135,15 @@
         <v>4553</v>
       </c>
       <c r="AJ19" s="4">
-        <f t="shared" ref="AJ19:AL19" si="111">AJ18*0.14</f>
-        <v>2391.1060249999991</v>
+        <v>2678</v>
       </c>
       <c r="AK19" s="4">
-        <f t="shared" si="111"/>
-        <v>2874.8616400000001</v>
+        <f t="shared" ref="AK19:AL19" si="110">AK18*0.14</f>
+        <v>2543.1650650000006</v>
       </c>
       <c r="AL19" s="4">
-        <f t="shared" si="111"/>
-        <v>3715.0015980000007</v>
+        <f t="shared" si="110"/>
+        <v>3654.7378700000013</v>
       </c>
       <c r="AN19" s="4">
         <v>167</v>
@@ -5201,47 +5188,47 @@
       </c>
       <c r="AY19" s="4">
         <f>SUM(AI19:AL19)</f>
-        <v>13533.969263000001</v>
+        <v>13428.902935000002</v>
       </c>
       <c r="AZ19" s="4">
         <f>AZ18*0.15</f>
-        <v>15967.183292250007</v>
+        <v>15978.144868500007</v>
       </c>
       <c r="BA19" s="4">
-        <f t="shared" ref="BA19:BI19" si="112">BA18*0.15</f>
-        <v>17562.179853990008</v>
+        <f t="shared" ref="BA19:BI19" si="111">BA18*0.15</f>
+        <v>18669.632418726</v>
       </c>
       <c r="BB19" s="4">
-        <f t="shared" si="112"/>
-        <v>18895.919388448201</v>
+        <f t="shared" si="111"/>
+        <v>21200.485692514631</v>
       </c>
       <c r="BC19" s="4">
-        <f t="shared" si="112"/>
-        <v>19734.544711689261</v>
+        <f t="shared" si="111"/>
+        <v>22141.121846965692</v>
       </c>
       <c r="BD19" s="4">
-        <f t="shared" si="112"/>
-        <v>20399.698534398693</v>
+        <f t="shared" si="111"/>
+        <v>22881.896944616776</v>
       </c>
       <c r="BE19" s="4">
-        <f t="shared" si="112"/>
-        <v>20851.979643866827</v>
+        <f t="shared" si="111"/>
+        <v>23380.701234207645</v>
       </c>
       <c r="BF19" s="4">
-        <f t="shared" si="112"/>
-        <v>21336.308434647886</v>
+        <f t="shared" si="111"/>
+        <v>23920.805440788674</v>
       </c>
       <c r="BG19" s="4">
-        <f t="shared" si="112"/>
-        <v>21588.198917945996</v>
+        <f t="shared" si="111"/>
+        <v>24196.867970887768</v>
       </c>
       <c r="BH19" s="4">
-        <f t="shared" si="112"/>
-        <v>21844.59727783428</v>
+        <f t="shared" si="111"/>
+        <v>24477.603907131459</v>
       </c>
       <c r="BI19" s="4">
-        <f t="shared" si="112"/>
-        <v>22105.6499197208</v>
+        <f t="shared" si="111"/>
+        <v>24763.157724335102</v>
       </c>
     </row>
     <row r="20" spans="2:153" x14ac:dyDescent="0.3">
@@ -5348,16 +5335,15 @@
         <v>-1</v>
       </c>
       <c r="AJ20" s="4">
-        <f t="shared" ref="AJ20:AL20" si="113">AJ18*0.001</f>
-        <v>17.079328749999995</v>
+        <v>15</v>
       </c>
       <c r="AK20" s="4">
-        <f t="shared" si="113"/>
-        <v>20.534725999999999</v>
+        <f t="shared" ref="AK20:AL20" si="112">AK18*0.001</f>
+        <v>18.165464750000002</v>
       </c>
       <c r="AL20" s="4">
-        <f t="shared" si="113"/>
-        <v>26.535725700000004</v>
+        <f t="shared" si="112"/>
+        <v>26.105270500000007</v>
       </c>
       <c r="AN20" s="4">
         <v>-37</v>
@@ -5402,47 +5388,47 @@
       </c>
       <c r="AY20" s="4">
         <f>SUM(AI20:AL20)</f>
-        <v>63.149780449999994</v>
+        <v>58.270735250000001</v>
       </c>
       <c r="AZ20" s="4">
-        <f t="shared" ref="AZ20:BI20" si="114">AZ18*0.001</f>
-        <v>106.44788861500005</v>
+        <f t="shared" ref="AZ20:BI20" si="113">AZ18*0.001</f>
+        <v>106.52096579000005</v>
       </c>
       <c r="BA20" s="4">
-        <f t="shared" si="114"/>
-        <v>117.08119902660006</v>
+        <f t="shared" si="113"/>
+        <v>124.46421612483999</v>
       </c>
       <c r="BB20" s="4">
-        <f t="shared" si="114"/>
-        <v>125.97279592298801</v>
+        <f t="shared" si="113"/>
+        <v>141.33657128343089</v>
       </c>
       <c r="BC20" s="4">
-        <f t="shared" si="114"/>
-        <v>131.56363141126175</v>
+        <f t="shared" si="113"/>
+        <v>147.60747897977129</v>
       </c>
       <c r="BD20" s="4">
-        <f t="shared" si="114"/>
-        <v>135.99799022932461</v>
+        <f t="shared" si="113"/>
+        <v>152.5459796307785</v>
       </c>
       <c r="BE20" s="4">
-        <f t="shared" si="114"/>
-        <v>139.01319762577884</v>
+        <f t="shared" si="113"/>
+        <v>155.8713415613843</v>
       </c>
       <c r="BF20" s="4">
-        <f t="shared" si="114"/>
-        <v>142.24205623098592</v>
+        <f t="shared" si="113"/>
+        <v>159.47203627192451</v>
       </c>
       <c r="BG20" s="4">
-        <f t="shared" si="114"/>
-        <v>143.92132611963999</v>
+        <f t="shared" si="113"/>
+        <v>161.3124531392518</v>
       </c>
       <c r="BH20" s="4">
-        <f t="shared" si="114"/>
-        <v>145.63064851889521</v>
+        <f t="shared" si="113"/>
+        <v>163.18402604754309</v>
       </c>
       <c r="BI20" s="4">
-        <f t="shared" si="114"/>
-        <v>147.37099946480532</v>
+        <f t="shared" si="113"/>
+        <v>165.08771816223404</v>
       </c>
     </row>
     <row r="21" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5450,604 +5436,604 @@
         <v>49</v>
       </c>
       <c r="C21" s="8">
-        <f t="shared" ref="C21:R21" si="115">C18-C19-C20</f>
+        <f t="shared" ref="C21:R21" si="114">C18-C19-C20</f>
         <v>724</v>
       </c>
       <c r="D21" s="8">
+        <f t="shared" si="114"/>
+        <v>197</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="114"/>
+        <v>256</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="114"/>
+        <v>1856</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="114"/>
+        <v>1629</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="114"/>
+        <v>2534</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="114"/>
+        <v>2883</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="114"/>
+        <v>3027</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="114"/>
+        <v>3561</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="114"/>
+        <v>2625</v>
+      </c>
+      <c r="M21" s="8">
+        <f t="shared" si="114"/>
+        <v>2134</v>
+      </c>
+      <c r="N21" s="8">
+        <f t="shared" si="114"/>
+        <v>3268</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" si="114"/>
+        <v>2535</v>
+      </c>
+      <c r="P21" s="8">
+        <f t="shared" si="114"/>
+        <v>5243</v>
+      </c>
+      <c r="Q21" s="8">
+        <f t="shared" si="114"/>
+        <v>6331</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" si="114"/>
+        <v>7222</v>
+      </c>
+      <c r="S21" s="8">
+        <f t="shared" ref="S21:V21" si="115">S18-S19-S20</f>
+        <v>8107</v>
+      </c>
+      <c r="T21" s="8">
+        <f t="shared" ref="T21:U21" si="116">T18-T19-T20</f>
+        <v>7778</v>
+      </c>
+      <c r="U21" s="8">
+        <f t="shared" si="116"/>
+        <v>3156</v>
+      </c>
+      <c r="V21" s="8">
         <f t="shared" si="115"/>
-        <v>197</v>
-      </c>
-      <c r="E21" s="8">
-        <f t="shared" si="115"/>
-        <v>256</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="115"/>
-        <v>1856</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="115"/>
-        <v>1629</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="115"/>
-        <v>2534</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" si="115"/>
-        <v>2883</v>
-      </c>
-      <c r="J21" s="8">
-        <f t="shared" si="115"/>
-        <v>3027</v>
-      </c>
-      <c r="K21" s="8">
-        <f t="shared" si="115"/>
-        <v>3561</v>
-      </c>
-      <c r="L21" s="8">
-        <f t="shared" si="115"/>
-        <v>2625</v>
-      </c>
-      <c r="M21" s="8">
-        <f t="shared" si="115"/>
-        <v>2134</v>
-      </c>
-      <c r="N21" s="8">
-        <f t="shared" si="115"/>
-        <v>3268</v>
-      </c>
-      <c r="O21" s="8">
-        <f t="shared" si="115"/>
-        <v>2535</v>
-      </c>
-      <c r="P21" s="8">
-        <f t="shared" si="115"/>
-        <v>5243</v>
-      </c>
-      <c r="Q21" s="8">
-        <f t="shared" si="115"/>
-        <v>6331</v>
-      </c>
-      <c r="R21" s="8">
-        <f t="shared" si="115"/>
-        <v>7222</v>
-      </c>
-      <c r="S21" s="8">
-        <f t="shared" ref="S21:V21" si="116">S18-S19-S20</f>
-        <v>8107</v>
-      </c>
-      <c r="T21" s="8">
-        <f t="shared" ref="T21:U21" si="117">T18-T19-T20</f>
-        <v>7778</v>
-      </c>
-      <c r="U21" s="8">
+        <v>14323</v>
+      </c>
+      <c r="W21" s="8">
+        <f t="shared" ref="W21:X21" si="117">W18-W19-W20</f>
+        <v>-3844</v>
+      </c>
+      <c r="X21" s="8">
         <f t="shared" si="117"/>
-        <v>3156</v>
-      </c>
-      <c r="V21" s="8">
-        <f t="shared" si="116"/>
-        <v>14323</v>
-      </c>
-      <c r="W21" s="8">
-        <f t="shared" ref="W21:X21" si="118">W18-W19-W20</f>
-        <v>-3844</v>
-      </c>
-      <c r="X21" s="8">
-        <f t="shared" si="118"/>
         <v>-2028</v>
       </c>
       <c r="Y21" s="8">
-        <f t="shared" ref="Y21" si="119">Y18-Y19-Y20</f>
+        <f t="shared" ref="Y21" si="118">Y18-Y19-Y20</f>
         <v>2872</v>
       </c>
       <c r="Z21" s="8">
-        <f t="shared" ref="Z21" si="120">Z18-Z19-Z20</f>
+        <f t="shared" ref="Z21" si="119">Z18-Z19-Z20</f>
         <v>278</v>
       </c>
       <c r="AA21" s="8">
-        <f t="shared" ref="AA21:AB21" si="121">AA18-AA19-AA20</f>
+        <f t="shared" ref="AA21:AB21" si="120">AA18-AA19-AA20</f>
         <v>3172</v>
       </c>
       <c r="AB21" s="8">
-        <f t="shared" si="121"/>
+        <f t="shared" si="120"/>
         <v>6750</v>
       </c>
       <c r="AC21" s="8">
-        <f t="shared" ref="AC21" si="122">AC18-AC19-AC20</f>
+        <f t="shared" ref="AC21" si="121">AC18-AC19-AC20</f>
         <v>9879</v>
       </c>
       <c r="AD21" s="8">
-        <f t="shared" ref="AD21" si="123">AD18-AD19-AD20</f>
+        <f t="shared" ref="AD21" si="122">AD18-AD19-AD20</f>
         <v>10624</v>
       </c>
       <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AF21" si="124">AE18-AE19-AE20</f>
+        <f t="shared" ref="AE21:AF21" si="123">AE18-AE19-AE20</f>
         <v>10431</v>
       </c>
       <c r="AF21" s="8">
+        <f t="shared" si="123"/>
+        <v>13485</v>
+      </c>
+      <c r="AG21" s="8">
+        <f t="shared" ref="AG21:AH21" si="124">AG18-AG19-AG20</f>
+        <v>15328</v>
+      </c>
+      <c r="AH21" s="8">
         <f t="shared" si="124"/>
-        <v>13485</v>
-      </c>
-      <c r="AG21" s="8">
-        <f t="shared" ref="AG21:AH21" si="125">AG18-AG19-AG20</f>
-        <v>15328</v>
-      </c>
-      <c r="AH21" s="8">
+        <v>20004</v>
+      </c>
+      <c r="AI21" s="8">
+        <f t="shared" ref="AI21:AL21" si="125">AI18-AI19-AI20</f>
+        <v>17127</v>
+      </c>
+      <c r="AJ21" s="8">
         <f t="shared" si="125"/>
-        <v>20004</v>
-      </c>
-      <c r="AI21" s="8">
-        <f t="shared" ref="AI21:AL21" si="126">AI18-AI19-AI20</f>
-        <v>17127</v>
-      </c>
-      <c r="AJ21" s="8">
+        <v>18164</v>
+      </c>
+      <c r="AK21" s="8">
+        <f t="shared" si="125"/>
+        <v>15604.134220250002</v>
+      </c>
+      <c r="AL21" s="8">
+        <f t="shared" si="125"/>
+        <v>22424.427359500005</v>
+      </c>
+      <c r="AN21" s="8">
+        <f t="shared" ref="AN21:AV21" si="126">AN18-AN19-AN20</f>
+        <v>-241</v>
+      </c>
+      <c r="AO21" s="8">
         <f t="shared" si="126"/>
-        <v>14671.143396249994</v>
-      </c>
-      <c r="AK21" s="8">
+        <v>596</v>
+      </c>
+      <c r="AP21" s="8">
         <f t="shared" si="126"/>
-        <v>17639.329633999998</v>
-      </c>
-      <c r="AL21" s="8">
+        <v>2371</v>
+      </c>
+      <c r="AQ21" s="8">
         <f t="shared" si="126"/>
-        <v>22794.188376300001</v>
-      </c>
-      <c r="AN21" s="8">
-        <f t="shared" ref="AN21:AV21" si="127">AN18-AN19-AN20</f>
-        <v>-241</v>
-      </c>
-      <c r="AO21" s="8">
+        <v>3033</v>
+      </c>
+      <c r="AR21" s="8">
+        <f t="shared" si="126"/>
+        <v>10073</v>
+      </c>
+      <c r="AS21" s="8">
+        <f t="shared" si="126"/>
+        <v>11588</v>
+      </c>
+      <c r="AT21" s="8">
+        <f t="shared" si="126"/>
+        <v>21331</v>
+      </c>
+      <c r="AU21" s="8">
+        <f t="shared" si="126"/>
+        <v>33364</v>
+      </c>
+      <c r="AV21" s="8">
+        <f t="shared" si="126"/>
+        <v>-2722</v>
+      </c>
+      <c r="AW21" s="8">
+        <f t="shared" ref="AW21:BE21" si="127">AW18-AW19-AW20</f>
+        <v>30425</v>
+      </c>
+      <c r="AX21" s="8">
+        <f t="shared" ref="AX21" si="128">AX18-AX19-AX20</f>
+        <v>59248</v>
+      </c>
+      <c r="AY21" s="8">
         <f t="shared" si="127"/>
-        <v>596</v>
-      </c>
-      <c r="AP21" s="8">
+        <v>73319.561579749905</v>
+      </c>
+      <c r="AZ21" s="8">
         <f t="shared" si="127"/>
-        <v>2371</v>
-      </c>
-      <c r="AQ21" s="8">
+        <v>90436.299955710041</v>
+      </c>
+      <c r="BA21" s="8">
         <f t="shared" si="127"/>
-        <v>3033</v>
-      </c>
-      <c r="AR21" s="8">
+        <v>105670.11948998916</v>
+      </c>
+      <c r="BB21" s="8">
         <f t="shared" si="127"/>
-        <v>10073</v>
-      </c>
-      <c r="AS21" s="8">
+        <v>119994.74901963281</v>
+      </c>
+      <c r="BC21" s="8">
         <f t="shared" si="127"/>
-        <v>11588</v>
-      </c>
-      <c r="AT21" s="8">
+        <v>125318.74965382583</v>
+      </c>
+      <c r="BD21" s="8">
         <f t="shared" si="127"/>
-        <v>21331</v>
-      </c>
-      <c r="AU21" s="8">
+        <v>129511.53670653095</v>
+      </c>
+      <c r="BE21" s="8">
         <f t="shared" si="127"/>
-        <v>33364</v>
-      </c>
-      <c r="AV21" s="8">
-        <f t="shared" si="127"/>
-        <v>-2722</v>
-      </c>
-      <c r="AW21" s="8">
-        <f t="shared" ref="AW21:BE21" si="128">AW18-AW19-AW20</f>
-        <v>30425</v>
-      </c>
-      <c r="AX21" s="8">
-        <f t="shared" ref="AX21" si="129">AX18-AX19-AX20</f>
-        <v>59248</v>
-      </c>
-      <c r="AY21" s="8">
-        <f t="shared" si="128"/>
-        <v>72231.661406549974</v>
-      </c>
-      <c r="AZ21" s="8">
-        <f t="shared" si="128"/>
-        <v>90374.257434135041</v>
-      </c>
-      <c r="BA21" s="8">
-        <f t="shared" si="128"/>
-        <v>99401.937973583466</v>
-      </c>
-      <c r="BB21" s="8">
-        <f t="shared" si="128"/>
-        <v>106950.90373861681</v>
-      </c>
-      <c r="BC21" s="8">
-        <f t="shared" si="128"/>
-        <v>111697.52306816122</v>
-      </c>
-      <c r="BD21" s="8">
-        <f t="shared" si="128"/>
-        <v>115462.2937046966</v>
-      </c>
-      <c r="BE21" s="8">
-        <f t="shared" si="128"/>
-        <v>118022.20478428624</v>
+        <v>132334.76898561529</v>
       </c>
       <c r="BF21" s="8">
-        <f t="shared" ref="BF21:BI21" si="130">BF18-BF19-BF20</f>
-        <v>120763.50574010704</v>
+        <f t="shared" ref="BF21:BI21" si="129">BF18-BF19-BF20</f>
+        <v>135391.75879486388</v>
       </c>
       <c r="BG21" s="8">
-        <f t="shared" si="130"/>
-        <v>122189.20587557433</v>
+        <f t="shared" si="129"/>
+        <v>136954.27271522477</v>
       </c>
       <c r="BH21" s="8">
-        <f t="shared" si="130"/>
-        <v>123640.42059254202</v>
+        <f t="shared" si="129"/>
+        <v>138543.2381143641</v>
       </c>
       <c r="BI21" s="8">
-        <f t="shared" si="130"/>
-        <v>125117.97854561971</v>
+        <f t="shared" si="129"/>
+        <v>140159.47271973672</v>
       </c>
       <c r="BJ21" s="1">
         <f>BI21*(1+$BL$29)</f>
-        <v>123866.79876016351</v>
+        <v>138757.87799253935</v>
       </c>
       <c r="BK21" s="1">
-        <f t="shared" ref="BK21:DV21" si="131">BJ21*(1+$BL$29)</f>
-        <v>122628.13077256187</v>
+        <f t="shared" ref="BK21:DV21" si="130">BJ21*(1+$BL$29)</f>
+        <v>137370.29921261396</v>
       </c>
       <c r="BL21" s="1">
+        <f t="shared" si="130"/>
+        <v>135996.59622048782</v>
+      </c>
+      <c r="BM21" s="1">
+        <f t="shared" si="130"/>
+        <v>134636.63025828294</v>
+      </c>
+      <c r="BN21" s="1">
+        <f t="shared" si="130"/>
+        <v>133290.26395570009</v>
+      </c>
+      <c r="BO21" s="1">
+        <f t="shared" si="130"/>
+        <v>131957.3613161431</v>
+      </c>
+      <c r="BP21" s="1">
+        <f t="shared" si="130"/>
+        <v>130637.78770298166</v>
+      </c>
+      <c r="BQ21" s="1">
+        <f t="shared" si="130"/>
+        <v>129331.40982595184</v>
+      </c>
+      <c r="BR21" s="1">
+        <f t="shared" si="130"/>
+        <v>128038.09572769231</v>
+      </c>
+      <c r="BS21" s="1">
+        <f t="shared" si="130"/>
+        <v>126757.71477041539</v>
+      </c>
+      <c r="BT21" s="1">
+        <f t="shared" si="130"/>
+        <v>125490.13762271123</v>
+      </c>
+      <c r="BU21" s="1">
+        <f t="shared" si="130"/>
+        <v>124235.23624648411</v>
+      </c>
+      <c r="BV21" s="1">
+        <f t="shared" si="130"/>
+        <v>122992.88388401928</v>
+      </c>
+      <c r="BW21" s="1">
+        <f t="shared" si="130"/>
+        <v>121762.95504517909</v>
+      </c>
+      <c r="BX21" s="1">
+        <f t="shared" si="130"/>
+        <v>120545.32549472729</v>
+      </c>
+      <c r="BY21" s="1">
+        <f t="shared" si="130"/>
+        <v>119339.87223978002</v>
+      </c>
+      <c r="BZ21" s="1">
+        <f t="shared" si="130"/>
+        <v>118146.47351738221</v>
+      </c>
+      <c r="CA21" s="1">
+        <f t="shared" si="130"/>
+        <v>116965.00878220839</v>
+      </c>
+      <c r="CB21" s="1">
+        <f t="shared" si="130"/>
+        <v>115795.3586943863</v>
+      </c>
+      <c r="CC21" s="1">
+        <f t="shared" si="130"/>
+        <v>114637.40510744244</v>
+      </c>
+      <c r="CD21" s="1">
+        <f t="shared" si="130"/>
+        <v>113491.03105636801</v>
+      </c>
+      <c r="CE21" s="1">
+        <f t="shared" si="130"/>
+        <v>112356.12074580434</v>
+      </c>
+      <c r="CF21" s="1">
+        <f t="shared" si="130"/>
+        <v>111232.55953834629</v>
+      </c>
+      <c r="CG21" s="1">
+        <f t="shared" si="130"/>
+        <v>110120.23394296283</v>
+      </c>
+      <c r="CH21" s="1">
+        <f t="shared" si="130"/>
+        <v>109019.03160353321</v>
+      </c>
+      <c r="CI21" s="1">
+        <f t="shared" si="130"/>
+        <v>107928.84128749787</v>
+      </c>
+      <c r="CJ21" s="1">
+        <f t="shared" si="130"/>
+        <v>106849.55287462288</v>
+      </c>
+      <c r="CK21" s="1">
+        <f t="shared" si="130"/>
+        <v>105781.05734587664</v>
+      </c>
+      <c r="CL21" s="1">
+        <f t="shared" si="130"/>
+        <v>104723.24677241787</v>
+      </c>
+      <c r="CM21" s="1">
+        <f t="shared" si="130"/>
+        <v>103676.01430469369</v>
+      </c>
+      <c r="CN21" s="1">
+        <f t="shared" si="130"/>
+        <v>102639.25416164675</v>
+      </c>
+      <c r="CO21" s="1">
+        <f t="shared" si="130"/>
+        <v>101612.86162003028</v>
+      </c>
+      <c r="CP21" s="1">
+        <f t="shared" si="130"/>
+        <v>100596.73300382997</v>
+      </c>
+      <c r="CQ21" s="1">
+        <f t="shared" si="130"/>
+        <v>99590.76567379167</v>
+      </c>
+      <c r="CR21" s="1">
+        <f t="shared" si="130"/>
+        <v>98594.858017053746</v>
+      </c>
+      <c r="CS21" s="1">
+        <f t="shared" si="130"/>
+        <v>97608.909436883201</v>
+      </c>
+      <c r="CT21" s="1">
+        <f t="shared" si="130"/>
+        <v>96632.820342514373</v>
+      </c>
+      <c r="CU21" s="1">
+        <f t="shared" si="130"/>
+        <v>95666.492139089227</v>
+      </c>
+      <c r="CV21" s="1">
+        <f t="shared" si="130"/>
+        <v>94709.82721769833</v>
+      </c>
+      <c r="CW21" s="1">
+        <f t="shared" si="130"/>
+        <v>93762.728945521347</v>
+      </c>
+      <c r="CX21" s="1">
+        <f t="shared" si="130"/>
+        <v>92825.101656066137</v>
+      </c>
+      <c r="CY21" s="1">
+        <f t="shared" si="130"/>
+        <v>91896.850639505472</v>
+      </c>
+      <c r="CZ21" s="1">
+        <f t="shared" si="130"/>
+        <v>90977.882133110412</v>
+      </c>
+      <c r="DA21" s="1">
+        <f t="shared" si="130"/>
+        <v>90068.103311779312</v>
+      </c>
+      <c r="DB21" s="1">
+        <f t="shared" si="130"/>
+        <v>89167.422278661514</v>
+      </c>
+      <c r="DC21" s="1">
+        <f t="shared" si="130"/>
+        <v>88275.748055874894</v>
+      </c>
+      <c r="DD21" s="1">
+        <f t="shared" si="130"/>
+        <v>87392.990575316144</v>
+      </c>
+      <c r="DE21" s="1">
+        <f t="shared" si="130"/>
+        <v>86519.060669562983</v>
+      </c>
+      <c r="DF21" s="1">
+        <f t="shared" si="130"/>
+        <v>85653.870062867354</v>
+      </c>
+      <c r="DG21" s="1">
+        <f t="shared" si="130"/>
+        <v>84797.331362238678</v>
+      </c>
+      <c r="DH21" s="1">
+        <f t="shared" si="130"/>
+        <v>83949.358048616297</v>
+      </c>
+      <c r="DI21" s="1">
+        <f t="shared" si="130"/>
+        <v>83109.864468130138</v>
+      </c>
+      <c r="DJ21" s="1">
+        <f t="shared" si="130"/>
+        <v>82278.765823448834</v>
+      </c>
+      <c r="DK21" s="1">
+        <f t="shared" si="130"/>
+        <v>81455.978165214343</v>
+      </c>
+      <c r="DL21" s="1">
+        <f t="shared" si="130"/>
+        <v>80641.418383562195</v>
+      </c>
+      <c r="DM21" s="1">
+        <f t="shared" si="130"/>
+        <v>79835.00419972658</v>
+      </c>
+      <c r="DN21" s="1">
+        <f t="shared" si="130"/>
+        <v>79036.65415772931</v>
+      </c>
+      <c r="DO21" s="1">
+        <f t="shared" si="130"/>
+        <v>78246.287616152011</v>
+      </c>
+      <c r="DP21" s="1">
+        <f t="shared" si="130"/>
+        <v>77463.824739990494</v>
+      </c>
+      <c r="DQ21" s="1">
+        <f t="shared" si="130"/>
+        <v>76689.186492590583</v>
+      </c>
+      <c r="DR21" s="1">
+        <f t="shared" si="130"/>
+        <v>75922.294627664684</v>
+      </c>
+      <c r="DS21" s="1">
+        <f t="shared" si="130"/>
+        <v>75163.071681388043</v>
+      </c>
+      <c r="DT21" s="1">
+        <f t="shared" si="130"/>
+        <v>74411.440964574154</v>
+      </c>
+      <c r="DU21" s="1">
+        <f t="shared" si="130"/>
+        <v>73667.326554928411</v>
+      </c>
+      <c r="DV21" s="1">
+        <f t="shared" si="130"/>
+        <v>72930.65328937913</v>
+      </c>
+      <c r="DW21" s="1">
+        <f t="shared" ref="DW21:EW21" si="131">DV21*(1+$BL$29)</f>
+        <v>72201.346756485334</v>
+      </c>
+      <c r="DX21" s="1">
         <f t="shared" si="131"/>
-        <v>121401.84946483625</v>
-      </c>
-      <c r="BM21" s="1">
+        <v>71479.333288920476</v>
+      </c>
+      <c r="DY21" s="1">
         <f t="shared" si="131"/>
-        <v>120187.83097018789</v>
-      </c>
-      <c r="BN21" s="1">
+        <v>70764.539956031265</v>
+      </c>
+      <c r="DZ21" s="1">
         <f t="shared" si="131"/>
-        <v>118985.95266048601</v>
-      </c>
-      <c r="BO21" s="1">
+        <v>70056.894556470957</v>
+      </c>
+      <c r="EA21" s="1">
         <f t="shared" si="131"/>
-        <v>117796.09313388115</v>
-      </c>
-      <c r="BP21" s="1">
+        <v>69356.325610906249</v>
+      </c>
+      <c r="EB21" s="1">
         <f t="shared" si="131"/>
-        <v>116618.13220254234</v>
-      </c>
-      <c r="BQ21" s="1">
+        <v>68662.762354797189</v>
+      </c>
+      <c r="EC21" s="1">
         <f t="shared" si="131"/>
-        <v>115451.95088051692</v>
-      </c>
-      <c r="BR21" s="1">
+        <v>67976.134731249214</v>
+      </c>
+      <c r="ED21" s="1">
         <f t="shared" si="131"/>
-        <v>114297.43137171175</v>
-      </c>
-      <c r="BS21" s="1">
+        <v>67296.37338393672</v>
+      </c>
+      <c r="EE21" s="1">
         <f t="shared" si="131"/>
-        <v>113154.45705799463</v>
-      </c>
-      <c r="BT21" s="1">
+        <v>66623.409650097354</v>
+      </c>
+      <c r="EF21" s="1">
         <f t="shared" si="131"/>
-        <v>112022.91248741468</v>
-      </c>
-      <c r="BU21" s="1">
+        <v>65957.175553596375</v>
+      </c>
+      <c r="EG21" s="1">
         <f t="shared" si="131"/>
-        <v>110902.68336254053</v>
-      </c>
-      <c r="BV21" s="1">
+        <v>65297.603798060409</v>
+      </c>
+      <c r="EH21" s="1">
         <f t="shared" si="131"/>
-        <v>109793.65652891512</v>
-      </c>
-      <c r="BW21" s="1">
+        <v>64644.627760079806</v>
+      </c>
+      <c r="EI21" s="1">
         <f t="shared" si="131"/>
-        <v>108695.71996362596</v>
-      </c>
-      <c r="BX21" s="1">
+        <v>63998.181482479005</v>
+      </c>
+      <c r="EJ21" s="1">
         <f t="shared" si="131"/>
-        <v>107608.7627639897</v>
-      </c>
-      <c r="BY21" s="1">
+        <v>63358.199667654211</v>
+      </c>
+      <c r="EK21" s="1">
         <f t="shared" si="131"/>
-        <v>106532.6751363498</v>
-      </c>
-      <c r="BZ21" s="1">
+        <v>62724.61767097767</v>
+      </c>
+      <c r="EL21" s="1">
         <f t="shared" si="131"/>
-        <v>105467.34838498631</v>
-      </c>
-      <c r="CA21" s="1">
+        <v>62097.371494267893</v>
+      </c>
+      <c r="EM21" s="1">
         <f t="shared" si="131"/>
-        <v>104412.67490113644</v>
-      </c>
-      <c r="CB21" s="1">
+        <v>61476.397779325212</v>
+      </c>
+      <c r="EN21" s="1">
         <f t="shared" si="131"/>
-        <v>103368.54815212508</v>
-      </c>
-      <c r="CC21" s="1">
+        <v>60861.633801531963</v>
+      </c>
+      <c r="EO21" s="1">
         <f t="shared" si="131"/>
-        <v>102334.86267060382</v>
-      </c>
-      <c r="CD21" s="1">
+        <v>60253.01746351664</v>
+      </c>
+      <c r="EP21" s="1">
         <f t="shared" si="131"/>
-        <v>101311.51404389778</v>
-      </c>
-      <c r="CE21" s="1">
+        <v>59650.487288881472</v>
+      </c>
+      <c r="EQ21" s="1">
         <f t="shared" si="131"/>
-        <v>100298.3989034588</v>
-      </c>
-      <c r="CF21" s="1">
+        <v>59053.982415992657</v>
+      </c>
+      <c r="ER21" s="1">
         <f t="shared" si="131"/>
-        <v>99295.414914424211</v>
-      </c>
-      <c r="CG21" s="1">
+        <v>58463.442591832732</v>
+      </c>
+      <c r="ES21" s="1">
         <f t="shared" si="131"/>
-        <v>98302.460765279975</v>
-      </c>
-      <c r="CH21" s="1">
+        <v>57878.808165914408</v>
+      </c>
+      <c r="ET21" s="1">
         <f t="shared" si="131"/>
-        <v>97319.436157627177</v>
-      </c>
-      <c r="CI21" s="1">
+        <v>57300.020084255266</v>
+      </c>
+      <c r="EU21" s="1">
         <f t="shared" si="131"/>
-        <v>96346.241796050905</v>
-      </c>
-      <c r="CJ21" s="1">
+        <v>56727.019883412715</v>
+      </c>
+      <c r="EV21" s="1">
         <f t="shared" si="131"/>
-        <v>95382.779378090388</v>
-      </c>
-      <c r="CK21" s="1">
+        <v>56159.749684578586</v>
+      </c>
+      <c r="EW21" s="1">
         <f t="shared" si="131"/>
-        <v>94428.951584309485</v>
-      </c>
-      <c r="CL21" s="1">
-        <f t="shared" si="131"/>
-        <v>93484.662068466394</v>
-      </c>
-      <c r="CM21" s="1">
-        <f t="shared" si="131"/>
-        <v>92549.81544778173</v>
-      </c>
-      <c r="CN21" s="1">
-        <f t="shared" si="131"/>
-        <v>91624.317293303917</v>
-      </c>
-      <c r="CO21" s="1">
-        <f t="shared" si="131"/>
-        <v>90708.074120370875</v>
-      </c>
-      <c r="CP21" s="1">
-        <f t="shared" si="131"/>
-        <v>89800.993379167165</v>
-      </c>
-      <c r="CQ21" s="1">
-        <f t="shared" si="131"/>
-        <v>88902.983445375488</v>
-      </c>
-      <c r="CR21" s="1">
-        <f t="shared" si="131"/>
-        <v>88013.95361092173</v>
-      </c>
-      <c r="CS21" s="1">
-        <f t="shared" si="131"/>
-        <v>87133.814074812515</v>
-      </c>
-      <c r="CT21" s="1">
-        <f t="shared" si="131"/>
-        <v>86262.475934064394</v>
-      </c>
-      <c r="CU21" s="1">
-        <f t="shared" si="131"/>
-        <v>85399.85117472375</v>
-      </c>
-      <c r="CV21" s="1">
-        <f t="shared" si="131"/>
-        <v>84545.852662976511</v>
-      </c>
-      <c r="CW21" s="1">
-        <f t="shared" si="131"/>
-        <v>83700.394136346746</v>
-      </c>
-      <c r="CX21" s="1">
-        <f t="shared" si="131"/>
-        <v>82863.39019498328</v>
-      </c>
-      <c r="CY21" s="1">
-        <f t="shared" si="131"/>
-        <v>82034.756293033453</v>
-      </c>
-      <c r="CZ21" s="1">
-        <f t="shared" si="131"/>
-        <v>81214.408730103125</v>
-      </c>
-      <c r="DA21" s="1">
-        <f t="shared" si="131"/>
-        <v>80402.264642802096</v>
-      </c>
-      <c r="DB21" s="1">
-        <f t="shared" si="131"/>
-        <v>79598.241996374069</v>
-      </c>
-      <c r="DC21" s="1">
-        <f t="shared" si="131"/>
-        <v>78802.259576410332</v>
-      </c>
-      <c r="DD21" s="1">
-        <f t="shared" si="131"/>
-        <v>78014.236980646223</v>
-      </c>
-      <c r="DE21" s="1">
-        <f t="shared" si="131"/>
-        <v>77234.094610839762</v>
-      </c>
-      <c r="DF21" s="1">
-        <f t="shared" si="131"/>
-        <v>76461.753664731368</v>
-      </c>
-      <c r="DG21" s="1">
-        <f t="shared" si="131"/>
-        <v>75697.13612808405</v>
-      </c>
-      <c r="DH21" s="1">
-        <f t="shared" si="131"/>
-        <v>74940.164766803209</v>
-      </c>
-      <c r="DI21" s="1">
-        <f t="shared" si="131"/>
-        <v>74190.763119135183</v>
-      </c>
-      <c r="DJ21" s="1">
-        <f t="shared" si="131"/>
-        <v>73448.855487943831</v>
-      </c>
-      <c r="DK21" s="1">
-        <f t="shared" si="131"/>
-        <v>72714.36693306439</v>
-      </c>
-      <c r="DL21" s="1">
-        <f t="shared" si="131"/>
-        <v>71987.223263733744</v>
-      </c>
-      <c r="DM21" s="1">
-        <f t="shared" si="131"/>
-        <v>71267.351031096405</v>
-      </c>
-      <c r="DN21" s="1">
-        <f t="shared" si="131"/>
-        <v>70554.677520785437</v>
-      </c>
-      <c r="DO21" s="1">
-        <f t="shared" si="131"/>
-        <v>69849.130745577582</v>
-      </c>
-      <c r="DP21" s="1">
-        <f t="shared" si="131"/>
-        <v>69150.639438121812</v>
-      </c>
-      <c r="DQ21" s="1">
-        <f t="shared" si="131"/>
-        <v>68459.1330437406</v>
-      </c>
-      <c r="DR21" s="1">
-        <f t="shared" si="131"/>
-        <v>67774.541713303188</v>
-      </c>
-      <c r="DS21" s="1">
-        <f t="shared" si="131"/>
-        <v>67096.796296170156</v>
-      </c>
-      <c r="DT21" s="1">
-        <f t="shared" si="131"/>
-        <v>66425.828333208454</v>
-      </c>
-      <c r="DU21" s="1">
-        <f t="shared" si="131"/>
-        <v>65761.570049876362</v>
-      </c>
-      <c r="DV21" s="1">
-        <f t="shared" si="131"/>
-        <v>65103.9543493776</v>
-      </c>
-      <c r="DW21" s="1">
-        <f t="shared" ref="DW21:EW21" si="132">DV21*(1+$BL$29)</f>
-        <v>64452.914805883825</v>
-      </c>
-      <c r="DX21" s="1">
-        <f t="shared" si="132"/>
-        <v>63808.385657824983</v>
-      </c>
-      <c r="DY21" s="1">
-        <f t="shared" si="132"/>
-        <v>63170.301801246736</v>
-      </c>
-      <c r="DZ21" s="1">
-        <f t="shared" si="132"/>
-        <v>62538.598783234265</v>
-      </c>
-      <c r="EA21" s="1">
-        <f t="shared" si="132"/>
-        <v>61913.212795401923</v>
-      </c>
-      <c r="EB21" s="1">
-        <f t="shared" si="132"/>
-        <v>61294.080667447903</v>
-      </c>
-      <c r="EC21" s="1">
-        <f t="shared" si="132"/>
-        <v>60681.139860773423</v>
-      </c>
-      <c r="ED21" s="1">
-        <f t="shared" si="132"/>
-        <v>60074.328462165686</v>
-      </c>
-      <c r="EE21" s="1">
-        <f t="shared" si="132"/>
-        <v>59473.585177544031</v>
-      </c>
-      <c r="EF21" s="1">
-        <f t="shared" si="132"/>
-        <v>58878.849325768591</v>
-      </c>
-      <c r="EG21" s="1">
-        <f t="shared" si="132"/>
-        <v>58290.060832510906</v>
-      </c>
-      <c r="EH21" s="1">
-        <f t="shared" si="132"/>
-        <v>57707.160224185798</v>
-      </c>
-      <c r="EI21" s="1">
-        <f t="shared" si="132"/>
-        <v>57130.088621943942</v>
-      </c>
-      <c r="EJ21" s="1">
-        <f t="shared" si="132"/>
-        <v>56558.787735724502</v>
-      </c>
-      <c r="EK21" s="1">
-        <f t="shared" si="132"/>
-        <v>55993.199858367254</v>
-      </c>
-      <c r="EL21" s="1">
-        <f t="shared" si="132"/>
-        <v>55433.267859783584</v>
-      </c>
-      <c r="EM21" s="1">
-        <f t="shared" si="132"/>
-        <v>54878.935181185749</v>
-      </c>
-      <c r="EN21" s="1">
-        <f t="shared" si="132"/>
-        <v>54330.145829373891</v>
-      </c>
-      <c r="EO21" s="1">
-        <f t="shared" si="132"/>
-        <v>53786.844371080151</v>
-      </c>
-      <c r="EP21" s="1">
-        <f t="shared" si="132"/>
-        <v>53248.975927369349</v>
-      </c>
-      <c r="EQ21" s="1">
-        <f t="shared" si="132"/>
-        <v>52716.486168095653</v>
-      </c>
-      <c r="ER21" s="1">
-        <f t="shared" si="132"/>
-        <v>52189.321306414698</v>
-      </c>
-      <c r="ES21" s="1">
-        <f t="shared" si="132"/>
-        <v>51667.428093350551</v>
-      </c>
-      <c r="ET21" s="1">
-        <f t="shared" si="132"/>
-        <v>51150.753812417046</v>
-      </c>
-      <c r="EU21" s="1">
-        <f t="shared" si="132"/>
-        <v>50639.246274292876</v>
-      </c>
-      <c r="EV21" s="1">
-        <f t="shared" si="132"/>
-        <v>50132.853811549947</v>
-      </c>
-      <c r="EW21" s="1">
-        <f t="shared" si="132"/>
-        <v>49631.525273434447</v>
+        <v>55598.152187732798</v>
       </c>
     </row>
     <row r="22" spans="2:153" x14ac:dyDescent="0.3">
@@ -6155,16 +6141,13 @@
         <v>10616.4</v>
       </c>
       <c r="AJ22" s="4">
-        <f>10616.4</f>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="AK22" s="4">
-        <f>10616.4</f>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="AL22" s="4">
-        <f>10616.4</f>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="AN22" s="4">
         <v>503.6</v>
@@ -6201,48 +6184,37 @@
         <v>10515</v>
       </c>
       <c r="AY22" s="4">
-        <f t="shared" ref="AY22:BI22" si="133">10616.4</f>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="AZ22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BA22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BB22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BC22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BD22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BE22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BF22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BG22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BH22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
       <c r="BI22" s="4">
-        <f t="shared" si="133"/>
-        <v>10616.4</v>
+        <v>10637</v>
       </c>
     </row>
     <row r="23" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6250,236 +6222,236 @@
         <v>50</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23:R23" si="134">C21/C22</f>
+        <f t="shared" ref="C23:R23" si="132">C21/C22</f>
         <v>1.437648927720413</v>
       </c>
       <c r="D23" s="6">
+        <f t="shared" si="132"/>
+        <v>0.39118347895154881</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="132"/>
+        <v>0.50833995234312945</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="132"/>
+        <v>3.6854646544876886</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="132"/>
+        <v>3.2347100873709294</v>
+      </c>
+      <c r="H23" s="6">
+        <f t="shared" si="132"/>
+        <v>5.0317712470214451</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="132"/>
+        <v>5.7247815726767275</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="132"/>
+        <v>6.0107227958697376</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="132"/>
+        <v>7.071088165210484</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="132"/>
+        <v>5.2124702144559167</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="132"/>
+        <v>4.2374900714853059</v>
+      </c>
+      <c r="N23" s="6">
+        <f t="shared" si="132"/>
+        <v>6.4892772041302615</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" si="132"/>
+        <v>5.0337569499602859</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="132"/>
+        <v>10.411040508339951</v>
+      </c>
+      <c r="Q23" s="6">
+        <f t="shared" si="132"/>
+        <v>12.571485305798252</v>
+      </c>
+      <c r="R23" s="6">
+        <f t="shared" si="132"/>
+        <v>14.340746624305003</v>
+      </c>
+      <c r="S23" s="6">
+        <f t="shared" ref="S23:V23" si="133">S21/S22</f>
+        <v>16.098093725178714</v>
+      </c>
+      <c r="T23" s="6">
+        <f t="shared" ref="T23:U23" si="134">T21/T22</f>
+        <v>15.401980198019801</v>
+      </c>
+      <c r="U23" s="6">
         <f t="shared" si="134"/>
-        <v>0.39118347895154881</v>
-      </c>
-      <c r="E23" s="6">
-        <f t="shared" si="134"/>
-        <v>0.50833995234312945</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="134"/>
-        <v>3.6854646544876886</v>
-      </c>
-      <c r="G23" s="6">
-        <f t="shared" si="134"/>
-        <v>3.2347100873709294</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="134"/>
-        <v>5.0317712470214451</v>
-      </c>
-      <c r="I23" s="6">
-        <f t="shared" si="134"/>
-        <v>5.7247815726767275</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="134"/>
-        <v>6.0107227958697376</v>
-      </c>
-      <c r="K23" s="6">
-        <f t="shared" si="134"/>
-        <v>7.071088165210484</v>
-      </c>
-      <c r="L23" s="6">
-        <f t="shared" si="134"/>
-        <v>5.2124702144559167</v>
-      </c>
-      <c r="M23" s="6">
-        <f t="shared" si="134"/>
-        <v>4.2374900714853059</v>
-      </c>
-      <c r="N23" s="6">
-        <f t="shared" si="134"/>
-        <v>6.4892772041302615</v>
-      </c>
-      <c r="O23" s="6">
-        <f t="shared" si="134"/>
-        <v>5.0337569499602859</v>
-      </c>
-      <c r="P23" s="6">
-        <f t="shared" si="134"/>
-        <v>10.411040508339951</v>
-      </c>
-      <c r="Q23" s="6">
-        <f t="shared" si="134"/>
-        <v>12.571485305798252</v>
-      </c>
-      <c r="R23" s="6">
-        <f t="shared" si="134"/>
-        <v>14.340746624305003</v>
-      </c>
-      <c r="S23" s="6">
-        <f t="shared" ref="S23:V23" si="135">S21/S22</f>
-        <v>16.098093725178714</v>
-      </c>
-      <c r="T23" s="6">
-        <f t="shared" ref="T23:U23" si="136">T21/T22</f>
-        <v>15.401980198019801</v>
-      </c>
-      <c r="U23" s="6">
-        <f t="shared" si="136"/>
         <v>6.21259842519685</v>
       </c>
       <c r="V23" s="6">
+        <f t="shared" si="133"/>
+        <v>28.194881889763778</v>
+      </c>
+      <c r="W23" s="6">
+        <f t="shared" ref="W23:X23" si="135">W21/W22</f>
+        <v>-7.5520628683693518</v>
+      </c>
+      <c r="X23" s="6">
         <f t="shared" si="135"/>
-        <v>28.194881889763778</v>
-      </c>
-      <c r="W23" s="6">
-        <f t="shared" ref="W23:X23" si="137">W21/W22</f>
-        <v>-7.5520628683693518</v>
-      </c>
-      <c r="X23" s="6">
-        <f t="shared" si="137"/>
         <v>-0.19931203931203931</v>
       </c>
       <c r="Y23" s="6">
-        <f t="shared" ref="Y23" si="138">Y21/Y22</f>
+        <f t="shared" ref="Y23" si="136">Y21/Y22</f>
         <v>0.28181728976547932</v>
       </c>
       <c r="Z23" s="6">
-        <f t="shared" ref="Z23" si="139">Z21/Z22</f>
+        <f t="shared" ref="Z23" si="137">Z21/Z22</f>
         <v>2.7201565557729943E-2</v>
       </c>
       <c r="AA23" s="6">
-        <f t="shared" ref="AA23:AB23" si="140">AA21/AA22</f>
+        <f t="shared" ref="AA23:AB23" si="138">AA21/AA22</f>
         <v>0.30946341463414634</v>
       </c>
       <c r="AB23" s="6">
-        <f t="shared" si="140"/>
+        <f t="shared" si="138"/>
         <v>0.65629557608167233</v>
       </c>
       <c r="AC23" s="6">
-        <f t="shared" ref="AC23" si="141">AC21/AC22</f>
+        <f t="shared" ref="AC23" si="139">AC21/AC22</f>
         <v>0.9570819608602984</v>
       </c>
       <c r="AD23" s="6">
-        <f t="shared" ref="AD23" si="142">AD21/AD22</f>
+        <f t="shared" ref="AD23" si="140">AD21/AD22</f>
         <v>1.0258787176516029</v>
       </c>
       <c r="AE23" s="6">
-        <f t="shared" ref="AE23:AF23" si="143">AE21/AE22</f>
+        <f t="shared" ref="AE23:AF23" si="141">AE21/AE22</f>
         <v>1.0036563071297988</v>
       </c>
       <c r="AF23" s="6">
+        <f t="shared" si="141"/>
+        <v>1.2975079380352159</v>
+      </c>
+      <c r="AG23" s="6">
+        <f t="shared" ref="AG23:AH23" si="142">AG21/AG22</f>
+        <v>1.4577270565858298</v>
+      </c>
+      <c r="AH23" s="6">
+        <f t="shared" si="142"/>
+        <v>1.8957543593631538</v>
+      </c>
+      <c r="AI23" s="6">
+        <f t="shared" ref="AI23:AL23" si="143">AI21/AI22</f>
+        <v>1.6132587317734826</v>
+      </c>
+      <c r="AJ23" s="6">
         <f t="shared" si="143"/>
-        <v>1.2975079380352159</v>
-      </c>
-      <c r="AG23" s="6">
-        <f t="shared" ref="AG23:AH23" si="144">AG21/AG22</f>
-        <v>1.4577270565858298</v>
-      </c>
-      <c r="AH23" s="6">
+        <v>1.7076243301682805</v>
+      </c>
+      <c r="AK23" s="6">
+        <f t="shared" si="143"/>
+        <v>1.4669675867490835</v>
+      </c>
+      <c r="AL23" s="6">
+        <f t="shared" si="143"/>
+        <v>2.1081533665037138</v>
+      </c>
+      <c r="AN23" s="6">
+        <f t="shared" ref="AN23:AV23" si="144">AN21/AN22</f>
+        <v>-0.4785544082605242</v>
+      </c>
+      <c r="AO23" s="6">
         <f t="shared" si="144"/>
-        <v>1.8957543593631538</v>
-      </c>
-      <c r="AI23" s="6">
-        <f t="shared" ref="AI23:AL23" si="145">AI21/AI22</f>
-        <v>1.6132587317734826</v>
-      </c>
-      <c r="AJ23" s="6">
+        <v>1.1834789515488482</v>
+      </c>
+      <c r="AP23" s="6">
+        <f t="shared" si="144"/>
+        <v>4.7081016679904684</v>
+      </c>
+      <c r="AQ23" s="6">
+        <f t="shared" si="144"/>
+        <v>6.0226370135027798</v>
+      </c>
+      <c r="AR23" s="6">
+        <f t="shared" si="144"/>
+        <v>20.001985702938839</v>
+      </c>
+      <c r="AS23" s="6">
+        <f t="shared" si="144"/>
+        <v>23.010325655281967</v>
+      </c>
+      <c r="AT23" s="6">
+        <f t="shared" si="144"/>
+        <v>42.35702938840349</v>
+      </c>
+      <c r="AU23" s="6">
+        <f t="shared" si="144"/>
+        <v>66.25099285146942</v>
+      </c>
+      <c r="AV23" s="6">
+        <f t="shared" si="144"/>
+        <v>-0.26634050880626225</v>
+      </c>
+      <c r="AW23" s="6">
+        <f t="shared" ref="AW23:BE23" si="145">AW21/AW22</f>
+        <v>2.9379103901120125</v>
+      </c>
+      <c r="AX23" s="6">
+        <f t="shared" ref="AX23" si="146">AX21/AX22</f>
+        <v>5.6346172135045176</v>
+      </c>
+      <c r="AY23" s="6">
         <f t="shared" si="145"/>
-        <v>1.3819320481754638</v>
-      </c>
-      <c r="AK23" s="6">
+        <v>6.8928797198223091</v>
+      </c>
+      <c r="AZ23" s="6">
         <f t="shared" si="145"/>
-        <v>1.6615170522964469</v>
-      </c>
-      <c r="AL23" s="6">
+        <v>8.5020494458691402</v>
+      </c>
+      <c r="BA23" s="6">
         <f t="shared" si="145"/>
-        <v>2.1470732429354586</v>
-      </c>
-      <c r="AN23" s="6">
-        <f t="shared" ref="AN23:AV23" si="146">AN21/AN22</f>
-        <v>-0.4785544082605242</v>
-      </c>
-      <c r="AO23" s="6">
-        <f t="shared" si="146"/>
-        <v>1.1834789515488482</v>
-      </c>
-      <c r="AP23" s="6">
-        <f t="shared" si="146"/>
-        <v>4.7081016679904684</v>
-      </c>
-      <c r="AQ23" s="6">
-        <f t="shared" si="146"/>
-        <v>6.0226370135027798</v>
-      </c>
-      <c r="AR23" s="6">
-        <f t="shared" si="146"/>
-        <v>20.001985702938839</v>
-      </c>
-      <c r="AS23" s="6">
-        <f t="shared" si="146"/>
-        <v>23.010325655281967</v>
-      </c>
-      <c r="AT23" s="6">
-        <f t="shared" si="146"/>
-        <v>42.35702938840349</v>
-      </c>
-      <c r="AU23" s="6">
-        <f t="shared" si="146"/>
-        <v>66.25099285146942</v>
-      </c>
-      <c r="AV23" s="6">
-        <f t="shared" si="146"/>
-        <v>-0.26634050880626225</v>
-      </c>
-      <c r="AW23" s="6">
-        <f t="shared" ref="AW23:BE23" si="147">AW21/AW22</f>
-        <v>2.9379103901120125</v>
-      </c>
-      <c r="AX23" s="6">
-        <f t="shared" ref="AX23" si="148">AX21/AX22</f>
-        <v>5.6346172135045176</v>
-      </c>
-      <c r="AY23" s="6">
+        <v>9.9342032048499718</v>
+      </c>
+      <c r="BB23" s="6">
+        <f t="shared" si="145"/>
+        <v>11.280882675531899</v>
+      </c>
+      <c r="BC23" s="6">
+        <f t="shared" si="145"/>
+        <v>11.781399798235013</v>
+      </c>
+      <c r="BD23" s="6">
+        <f t="shared" si="145"/>
+        <v>12.175569869938043</v>
+      </c>
+      <c r="BE23" s="6">
+        <f t="shared" si="145"/>
+        <v>12.4409860849502</v>
+      </c>
+      <c r="BF23" s="6">
+        <f t="shared" ref="BF23:BI23" si="147">BF21/BF22</f>
+        <v>12.728378188856246</v>
+      </c>
+      <c r="BG23" s="6">
         <f t="shared" si="147"/>
-        <v>6.8037810751808498</v>
-      </c>
-      <c r="AZ23" s="6">
+        <v>12.875272418466182</v>
+      </c>
+      <c r="BH23" s="6">
         <f t="shared" si="147"/>
-        <v>8.5127027461413523</v>
-      </c>
-      <c r="BA23" s="6">
+        <v>13.024653390463861</v>
+      </c>
+      <c r="BI23" s="6">
         <f t="shared" si="147"/>
-        <v>9.3630550820978371</v>
-      </c>
-      <c r="BB23" s="6">
-        <f t="shared" si="147"/>
-        <v>10.074121523173281</v>
-      </c>
-      <c r="BC23" s="6">
-        <f t="shared" si="147"/>
-        <v>10.521224056004034</v>
-      </c>
-      <c r="BD23" s="6">
-        <f t="shared" si="147"/>
-        <v>10.875842442324762</v>
-      </c>
-      <c r="BE23" s="6">
-        <f t="shared" si="147"/>
-        <v>11.116970421638808</v>
-      </c>
-      <c r="BF23" s="6">
-        <f t="shared" ref="BF23:BI23" si="149">BF21/BF22</f>
-        <v>11.37518421876597</v>
-      </c>
-      <c r="BG23" s="6">
-        <f t="shared" si="149"/>
-        <v>11.509476458646466</v>
-      </c>
-      <c r="BH23" s="6">
-        <f t="shared" si="149"/>
-        <v>11.646172016177049</v>
-      </c>
-      <c r="BI23" s="6">
-        <f t="shared" si="149"/>
-        <v>11.785348945557789</v>
+        <v>13.176597980608886</v>
       </c>
     </row>
     <row r="25" spans="2:153" x14ac:dyDescent="0.3">
@@ -6495,128 +6467,128 @@
         <v>0.33163394286677339</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" ref="H25:V25" si="150">H3/D3-1</f>
+        <f t="shared" ref="H25:V25" si="148">H3/D3-1</f>
         <v>0.28769448373408779</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.17303948832035587</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>8.166969147005454E-2</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>8.4733428255022947E-2</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.12528245041426067</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.17720618739998817</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.13069351230425053</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.22045911968030807</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.40127175368139234</v>
       </c>
       <c r="Q25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.32844988168957356</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.40588025800324479</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.37403503740350375</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>0.15444630204601539</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>3.9830219426232549E-2</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="150"/>
+        <f t="shared" si="148"/>
         <v>5.0664264805224679E-3</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" ref="W25:W27" si="151">W3/S3-1</f>
+        <f t="shared" ref="W25:W27" si="149">W3/S3-1</f>
         <v>-1.8020211859247515E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" ref="X25:X27" si="152">X3/T3-1</f>
+        <f t="shared" ref="X25:X27" si="150">X3/T3-1</f>
         <v>-2.4636231984001111E-2</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" ref="Y25:Y27" si="153">Y3/U3-1</f>
+        <f t="shared" ref="Y25:Y27" si="151">Y3/U3-1</f>
         <v>8.1347036956046281E-2</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" ref="Z25:Z27" si="154">Z3/V3-1</f>
+        <f t="shared" ref="Z25:Z27" si="152">Z3/V3-1</f>
         <v>-1.2392181023860194E-2</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" ref="AA25:AA27" si="155">AA3/W3-1</f>
+        <f t="shared" ref="AA25:AA27" si="153">AA3/W3-1</f>
         <v>9.317155256398868E-3</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" ref="AB25:AB27" si="156">AB3/X3-1</f>
+        <f t="shared" ref="AB25:AB27" si="154">AB3/X3-1</f>
         <v>4.342907644719407E-2</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" ref="AC25:AC27" si="157">AC3/Y3-1</f>
+        <f t="shared" ref="AC25:AC27" si="155">AC3/Y3-1</f>
         <v>6.4560161779575242E-2</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" ref="AD25:AD27" si="158">AD3/Z3-1</f>
+        <f t="shared" ref="AD25:AD27" si="156">AD3/Z3-1</f>
         <v>8.7507620762501626E-2</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AE27" si="159">AE3/AA3-1</f>
+        <f t="shared" ref="AE25:AE27" si="157">AE3/AA3-1</f>
         <v>6.9040557378775347E-2</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" ref="AF25:AF27" si="160">AF3/AB3-1</f>
+        <f t="shared" ref="AF25:AF27" si="158">AF3/AB3-1</f>
         <v>4.2976690608483636E-2</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" ref="AG25:AG27" si="161">AG3/AC3-1</f>
+        <f t="shared" ref="AG25:AG27" si="159">AG3/AC3-1</f>
         <v>7.0127115290243847E-2</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" ref="AH25:AH27" si="162">AH3/AD3-1</f>
+        <f t="shared" ref="AH25:AH27" si="160">AH3/AD3-1</f>
         <v>7.200500632309037E-2</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" ref="AI25:AI27" si="163">AI3/AE3-1</f>
+        <f t="shared" ref="AI25:AI27" si="161">AI3/AE3-1</f>
         <v>5.0151850939834208E-2</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" ref="AJ25:AJ27" si="164">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ25:AJ27" si="162">AJ3/AF3-1</f>
+        <v>0.10844743296139292</v>
+      </c>
+      <c r="AK25" s="10">
+        <f t="shared" ref="AK25:AK27" si="163">AK3/AG3-1</f>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="AK25" s="10">
-        <f t="shared" ref="AK25:AK27" si="165">AK3/AG3-1</f>
+      <c r="AL25" s="10">
+        <f t="shared" ref="AL25:AL27" si="164">AL3/AH3-1</f>
         <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="AL25" s="10">
-        <f t="shared" ref="AL25:AL27" si="166">AL3/AH3-1</f>
-        <v>3.0000000000000027E-2</v>
       </c>
       <c r="AN25" s="10"/>
       <c r="AO25" s="10">
@@ -6624,83 +6596,83 @@
         <v>0.131107305936073</v>
       </c>
       <c r="AP25" s="10">
-        <f t="shared" ref="AP25:BE25" si="167">AP3/AO3-1</f>
+        <f t="shared" ref="AP25:BE25" si="165">AP3/AO3-1</f>
         <v>0.19423979411616288</v>
       </c>
       <c r="AQ25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>0.25254317857708752</v>
       </c>
       <c r="AR25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>0.19686772593867019</v>
       </c>
       <c r="AS25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>0.13030335059718845</v>
       </c>
       <c r="AT25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>0.34604474867056934</v>
       </c>
       <c r="AU25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>0.11982493110714865</v>
       </c>
       <c r="AV25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>4.6073610243726471E-3</v>
       </c>
       <c r="AW25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>5.3462110077768354E-2</v>
       </c>
       <c r="AX25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>6.4184581475416946E-2</v>
       </c>
       <c r="AY25" s="10">
-        <f t="shared" si="167"/>
-        <v>4.151235168612355E-2</v>
+        <f t="shared" si="165"/>
+        <v>6.0229259927068624E-2</v>
       </c>
       <c r="AZ25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BA25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BB25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BC25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE25" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="165"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF25" s="10">
-        <f t="shared" ref="BF25:BF27" si="168">BF3/BE3-1</f>
+        <f t="shared" ref="BF25:BF27" si="166">BF3/BE3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG25" s="10">
-        <f t="shared" ref="BG25:BG27" si="169">BG3/BF3-1</f>
+        <f t="shared" ref="BG25:BG27" si="167">BG3/BF3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH25" s="10">
-        <f t="shared" ref="BH25:BH27" si="170">BH3/BG3-1</f>
+        <f t="shared" ref="BH25:BH27" si="168">BH3/BG3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI25" s="10">
-        <f t="shared" ref="BI25:BI27" si="171">BI3/BH3-1</f>
+        <f t="shared" ref="BI25:BI27" si="169">BI3/BH3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -6717,212 +6689,212 @@
         <v>0.62245409015025044</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" ref="H26:V26" si="172">H4/D4-1</f>
+        <f t="shared" ref="H26:V26" si="170">H4/D4-1</f>
         <v>0.5913701741105224</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.52443910256410264</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.44725010455876202</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.30766064721922115</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.3104366853772238</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.32522996057818654</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.33276740237691005</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.32238265727662596</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.40365906780891536</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.43351512146752613</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.47713782355332701</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.5181636964089138</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.42433019551049966</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.28970971386410271</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="170"/>
         <v>0.21095799922934355</v>
       </c>
       <c r="W26" s="10">
+        <f t="shared" si="149"/>
+        <v>0.17563250827993016</v>
+      </c>
+      <c r="X26" s="10">
+        <f t="shared" si="150"/>
+        <v>0.17399593289273008</v>
+      </c>
+      <c r="Y26" s="10">
         <f t="shared" si="151"/>
-        <v>0.17563250827993016</v>
-      </c>
-      <c r="X26" s="10">
+        <v>0.21140231693363853</v>
+      </c>
+      <c r="Z26" s="10">
         <f t="shared" si="152"/>
-        <v>0.17399593289273008</v>
-      </c>
-      <c r="Y26" s="10">
+        <v>0.19208739923631746</v>
+      </c>
+      <c r="AA26" s="10">
         <f t="shared" si="153"/>
-        <v>0.21140231693363853</v>
-      </c>
-      <c r="Z26" s="10">
+        <v>0.17316508026471511</v>
+      </c>
+      <c r="AB26" s="10">
         <f t="shared" si="154"/>
-        <v>0.19208739923631746</v>
-      </c>
-      <c r="AA26" s="10">
+        <v>0.16535981069920669</v>
+      </c>
+      <c r="AC26" s="10">
         <f t="shared" si="155"/>
-        <v>0.17316508026471511</v>
-      </c>
-      <c r="AB26" s="10">
+        <v>0.179321438585617</v>
+      </c>
+      <c r="AD26" s="10">
         <f t="shared" si="156"/>
-        <v>0.16535981069920669</v>
-      </c>
-      <c r="AC26" s="10">
+        <v>0.1853876170986235</v>
+      </c>
+      <c r="AE26" s="10">
         <f t="shared" si="157"/>
-        <v>0.179321438585617</v>
-      </c>
-      <c r="AD26" s="10">
+        <v>0.17080864486977276</v>
+      </c>
+      <c r="AF26" s="10">
         <f t="shared" si="158"/>
-        <v>0.1853876170986235</v>
-      </c>
-      <c r="AE26" s="10">
+        <v>0.14673992382317413</v>
+      </c>
+      <c r="AG26" s="10">
         <f t="shared" si="159"/>
-        <v>0.17080864486977276</v>
-      </c>
-      <c r="AF26" s="10">
+        <v>0.14220642706977671</v>
+      </c>
+      <c r="AH26" s="10">
         <f t="shared" si="160"/>
-        <v>0.14673992382317413</v>
-      </c>
-      <c r="AG26" s="10">
+        <v>0.13197795363400466</v>
+      </c>
+      <c r="AI26" s="10">
         <f t="shared" si="161"/>
-        <v>0.14220642706977671</v>
-      </c>
-      <c r="AH26" s="10">
+        <v>0.11285468093885775</v>
+      </c>
+      <c r="AJ26" s="10">
         <f t="shared" si="162"/>
-        <v>0.13197795363400466</v>
-      </c>
-      <c r="AI26" s="10">
+        <v>0.15100453661697988</v>
+      </c>
+      <c r="AK26" s="10">
         <f t="shared" si="163"/>
-        <v>0.11285468093885775</v>
-      </c>
-      <c r="AJ26" s="10">
+        <v>0.1399999999999999</v>
+      </c>
+      <c r="AL26" s="10">
         <f t="shared" si="164"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AK26" s="10">
-        <f t="shared" si="165"/>
-        <v>0.10000000000000009</v>
-      </c>
-      <c r="AL26" s="10">
-        <f t="shared" si="166"/>
-        <v>0.10000000000000009</v>
+        <v>0.12999999999999989</v>
       </c>
       <c r="AN26" s="10"/>
       <c r="AO26" s="10">
-        <f t="shared" ref="AO26:BE26" si="173">AO4/AN4-1</f>
+        <f t="shared" ref="AO26:BE26" si="171">AO4/AN4-1</f>
         <v>0.46699809604400255</v>
       </c>
       <c r="AP26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.48972528661042602</v>
       </c>
       <c r="AQ26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.43492570543536124</v>
       </c>
       <c r="AR26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.53425304415286545</v>
       </c>
       <c r="AS26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.3203513168887131</v>
       </c>
       <c r="AT26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.41655080547808354</v>
       </c>
       <c r="AU26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.34020770030972858</v>
       </c>
       <c r="AV26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.18877365316727701</v>
       </c>
       <c r="AW26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.17638943197999124</v>
       </c>
       <c r="AX26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>0.14659859892504823</v>
       </c>
       <c r="AY26" s="10">
-        <f t="shared" si="173"/>
-        <v>0.10289677504047612</v>
+        <f t="shared" si="171"/>
+        <v>0.13359630026692337</v>
       </c>
       <c r="AZ26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="BA26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="BB26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BC26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BD26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE26" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="171"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF26" s="10">
+        <f t="shared" si="166"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BG26" s="10">
+        <f t="shared" si="167"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BH26" s="10">
         <f t="shared" si="168"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BG26" s="10">
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BI26" s="10">
         <f t="shared" si="169"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BH26" s="10">
-        <f t="shared" si="170"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BI26" s="10">
-        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -6939,212 +6911,212 @@
         <v>0.42918743349946809</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" ref="H27:V27" si="174">H5/D5-1</f>
+        <f t="shared" ref="H27:V27" si="172">H5/D5-1</f>
         <v>0.39338690554604128</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.29334308705193846</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.19734339073329688</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.16962501469378166</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.1988806111258179</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.23693792420814486</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.20797701117665746</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.26385259631490787</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.40230900258658764</v>
       </c>
       <c r="Q27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.37387290836084075</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.43594816839553041</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.43823888034777081</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.27181932697498645</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>0.15255083467679031</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="172"/>
         <v>9.4436701047349692E-2</v>
       </c>
       <c r="W27" s="10">
+        <f t="shared" si="149"/>
+        <v>7.3038574245747334E-2</v>
+      </c>
+      <c r="X27" s="10">
+        <f t="shared" si="150"/>
+        <v>7.2108241952600016E-2</v>
+      </c>
+      <c r="Y27" s="10">
         <f t="shared" si="151"/>
-        <v>7.3038574245747334E-2</v>
-      </c>
-      <c r="X27" s="10">
+        <v>0.14699671515720314</v>
+      </c>
+      <c r="Z27" s="10">
         <f t="shared" si="152"/>
-        <v>7.2108241952600016E-2</v>
-      </c>
-      <c r="Y27" s="10">
+        <v>8.5814921549791867E-2</v>
+      </c>
+      <c r="AA27" s="10">
         <f t="shared" si="153"/>
-        <v>0.14699671515720314</v>
-      </c>
-      <c r="Z27" s="10">
+        <v>9.3727456975026602E-2</v>
+      </c>
+      <c r="AB27" s="10">
         <f t="shared" si="154"/>
-        <v>8.5814921549791867E-2</v>
-      </c>
-      <c r="AA27" s="10">
+        <v>0.10845967302901816</v>
+      </c>
+      <c r="AC27" s="10">
         <f t="shared" si="155"/>
-        <v>9.3727456975026602E-2</v>
-      </c>
-      <c r="AB27" s="10">
+        <v>0.125742519728405</v>
+      </c>
+      <c r="AD27" s="10">
         <f t="shared" si="156"/>
-        <v>0.10845967302901816</v>
-      </c>
-      <c r="AC27" s="10">
+        <v>0.13911825420230017</v>
+      </c>
+      <c r="AE27" s="10">
         <f t="shared" si="157"/>
-        <v>0.125742519728405</v>
-      </c>
-      <c r="AD27" s="10">
+        <v>0.12527677884388888</v>
+      </c>
+      <c r="AF27" s="10">
         <f t="shared" si="158"/>
-        <v>0.13911825420230017</v>
-      </c>
-      <c r="AE27" s="10">
+        <v>0.10115862869559389</v>
+      </c>
+      <c r="AG27" s="10">
         <f t="shared" si="159"/>
-        <v>0.12527677884388888</v>
-      </c>
-      <c r="AF27" s="10">
+        <v>0.11038348371225104</v>
+      </c>
+      <c r="AH27" s="10">
         <f t="shared" si="160"/>
-        <v>0.10115862869559389</v>
-      </c>
-      <c r="AG27" s="10">
+        <v>0.10491230341078239</v>
+      </c>
+      <c r="AI27" s="10">
         <f t="shared" si="161"/>
-        <v>0.11038348371225104</v>
-      </c>
-      <c r="AH27" s="10">
+        <v>8.6202926461660834E-2</v>
+      </c>
+      <c r="AJ27" s="10">
         <f t="shared" si="162"/>
-        <v>0.10491230341078239</v>
-      </c>
-      <c r="AI27" s="10">
+        <v>0.13329774221669588</v>
+      </c>
+      <c r="AK27" s="10">
         <f t="shared" si="163"/>
-        <v>8.6202926461660834E-2</v>
-      </c>
-      <c r="AJ27" s="10">
+        <v>0.10170565909477136</v>
+      </c>
+      <c r="AL27" s="10">
         <f t="shared" si="164"/>
-        <v>7.9196429174804184E-2</v>
-      </c>
-      <c r="AK27" s="10">
-        <f t="shared" si="165"/>
-        <v>7.4470439396514321E-2</v>
-      </c>
-      <c r="AL27" s="10">
-        <f t="shared" si="166"/>
-        <v>6.9350025560194206E-2</v>
+        <v>9.0592890005964044E-2</v>
       </c>
       <c r="AN27" s="10"/>
       <c r="AO27" s="10">
-        <f t="shared" ref="AO27:BE27" si="175">AO5/AN5-1</f>
+        <f t="shared" ref="AO27:BE27" si="173">AO5/AN5-1</f>
         <v>0.20247673843664304</v>
       </c>
       <c r="AP27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.27083528026465808</v>
       </c>
       <c r="AQ27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.30796326119408479</v>
       </c>
       <c r="AR27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.3093396152159491</v>
       </c>
       <c r="AS27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.20454125820676983</v>
       </c>
       <c r="AT27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.37623430604373276</v>
       </c>
       <c r="AU27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.21695366571345676</v>
       </c>
       <c r="AV27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>9.399517263985091E-2</v>
       </c>
       <c r="AW27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.1182957412988368</v>
       </c>
       <c r="AX27" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="173"/>
         <v>0.1099089224666614</v>
       </c>
       <c r="AY27" s="10">
-        <f t="shared" si="175"/>
-        <v>7.6695007045907371E-2</v>
+        <f t="shared" si="173"/>
+        <v>0.10227978600505661</v>
       </c>
       <c r="AZ27" s="10">
-        <f t="shared" si="175"/>
-        <v>7.348402817248334E-2</v>
+        <f t="shared" si="173"/>
+        <v>7.3577459177837312E-2</v>
       </c>
       <c r="BA27" s="10">
-        <f t="shared" si="175"/>
-        <v>6.3845339135212287E-2</v>
+        <f t="shared" si="173"/>
+        <v>6.3938124151305731E-2</v>
       </c>
       <c r="BB27" s="10">
-        <f t="shared" si="175"/>
-        <v>4.8155575805053141E-2</v>
+        <f t="shared" si="173"/>
+        <v>4.8224631792403327E-2</v>
       </c>
       <c r="BC27" s="10">
-        <f t="shared" si="175"/>
-        <v>3.2240492281612632E-2</v>
+        <f t="shared" si="173"/>
+        <v>3.2286240381456333E-2</v>
       </c>
       <c r="BD27" s="10">
-        <f t="shared" si="175"/>
-        <v>2.6166252955616587E-2</v>
+        <f t="shared" si="173"/>
+        <v>2.6189024660443261E-2</v>
       </c>
       <c r="BE27" s="10">
-        <f t="shared" si="175"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="173"/>
+        <v>2.000000000000024E-2</v>
       </c>
       <c r="BF27" s="10">
+        <f t="shared" si="166"/>
+        <v>1.6212008944810119E-2</v>
+      </c>
+      <c r="BG27" s="10">
+        <f t="shared" si="167"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BH27" s="10">
         <f t="shared" si="168"/>
-        <v>1.6189290016107805E-2</v>
-      </c>
-      <c r="BG27" s="10">
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BI27" s="10">
         <f t="shared" si="169"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BH27" s="10">
-        <f t="shared" si="170"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BI27" s="10">
-        <f t="shared" si="171"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -7153,19 +7125,19 @@
         <v>52</v>
       </c>
       <c r="C28" s="10">
-        <f t="shared" ref="C28:F28" si="176">C7/C5</f>
+        <f t="shared" ref="C28:F28" si="174">C7/C5</f>
         <v>0.37167497339978722</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="174"/>
         <v>0.38213674087735477</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="174"/>
         <v>0.37022220190197513</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="174"/>
         <v>0.36324086480406265</v>
       </c>
       <c r="G28" s="10">
@@ -7173,216 +7145,216 @@
         <v>0.39784883037498531</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" ref="H28:V28" si="177">H7/H5</f>
+        <f t="shared" ref="H28:V28" si="175">H7/H5</f>
         <v>0.4207918919941005</v>
       </c>
       <c r="I28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.4166607748868778</v>
+      </c>
+      <c r="J28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.38126355635991876</v>
+      </c>
+      <c r="K28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.4318257956448911</v>
+      </c>
+      <c r="L28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.42689735663365086</v>
+      </c>
+      <c r="M28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.40981123447792972</v>
+      </c>
+      <c r="N28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.38267552637899288</v>
+      </c>
+      <c r="O28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.41344165827280921</v>
+      </c>
+      <c r="P28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.40772899046247973</v>
+      </c>
+      <c r="Q28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.40604295595194756</v>
+      </c>
+      <c r="R28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.36853171916689897</v>
+      </c>
+      <c r="S28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.42495254243535635</v>
+      </c>
+      <c r="T28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.43247258577997877</v>
+      </c>
+      <c r="U28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.43210121647475003</v>
+      </c>
+      <c r="V28" s="10">
+        <f t="shared" si="175"/>
+        <v>0.39717783017494834</v>
+      </c>
+      <c r="W28" s="10">
+        <f t="shared" ref="W28:AE28" si="176">W7/W5</f>
+        <v>0.42891862182680085</v>
+      </c>
+      <c r="X28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.4521008957883102</v>
+      </c>
+      <c r="Y28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.44714833085498934</v>
+      </c>
+      <c r="Z28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.42602075011393797</v>
+      </c>
+      <c r="AA28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.46771306082067871</v>
+      </c>
+      <c r="AB28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.48376654785203488</v>
+      </c>
+      <c r="AC28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.47567495789157344</v>
+      </c>
+      <c r="AD28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.45544566106342044</v>
+      </c>
+      <c r="AE28" s="10">
+        <f t="shared" si="176"/>
+        <v>0.49318624269954575</v>
+      </c>
+      <c r="AF28" s="10">
+        <f t="shared" ref="AF28:AH28" si="177">AF7/AF5</f>
+        <v>0.50137521371564497</v>
+      </c>
+      <c r="AG28" s="10">
         <f t="shared" si="177"/>
-        <v>0.4166607748868778</v>
-      </c>
-      <c r="J28" s="10">
+        <v>0.49031640829069029</v>
+      </c>
+      <c r="AH28" s="10">
         <f t="shared" si="177"/>
-        <v>0.38126355635991876</v>
-      </c>
-      <c r="K28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.4318257956448911</v>
-      </c>
-      <c r="L28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.42689735663365086</v>
-      </c>
-      <c r="M28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.40981123447792972</v>
-      </c>
-      <c r="N28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.38267552637899288</v>
-      </c>
-      <c r="O28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.41344165827280921</v>
-      </c>
-      <c r="P28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.40772899046247973</v>
-      </c>
-      <c r="Q28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.40604295595194756</v>
-      </c>
-      <c r="R28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.36853171916689897</v>
-      </c>
-      <c r="S28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.42495254243535635</v>
-      </c>
-      <c r="T28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.43247258577997877</v>
-      </c>
-      <c r="U28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.43210121647475003</v>
-      </c>
-      <c r="V28" s="10">
-        <f t="shared" si="177"/>
-        <v>0.39717783017494834</v>
-      </c>
-      <c r="W28" s="10">
-        <f t="shared" ref="W28:AE28" si="178">W7/W5</f>
-        <v>0.42891862182680085</v>
-      </c>
-      <c r="X28" s="10">
+        <v>0.47339077276987307</v>
+      </c>
+      <c r="AI28" s="10">
+        <f t="shared" ref="AI28:AL28" si="178">AI7/AI5</f>
+        <v>0.50550855351487467</v>
+      </c>
+      <c r="AJ28" s="10">
         <f t="shared" si="178"/>
-        <v>0.4521008957883102</v>
-      </c>
-      <c r="Y28" s="10">
+        <v>0.51813931855314788</v>
+      </c>
+      <c r="AK28" s="10">
         <f t="shared" si="178"/>
-        <v>0.44714833085498934</v>
-      </c>
-      <c r="Z28" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="AL28" s="10">
         <f t="shared" si="178"/>
-        <v>0.42602075011393797</v>
-      </c>
-      <c r="AA28" s="10">
-        <f t="shared" si="178"/>
-        <v>0.46771306082067871</v>
-      </c>
-      <c r="AB28" s="10">
-        <f t="shared" si="178"/>
-        <v>0.48376654785203488</v>
-      </c>
-      <c r="AC28" s="10">
-        <f t="shared" si="178"/>
-        <v>0.47567495789157344</v>
-      </c>
-      <c r="AD28" s="10">
-        <f t="shared" si="178"/>
-        <v>0.45544566106342044</v>
-      </c>
-      <c r="AE28" s="10">
-        <f t="shared" si="178"/>
-        <v>0.49318624269954575</v>
-      </c>
-      <c r="AF28" s="10">
-        <f t="shared" ref="AF28:AH28" si="179">AF7/AF5</f>
-        <v>0.50137521371564497</v>
-      </c>
-      <c r="AG28" s="10">
+        <v>0.49</v>
+      </c>
+      <c r="AN28" s="10">
+        <f t="shared" ref="AN28:BE28" si="179">AN7/AN5</f>
+        <v>0.29482626871038792</v>
+      </c>
+      <c r="AO28" s="10">
         <f t="shared" si="179"/>
-        <v>0.49031640829069029</v>
-      </c>
-      <c r="AH28" s="10">
+        <v>0.33040203353083003</v>
+      </c>
+      <c r="AP28" s="10">
         <f t="shared" si="179"/>
-        <v>0.47339077276987307</v>
-      </c>
-      <c r="AI28" s="10">
-        <f t="shared" ref="AI28:AL28" si="180">AI7/AI5</f>
-        <v>0.50550855351487467</v>
-      </c>
-      <c r="AJ28" s="10">
+        <v>0.35093060366064405</v>
+      </c>
+      <c r="AQ28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.3706835482891615</v>
+      </c>
+      <c r="AR28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.40247416128852193</v>
+      </c>
+      <c r="AS28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.40990011478600608</v>
+      </c>
+      <c r="AT28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.3956779186870571</v>
+      </c>
+      <c r="AU28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.42032514441639601</v>
+      </c>
+      <c r="AV28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.43805339865326287</v>
+      </c>
+      <c r="AW28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.46982088955000567</v>
+      </c>
+      <c r="AX28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.48854393464156787</v>
+      </c>
+      <c r="AY28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.50263286303760679</v>
+      </c>
+      <c r="AZ28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.51</v>
+      </c>
+      <c r="BA28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.52</v>
+      </c>
+      <c r="BB28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.53</v>
+      </c>
+      <c r="BC28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.53</v>
+      </c>
+      <c r="BD28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.53</v>
+      </c>
+      <c r="BE28" s="10">
+        <f t="shared" si="179"/>
+        <v>0.53</v>
+      </c>
+      <c r="BF28" s="10">
+        <f t="shared" ref="BF28:BI28" si="180">BF7/BF5</f>
+        <v>0.53</v>
+      </c>
+      <c r="BG28" s="10">
         <f t="shared" si="180"/>
-        <v>0.5</v>
-      </c>
-      <c r="AK28" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="BH28" s="10">
         <f t="shared" si="180"/>
-        <v>0.5</v>
-      </c>
-      <c r="AL28" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="BI28" s="10">
         <f t="shared" si="180"/>
-        <v>0.48</v>
-      </c>
-      <c r="AN28" s="10">
-        <f t="shared" ref="AN28:BE28" si="181">AN7/AN5</f>
-        <v>0.29482626871038792</v>
-      </c>
-      <c r="AO28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.33040203353083003</v>
-      </c>
-      <c r="AP28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.35093060366064405</v>
-      </c>
-      <c r="AQ28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.3706835482891615</v>
-      </c>
-      <c r="AR28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.40247416128852193</v>
-      </c>
-      <c r="AS28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.40990011478600608</v>
-      </c>
-      <c r="AT28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.3956779186870571</v>
-      </c>
-      <c r="AU28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.42032514441639601</v>
-      </c>
-      <c r="AV28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.43805339865326287</v>
-      </c>
-      <c r="AW28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.46982088955000567</v>
-      </c>
-      <c r="AX28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.48854393464156787</v>
-      </c>
-      <c r="AY28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.49540127217672852</v>
-      </c>
-      <c r="AZ28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.5</v>
-      </c>
-      <c r="BA28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.5</v>
-      </c>
-      <c r="BB28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.5</v>
-      </c>
-      <c r="BC28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.5</v>
-      </c>
-      <c r="BD28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.5</v>
-      </c>
-      <c r="BE28" s="10">
-        <f t="shared" si="181"/>
-        <v>0.5</v>
-      </c>
-      <c r="BF28" s="10">
-        <f t="shared" ref="BF28:BI28" si="182">BF7/BF5</f>
-        <v>0.5</v>
-      </c>
-      <c r="BG28" s="10">
-        <f t="shared" si="182"/>
-        <v>0.5</v>
-      </c>
-      <c r="BH28" s="10">
-        <f t="shared" si="182"/>
-        <v>0.5</v>
-      </c>
-      <c r="BI28" s="10">
-        <f t="shared" si="182"/>
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="29" spans="2:153" x14ac:dyDescent="0.3">
@@ -7390,19 +7362,19 @@
         <v>53</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:F29" si="183">C14/C5</f>
+        <f t="shared" ref="C29:F29" si="181">C14/C5</f>
         <v>2.8140225121800973E-2</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>1.6545909629824794E-2</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>7.932516459400147E-3</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="181"/>
         <v>3.5184358096372388E-2</v>
       </c>
       <c r="G29" s="10">
@@ -7410,216 +7382,216 @@
         <v>3.7753222836095765E-2</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" ref="H29:V29" si="184">H14/H5</f>
+        <f t="shared" ref="H29:V29" si="182">H14/H5</f>
         <v>5.6404341413606625E-2</v>
       </c>
       <c r="I29" s="10">
+        <f t="shared" si="182"/>
+        <v>6.5822963800904979E-2</v>
+      </c>
+      <c r="J29" s="10">
+        <f t="shared" si="182"/>
+        <v>5.230509926363925E-2</v>
+      </c>
+      <c r="K29" s="10">
+        <f t="shared" si="182"/>
+        <v>7.4036850921273031E-2</v>
+      </c>
+      <c r="L29" s="10">
+        <f t="shared" si="182"/>
+        <v>4.8640464324017411E-2</v>
+      </c>
+      <c r="M29" s="10">
+        <f t="shared" si="182"/>
+        <v>4.5112244752147014E-2</v>
+      </c>
+      <c r="N29" s="10">
+        <f t="shared" si="182"/>
+        <v>4.4363370197971111E-2</v>
+      </c>
+      <c r="O29" s="10">
+        <f t="shared" si="182"/>
+        <v>5.2868048560674334E-2</v>
+      </c>
+      <c r="P29" s="10">
+        <f t="shared" si="182"/>
+        <v>6.5716663667446468E-2</v>
+      </c>
+      <c r="Q29" s="10">
+        <f t="shared" si="182"/>
+        <v>6.4423526964480726E-2</v>
+      </c>
+      <c r="R29" s="10">
+        <f t="shared" si="182"/>
+        <v>5.4740950181195493E-2</v>
+      </c>
+      <c r="S29" s="10">
+        <f t="shared" si="182"/>
+        <v>8.1691516614755155E-2</v>
+      </c>
+      <c r="T29" s="10">
+        <f t="shared" si="182"/>
+        <v>6.8111071807569867E-2</v>
+      </c>
+      <c r="U29" s="10">
+        <f t="shared" si="182"/>
+        <v>4.3785871566256365E-2</v>
+      </c>
+      <c r="V29" s="10">
+        <f t="shared" si="182"/>
+        <v>2.5179751404535267E-2</v>
+      </c>
+      <c r="W29" s="10">
+        <f t="shared" ref="W29:AE29" si="183">W14/W5</f>
+        <v>3.1508708048504003E-2</v>
+      </c>
+      <c r="X29" s="10">
+        <f t="shared" si="183"/>
+        <v>2.7360311463780786E-2</v>
+      </c>
+      <c r="Y29" s="10">
+        <f t="shared" si="183"/>
+        <v>1.986609074672898E-2</v>
+      </c>
+      <c r="Z29" s="10">
+        <f t="shared" si="183"/>
+        <v>1.8344012224873328E-2</v>
+      </c>
+      <c r="AA29" s="10">
+        <f t="shared" si="183"/>
+        <v>3.7484885126964934E-2</v>
+      </c>
+      <c r="AB29" s="10">
+        <f t="shared" si="183"/>
+        <v>5.7157527365812637E-2</v>
+      </c>
+      <c r="AC29" s="10">
+        <f t="shared" si="183"/>
+        <v>7.8192377850618167E-2</v>
+      </c>
+      <c r="AD29" s="10">
+        <f t="shared" si="183"/>
+        <v>7.771782938438819E-2</v>
+      </c>
+      <c r="AE29" s="10">
+        <f t="shared" si="183"/>
+        <v>0.10680817511321374</v>
+      </c>
+      <c r="AF29" s="10">
+        <f t="shared" ref="AF29:AH29" si="184">AF14/AF5</f>
+        <v>9.9150543665569649E-2</v>
+      </c>
+      <c r="AG29" s="10">
         <f t="shared" si="184"/>
-        <v>6.5822963800904979E-2</v>
-      </c>
-      <c r="J29" s="10">
+        <v>0.1095879202150091</v>
+      </c>
+      <c r="AH29" s="10">
         <f t="shared" si="184"/>
-        <v>5.230509926363925E-2</v>
-      </c>
-      <c r="K29" s="10">
-        <f t="shared" si="184"/>
-        <v>7.4036850921273031E-2</v>
-      </c>
-      <c r="L29" s="10">
-        <f t="shared" si="184"/>
-        <v>4.8640464324017411E-2</v>
-      </c>
-      <c r="M29" s="10">
-        <f t="shared" si="184"/>
-        <v>4.5112244752147014E-2</v>
-      </c>
-      <c r="N29" s="10">
-        <f t="shared" si="184"/>
-        <v>4.4363370197971111E-2</v>
-      </c>
-      <c r="O29" s="10">
-        <f t="shared" si="184"/>
-        <v>5.2868048560674334E-2</v>
-      </c>
-      <c r="P29" s="10">
-        <f t="shared" si="184"/>
-        <v>6.5716663667446468E-2</v>
-      </c>
-      <c r="Q29" s="10">
-        <f t="shared" si="184"/>
-        <v>6.4423526964480726E-2</v>
-      </c>
-      <c r="R29" s="10">
-        <f t="shared" si="184"/>
-        <v>5.4740950181195493E-2</v>
-      </c>
-      <c r="S29" s="10">
-        <f t="shared" si="184"/>
-        <v>8.1691516614755155E-2</v>
-      </c>
-      <c r="T29" s="10">
-        <f t="shared" si="184"/>
-        <v>6.8111071807569867E-2</v>
-      </c>
-      <c r="U29" s="10">
-        <f t="shared" si="184"/>
-        <v>4.3785871566256365E-2</v>
-      </c>
-      <c r="V29" s="10">
-        <f t="shared" si="184"/>
-        <v>2.5179751404535267E-2</v>
-      </c>
-      <c r="W29" s="10">
-        <f t="shared" ref="W29:AE29" si="185">W14/W5</f>
-        <v>3.1508708048504003E-2</v>
-      </c>
-      <c r="X29" s="10">
+        <v>0.1129068330919315</v>
+      </c>
+      <c r="AI29" s="10">
+        <f t="shared" ref="AI29:AL29" si="185">AI14/AI5</f>
+        <v>0.11823315153500742</v>
+      </c>
+      <c r="AJ29" s="10">
         <f t="shared" si="185"/>
-        <v>2.7360311463780786E-2</v>
-      </c>
-      <c r="Y29" s="10">
+        <v>0.11431586981669867</v>
+      </c>
+      <c r="AK29" s="10">
         <f t="shared" si="185"/>
-        <v>1.986609074672898E-2</v>
-      </c>
-      <c r="Z29" s="10">
+        <v>9.9778935084610471E-2</v>
+      </c>
+      <c r="AL29" s="10">
         <f t="shared" si="185"/>
-        <v>1.8344012224873328E-2</v>
-      </c>
-      <c r="AA29" s="10">
-        <f t="shared" si="185"/>
-        <v>3.7484885126964934E-2</v>
-      </c>
-      <c r="AB29" s="10">
-        <f t="shared" si="185"/>
-        <v>5.7157527365812637E-2</v>
-      </c>
-      <c r="AC29" s="10">
-        <f t="shared" si="185"/>
-        <v>7.8192377850618167E-2</v>
-      </c>
-      <c r="AD29" s="10">
-        <f t="shared" si="185"/>
-        <v>7.771782938438819E-2</v>
-      </c>
-      <c r="AE29" s="10">
-        <f t="shared" si="185"/>
-        <v>0.10680817511321374</v>
-      </c>
-      <c r="AF29" s="10">
-        <f t="shared" ref="AF29:AH29" si="186">AF14/AF5</f>
-        <v>9.9150543665569649E-2</v>
-      </c>
-      <c r="AG29" s="10">
+        <v>0.12148549432136835</v>
+      </c>
+      <c r="AN29" s="10">
+        <f t="shared" ref="AN29:BE29" si="186">AN14/AN5</f>
+        <v>2.000269699285297E-3</v>
+      </c>
+      <c r="AO29" s="10">
         <f t="shared" si="186"/>
-        <v>0.1095879202150091</v>
-      </c>
-      <c r="AH29" s="10">
+        <v>2.0867988710913405E-2</v>
+      </c>
+      <c r="AP29" s="10">
         <f t="shared" si="186"/>
-        <v>0.1129068330919315</v>
-      </c>
-      <c r="AI29" s="10">
-        <f t="shared" ref="AI29:AL29" si="187">AI14/AI5</f>
-        <v>0.11823315153500742</v>
-      </c>
-      <c r="AJ29" s="10">
+        <v>3.0782354195621642E-2</v>
+      </c>
+      <c r="AQ29" s="10">
+        <f t="shared" si="186"/>
+        <v>2.3090416380870993E-2</v>
+      </c>
+      <c r="AR29" s="10">
+        <f t="shared" si="186"/>
+        <v>5.3330585219441187E-2</v>
+      </c>
+      <c r="AS29" s="10">
+        <f t="shared" si="186"/>
+        <v>5.1831941879781268E-2</v>
+      </c>
+      <c r="AT29" s="10">
+        <f t="shared" si="186"/>
+        <v>5.9313999751336569E-2</v>
+      </c>
+      <c r="AU29" s="10">
+        <f t="shared" si="186"/>
+        <v>5.2954097509269465E-2</v>
+      </c>
+      <c r="AV29" s="10">
+        <f t="shared" si="186"/>
+        <v>2.3829581912242232E-2</v>
+      </c>
+      <c r="AW29" s="10">
+        <f t="shared" si="186"/>
+        <v>6.4114407996033296E-2</v>
+      </c>
+      <c r="AX29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.1075194487420038</v>
+      </c>
+      <c r="AY29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.1136527405332559</v>
+      </c>
+      <c r="AZ29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.13163240119080352</v>
+      </c>
+      <c r="BA29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.14572210245234218</v>
+      </c>
+      <c r="BB29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.15871904003787402</v>
+      </c>
+      <c r="BC29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.16062666515368212</v>
+      </c>
+      <c r="BD29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.16171413413855437</v>
+      </c>
+      <c r="BE29" s="10">
+        <f t="shared" si="186"/>
+        <v>0.16183893741331759</v>
+      </c>
+      <c r="BF29" s="10">
+        <f t="shared" ref="BF29:BI29" si="187">BF14/BF5</f>
+        <v>0.16278123711468764</v>
+      </c>
+      <c r="BG29" s="10">
         <f t="shared" si="187"/>
-        <v>0.10291868938688288</v>
-      </c>
-      <c r="AK29" s="10">
+        <v>0.16275622741099935</v>
+      </c>
+      <c r="BH29" s="10">
         <f t="shared" si="187"/>
-        <v>0.11618706586848795</v>
-      </c>
-      <c r="AL29" s="10">
+        <v>0.16273072246565398</v>
+      </c>
+      <c r="BI29" s="10">
         <f t="shared" si="187"/>
-        <v>0.12604236637651955</v>
-      </c>
-      <c r="AN29" s="10">
-        <f t="shared" ref="AN29:BE29" si="188">AN14/AN5</f>
-        <v>2.000269699285297E-3</v>
-      </c>
-      <c r="AO29" s="10">
-        <f t="shared" si="188"/>
-        <v>2.0867988710913405E-2</v>
-      </c>
-      <c r="AP29" s="10">
-        <f t="shared" si="188"/>
-        <v>3.0782354195621642E-2</v>
-      </c>
-      <c r="AQ29" s="10">
-        <f t="shared" si="188"/>
-        <v>2.3090416380870993E-2</v>
-      </c>
-      <c r="AR29" s="10">
-        <f t="shared" si="188"/>
-        <v>5.3330585219441187E-2</v>
-      </c>
-      <c r="AS29" s="10">
-        <f t="shared" si="188"/>
-        <v>5.1831941879781268E-2</v>
-      </c>
-      <c r="AT29" s="10">
-        <f t="shared" si="188"/>
-        <v>5.9313999751336569E-2</v>
-      </c>
-      <c r="AU29" s="10">
-        <f t="shared" si="188"/>
-        <v>5.2954097509269465E-2</v>
-      </c>
-      <c r="AV29" s="10">
-        <f t="shared" si="188"/>
-        <v>2.3829581912242232E-2</v>
-      </c>
-      <c r="AW29" s="10">
-        <f t="shared" si="188"/>
-        <v>6.4114407996033296E-2</v>
-      </c>
-      <c r="AX29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.1075194487420038</v>
-      </c>
-      <c r="AY29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.11644721622224849</v>
-      </c>
-      <c r="AZ29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.13609238614352212</v>
-      </c>
-      <c r="BA29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.14113833995967062</v>
-      </c>
-      <c r="BB29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.14512611859442434</v>
-      </c>
-      <c r="BC29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.14683313651576702</v>
-      </c>
-      <c r="BD29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.14782537355703679</v>
-      </c>
-      <c r="BE29" s="10">
-        <f t="shared" si="188"/>
-        <v>0.14795580959312712</v>
-      </c>
-      <c r="BF29" s="10">
-        <f t="shared" ref="BF29:BI29" si="189">BF14/BF5</f>
-        <v>0.14879851375279768</v>
-      </c>
-      <c r="BG29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.14877562692746168</v>
-      </c>
-      <c r="BH29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.14875228689766357</v>
-      </c>
-      <c r="BI29" s="10">
-        <f t="shared" si="189"/>
-        <v>0.14872848468905753</v>
+        <v>0.16270471247188584</v>
       </c>
       <c r="BK29" t="s">
         <v>61</v>
@@ -7633,19 +7605,19 @@
         <v>54</v>
       </c>
       <c r="C30" s="10">
-        <f t="shared" ref="C30:F30" si="190">C8/C5</f>
+        <f t="shared" ref="C30:F30" si="188">C8/C5</f>
         <v>0.1315170521364171</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="188"/>
         <v>0.13589777367935713</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="188"/>
         <v>0.1467629846378932</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="188"/>
         <v>0.14844590012075495</v>
       </c>
       <c r="G30" s="10">
@@ -7653,215 +7625,215 @@
         <v>0.15265859488264566</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" ref="H30:V30" si="191">H8/H5</f>
+        <f t="shared" ref="H30:V30" si="189">H8/H5</f>
         <v>0.1499829822637371</v>
       </c>
       <c r="I30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.14626343325791855</v>
+      </c>
+      <c r="J30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.13854081759529172</v>
+      </c>
+      <c r="K30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.14407035175879396</v>
+      </c>
+      <c r="L30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.14622105860828971</v>
+      </c>
+      <c r="M30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.14528229090753206</v>
+      </c>
+      <c r="N30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.13943753788441965</v>
+      </c>
+      <c r="O30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.15282563749138525</v>
+      </c>
+      <c r="P30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.15527712794673384</v>
+      </c>
+      <c r="Q30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.15294607103853555</v>
+      </c>
+      <c r="R30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.1471387041535582</v>
+      </c>
+      <c r="S30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.15232495991448422</v>
+      </c>
+      <c r="T30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.15597806862398303</v>
+      </c>
+      <c r="U30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.16693137927300292</v>
+      </c>
+      <c r="V30" s="10">
+        <f t="shared" si="189"/>
+        <v>0.16334090181352429</v>
+      </c>
+      <c r="W30" s="10">
+        <f t="shared" ref="W30:AE30" si="190">W8/W5</f>
+        <v>0.17408367970870117</v>
+      </c>
+      <c r="X30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.1677912136859297</v>
+      </c>
+      <c r="Y30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.16194207756036538</v>
+      </c>
+      <c r="Z30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.15484169325219163</v>
+      </c>
+      <c r="AA30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.16414359521977417</v>
+      </c>
+      <c r="AB30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.15853939858464242</v>
+      </c>
+      <c r="AC30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.15595144077213924</v>
+      </c>
+      <c r="AD30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.15353522278640394</v>
+      </c>
+      <c r="AE30" s="10">
+        <f t="shared" si="190"/>
+        <v>0.15572209080823093</v>
+      </c>
+      <c r="AF30" s="10">
+        <f t="shared" ref="AF30:AH30" si="191">AF8/AF5</f>
+        <v>0.1592544787365604</v>
+      </c>
+      <c r="AG30" s="10">
         <f t="shared" si="191"/>
-        <v>0.14626343325791855</v>
-      </c>
-      <c r="J30" s="10">
+        <v>0.15521441114824674</v>
+      </c>
+      <c r="AH30" s="10">
         <f t="shared" si="191"/>
-        <v>0.13854081759529172</v>
-      </c>
-      <c r="K30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.14407035175879396</v>
-      </c>
-      <c r="L30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.14622105860828971</v>
-      </c>
-      <c r="M30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.14528229090753206</v>
-      </c>
-      <c r="N30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.13943753788441965</v>
-      </c>
-      <c r="O30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15282563749138525</v>
-      </c>
-      <c r="P30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15527712794673384</v>
-      </c>
-      <c r="Q30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15294607103853555</v>
-      </c>
-      <c r="R30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.1471387041535582</v>
-      </c>
-      <c r="S30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15232495991448422</v>
-      </c>
-      <c r="T30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.15597806862398303</v>
-      </c>
-      <c r="U30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.16693137927300292</v>
-      </c>
-      <c r="V30" s="10">
-        <f t="shared" si="191"/>
-        <v>0.16334090181352429</v>
-      </c>
-      <c r="W30" s="10">
-        <f t="shared" ref="W30:AE30" si="192">W8/W5</f>
-        <v>0.17408367970870117</v>
-      </c>
-      <c r="X30" s="10">
+        <v>0.14889878163074038</v>
+      </c>
+      <c r="AI30" s="10">
+        <f t="shared" ref="AI30:AL30" si="192">AI8/AI5</f>
+        <v>0.15798467240969505</v>
+      </c>
+      <c r="AJ30" s="10">
         <f t="shared" si="192"/>
-        <v>0.1677912136859297</v>
-      </c>
-      <c r="Y30" s="10">
+        <v>0.15489379971616318</v>
+      </c>
+      <c r="AK30" s="10">
         <f t="shared" si="192"/>
-        <v>0.16194207756036538</v>
-      </c>
-      <c r="Z30" s="10">
+        <v>0.16</v>
+      </c>
+      <c r="AL30" s="10">
         <f t="shared" si="192"/>
-        <v>0.15484169325219163</v>
-      </c>
-      <c r="AA30" s="10">
-        <f t="shared" si="192"/>
-        <v>0.16414359521977417</v>
-      </c>
-      <c r="AB30" s="10">
-        <f t="shared" si="192"/>
-        <v>0.15853939858464242</v>
-      </c>
-      <c r="AC30" s="10">
-        <f t="shared" si="192"/>
-        <v>0.15595144077213924</v>
-      </c>
-      <c r="AD30" s="10">
-        <f t="shared" si="192"/>
-        <v>0.15353522278640394</v>
-      </c>
-      <c r="AE30" s="10">
-        <f t="shared" si="192"/>
-        <v>0.15572209080823093</v>
-      </c>
-      <c r="AF30" s="10">
-        <f t="shared" ref="AF30:AH30" si="193">AF8/AF5</f>
-        <v>0.1592544787365604</v>
-      </c>
-      <c r="AG30" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="AN30" s="10">
+        <f t="shared" ref="AN30:BE30" si="193">AN8/AN5</f>
+        <v>0.12098260439609836</v>
+      </c>
+      <c r="AO30" s="10">
         <f t="shared" si="193"/>
-        <v>0.15521441114824674</v>
-      </c>
-      <c r="AH30" s="10">
+        <v>0.1253200755097845</v>
+      </c>
+      <c r="AP30" s="10">
         <f t="shared" si="193"/>
-        <v>0.14889878163074038</v>
-      </c>
-      <c r="AI30" s="10">
-        <f t="shared" ref="AI30:AL30" si="194">AI8/AI5</f>
-        <v>0.15798467240969505</v>
-      </c>
-      <c r="AJ30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.16</v>
-      </c>
-      <c r="AK30" s="10">
-        <f t="shared" si="194"/>
-        <v>0.16</v>
-      </c>
-      <c r="AL30" s="10">
+        <v>0.12956385536852788</v>
+      </c>
+      <c r="AQ30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.14195517974205302</v>
+      </c>
+      <c r="AR30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.14610948657503425</v>
+      </c>
+      <c r="AS30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.14341477673765338</v>
+      </c>
+      <c r="AT30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15157072402503211</v>
+      </c>
+      <c r="AU30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15987118525739535</v>
+      </c>
+      <c r="AV30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.16401126107283703</v>
+      </c>
+      <c r="AW30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.1576572109571405</v>
+      </c>
+      <c r="AX30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15440647439725749</v>
+      </c>
+      <c r="AY30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15542371502447827</v>
+      </c>
+      <c r="AZ30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15</v>
+      </c>
+      <c r="BA30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15</v>
+      </c>
+      <c r="BB30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15</v>
+      </c>
+      <c r="BC30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15</v>
+      </c>
+      <c r="BD30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="BE30" s="10">
+        <f t="shared" si="193"/>
+        <v>0.15</v>
+      </c>
+      <c r="BF30" s="10">
+        <f t="shared" ref="BF30:BI30" si="194">BF8/BF5</f>
+        <v>0.15</v>
+      </c>
+      <c r="BG30" s="10">
         <f t="shared" si="194"/>
         <v>0.15</v>
       </c>
-      <c r="AN30" s="10">
-        <f t="shared" ref="AN30:BE30" si="195">AN8/AN5</f>
-        <v>0.12098260439609836</v>
-      </c>
-      <c r="AO30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.1253200755097845</v>
-      </c>
-      <c r="AP30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.12956385536852788</v>
-      </c>
-      <c r="AQ30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.14195517974205302</v>
-      </c>
-      <c r="AR30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.14610948657503425</v>
-      </c>
-      <c r="AS30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.14341477673765338</v>
-      </c>
-      <c r="AT30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15157072402503211</v>
-      </c>
-      <c r="AU30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15987118525739535</v>
-      </c>
-      <c r="AV30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.16401126107283703</v>
-      </c>
-      <c r="AW30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.1576572109571405</v>
-      </c>
-      <c r="AX30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15440647439725749</v>
-      </c>
-      <c r="AY30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15661971636190025</v>
-      </c>
-      <c r="AZ30" s="10">
-        <f t="shared" si="195"/>
+      <c r="BH30" s="10">
+        <f t="shared" si="194"/>
         <v>0.15</v>
       </c>
-      <c r="BA30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15</v>
-      </c>
-      <c r="BB30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15</v>
-      </c>
-      <c r="BC30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15</v>
-      </c>
-      <c r="BD30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.15</v>
-      </c>
-      <c r="BE30" s="10">
-        <f t="shared" si="195"/>
-        <v>0.14999999999999997</v>
-      </c>
-      <c r="BF30" s="10">
-        <f t="shared" ref="BF30:BI30" si="196">BF8/BF5</f>
-        <v>0.15</v>
-      </c>
-      <c r="BG30" s="10">
-        <f t="shared" si="196"/>
-        <v>0.15</v>
-      </c>
-      <c r="BH30" s="10">
-        <f t="shared" si="196"/>
-        <v>0.15</v>
-      </c>
       <c r="BI30" s="10">
-        <f t="shared" si="196"/>
+        <f t="shared" si="194"/>
         <v>0.15</v>
       </c>
       <c r="BK30" t="s">
@@ -7884,212 +7856,212 @@
         <v>0.4057291666666667</v>
       </c>
       <c r="H31" s="10">
-        <f t="shared" ref="H31:V31" si="197">H9/D9-1</f>
+        <f t="shared" ref="H31:V31" si="195">H9/D9-1</f>
         <v>0.30148048452220721</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.33239209358612354</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.42761627906976751</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>1.9370137087810302</v>
       </c>
       <c r="L31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>2.1247845570492934</v>
       </c>
       <c r="M31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>1.7853466545564638</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.98330278965587459</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.17635927841554189</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.14594594594594601</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.19304347826086965</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.23706365503080074</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.33919571045576413</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.33529072006160954</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.310131195335277</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="197"/>
+        <f t="shared" si="195"/>
         <v>0.27089385011204259</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" ref="W31" si="198">W9/S9-1</f>
+        <f t="shared" ref="W31" si="196">W9/S9-1</f>
         <v>0.18850096092248569</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" ref="X31" si="199">X9/T9-1</f>
+        <f t="shared" ref="X31" si="197">X9/T9-1</f>
         <v>0.3028620863672411</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" ref="Y31" si="200">Y9/U9-1</f>
+        <f t="shared" ref="Y31" si="198">Y9/U9-1</f>
         <v>0.35500695410292082</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" ref="Z31" si="201">Z9/V9-1</f>
+        <f t="shared" ref="Z31" si="199">Z9/V9-1</f>
         <v>0.35923724939593815</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" ref="AA31" si="202">AA9/W9-1</f>
+        <f t="shared" ref="AA31" si="200">AA9/W9-1</f>
         <v>0.37784665139469076</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" ref="AB31" si="203">AB9/X9-1</f>
+        <f t="shared" ref="AB31" si="201">AB9/X9-1</f>
         <v>0.21353474988933163</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" ref="AC31" si="204">AC9/Y9-1</f>
+        <f t="shared" ref="AC31" si="202">AC9/Y9-1</f>
         <v>8.8170387477546797E-2</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" ref="AD31" si="205">AD9/Z9-1</f>
+        <f t="shared" ref="AD31" si="203">AD9/Z9-1</f>
         <v>5.880657249927923E-2</v>
       </c>
       <c r="AE31" s="10">
-        <f t="shared" ref="AE31" si="206">AE9/AA9-1</f>
+        <f t="shared" ref="AE31" si="204">AE9/AA9-1</f>
         <v>-1.2713936430317485E-3</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" ref="AF31" si="207">AF9/AB9-1</f>
+        <f t="shared" ref="AF31" si="205">AF9/AB9-1</f>
         <v>1.7007888377182923E-2</v>
       </c>
       <c r="AG31" s="10">
-        <f t="shared" ref="AG31" si="208">AG9/AC9-1</f>
+        <f t="shared" ref="AG31" si="206">AG9/AC9-1</f>
         <v>4.9143989058152204E-2</v>
       </c>
       <c r="AH31" s="10">
-        <f t="shared" ref="AH31" si="209">AH9/AD9-1</f>
+        <f t="shared" ref="AH31" si="207">AH9/AD9-1</f>
         <v>6.9561666212905049E-2</v>
       </c>
       <c r="AI31" s="10">
-        <f t="shared" ref="AI31" si="210">AI9/AE9-1</f>
+        <f t="shared" ref="AI31" si="208">AI9/AE9-1</f>
         <v>0.12583235409322358</v>
       </c>
       <c r="AJ31" s="10">
-        <f t="shared" ref="AJ31" si="211">AJ9/AF9-1</f>
-        <v>9.000000000000008E-2</v>
+        <f t="shared" ref="AJ31" si="209">AJ9/AF9-1</f>
+        <v>0.21798780487804881</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" ref="AK31" si="212">AK9/AG9-1</f>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" ref="AK31" si="210">AK9/AG9-1</f>
+        <v>0.24</v>
       </c>
       <c r="AL31" s="10">
-        <f t="shared" ref="AL31" si="213">AL9/AH9-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AL31" si="211">AL9/AH9-1</f>
+        <v>0.19999999999999996</v>
       </c>
       <c r="AN31" s="10"/>
       <c r="AO31" s="10">
-        <f t="shared" ref="AO31:BE31" si="214">AO9/AN9-1</f>
+        <f t="shared" ref="AO31:BE31" si="212">AO9/AN9-1</f>
         <v>0.21283471837488466</v>
       </c>
       <c r="AP31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>0.37666539779215835</v>
       </c>
       <c r="AQ31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>0.3919535462463708</v>
       </c>
       <c r="AR31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>0.37206992451330945</v>
       </c>
       <c r="AS31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>1.6011292891269728</v>
       </c>
       <c r="AT31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>0.18941333630190349</v>
       </c>
       <c r="AU31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>0.31152604239786608</v>
       </c>
       <c r="AV31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>0.3061621351602084</v>
       </c>
       <c r="AW31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>0.16949175692841445</v>
       </c>
       <c r="AX31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
         <v>3.4126743126766446E-2</v>
       </c>
       <c r="AY31" s="10">
-        <f t="shared" si="214"/>
-        <v>8.510469371160112E-2</v>
+        <f t="shared" si="212"/>
+        <v>0.19747244307914702</v>
       </c>
       <c r="AZ31" s="10">
-        <f t="shared" si="214"/>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" si="212"/>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="BA31" s="10">
-        <f t="shared" si="214"/>
+        <f t="shared" si="212"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BB31" s="10">
+        <f t="shared" si="212"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BB31" s="10">
-        <f t="shared" si="214"/>
+      <c r="BC31" s="10">
+        <f t="shared" si="212"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC31" s="10">
-        <f t="shared" si="214"/>
+      <c r="BD31" s="10">
+        <f t="shared" si="212"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD31" s="10">
-        <f t="shared" si="214"/>
+      <c r="BE31" s="10">
+        <f t="shared" si="212"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE31" s="10">
-        <f t="shared" si="214"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BF31" s="10">
-        <f t="shared" ref="BF31" si="215">BF9/BE9-1</f>
+        <f t="shared" ref="BF31" si="213">BF9/BE9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG31" s="10">
-        <f t="shared" ref="BG31" si="216">BG9/BF9-1</f>
+        <f t="shared" ref="BG31" si="214">BG9/BF9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH31" s="10">
-        <f t="shared" ref="BH31" si="217">BH9/BG9-1</f>
+        <f t="shared" ref="BH31" si="215">BH9/BG9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI31" s="10">
-        <f t="shared" ref="BI31" si="218">BI9/BH9-1</f>
+        <f t="shared" ref="BI31" si="216">BI9/BH9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK31" t="s">
@@ -8097,7 +8069,7 @@
       </c>
       <c r="BL31" s="4">
         <f>NPV(BL30,AX21:EW21)</f>
-        <v>2050134.9840692843</v>
+        <v>2269554.1773097329</v>
       </c>
     </row>
     <row r="32" spans="2:153" x14ac:dyDescent="0.3">
@@ -8105,19 +8077,19 @@
         <v>56</v>
       </c>
       <c r="C32" s="10">
-        <f t="shared" ref="C32:F32" si="219">C10/C5</f>
+        <f t="shared" ref="C32:F32" si="217">C10/C5</f>
         <v>0.13476507812062496</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="217"/>
         <v>0.14619944671321303</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="217"/>
         <v>0.13588149231894661</v>
       </c>
       <c r="F32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="217"/>
         <v>0.10444477527996957</v>
       </c>
       <c r="G32" s="10">
@@ -8125,215 +8097,215 @@
         <v>0.13242035970377336</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:V32" si="220">H10/H5</f>
+        <f t="shared" ref="H32:V32" si="218">H10/H5</f>
         <v>0.13703059410808152</v>
       </c>
       <c r="I32" s="10">
+        <f t="shared" si="218"/>
+        <v>0.12659078054298642</v>
+      </c>
+      <c r="J32" s="10">
+        <f t="shared" si="218"/>
+        <v>0.10595029219568131</v>
+      </c>
+      <c r="K32" s="10">
+        <f t="shared" si="218"/>
+        <v>6.137353433835846E-2</v>
+      </c>
+      <c r="L32" s="10">
+        <f t="shared" si="218"/>
+        <v>6.767711816289193E-2</v>
+      </c>
+      <c r="M32" s="10">
+        <f t="shared" si="218"/>
+        <v>6.7904145410897246E-2</v>
+      </c>
+      <c r="N32" s="10">
+        <f t="shared" si="218"/>
+        <v>7.0587966192801679E-2</v>
+      </c>
+      <c r="O32" s="10">
+        <f t="shared" si="218"/>
+        <v>6.3987700789906163E-2</v>
+      </c>
+      <c r="P32" s="10">
+        <f t="shared" si="218"/>
+        <v>4.8868544178513586E-2</v>
+      </c>
+      <c r="Q32" s="10">
+        <f t="shared" si="218"/>
+        <v>5.6518799729575124E-2</v>
+      </c>
+      <c r="R32" s="10">
+        <f t="shared" si="218"/>
+        <v>5.8962207797379637E-2</v>
+      </c>
+      <c r="S32" s="10">
+        <f t="shared" si="218"/>
+        <v>5.7197884221972389E-2</v>
+      </c>
+      <c r="T32" s="10">
+        <f t="shared" si="218"/>
+        <v>6.6536964980544747E-2</v>
+      </c>
+      <c r="U32" s="10">
+        <f t="shared" si="218"/>
+        <v>7.2284590116593869E-2</v>
+      </c>
+      <c r="V32" s="10">
+        <f t="shared" si="218"/>
+        <v>7.8668529677175206E-2</v>
+      </c>
+      <c r="W32" s="10">
+        <f t="shared" ref="W32:AE32" si="219">W10/W5</f>
+        <v>7.1450654391810656E-2</v>
+      </c>
+      <c r="X32" s="10">
+        <f t="shared" si="219"/>
+        <v>8.3194483395747074E-2</v>
+      </c>
+      <c r="Y32" s="10">
+        <f t="shared" si="219"/>
+        <v>8.6655494449296225E-2</v>
+      </c>
+      <c r="Z32" s="10">
+        <f t="shared" si="219"/>
+        <v>8.5909224953754595E-2</v>
+      </c>
+      <c r="AA32" s="10">
+        <f t="shared" si="219"/>
+        <v>7.9869344681920251E-2</v>
+      </c>
+      <c r="AB32" s="10">
+        <f t="shared" si="219"/>
+        <v>7.9958030405631667E-2</v>
+      </c>
+      <c r="AC32" s="10">
+        <f t="shared" si="219"/>
+        <v>7.3740416401668965E-2</v>
+      </c>
+      <c r="AD32" s="10">
+        <f t="shared" si="219"/>
+        <v>7.5911532645724603E-2</v>
+      </c>
+      <c r="AE32" s="10">
+        <f t="shared" si="219"/>
+        <v>6.7418866397326138E-2</v>
+      </c>
+      <c r="AF32" s="10">
+        <f t="shared" ref="AF32:AH32" si="220">AF10/AF5</f>
+        <v>7.1038066726585886E-2</v>
+      </c>
+      <c r="AG32" s="10">
         <f t="shared" si="220"/>
-        <v>0.12659078054298642</v>
-      </c>
-      <c r="J32" s="10">
+        <v>6.6774926515480532E-2</v>
+      </c>
+      <c r="AH32" s="10">
         <f t="shared" si="220"/>
-        <v>0.10595029219568131</v>
-      </c>
-      <c r="K32" s="10">
-        <f t="shared" si="220"/>
-        <v>6.137353433835846E-2</v>
-      </c>
-      <c r="L32" s="10">
-        <f t="shared" si="220"/>
-        <v>6.767711816289193E-2</v>
-      </c>
-      <c r="M32" s="10">
-        <f t="shared" si="220"/>
-        <v>6.7904145410897246E-2</v>
-      </c>
-      <c r="N32" s="10">
-        <f t="shared" si="220"/>
-        <v>7.0587966192801679E-2</v>
-      </c>
-      <c r="O32" s="10">
-        <f t="shared" si="220"/>
-        <v>6.3987700789906163E-2</v>
-      </c>
-      <c r="P32" s="10">
-        <f t="shared" si="220"/>
-        <v>4.8868544178513586E-2</v>
-      </c>
-      <c r="Q32" s="10">
-        <f t="shared" si="220"/>
-        <v>5.6518799729575124E-2</v>
-      </c>
-      <c r="R32" s="10">
-        <f t="shared" si="220"/>
-        <v>5.8962207797379637E-2</v>
-      </c>
-      <c r="S32" s="10">
-        <f t="shared" si="220"/>
-        <v>5.7197884221972389E-2</v>
-      </c>
-      <c r="T32" s="10">
-        <f t="shared" si="220"/>
-        <v>6.6536964980544747E-2</v>
-      </c>
-      <c r="U32" s="10">
-        <f t="shared" si="220"/>
-        <v>7.2284590116593869E-2</v>
-      </c>
-      <c r="V32" s="10">
-        <f t="shared" si="220"/>
-        <v>7.8668529677175206E-2</v>
-      </c>
-      <c r="W32" s="10">
-        <f t="shared" ref="W32:AE32" si="221">W10/W5</f>
-        <v>7.1450654391810656E-2</v>
-      </c>
-      <c r="X32" s="10">
+        <v>6.9885831132316611E-2</v>
+      </c>
+      <c r="AI32" s="10">
+        <f t="shared" ref="AI32:AL32" si="221">AI10/AI5</f>
+        <v>6.2717210455652123E-2</v>
+      </c>
+      <c r="AJ32" s="10">
         <f t="shared" si="221"/>
-        <v>8.3194483395747074E-2</v>
-      </c>
-      <c r="Y32" s="10">
+        <v>6.80731297181906E-2</v>
+      </c>
+      <c r="AK32" s="10">
         <f t="shared" si="221"/>
-        <v>8.6655494449296225E-2</v>
-      </c>
-      <c r="Z32" s="10">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AL32" s="10">
         <f t="shared" si="221"/>
-        <v>8.5909224953754595E-2</v>
-      </c>
-      <c r="AA32" s="10">
-        <f t="shared" si="221"/>
-        <v>7.9869344681920251E-2</v>
-      </c>
-      <c r="AB32" s="10">
-        <f t="shared" si="221"/>
-        <v>7.9958030405631667E-2</v>
-      </c>
-      <c r="AC32" s="10">
-        <f t="shared" si="221"/>
-        <v>7.3740416401668965E-2</v>
-      </c>
-      <c r="AD32" s="10">
-        <f t="shared" si="221"/>
-        <v>7.5911532645724603E-2</v>
-      </c>
-      <c r="AE32" s="10">
-        <f t="shared" si="221"/>
-        <v>6.7418866397326138E-2</v>
-      </c>
-      <c r="AF32" s="10">
-        <f t="shared" ref="AF32:AH32" si="222">AF10/AF5</f>
-        <v>7.1038066726585886E-2</v>
-      </c>
-      <c r="AG32" s="10">
+        <v>6.5000000000000002E-2</v>
+      </c>
+      <c r="AN32" s="10">
+        <f t="shared" ref="AN32:BE32" si="222">AN10/AN5</f>
+        <v>0.10422753629702881</v>
+      </c>
+      <c r="AO32" s="10">
         <f t="shared" si="222"/>
-        <v>6.6774926515480532E-2</v>
-      </c>
-      <c r="AH32" s="10">
+        <v>0.11718969029774032</v>
+      </c>
+      <c r="AP32" s="10">
         <f t="shared" si="222"/>
-        <v>6.9885831132316611E-2</v>
-      </c>
-      <c r="AI32" s="10">
-        <f t="shared" ref="AI32:AL32" si="223">AI10/AI5</f>
-        <v>6.2717210455652123E-2</v>
-      </c>
-      <c r="AJ32" s="10">
+        <v>0.11828336532168517</v>
+      </c>
+      <c r="AQ32" s="10">
+        <f t="shared" si="222"/>
+        <v>0.12717438970910686</v>
+      </c>
+      <c r="AR32" s="10">
+        <f t="shared" si="222"/>
+        <v>0.12382400048091993</v>
+      </c>
+      <c r="AS32" s="10">
+        <f t="shared" si="222"/>
+        <v>6.7299534439366607E-2</v>
+      </c>
+      <c r="AT32" s="10">
+        <f t="shared" si="222"/>
+        <v>5.7011272742343237E-2</v>
+      </c>
+      <c r="AU32" s="10">
+        <f t="shared" si="222"/>
+        <v>6.9283686161993263E-2</v>
+      </c>
+      <c r="AV32" s="10">
+        <f t="shared" si="222"/>
+        <v>8.2177815219569517E-2</v>
+      </c>
+      <c r="AW32" s="10">
+        <f t="shared" si="222"/>
+        <v>7.7194081265168718E-2</v>
+      </c>
+      <c r="AX32" s="10">
+        <f t="shared" si="222"/>
+        <v>6.8824172086293947E-2</v>
+      </c>
+      <c r="AY32" s="10">
+        <f t="shared" si="222"/>
+        <v>6.5227549603972118E-2</v>
+      </c>
+      <c r="AZ32" s="10">
+        <f t="shared" si="222"/>
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="BA32" s="10">
+        <f t="shared" si="222"/>
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="BB32" s="10">
+        <f t="shared" si="222"/>
+        <v>0.06</v>
+      </c>
+      <c r="BC32" s="10">
+        <f t="shared" si="222"/>
+        <v>0.06</v>
+      </c>
+      <c r="BD32" s="10">
+        <f t="shared" si="222"/>
+        <v>0.06</v>
+      </c>
+      <c r="BE32" s="10">
+        <f t="shared" si="222"/>
+        <v>0.06</v>
+      </c>
+      <c r="BF32" s="10">
+        <f t="shared" ref="BF32:BI32" si="223">BF10/BF5</f>
+        <v>0.06</v>
+      </c>
+      <c r="BG32" s="10">
         <f t="shared" si="223"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="AK32" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="BH32" s="10">
         <f t="shared" si="223"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="AL32" s="10">
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="BI32" s="10">
         <f t="shared" si="223"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="AN32" s="10">
-        <f t="shared" ref="AN32:BE32" si="224">AN10/AN5</f>
-        <v>0.10422753629702881</v>
-      </c>
-      <c r="AO32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.11718969029774032</v>
-      </c>
-      <c r="AP32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.11828336532168517</v>
-      </c>
-      <c r="AQ32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.12717438970910686</v>
-      </c>
-      <c r="AR32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.12382400048091993</v>
-      </c>
-      <c r="AS32" s="10">
-        <f t="shared" si="224"/>
-        <v>6.7299534439366607E-2</v>
-      </c>
-      <c r="AT32" s="10">
-        <f t="shared" si="224"/>
-        <v>5.7011272742343237E-2</v>
-      </c>
-      <c r="AU32" s="10">
-        <f t="shared" si="224"/>
-        <v>6.9283686161993263E-2</v>
-      </c>
-      <c r="AV32" s="10">
-        <f t="shared" si="224"/>
-        <v>8.2177815219569517E-2</v>
-      </c>
-      <c r="AW32" s="10">
-        <f t="shared" si="224"/>
-        <v>7.7194081265168718E-2</v>
-      </c>
-      <c r="AX32" s="10">
-        <f t="shared" si="224"/>
-        <v>6.8824172086293947E-2</v>
-      </c>
-      <c r="AY32" s="10">
-        <f t="shared" si="224"/>
-        <v>6.4482658923057337E-2</v>
-      </c>
-      <c r="AZ32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.06</v>
-      </c>
-      <c r="BA32" s="10">
-        <f t="shared" si="224"/>
-        <v>6.0000000000000005E-2</v>
-      </c>
-      <c r="BB32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.06</v>
-      </c>
-      <c r="BC32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.06</v>
-      </c>
-      <c r="BD32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.06</v>
-      </c>
-      <c r="BE32" s="10">
-        <f t="shared" si="224"/>
-        <v>0.06</v>
-      </c>
-      <c r="BF32" s="10">
-        <f t="shared" ref="BF32:BI32" si="225">BF10/BF5</f>
-        <v>0.06</v>
-      </c>
-      <c r="BG32" s="10">
-        <f t="shared" si="225"/>
-        <v>0.06</v>
-      </c>
-      <c r="BH32" s="10">
-        <f t="shared" si="225"/>
-        <v>0.06</v>
-      </c>
-      <c r="BI32" s="10">
-        <f t="shared" si="225"/>
         <v>0.06</v>
       </c>
       <c r="BK32" t="s">
@@ -8357,212 +8329,212 @@
         <v>0.34213836477987414</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" ref="H33:V33" si="226">H11/D11-1</f>
+        <f t="shared" ref="H33:V33" si="224">H11/D11-1</f>
         <v>0.27116704805491998</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>8.4375000000000089E-2</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>6.9923371647509613E-2</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>9.9343955014058016E-2</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.14311431143114306</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.29490874159462055</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.26410026857654434</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.23785166240409206</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.24409448818897639</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.23738872403560829</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.39376770538243622</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.36845730027548207</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.36582278481012653</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.29076738609112707</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="226"/>
+        <f t="shared" si="224"/>
         <v>0.28302845528455278</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" ref="W33" si="227">W11/S11-1</f>
+        <f t="shared" ref="W33" si="225">W11/S11-1</f>
         <v>0.30548565676899853</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" ref="X33" si="228">X11/T11-1</f>
+        <f t="shared" ref="X33" si="226">X11/T11-1</f>
         <v>0.34522706209453191</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33" si="229">Y11/U11-1</f>
+        <f t="shared" ref="Y33" si="227">Y11/U11-1</f>
         <v>0.42173711100789602</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" ref="Z33" si="230">Z11/V11-1</f>
+        <f t="shared" ref="Z33" si="228">Z11/V11-1</f>
         <v>0.32000000000000006</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" ref="AA33" si="231">AA11/W11-1</f>
+        <f t="shared" ref="AA33" si="229">AA11/W11-1</f>
         <v>0.17309175019275247</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" ref="AB33" si="232">AB11/X11-1</f>
+        <f t="shared" ref="AB33" si="230">AB11/X11-1</f>
         <v>0.10299689975887016</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" ref="AC33" si="233">AC11/Y11-1</f>
+        <f t="shared" ref="AC33" si="231">AC11/Y11-1</f>
         <v>-0.16334531198954594</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" ref="AD33" si="234">AD11/Z11-1</f>
+        <f t="shared" ref="AD33" si="232">AD11/Z11-1</f>
         <v>-9.6909690969096962E-2</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" ref="AE33" si="235">AE11/AA11-1</f>
+        <f t="shared" ref="AE33" si="233">AE11/AA11-1</f>
         <v>-9.8915543871179734E-2</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" ref="AF33" si="236">AF11/AB11-1</f>
+        <f t="shared" ref="AF33" si="234">AF11/AB11-1</f>
         <v>-5.0281074328544673E-2</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" ref="AG33" si="237">AG11/AC11-1</f>
+        <f t="shared" ref="AG33" si="235">AG11/AC11-1</f>
         <v>5.9351815696993437E-2</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" ref="AH33" si="238">AH11/AD11-1</f>
+        <f t="shared" ref="AH33" si="236">AH11/AD11-1</f>
         <v>-4.8837209302325602E-2</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" ref="AI33" si="239">AI11/AE11-1</f>
+        <f t="shared" ref="AI33" si="237">AI11/AE11-1</f>
         <v>-4.1575492341356712E-2</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" ref="AJ33" si="240">AJ11/AF11-1</f>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" ref="AJ33" si="238">AJ11/AF11-1</f>
+        <v>-2.4991779020059224E-2</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" ref="AK33" si="241">AK11/AG11-1</f>
+        <f t="shared" ref="AK33" si="239">AK11/AG11-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" ref="AL33" si="242">AL11/AH11-1</f>
+        <f t="shared" ref="AL33" si="240">AL11/AH11-1</f>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="AN33" s="10"/>
       <c r="AO33" s="10">
-        <f t="shared" ref="AO33:BE33" si="243">AO11/AN11-1</f>
+        <f t="shared" ref="AO33:BE33" si="241">AO11/AN11-1</f>
         <v>0.12564432989690721</v>
       </c>
       <c r="AP33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>0.39210074413279905</v>
       </c>
       <c r="AQ33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>0.51027960526315796</v>
       </c>
       <c r="AR33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>0.18050639803974944</v>
       </c>
       <c r="AS33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>0.19995387453874547</v>
       </c>
       <c r="AT33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>0.28156832596578907</v>
       </c>
       <c r="AU33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>0.32318536292741462</v>
       </c>
       <c r="AV33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>0.34772753031848569</v>
       </c>
       <c r="AW33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>-6.3072912286603611E-3</v>
       </c>
       <c r="AX33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>-3.8676371022342559E-2</v>
       </c>
       <c r="AY33" s="10">
-        <f t="shared" si="243"/>
-        <v>1.2276608856413462E-2</v>
+        <f t="shared" si="241"/>
+        <v>2.9087067523549948E-3</v>
       </c>
       <c r="AZ33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BA33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BB33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BC33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE33" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="241"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF33" s="10">
-        <f t="shared" ref="BF33" si="244">BF11/BE11-1</f>
+        <f t="shared" ref="BF33" si="242">BF11/BE11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG33" s="10">
-        <f t="shared" ref="BG33" si="245">BG11/BF11-1</f>
+        <f t="shared" ref="BG33" si="243">BG11/BF11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH33" s="10">
-        <f t="shared" ref="BH33" si="246">BH11/BG11-1</f>
+        <f t="shared" ref="BH33" si="244">BH11/BG11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI33" s="10">
-        <f t="shared" ref="BI33" si="247">BI11/BH11-1</f>
+        <f t="shared" ref="BI33" si="245">BI11/BH11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK33" t="s">
@@ -8570,7 +8542,7 @@
       </c>
       <c r="BL33" s="4">
         <f>BL31+BL32</f>
-        <v>2098713.9840692841</v>
+        <v>2318133.1773097329</v>
       </c>
     </row>
     <row r="34" spans="2:64" x14ac:dyDescent="0.3">
@@ -8578,235 +8550,235 @@
         <v>47</v>
       </c>
       <c r="C34" s="10">
-        <f t="shared" ref="C34:V34" si="248">C19/C18</f>
+        <f t="shared" ref="C34:V34" si="246">C19/C18</f>
         <v>0.2402938090241343</v>
       </c>
       <c r="D34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.70120120120120122</v>
+      </c>
+      <c r="E34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.18354430379746836</v>
+      </c>
+      <c r="F34" s="10">
+        <f t="shared" si="246"/>
+        <v>8.5470085470085479E-3</v>
+      </c>
+      <c r="G34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.14979123173277661</v>
+      </c>
+      <c r="H34" s="10">
+        <f t="shared" si="246"/>
+        <v>2.8406909788867563E-2</v>
+      </c>
+      <c r="I34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.14985250737463127</v>
+      </c>
+      <c r="J34" s="10">
+        <f t="shared" si="246"/>
+        <v>9.7611940298507463E-2</v>
+      </c>
+      <c r="K34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.18995682799363781</v>
+      </c>
+      <c r="L34" s="10">
+        <f t="shared" si="246"/>
+        <v>8.8958116995500172E-2</v>
+      </c>
+      <c r="M34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.18768996960486323</v>
+      </c>
+      <c r="N34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.19393042190969653</v>
+      </c>
+      <c r="O34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.21992314513745195</v>
+      </c>
+      <c r="P34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.1581739270213792</v>
+      </c>
+      <c r="Q34" s="10">
+        <f t="shared" si="246"/>
+        <v>8.3565868703186955E-2</v>
+      </c>
+      <c r="R34" s="10">
+        <f t="shared" si="246"/>
+        <v>7.2891178364455897E-2</v>
+      </c>
+      <c r="S34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.20997273081417997</v>
+      </c>
+      <c r="T34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.1005327773917072</v>
+      </c>
+      <c r="U34" s="10">
+        <f t="shared" si="246"/>
+        <v>0.26767091541135574</v>
+      </c>
+      <c r="V34" s="10">
+        <f t="shared" si="246"/>
+        <v>4.0980313378867012E-2</v>
+      </c>
+      <c r="W34" s="10">
+        <f t="shared" ref="W34:AE34" si="247">W19/W18</f>
+        <v>0.27008547008547007</v>
+      </c>
+      <c r="X34" s="10">
+        <f t="shared" si="247"/>
+        <v>0.24010554089709762</v>
+      </c>
+      <c r="Y34" s="10">
+        <f t="shared" si="247"/>
+        <v>2.34375E-2</v>
+      </c>
+      <c r="Z34" s="10">
+        <f t="shared" si="247"/>
+        <v>1.2754677754677755</v>
+      </c>
+      <c r="AA34" s="10">
+        <f t="shared" si="247"/>
+        <v>0.23015294974508377</v>
+      </c>
+      <c r="AB34" s="10">
+        <f t="shared" si="247"/>
+        <v>0.10630702102340341</v>
+      </c>
+      <c r="AC34" s="10">
+        <f t="shared" si="247"/>
+        <v>0.18918697185987365</v>
+      </c>
+      <c r="AD34" s="10">
+        <f t="shared" si="247"/>
+        <v>0.22373228116323249</v>
+      </c>
+      <c r="AE34" s="10">
+        <f t="shared" si="247"/>
+        <v>0.1900177154740815</v>
+      </c>
+      <c r="AF34" s="10">
+        <f t="shared" ref="AF34:AH34" si="248">AF19/AF18</f>
+        <v>0.11590685470646113</v>
+      </c>
+      <c r="AG34" s="10">
         <f t="shared" si="248"/>
-        <v>0.70120120120120122</v>
-      </c>
-      <c r="E34" s="10">
+        <v>0.15002494871652713</v>
+      </c>
+      <c r="AH34" s="10">
         <f t="shared" si="248"/>
-        <v>0.18354430379746836</v>
-      </c>
-      <c r="F34" s="10">
-        <f t="shared" si="248"/>
-        <v>8.5470085470085479E-3</v>
-      </c>
-      <c r="G34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.14979123173277661</v>
-      </c>
-      <c r="H34" s="10">
-        <f t="shared" si="248"/>
-        <v>2.8406909788867563E-2</v>
-      </c>
-      <c r="I34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.14985250737463127</v>
-      </c>
-      <c r="J34" s="10">
-        <f t="shared" si="248"/>
-        <v>9.7611940298507463E-2</v>
-      </c>
-      <c r="K34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.18995682799363781</v>
-      </c>
-      <c r="L34" s="10">
-        <f t="shared" si="248"/>
-        <v>8.8958116995500172E-2</v>
-      </c>
-      <c r="M34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.18768996960486323</v>
-      </c>
-      <c r="N34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.19393042190969653</v>
-      </c>
-      <c r="O34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.21992314513745195</v>
-      </c>
-      <c r="P34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.1581739270213792</v>
-      </c>
-      <c r="Q34" s="10">
-        <f t="shared" si="248"/>
-        <v>8.3565868703186955E-2</v>
-      </c>
-      <c r="R34" s="10">
-        <f t="shared" si="248"/>
-        <v>7.2891178364455897E-2</v>
-      </c>
-      <c r="S34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.20997273081417997</v>
-      </c>
-      <c r="T34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.1005327773917072</v>
-      </c>
-      <c r="U34" s="10">
-        <f t="shared" si="248"/>
-        <v>0.26767091541135574</v>
-      </c>
-      <c r="V34" s="10">
-        <f t="shared" si="248"/>
-        <v>4.0980313378867012E-2</v>
-      </c>
-      <c r="W34" s="10">
-        <f t="shared" ref="W34:AE34" si="249">W19/W18</f>
-        <v>0.27008547008547007</v>
-      </c>
-      <c r="X34" s="10">
+        <v>0.10403150029084075</v>
+      </c>
+      <c r="AI34" s="10">
+        <f t="shared" ref="AI34:AL34" si="249">AI19/AI18</f>
+        <v>0.21001891231145348</v>
+      </c>
+      <c r="AJ34" s="10">
         <f t="shared" si="249"/>
-        <v>0.24010554089709762</v>
-      </c>
-      <c r="Y34" s="10">
+        <v>0.1283981397132857</v>
+      </c>
+      <c r="AK34" s="10">
         <f t="shared" si="249"/>
-        <v>2.34375E-2</v>
-      </c>
-      <c r="Z34" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AL34" s="10">
         <f t="shared" si="249"/>
-        <v>1.2754677754677755</v>
-      </c>
-      <c r="AA34" s="10">
-        <f t="shared" si="249"/>
-        <v>0.23015294974508377</v>
-      </c>
-      <c r="AB34" s="10">
-        <f t="shared" si="249"/>
-        <v>0.10630702102340341</v>
-      </c>
-      <c r="AC34" s="10">
-        <f t="shared" si="249"/>
-        <v>0.18918697185987365</v>
-      </c>
-      <c r="AD34" s="10">
-        <f t="shared" si="249"/>
-        <v>0.22373228116323249</v>
-      </c>
-      <c r="AE34" s="10">
-        <f t="shared" si="249"/>
-        <v>0.1900177154740815</v>
-      </c>
-      <c r="AF34" s="10">
-        <f t="shared" ref="AF34:AH34" si="250">AF19/AF18</f>
-        <v>0.11590685470646113</v>
-      </c>
-      <c r="AG34" s="10">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="AN34" s="10">
+        <f t="shared" ref="AN34:BE34" si="250">AN19/AN18</f>
+        <v>-1.5045045045045045</v>
+      </c>
+      <c r="AO34" s="10">
         <f t="shared" si="250"/>
-        <v>0.15002494871652713</v>
-      </c>
-      <c r="AH34" s="10">
+        <v>0.60586734693877553</v>
+      </c>
+      <c r="AP34" s="10">
         <f t="shared" si="250"/>
-        <v>0.10403150029084075</v>
-      </c>
-      <c r="AI34" s="10">
-        <f t="shared" ref="AI34:AL34" si="251">AI19/AI18</f>
-        <v>0.21001891231145348</v>
-      </c>
-      <c r="AJ34" s="10">
+        <v>0.36613566289825283</v>
+      </c>
+      <c r="AQ34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.20225899658523772</v>
+      </c>
+      <c r="AR34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.106207264008525</v>
+      </c>
+      <c r="AS34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.16980322003577816</v>
+      </c>
+      <c r="AT34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.1184134337000579</v>
+      </c>
+      <c r="AU34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.12557993237398757</v>
+      </c>
+      <c r="AV34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.54194743935309975</v>
+      </c>
+      <c r="AW34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.18957850733551668</v>
+      </c>
+      <c r="AX34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.13503075174162707</v>
+      </c>
+      <c r="AY34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.15469885944132447</v>
+      </c>
+      <c r="AZ34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.15</v>
+      </c>
+      <c r="BA34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.15</v>
+      </c>
+      <c r="BB34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.15</v>
+      </c>
+      <c r="BC34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.15</v>
+      </c>
+      <c r="BD34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.15</v>
+      </c>
+      <c r="BE34" s="10">
+        <f t="shared" si="250"/>
+        <v>0.15</v>
+      </c>
+      <c r="BF34" s="10">
+        <f t="shared" ref="BF34:BI34" si="251">BF19/BF18</f>
+        <v>0.15</v>
+      </c>
+      <c r="BG34" s="10">
         <f t="shared" si="251"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AK34" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="BH34" s="10">
         <f t="shared" si="251"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AL34" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="BI34" s="10">
         <f t="shared" si="251"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AN34" s="10">
-        <f t="shared" ref="AN34:BE34" si="252">AN19/AN18</f>
-        <v>-1.5045045045045045</v>
-      </c>
-      <c r="AO34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.60586734693877553</v>
-      </c>
-      <c r="AP34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.36613566289825283</v>
-      </c>
-      <c r="AQ34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.20225899658523772</v>
-      </c>
-      <c r="AR34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.106207264008525</v>
-      </c>
-      <c r="AS34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.16980322003577816</v>
-      </c>
-      <c r="AT34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.1184134337000579</v>
-      </c>
-      <c r="AU34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.12557993237398757</v>
-      </c>
-      <c r="AV34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.54194743935309975</v>
-      </c>
-      <c r="AW34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.18957850733551668</v>
-      </c>
-      <c r="AX34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.13503075174162707</v>
-      </c>
-      <c r="AY34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.15768567597071112</v>
-      </c>
-      <c r="AZ34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.15</v>
-      </c>
-      <c r="BA34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.15</v>
-      </c>
-      <c r="BB34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.15</v>
-      </c>
-      <c r="BC34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.15</v>
-      </c>
-      <c r="BD34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.15</v>
-      </c>
-      <c r="BE34" s="10">
-        <f t="shared" si="252"/>
-        <v>0.15</v>
-      </c>
-      <c r="BF34" s="10">
-        <f t="shared" ref="BF34:BI34" si="253">BF19/BF18</f>
-        <v>0.15</v>
-      </c>
-      <c r="BG34" s="10">
-        <f t="shared" si="253"/>
-        <v>0.15</v>
-      </c>
-      <c r="BH34" s="10">
-        <f t="shared" si="253"/>
-        <v>0.15</v>
-      </c>
-      <c r="BI34" s="10">
-        <f t="shared" si="253"/>
         <v>0.15</v>
       </c>
       <c r="BK34" t="s">
@@ -8814,7 +8786,7 @@
       </c>
       <c r="BL34" s="3">
         <f>BL33/BE22</f>
-        <v>197.68603142960743</v>
+        <v>217.93110626207886</v>
       </c>
     </row>
     <row r="35" spans="2:64" x14ac:dyDescent="0.3">
@@ -8822,19 +8794,19 @@
         <v>58</v>
       </c>
       <c r="C35" s="10">
-        <f t="shared" ref="C35:F35" si="254">C21/C5</f>
+        <f t="shared" ref="C35:F35" si="252">C21/C5</f>
         <v>2.027216217729742E-2</v>
       </c>
       <c r="D35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="252"/>
         <v>5.1903570017125542E-3</v>
       </c>
       <c r="E35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="252"/>
         <v>5.8522311631309439E-3</v>
       </c>
       <c r="F35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="252"/>
         <v>3.0701536731014178E-2</v>
       </c>
       <c r="G35" s="10">
@@ -8842,223 +8814,223 @@
         <v>3.1914893617021274E-2</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" ref="H35:V35" si="255">H21/H5</f>
+        <f t="shared" ref="H35:V35" si="253">H21/H5</f>
         <v>4.791438187800174E-2</v>
       </c>
       <c r="I35" s="10">
+        <f t="shared" si="253"/>
+        <v>5.0958003393665158E-2</v>
+      </c>
+      <c r="J35" s="10">
+        <f t="shared" si="253"/>
+        <v>4.1819211693353411E-2</v>
+      </c>
+      <c r="K35" s="10">
+        <f t="shared" si="253"/>
+        <v>5.9648241206030149E-2</v>
+      </c>
+      <c r="L35" s="10">
+        <f t="shared" si="253"/>
+        <v>4.1401173427544007E-2</v>
+      </c>
+      <c r="M35" s="10">
+        <f t="shared" si="253"/>
+        <v>3.0493991226189964E-2</v>
+      </c>
+      <c r="N35" s="10">
+        <f t="shared" si="253"/>
+        <v>3.7375481775449755E-2</v>
+      </c>
+      <c r="O35" s="10">
+        <f t="shared" si="253"/>
+        <v>3.3597518952446587E-2</v>
+      </c>
+      <c r="P35" s="10">
+        <f t="shared" si="253"/>
+        <v>5.896841821126507E-2</v>
+      </c>
+      <c r="Q35" s="10">
+        <f t="shared" si="253"/>
+        <v>6.5848458058141351E-2</v>
+      </c>
+      <c r="R35" s="10">
+        <f t="shared" si="253"/>
+        <v>5.7520608498267692E-2</v>
+      </c>
+      <c r="S35" s="10">
+        <f t="shared" si="253"/>
+        <v>7.470650030409702E-2</v>
+      </c>
+      <c r="T35" s="10">
+        <f t="shared" si="253"/>
+        <v>6.8783162362928904E-2</v>
+      </c>
+      <c r="U35" s="10">
+        <f t="shared" si="253"/>
+        <v>2.8480669963541854E-2</v>
+      </c>
+      <c r="V35" s="10">
+        <f t="shared" si="253"/>
+        <v>0.1042339824760574</v>
+      </c>
+      <c r="W35" s="10">
+        <f t="shared" ref="W35:AE35" si="254">W21/W5</f>
+        <v>-3.3011576380062517E-2</v>
+      </c>
+      <c r="X35" s="10">
+        <f t="shared" si="254"/>
+        <v>-1.6727980599501788E-2</v>
+      </c>
+      <c r="Y35" s="10">
+        <f t="shared" si="254"/>
+        <v>2.2596203019645794E-2</v>
+      </c>
+      <c r="Z35" s="10">
+        <f t="shared" si="254"/>
+        <v>1.8632208251789495E-3</v>
+      </c>
+      <c r="AA35" s="10">
+        <f t="shared" si="254"/>
+        <v>2.4906170008951147E-2</v>
+      </c>
+      <c r="AB35" s="10">
+        <f t="shared" si="254"/>
+        <v>5.0229567728060844E-2</v>
+      </c>
+      <c r="AC35" s="10">
+        <f t="shared" si="254"/>
+        <v>6.9043841686293975E-2</v>
+      </c>
+      <c r="AD35" s="10">
+        <f t="shared" si="254"/>
+        <v>6.2508457822676972E-2</v>
+      </c>
+      <c r="AE35" s="10">
+        <f t="shared" si="254"/>
+        <v>7.2784743882271671E-2</v>
+      </c>
+      <c r="AF35" s="10">
+        <f t="shared" ref="AF35:AH35" si="255">AF21/AF5</f>
+        <v>9.1129026808220201E-2</v>
+      </c>
+      <c r="AG35" s="10">
         <f t="shared" si="255"/>
-        <v>5.0958003393665158E-2</v>
-      </c>
-      <c r="J35" s="10">
+        <v>9.6477148989469838E-2</v>
+      </c>
+      <c r="AH35" s="10">
         <f t="shared" si="255"/>
-        <v>4.1819211693353411E-2</v>
-      </c>
-      <c r="K35" s="10">
-        <f t="shared" si="255"/>
-        <v>5.9648241206030149E-2</v>
-      </c>
-      <c r="L35" s="10">
-        <f t="shared" si="255"/>
-        <v>4.1401173427544007E-2</v>
-      </c>
-      <c r="M35" s="10">
-        <f t="shared" si="255"/>
-        <v>3.0493991226189964E-2</v>
-      </c>
-      <c r="N35" s="10">
-        <f t="shared" si="255"/>
-        <v>3.7375481775449755E-2</v>
-      </c>
-      <c r="O35" s="10">
-        <f t="shared" si="255"/>
-        <v>3.3597518952446587E-2</v>
-      </c>
-      <c r="P35" s="10">
-        <f t="shared" si="255"/>
-        <v>5.896841821126507E-2</v>
-      </c>
-      <c r="Q35" s="10">
-        <f t="shared" si="255"/>
-        <v>6.5848458058141351E-2</v>
-      </c>
-      <c r="R35" s="10">
-        <f t="shared" si="255"/>
-        <v>5.7520608498267692E-2</v>
-      </c>
-      <c r="S35" s="10">
-        <f t="shared" si="255"/>
-        <v>7.470650030409702E-2</v>
-      </c>
-      <c r="T35" s="10">
-        <f t="shared" si="255"/>
-        <v>6.8783162362928904E-2</v>
-      </c>
-      <c r="U35" s="10">
-        <f t="shared" si="255"/>
-        <v>2.8480669963541854E-2</v>
-      </c>
-      <c r="V35" s="10">
-        <f t="shared" si="255"/>
-        <v>0.1042339824760574</v>
-      </c>
-      <c r="W35" s="10">
-        <f t="shared" ref="W35:AE35" si="256">W21/W5</f>
-        <v>-3.3011576380062517E-2</v>
-      </c>
-      <c r="X35" s="10">
+        <v>0.10652210956803272</v>
+      </c>
+      <c r="AI35" s="10">
+        <f t="shared" ref="AI35:AL35" si="256">AI21/AI5</f>
+        <v>0.1100233190078822</v>
+      </c>
+      <c r="AJ35" s="10">
         <f t="shared" si="256"/>
-        <v>-1.6727980599501788E-2</v>
-      </c>
-      <c r="Y35" s="10">
+        <v>0.10831117100571251</v>
+      </c>
+      <c r="AK35" s="10">
         <f t="shared" si="256"/>
-        <v>2.2596203019645794E-2</v>
-      </c>
-      <c r="Z35" s="10">
+        <v>8.914830009953971E-2</v>
+      </c>
+      <c r="AL35" s="10">
         <f t="shared" si="256"/>
-        <v>1.8632208251789495E-3</v>
-      </c>
-      <c r="AA35" s="10">
-        <f t="shared" si="256"/>
-        <v>2.4906170008951147E-2</v>
-      </c>
-      <c r="AB35" s="10">
-        <f t="shared" si="256"/>
-        <v>5.0229567728060844E-2</v>
-      </c>
-      <c r="AC35" s="10">
-        <f t="shared" si="256"/>
-        <v>6.9043841686293975E-2</v>
-      </c>
-      <c r="AD35" s="10">
-        <f t="shared" si="256"/>
-        <v>6.2508457822676972E-2</v>
-      </c>
-      <c r="AE35" s="10">
-        <f t="shared" si="256"/>
-        <v>7.2784743882271671E-2</v>
-      </c>
-      <c r="AF35" s="10">
-        <f t="shared" ref="AF35:AH35" si="257">AF21/AF5</f>
-        <v>9.1129026808220201E-2</v>
-      </c>
-      <c r="AG35" s="10">
+        <v>0.10949180423517793</v>
+      </c>
+      <c r="AN35" s="10">
+        <f t="shared" ref="AN35:BE35" si="257">AN21/AN5</f>
+        <v>-2.7082303231896437E-3</v>
+      </c>
+      <c r="AO35" s="10">
         <f t="shared" si="257"/>
-        <v>9.6477148989469838E-2</v>
-      </c>
-      <c r="AH35" s="10">
+        <v>5.5697811337681999E-3</v>
+      </c>
+      <c r="AP35" s="10">
         <f t="shared" si="257"/>
-        <v>0.10652210956803272</v>
-      </c>
-      <c r="AI35" s="10">
-        <f t="shared" ref="AI35:AL35" si="258">AI21/AI5</f>
-        <v>0.1100233190078822</v>
-      </c>
-      <c r="AJ35" s="10">
-        <f t="shared" si="258"/>
-        <v>9.1869053883544508E-2</v>
-      </c>
-      <c r="AK35" s="10">
-        <f t="shared" si="258"/>
-        <v>0.10333003434389727</v>
-      </c>
-      <c r="AL35" s="10">
-        <f t="shared" si="258"/>
-        <v>0.11350818038090509</v>
-      </c>
-      <c r="AN35" s="10">
-        <f t="shared" ref="AN35:BE35" si="259">AN21/AN5</f>
-        <v>-2.7082303231896437E-3</v>
-      </c>
-      <c r="AO35" s="10">
-        <f t="shared" si="259"/>
-        <v>5.5697811337681999E-3</v>
-      </c>
-      <c r="AP35" s="10">
-        <f t="shared" si="259"/>
         <v>1.7435490157147373E-2</v>
       </c>
       <c r="AQ35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>1.7052162864178651E-2</v>
       </c>
       <c r="AR35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>4.3252736305590261E-2</v>
       </c>
       <c r="AS35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>4.1308703060722513E-2</v>
       </c>
       <c r="AT35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>5.5252496995316841E-2</v>
       </c>
       <c r="AU35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>7.1014128755145567E-2</v>
       </c>
       <c r="AV35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>-5.2958950004183018E-3</v>
       </c>
       <c r="AW35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>5.2932835755978319E-2</v>
       </c>
       <c r="AX35" s="10">
-        <f t="shared" si="259"/>
+        <f t="shared" si="257"/>
         <v>9.2871171971866534E-2</v>
       </c>
       <c r="AY35" s="10">
-        <f t="shared" si="259"/>
-        <v>0.10515795613237959</v>
+        <f t="shared" si="257"/>
+        <v>0.10426420773602942</v>
       </c>
       <c r="AZ35" s="10">
-        <f t="shared" si="259"/>
-        <v>0.12256421472412569</v>
+        <f t="shared" si="257"/>
+        <v>0.1197911652024693</v>
       </c>
       <c r="BA35" s="10">
-        <f t="shared" si="259"/>
-        <v>0.12671712225239701</v>
+        <f t="shared" si="257"/>
+        <v>0.13155817217561713</v>
       </c>
       <c r="BB35" s="10">
-        <f t="shared" si="259"/>
-        <v>0.13007659491982979</v>
+        <f t="shared" si="257"/>
+        <v>0.1425192451013447</v>
       </c>
       <c r="BC35" s="10">
-        <f t="shared" si="259"/>
-        <v>0.13160650384000341</v>
+        <f t="shared" si="257"/>
+        <v>0.14418735867305338</v>
       </c>
       <c r="BD35" s="10">
-        <f t="shared" si="259"/>
-        <v>0.13257335961263461</v>
+        <f t="shared" si="257"/>
+        <v>0.14520856181688535</v>
       </c>
       <c r="BE35" s="10">
-        <f t="shared" si="259"/>
-        <v>0.13285552904465028</v>
+        <f t="shared" si="257"/>
+        <v>0.14546468117016378</v>
       </c>
       <c r="BF35" s="10">
         <f>BJ21/BF5</f>
-        <v>0.13721330021770192</v>
+        <v>0.15009178501458542</v>
       </c>
       <c r="BG35" s="10">
-        <f t="shared" ref="BG35:BI35" si="260">BG21/BG5</f>
-        <v>0.13401480067190805</v>
+        <f t="shared" ref="BG35:BI35" si="258">BG21/BG5</f>
+        <v>0.14667411795286345</v>
       </c>
       <c r="BH35" s="10">
-        <f t="shared" si="260"/>
-        <v>0.13426382714395338</v>
+        <f t="shared" si="258"/>
+        <v>0.14690678668579016</v>
       </c>
       <c r="BI35" s="10">
-        <f t="shared" si="260"/>
-        <v>0.13452310844034301</v>
+        <f t="shared" si="258"/>
+        <v>0.14714909880811181</v>
       </c>
       <c r="BK35" t="s">
         <v>67</v>
       </c>
       <c r="BL35" s="3">
         <f>Main!D3</f>
-        <v>204.88</v>
+        <v>229.8</v>
       </c>
     </row>
     <row r="36" spans="2:64" x14ac:dyDescent="0.3">
@@ -9067,7 +9039,7 @@
       </c>
       <c r="BL36" s="13">
         <f>BL34/BL35-1</f>
-        <v>-3.5113083611834073E-2</v>
+        <v>-5.1648797815148639E-2</v>
       </c>
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.3">

--- a/Financial Analysis/AMZN.xlsx
+++ b/Financial Analysis/AMZN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1628EEFC-1879-4B65-9E09-C78E9BE743B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD34FDC-F226-4C2B-B318-3C2DA63574EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EA1D195A-C8DC-4C80-AD05-94F317AC85A7}"/>
   </bookViews>
@@ -289,7 +289,7 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Fairly valued</t>
+    <t>Slightly overvalued</t>
   </si>
 </sst>
 </file>
@@ -402,14 +402,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
@@ -426,7 +426,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22837140" y="0"/>
+          <a:off x="23461980" y="0"/>
           <a:ext cx="0" cy="6743700"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -877,17 +877,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>229.8</v>
+        <v>250.9</v>
       </c>
       <c r="E3" s="2">
-        <v>45887</v>
+        <v>45961</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45887</v>
+        <v>45961</v>
       </c>
       <c r="G3" s="2">
-        <v>45961</v>
+        <v>46051</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -906,10 +906,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -929,7 +930,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>2444382.6</v>
+        <v>2678106.6</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -954,7 +955,7 @@
         <v>101202</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -973,10 +974,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
+        <f>52623</f>
         <v>52623</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -1016,7 +1018,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>2395803.6</v>
+        <v>2629527.6</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1752,12 +1754,11 @@
         <v>68246</v>
       </c>
       <c r="AK3" s="4">
-        <f>AG3*1.05</f>
-        <v>70981.05</v>
+        <v>74058</v>
       </c>
       <c r="AL3" s="4">
-        <f>AH3*1.04</f>
-        <v>85515.040000000008</v>
+        <f>AH3*1.08</f>
+        <v>88804.08</v>
       </c>
       <c r="AN3" s="4">
         <v>70080</v>
@@ -1802,47 +1803,47 @@
       </c>
       <c r="AY3" s="4">
         <f>SUM(AI3:AL3)</f>
-        <v>288712.08999999997</v>
+        <v>295078.08</v>
       </c>
       <c r="AZ3" s="4">
         <f>AY3*1.05</f>
-        <v>303147.69449999998</v>
+        <v>309831.98400000005</v>
       </c>
       <c r="BA3" s="4">
         <f>AZ3*1.04</f>
-        <v>315273.60227999999</v>
+        <v>322225.26336000004</v>
       </c>
       <c r="BB3" s="4">
         <f>BA3*1.03</f>
-        <v>324731.81034839997</v>
+        <v>331892.02126080007</v>
       </c>
       <c r="BC3" s="4">
         <f t="shared" ref="BC3:BD3" si="0">BB3*1.02</f>
-        <v>331226.44655536796</v>
+        <v>338529.86168601608</v>
       </c>
       <c r="BD3" s="4">
         <f t="shared" si="0"/>
-        <v>337850.97548647533</v>
+        <v>345300.45891973644</v>
       </c>
       <c r="BE3" s="4">
         <f>BD3*1.02</f>
-        <v>344607.99499620486</v>
+        <v>352206.46809813118</v>
       </c>
       <c r="BF3" s="4">
         <f>BE3*1.01</f>
-        <v>348054.07494616689</v>
+        <v>355728.53277911252</v>
       </c>
       <c r="BG3" s="4">
         <f t="shared" ref="BG3:BI3" si="1">BF3*1.01</f>
-        <v>351534.61569562857</v>
+        <v>359285.81810690364</v>
       </c>
       <c r="BH3" s="4">
         <f t="shared" si="1"/>
-        <v>355049.96185258485</v>
+        <v>362878.67628797266</v>
       </c>
       <c r="BI3" s="4">
         <f t="shared" si="1"/>
-        <v>358600.4614711107</v>
+        <v>366507.46305085241</v>
       </c>
     </row>
     <row r="4" spans="2:61" x14ac:dyDescent="0.3">
@@ -1952,8 +1953,7 @@
         <v>99456</v>
       </c>
       <c r="AK4" s="4">
-        <f>AG4*1.14</f>
-        <v>104054.63999999998</v>
+        <v>106111</v>
       </c>
       <c r="AL4" s="4">
         <f>AH4*1.13</f>
@@ -2002,47 +2002,47 @@
       </c>
       <c r="AY4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>414497.22</v>
+        <v>416553.57999999996</v>
       </c>
       <c r="AZ4" s="4">
         <f>AY4*1.09</f>
-        <v>451801.96980000002</v>
+        <v>454043.40220000001</v>
       </c>
       <c r="BA4" s="4">
         <f>AZ4*1.08</f>
-        <v>487946.12738400005</v>
+        <v>490366.87437600002</v>
       </c>
       <c r="BB4" s="4">
         <f>BA4*1.06</f>
-        <v>517222.8950270401</v>
+        <v>519788.88683856005</v>
       </c>
       <c r="BC4" s="4">
         <f>BB4*1.04</f>
-        <v>537911.81082812173</v>
+        <v>540580.44231210242</v>
       </c>
       <c r="BD4" s="4">
         <f t="shared" ref="BD4" si="2">BC4*1.03</f>
-        <v>554049.16515296535</v>
+        <v>556797.85558146553</v>
       </c>
       <c r="BE4" s="4">
         <f>BD4*1.02</f>
-        <v>565130.1484560247</v>
+        <v>567933.81269309483</v>
       </c>
       <c r="BF4" s="4">
         <f t="shared" ref="BF4" si="3">BE4*1.02</f>
-        <v>576432.75142514519</v>
+        <v>579292.4889469567</v>
       </c>
       <c r="BG4" s="4">
         <f>BF4*1.01</f>
-        <v>582197.07893939666</v>
+        <v>585085.41383642622</v>
       </c>
       <c r="BH4" s="4">
         <f t="shared" ref="BH4:BI4" si="4">BG4*1.01</f>
-        <v>588019.04972879065</v>
+        <v>590936.26797479053</v>
       </c>
       <c r="BI4" s="4">
         <f t="shared" si="4"/>
-        <v>593899.24022607855</v>
+        <v>596845.6306545384</v>
       </c>
     </row>
     <row r="5" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2187,11 +2187,11 @@
       </c>
       <c r="AK5" s="8">
         <f t="shared" si="14"/>
-        <v>175035.69</v>
+        <v>180169</v>
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="14"/>
-        <v>204804.62</v>
+        <v>208093.65999999997</v>
       </c>
       <c r="AN5" s="8">
         <f t="shared" ref="AN5:AU5" si="15">AN3+AN4</f>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="AY5" s="8">
         <f t="shared" si="16"/>
-        <v>703209.30999999994</v>
+        <v>711631.65999999992</v>
       </c>
       <c r="AZ5" s="8">
         <f t="shared" si="16"/>
-        <v>754949.66430000006</v>
+        <v>763875.38620000007</v>
       </c>
       <c r="BA5" s="8">
         <f t="shared" si="16"/>
-        <v>803219.72966399998</v>
+        <v>812592.13773600012</v>
       </c>
       <c r="BB5" s="8">
         <f t="shared" si="16"/>
-        <v>841954.70537544007</v>
+        <v>851680.90809936007</v>
       </c>
       <c r="BC5" s="8">
         <f t="shared" si="16"/>
-        <v>869138.25738348975</v>
+        <v>879110.3039981185</v>
       </c>
       <c r="BD5" s="8">
         <f t="shared" si="16"/>
-        <v>891900.14063944062</v>
+        <v>902098.31450120197</v>
       </c>
       <c r="BE5" s="8">
         <f t="shared" si="16"/>
-        <v>909738.14345222956</v>
+        <v>920140.28079122608</v>
       </c>
       <c r="BF5" s="8">
         <f t="shared" ref="BF5:BI5" si="18">BF3+BF4</f>
-        <v>924486.82637131214</v>
+        <v>935021.02172606927</v>
       </c>
       <c r="BG5" s="8">
         <f t="shared" si="18"/>
-        <v>933731.69463502523</v>
+        <v>944371.2319433298</v>
       </c>
       <c r="BH5" s="8">
         <f t="shared" si="18"/>
-        <v>943069.0115813755</v>
+        <v>953814.94426276325</v>
       </c>
       <c r="BI5" s="8">
         <f t="shared" si="18"/>
-        <v>952499.70169718924</v>
+        <v>963353.09370539081</v>
       </c>
     </row>
     <row r="6" spans="2:61" x14ac:dyDescent="0.3">
@@ -2389,12 +2389,11 @@
         <v>80809</v>
       </c>
       <c r="AK6" s="4">
-        <f t="shared" ref="AK6" si="19">AK5-AK7</f>
-        <v>87517.845000000001</v>
+        <v>88670</v>
       </c>
       <c r="AL6" s="4">
         <f>AL5-AL7</f>
-        <v>104450.35619999999</v>
+        <v>106127.76659999999</v>
       </c>
       <c r="AN6" s="4">
         <v>62752</v>
@@ -2439,47 +2438,47 @@
       </c>
       <c r="AY6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>349753.20120000001</v>
+        <v>352582.76659999997</v>
       </c>
       <c r="AZ6" s="4">
-        <f t="shared" ref="AZ6:BE6" si="20">AZ5-AZ7</f>
-        <v>369925.33550700004</v>
+        <f t="shared" ref="AZ6:BE6" si="19">AZ5-AZ7</f>
+        <v>374298.93923800002</v>
       </c>
       <c r="BA6" s="4">
+        <f t="shared" si="19"/>
+        <v>390044.22611328005</v>
+      </c>
+      <c r="BB6" s="4">
+        <f t="shared" si="19"/>
+        <v>400290.02680669923</v>
+      </c>
+      <c r="BC6" s="4">
+        <f t="shared" si="19"/>
+        <v>413181.84287911566</v>
+      </c>
+      <c r="BD6" s="4">
+        <f t="shared" si="19"/>
+        <v>423986.20781556488</v>
+      </c>
+      <c r="BE6" s="4">
+        <f t="shared" si="19"/>
+        <v>432465.93197187624</v>
+      </c>
+      <c r="BF6" s="4">
+        <f t="shared" ref="BF6:BI6" si="20">BF5-BF7</f>
+        <v>439459.88021125254</v>
+      </c>
+      <c r="BG6" s="4">
         <f t="shared" si="20"/>
-        <v>385545.47023871995</v>
-      </c>
-      <c r="BB6" s="4">
+        <v>443854.47901336499</v>
+      </c>
+      <c r="BH6" s="4">
         <f t="shared" si="20"/>
-        <v>395718.71152645681</v>
-      </c>
-      <c r="BC6" s="4">
+        <v>448293.02380349871</v>
+      </c>
+      <c r="BI6" s="4">
         <f t="shared" si="20"/>
-        <v>408494.98097024014</v>
-      </c>
-      <c r="BD6" s="4">
-        <f t="shared" si="20"/>
-        <v>419193.06610053708</v>
-      </c>
-      <c r="BE6" s="4">
-        <f t="shared" si="20"/>
-        <v>427576.92742254789</v>
-      </c>
-      <c r="BF6" s="4">
-        <f t="shared" ref="BF6:BI6" si="21">BF5-BF7</f>
-        <v>434508.8083945167</v>
-      </c>
-      <c r="BG6" s="4">
-        <f t="shared" si="21"/>
-        <v>438853.89647846186</v>
-      </c>
-      <c r="BH6" s="4">
-        <f t="shared" si="21"/>
-        <v>443242.43544324645</v>
-      </c>
-      <c r="BI6" s="4">
-        <f t="shared" si="21"/>
-        <v>447674.85979767895</v>
+        <v>452775.95404153364</v>
       </c>
     </row>
     <row r="7" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2487,236 +2486,236 @@
         <v>32</v>
       </c>
       <c r="C7" s="8">
-        <f t="shared" ref="C7:T7" si="22">C5-C6</f>
+        <f t="shared" ref="C7:T7" si="21">C5-C6</f>
         <v>13274</v>
       </c>
       <c r="D7" s="8">
+        <f t="shared" si="21"/>
+        <v>14504</v>
+      </c>
+      <c r="E7" s="8">
+        <f t="shared" si="21"/>
+        <v>16195</v>
+      </c>
+      <c r="F7" s="8">
+        <f t="shared" si="21"/>
+        <v>21959</v>
+      </c>
+      <c r="G7" s="8">
+        <f t="shared" si="21"/>
+        <v>20307</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="21"/>
+        <v>22254</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="21"/>
+        <v>23573</v>
+      </c>
+      <c r="J7" s="8">
+        <f t="shared" si="21"/>
+        <v>27597</v>
+      </c>
+      <c r="K7" s="8">
+        <f t="shared" si="21"/>
+        <v>25780</v>
+      </c>
+      <c r="L7" s="8">
+        <f t="shared" si="21"/>
+        <v>27067</v>
+      </c>
+      <c r="M7" s="8">
+        <f t="shared" si="21"/>
+        <v>28679</v>
+      </c>
+      <c r="N7" s="8">
+        <f t="shared" si="21"/>
+        <v>33460</v>
+      </c>
+      <c r="O7" s="8">
+        <f t="shared" si="21"/>
+        <v>31195</v>
+      </c>
+      <c r="P7" s="8">
+        <f t="shared" si="21"/>
+        <v>36252</v>
+      </c>
+      <c r="Q7" s="8">
+        <f t="shared" si="21"/>
+        <v>39039</v>
+      </c>
+      <c r="R7" s="8">
+        <f t="shared" si="21"/>
+        <v>46271</v>
+      </c>
+      <c r="S7" s="8">
+        <f t="shared" si="21"/>
+        <v>46115</v>
+      </c>
+      <c r="T7" s="8">
+        <f t="shared" si="21"/>
+        <v>48904</v>
+      </c>
+      <c r="U7" s="8">
+        <f t="shared" ref="U7:V7" si="22">U5-U6</f>
+        <v>47882</v>
+      </c>
+      <c r="V7" s="8">
         <f t="shared" si="22"/>
-        <v>14504</v>
-      </c>
-      <c r="E7" s="8">
-        <f t="shared" si="22"/>
-        <v>16195</v>
-      </c>
-      <c r="F7" s="8">
-        <f t="shared" si="22"/>
-        <v>21959</v>
-      </c>
-      <c r="G7" s="8">
-        <f t="shared" si="22"/>
-        <v>20307</v>
-      </c>
-      <c r="H7" s="8">
-        <f t="shared" si="22"/>
-        <v>22254</v>
-      </c>
-      <c r="I7" s="8">
-        <f t="shared" si="22"/>
-        <v>23573</v>
-      </c>
-      <c r="J7" s="8">
-        <f t="shared" si="22"/>
-        <v>27597</v>
-      </c>
-      <c r="K7" s="8">
-        <f t="shared" si="22"/>
-        <v>25780</v>
-      </c>
-      <c r="L7" s="8">
-        <f t="shared" si="22"/>
-        <v>27067</v>
-      </c>
-      <c r="M7" s="8">
-        <f t="shared" si="22"/>
-        <v>28679</v>
-      </c>
-      <c r="N7" s="8">
-        <f t="shared" si="22"/>
-        <v>33460</v>
-      </c>
-      <c r="O7" s="8">
-        <f t="shared" si="22"/>
-        <v>31195</v>
-      </c>
-      <c r="P7" s="8">
-        <f t="shared" si="22"/>
-        <v>36252</v>
-      </c>
-      <c r="Q7" s="8">
-        <f t="shared" si="22"/>
-        <v>39039</v>
-      </c>
-      <c r="R7" s="8">
-        <f t="shared" si="22"/>
-        <v>46271</v>
-      </c>
-      <c r="S7" s="8">
-        <f t="shared" si="22"/>
-        <v>46115</v>
-      </c>
-      <c r="T7" s="8">
-        <f t="shared" si="22"/>
-        <v>48904</v>
-      </c>
-      <c r="U7" s="8">
-        <f t="shared" ref="U7:V7" si="23">U5-U6</f>
-        <v>47882</v>
-      </c>
-      <c r="V7" s="8">
+        <v>54577</v>
+      </c>
+      <c r="W7" s="8">
+        <f t="shared" ref="W7:X7" si="23">W5-W6</f>
+        <v>49945</v>
+      </c>
+      <c r="X7" s="8">
         <f t="shared" si="23"/>
-        <v>54577</v>
-      </c>
-      <c r="W7" s="8">
-        <f t="shared" ref="W7:X7" si="24">W5-W6</f>
-        <v>49945</v>
-      </c>
-      <c r="X7" s="8">
-        <f t="shared" si="24"/>
         <v>54810</v>
       </c>
       <c r="Y7" s="8">
-        <f t="shared" ref="Y7" si="25">Y5-Y6</f>
+        <f t="shared" ref="Y7" si="24">Y5-Y6</f>
         <v>56833</v>
       </c>
       <c r="Z7" s="8">
-        <f t="shared" ref="Z7" si="26">Z5-Z6</f>
+        <f t="shared" ref="Z7" si="25">Z5-Z6</f>
         <v>63564</v>
       </c>
       <c r="AA7" s="8">
-        <f t="shared" ref="AA7:AB7" si="27">AA5-AA6</f>
+        <f t="shared" ref="AA7:AB7" si="26">AA5-AA6</f>
         <v>59567</v>
       </c>
       <c r="AB7" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>65010</v>
       </c>
       <c r="AC7" s="8">
-        <f t="shared" ref="AC7" si="28">AC5-AC6</f>
+        <f t="shared" ref="AC7" si="27">AC5-AC6</f>
         <v>68061</v>
       </c>
       <c r="AD7" s="8">
-        <f t="shared" ref="AD7" si="29">AD5-AD6</f>
+        <f t="shared" ref="AD7" si="28">AD5-AD6</f>
         <v>77408</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" ref="AE7:AJ7" si="30">AE5-AE6</f>
+        <f t="shared" ref="AE7:AK7" si="29">AE5-AE6</f>
         <v>70680</v>
       </c>
       <c r="AF7" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>74192</v>
       </c>
       <c r="AG7" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>77900</v>
       </c>
       <c r="AH7" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>88899</v>
       </c>
       <c r="AI7" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>78691</v>
       </c>
       <c r="AJ7" s="8">
-        <f t="shared" si="30"/>
+        <f t="shared" si="29"/>
         <v>86893</v>
       </c>
       <c r="AK7" s="8">
-        <f t="shared" ref="AK7" si="31">AK5*0.5</f>
-        <v>87517.845000000001</v>
+        <f t="shared" si="29"/>
+        <v>91499</v>
       </c>
       <c r="AL7" s="8">
         <f>AL5*0.49</f>
-        <v>100354.2638</v>
+        <v>101965.89339999999</v>
       </c>
       <c r="AN7" s="8">
-        <f t="shared" ref="AN7:AW7" si="32">AN5-AN6</f>
+        <f t="shared" ref="AN7:AW7" si="30">AN5-AN6</f>
         <v>26236</v>
       </c>
       <c r="AO7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>35355</v>
       </c>
       <c r="AP7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>47722</v>
       </c>
       <c r="AQ7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>65932</v>
       </c>
       <c r="AR7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>93731</v>
       </c>
       <c r="AS7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>114986</v>
       </c>
       <c r="AT7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>152757</v>
       </c>
       <c r="AU7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>197478</v>
       </c>
       <c r="AV7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>225152</v>
       </c>
       <c r="AW7" s="8">
-        <f t="shared" si="32"/>
+        <f t="shared" si="30"/>
         <v>270046</v>
       </c>
       <c r="AX7" s="8">
-        <f t="shared" ref="AX7:AY7" si="33">AX5-AX6</f>
+        <f t="shared" ref="AX7:AY7" si="31">AX5-AX6</f>
         <v>311671</v>
       </c>
       <c r="AY7" s="8">
-        <f t="shared" si="33"/>
-        <v>353456.10879999993</v>
+        <f t="shared" si="31"/>
+        <v>359048.89339999994</v>
       </c>
       <c r="AZ7" s="8">
         <f>AZ5*0.51</f>
-        <v>385024.32879300002</v>
+        <v>389576.44696200005</v>
       </c>
       <c r="BA7" s="8">
         <f>BA5*0.52</f>
-        <v>417674.25942528003</v>
+        <v>422547.91162272007</v>
       </c>
       <c r="BB7" s="8">
         <f>BB5*0.53</f>
-        <v>446235.99384898326</v>
+        <v>451390.88129266084</v>
       </c>
       <c r="BC7" s="8">
-        <f t="shared" ref="BC7:BI7" si="34">BC5*0.53</f>
-        <v>460643.27641324961</v>
+        <f t="shared" ref="BC7:BI7" si="32">BC5*0.53</f>
+        <v>465928.46111900284</v>
       </c>
       <c r="BD7" s="8">
-        <f t="shared" si="34"/>
-        <v>472707.07453890354</v>
+        <f t="shared" si="32"/>
+        <v>478112.10668563709</v>
       </c>
       <c r="BE7" s="8">
-        <f t="shared" si="34"/>
-        <v>482161.21602968167</v>
+        <f t="shared" si="32"/>
+        <v>487674.34881934983</v>
       </c>
       <c r="BF7" s="8">
-        <f t="shared" si="34"/>
-        <v>489978.01797679544</v>
+        <f t="shared" si="32"/>
+        <v>495561.14151481673</v>
       </c>
       <c r="BG7" s="8">
-        <f t="shared" si="34"/>
-        <v>494877.79815656337</v>
+        <f t="shared" si="32"/>
+        <v>500516.7529299648</v>
       </c>
       <c r="BH7" s="8">
-        <f t="shared" si="34"/>
-        <v>499826.57613812905</v>
+        <f t="shared" si="32"/>
+        <v>505521.92045926454</v>
       </c>
       <c r="BI7" s="8">
-        <f t="shared" si="34"/>
-        <v>504824.8418995103</v>
+        <f t="shared" si="32"/>
+        <v>510577.13966385718</v>
       </c>
     </row>
     <row r="8" spans="2:61" x14ac:dyDescent="0.3">
@@ -2826,12 +2825,11 @@
         <v>25976</v>
       </c>
       <c r="AK8" s="4">
-        <f t="shared" ref="AK8" si="35">AK5*0.16</f>
-        <v>28005.7104</v>
+        <v>27679</v>
       </c>
       <c r="AL8" s="4">
         <f>AL5*0.15</f>
-        <v>30720.692999999999</v>
+        <v>31214.048999999995</v>
       </c>
       <c r="AN8" s="4">
         <v>10766</v>
@@ -2876,47 +2874,47 @@
       </c>
       <c r="AY8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>109295.4034</v>
+        <v>109462.049</v>
       </c>
       <c r="AZ8" s="4">
-        <f t="shared" ref="AZ8:BE8" si="36">AZ5*0.15</f>
-        <v>113242.449645</v>
+        <f t="shared" ref="AZ8:BE8" si="33">AZ5*0.15</f>
+        <v>114581.30793000001</v>
       </c>
       <c r="BA8" s="4">
-        <f t="shared" si="36"/>
-        <v>120482.95944959999</v>
+        <f t="shared" si="33"/>
+        <v>121888.82066040002</v>
       </c>
       <c r="BB8" s="4">
-        <f t="shared" si="36"/>
-        <v>126293.20580631601</v>
+        <f t="shared" si="33"/>
+        <v>127752.13621490401</v>
       </c>
       <c r="BC8" s="4">
-        <f t="shared" si="36"/>
-        <v>130370.73860752345</v>
+        <f t="shared" si="33"/>
+        <v>131866.54559971776</v>
       </c>
       <c r="BD8" s="4">
-        <f t="shared" si="36"/>
-        <v>133785.02109591608</v>
+        <f t="shared" si="33"/>
+        <v>135314.7471751803</v>
       </c>
       <c r="BE8" s="4">
-        <f t="shared" si="36"/>
-        <v>136460.72151783443</v>
+        <f t="shared" si="33"/>
+        <v>138021.04211868389</v>
       </c>
       <c r="BF8" s="4">
-        <f t="shared" ref="BF8:BI8" si="37">BF5*0.15</f>
-        <v>138673.02395569682</v>
+        <f t="shared" ref="BF8:BI8" si="34">BF5*0.15</f>
+        <v>140253.15325891037</v>
       </c>
       <c r="BG8" s="4">
-        <f t="shared" si="37"/>
-        <v>140059.75419525377</v>
+        <f t="shared" si="34"/>
+        <v>141655.68479149946</v>
       </c>
       <c r="BH8" s="4">
-        <f t="shared" si="37"/>
-        <v>141460.35173720631</v>
+        <f t="shared" si="34"/>
+        <v>143072.24163941448</v>
       </c>
       <c r="BI8" s="4">
-        <f t="shared" si="37"/>
-        <v>142874.95525457838</v>
+        <f t="shared" si="34"/>
+        <v>144502.96405580861</v>
       </c>
     </row>
     <row r="9" spans="2:61" x14ac:dyDescent="0.3">
@@ -3026,12 +3024,11 @@
         <v>27166</v>
       </c>
       <c r="AK9" s="4">
-        <f>AG9*1.24</f>
-        <v>27583.8</v>
+        <v>28962</v>
       </c>
       <c r="AL9" s="4">
-        <f>AH9*1.2</f>
-        <v>28285.200000000001</v>
+        <f>AH9*1.3</f>
+        <v>30642.3</v>
       </c>
       <c r="AN9" s="4">
         <v>4332</v>
@@ -3076,47 +3073,47 @@
       </c>
       <c r="AY9" s="4">
         <f>SUM(AI9:AL9)</f>
-        <v>106029</v>
+        <v>109764.3</v>
       </c>
       <c r="AZ9" s="4">
-        <f>AY9*1.08</f>
-        <v>114511.32</v>
+        <f>AY9*1.12</f>
+        <v>122936.01600000002</v>
       </c>
       <c r="BA9" s="4">
-        <f>AZ9*1.04</f>
-        <v>119091.77280000001</v>
+        <f>AZ9*1.06</f>
+        <v>130312.17696000003</v>
       </c>
       <c r="BB9" s="4">
-        <f>BA9*1.03</f>
-        <v>122664.52598400001</v>
+        <f>BA9*1.04</f>
+        <v>135524.66403840002</v>
       </c>
       <c r="BC9" s="4">
-        <f t="shared" ref="BC9:BE9" si="38">BB9*1.02</f>
-        <v>125117.81650368001</v>
+        <f>BB9*1.03</f>
+        <v>139590.40395955203</v>
       </c>
       <c r="BD9" s="4">
-        <f t="shared" si="38"/>
-        <v>127620.1728337536</v>
+        <f t="shared" ref="BC9:BE9" si="35">BC9*1.02</f>
+        <v>142382.21203874308</v>
       </c>
       <c r="BE9" s="4">
-        <f t="shared" si="38"/>
-        <v>130172.57629042868</v>
+        <f t="shared" si="35"/>
+        <v>145229.85627951793</v>
       </c>
       <c r="BF9" s="4">
         <f>BE9*1.01</f>
-        <v>131474.30205333297</v>
+        <v>146682.15484231312</v>
       </c>
       <c r="BG9" s="4">
-        <f t="shared" ref="BG9:BI9" si="39">BF9*1.01</f>
-        <v>132789.04507386629</v>
+        <f t="shared" ref="BG9:BI9" si="36">BF9*1.01</f>
+        <v>148148.97639073624</v>
       </c>
       <c r="BH9" s="4">
-        <f t="shared" si="39"/>
-        <v>134116.93552460495</v>
+        <f t="shared" si="36"/>
+        <v>149630.4661546436</v>
       </c>
       <c r="BI9" s="4">
-        <f t="shared" si="39"/>
-        <v>135458.10487985102</v>
+        <f t="shared" si="36"/>
+        <v>151126.77081619002</v>
       </c>
     </row>
     <row r="10" spans="2:61" x14ac:dyDescent="0.3">
@@ -3226,12 +3223,11 @@
         <v>11416</v>
       </c>
       <c r="AK10" s="4">
-        <f>AK5*0.065</f>
-        <v>11377.31985</v>
+        <v>11686</v>
       </c>
       <c r="AL10" s="4">
         <f>AL5*0.065</f>
-        <v>13312.300300000001</v>
+        <v>13526.087899999999</v>
       </c>
       <c r="AN10" s="4">
         <v>9275</v>
@@ -3276,47 +3272,47 @@
       </c>
       <c r="AY10" s="4">
         <f>SUM(AI10:AL10)</f>
-        <v>45868.620150000002</v>
+        <v>46391.087899999999</v>
       </c>
       <c r="AZ10" s="4">
         <f>AZ5*0.06</f>
-        <v>45296.979857999999</v>
+        <v>45832.523172000001</v>
       </c>
       <c r="BA10" s="4">
-        <f t="shared" ref="BA10:BI10" si="40">BA5*0.06</f>
-        <v>48193.183779839994</v>
+        <f t="shared" ref="BA10:BI10" si="37">BA5*0.06</f>
+        <v>48755.528264160006</v>
       </c>
       <c r="BB10" s="4">
-        <f t="shared" si="40"/>
-        <v>50517.2823225264</v>
+        <f t="shared" si="37"/>
+        <v>51100.854485961601</v>
       </c>
       <c r="BC10" s="4">
-        <f t="shared" si="40"/>
-        <v>52148.295443009381</v>
+        <f t="shared" si="37"/>
+        <v>52746.61823988711</v>
       </c>
       <c r="BD10" s="4">
-        <f t="shared" si="40"/>
-        <v>53514.008438366436</v>
+        <f t="shared" si="37"/>
+        <v>54125.898870072117</v>
       </c>
       <c r="BE10" s="4">
-        <f t="shared" si="40"/>
-        <v>54584.288607133771</v>
+        <f t="shared" si="37"/>
+        <v>55208.416847473563</v>
       </c>
       <c r="BF10" s="4">
-        <f t="shared" si="40"/>
-        <v>55469.209582278723</v>
+        <f t="shared" si="37"/>
+        <v>56101.261303564155</v>
       </c>
       <c r="BG10" s="4">
-        <f t="shared" si="40"/>
-        <v>56023.901678101509</v>
+        <f t="shared" si="37"/>
+        <v>56662.273916599785</v>
       </c>
       <c r="BH10" s="4">
-        <f t="shared" si="40"/>
-        <v>56584.140694882524</v>
+        <f t="shared" si="37"/>
+        <v>57228.896655765791</v>
       </c>
       <c r="BI10" s="4">
-        <f t="shared" si="40"/>
-        <v>57149.982101831352</v>
+        <f t="shared" si="37"/>
+        <v>57801.18562232345</v>
       </c>
     </row>
     <row r="11" spans="2:61" x14ac:dyDescent="0.3">
@@ -3426,12 +3422,11 @@
         <v>2965</v>
       </c>
       <c r="AK11" s="4">
-        <f t="shared" ref="AK11:AL11" si="41">AG11*1.04</f>
-        <v>2821.52</v>
+        <v>2875</v>
       </c>
       <c r="AL11" s="4">
-        <f t="shared" si="41"/>
-        <v>2977.52</v>
+        <f>AH11*1.05</f>
+        <v>3006.15</v>
       </c>
       <c r="AN11" s="4">
         <v>1552</v>
@@ -3476,47 +3471,47 @@
       </c>
       <c r="AY11" s="4">
         <f>SUM(AI11:AL11)</f>
-        <v>11392.04</v>
+        <v>11474.15</v>
       </c>
       <c r="AZ11" s="4">
-        <f>AY11*1.02</f>
-        <v>11619.880800000001</v>
+        <f>AY11*1.03</f>
+        <v>11818.3745</v>
       </c>
       <c r="BA11" s="4">
         <f>AZ11*1.02</f>
-        <v>11852.278416000001</v>
+        <v>12054.74199</v>
       </c>
       <c r="BB11" s="4">
         <f>BA11*1.02</f>
-        <v>12089.323984320001</v>
+        <v>12295.8368298</v>
       </c>
       <c r="BC11" s="4">
         <f>BB11*1.02</f>
-        <v>12331.1104640064</v>
+        <v>12541.753566396001</v>
       </c>
       <c r="BD11" s="4">
-        <f t="shared" ref="BD11:BE11" si="42">BC11*1.01</f>
-        <v>12454.421568646465</v>
+        <f t="shared" ref="BD11:BE11" si="38">BC11*1.01</f>
+        <v>12667.171102059961</v>
       </c>
       <c r="BE11" s="4">
-        <f t="shared" si="42"/>
-        <v>12578.96578433293</v>
+        <f t="shared" si="38"/>
+        <v>12793.842813080561</v>
       </c>
       <c r="BF11" s="4">
-        <f t="shared" ref="BF11" si="43">BE11*1.01</f>
-        <v>12704.75544217626</v>
+        <f t="shared" ref="BF11" si="39">BE11*1.01</f>
+        <v>12921.781241211365</v>
       </c>
       <c r="BG11" s="4">
-        <f t="shared" ref="BG11" si="44">BF11*1.01</f>
-        <v>12831.802996598022</v>
+        <f t="shared" ref="BG11" si="40">BF11*1.01</f>
+        <v>13050.99905362348</v>
       </c>
       <c r="BH11" s="4">
-        <f t="shared" ref="BH11" si="45">BG11*1.01</f>
-        <v>12960.121026564002</v>
+        <f t="shared" ref="BH11" si="41">BG11*1.01</f>
+        <v>13181.509044159715</v>
       </c>
       <c r="BI11" s="4">
-        <f t="shared" ref="BI11" si="46">BH11*1.01</f>
-        <v>13089.722236829642</v>
+        <f t="shared" ref="BI11" si="42">BH11*1.01</f>
+        <v>13313.324134601313</v>
       </c>
     </row>
     <row r="12" spans="2:61" x14ac:dyDescent="0.3">
@@ -3626,11 +3621,10 @@
         <v>199</v>
       </c>
       <c r="AK12" s="4">
-        <f t="shared" ref="AK12:AL12" si="47">AG12*1.01</f>
-        <v>264.62</v>
+        <v>2875</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" si="47"/>
+        <f t="shared" ref="AK12:AL12" si="43">AH12*1.01</f>
         <v>177.76</v>
       </c>
       <c r="AN12" s="4">
@@ -3676,47 +3670,47 @@
       </c>
       <c r="AY12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>949.38</v>
+        <v>3559.76</v>
       </c>
       <c r="AZ12" s="4">
-        <f t="shared" ref="AZ12:BE12" si="48">AY12*1.03</f>
-        <v>977.8614</v>
+        <f t="shared" ref="AZ12:BE12" si="44">AY12*1.03</f>
+        <v>3666.5528000000004</v>
       </c>
       <c r="BA12" s="4">
-        <f t="shared" si="48"/>
-        <v>1007.1972420000001</v>
+        <f t="shared" si="44"/>
+        <v>3776.5493840000004</v>
       </c>
       <c r="BB12" s="4">
-        <f t="shared" si="48"/>
-        <v>1037.4131592600002</v>
+        <f t="shared" si="44"/>
+        <v>3889.8458655200006</v>
       </c>
       <c r="BC12" s="4">
-        <f t="shared" si="48"/>
-        <v>1068.5355540378002</v>
+        <f t="shared" si="44"/>
+        <v>4006.5412414856009</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="48"/>
-        <v>1100.5916206589343</v>
+        <f t="shared" si="44"/>
+        <v>4126.7374787301687</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="48"/>
-        <v>1133.6093692787024</v>
+        <f t="shared" si="44"/>
+        <v>4250.5396030920738</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" ref="BF12" si="49">BE12*1.03</f>
-        <v>1167.6176503570634</v>
+        <f t="shared" ref="BF12" si="45">BE12*1.03</f>
+        <v>4378.0557911848364</v>
       </c>
       <c r="BG12" s="4">
-        <f t="shared" ref="BG12" si="50">BF12*1.03</f>
-        <v>1202.6461798677753</v>
+        <f t="shared" ref="BG12" si="46">BF12*1.03</f>
+        <v>4509.3974649203819</v>
       </c>
       <c r="BH12" s="4">
-        <f t="shared" ref="BH12" si="51">BG12*1.03</f>
-        <v>1238.7255652638087</v>
+        <f t="shared" ref="BH12" si="47">BG12*1.03</f>
+        <v>4644.6793888679931</v>
       </c>
       <c r="BI12" s="4">
-        <f t="shared" ref="BI12" si="52">BH12*1.03</f>
-        <v>1275.887332221723</v>
+        <f t="shared" ref="BI12" si="48">BH12*1.03</f>
+        <v>4784.0197705340333</v>
       </c>
     </row>
     <row r="13" spans="2:61" x14ac:dyDescent="0.3">
@@ -3724,237 +3718,237 @@
         <v>40</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:R13" si="53">SUM(C8:C12)</f>
+        <f t="shared" ref="C13:R13" si="49">SUM(C8:C12)</f>
         <v>12269</v>
       </c>
       <c r="D13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>13876</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>15848</v>
       </c>
       <c r="F13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>19832</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>18380</v>
       </c>
       <c r="H13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>19271</v>
       </c>
       <c r="I13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>19849</v>
       </c>
       <c r="J13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>23811</v>
       </c>
       <c r="K13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>21360</v>
       </c>
       <c r="L13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>23983</v>
       </c>
       <c r="M13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>25522</v>
       </c>
       <c r="N13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>29581</v>
       </c>
       <c r="O13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>27206</v>
       </c>
       <c r="P13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>30409</v>
       </c>
       <c r="Q13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>32845</v>
       </c>
       <c r="R13" s="4">
-        <f t="shared" si="53"/>
+        <f t="shared" si="49"/>
         <v>39398</v>
       </c>
       <c r="S13" s="4">
-        <f t="shared" ref="S13:V13" si="54">SUM(S8:S12)</f>
+        <f t="shared" ref="S13:V13" si="50">SUM(S8:S12)</f>
         <v>37250</v>
       </c>
       <c r="T13" s="4">
-        <f t="shared" ref="T13:U13" si="55">SUM(T8:T12)</f>
+        <f t="shared" ref="T13:U13" si="51">SUM(T8:T12)</f>
         <v>41202</v>
       </c>
       <c r="U13" s="4">
+        <f t="shared" si="51"/>
+        <v>43030</v>
+      </c>
+      <c r="V13" s="4">
+        <f t="shared" si="50"/>
+        <v>51117</v>
+      </c>
+      <c r="W13" s="4">
+        <f t="shared" ref="W13:X13" si="52">SUM(W8:W12)</f>
+        <v>46276</v>
+      </c>
+      <c r="X13" s="4">
+        <f t="shared" si="52"/>
+        <v>51493</v>
+      </c>
+      <c r="Y13" s="4">
+        <f t="shared" ref="Y13" si="53">SUM(Y8:Y12)</f>
+        <v>54308</v>
+      </c>
+      <c r="Z13" s="4">
+        <f t="shared" ref="Z13" si="54">SUM(Z8:Z12)</f>
+        <v>60827</v>
+      </c>
+      <c r="AA13" s="4">
+        <f t="shared" ref="AA13:AB13" si="55">SUM(AA8:AA12)</f>
+        <v>54793</v>
+      </c>
+      <c r="AB13" s="4">
         <f t="shared" si="55"/>
-        <v>43030</v>
-      </c>
-      <c r="V13" s="4">
-        <f t="shared" si="54"/>
-        <v>51117</v>
-      </c>
-      <c r="W13" s="4">
-        <f t="shared" ref="W13:X13" si="56">SUM(W8:W12)</f>
-        <v>46276</v>
-      </c>
-      <c r="X13" s="4">
-        <f t="shared" si="56"/>
-        <v>51493</v>
-      </c>
-      <c r="Y13" s="4">
-        <f t="shared" ref="Y13" si="57">SUM(Y8:Y12)</f>
-        <v>54308</v>
-      </c>
-      <c r="Z13" s="4">
-        <f t="shared" ref="Z13" si="58">SUM(Z8:Z12)</f>
-        <v>60827</v>
-      </c>
-      <c r="AA13" s="4">
-        <f t="shared" ref="AA13:AB13" si="59">SUM(AA8:AA12)</f>
-        <v>54793</v>
-      </c>
-      <c r="AB13" s="4">
+        <v>57329</v>
+      </c>
+      <c r="AC13" s="4">
+        <f t="shared" ref="AC13" si="56">SUM(AC8:AC12)</f>
+        <v>56873</v>
+      </c>
+      <c r="AD13" s="4">
+        <f t="shared" ref="AD13" si="57">SUM(AD8:AD12)</f>
+        <v>64199</v>
+      </c>
+      <c r="AE13" s="4">
+        <f t="shared" ref="AE13:AF13" si="58">SUM(AE8:AE12)</f>
+        <v>55373</v>
+      </c>
+      <c r="AF13" s="4">
+        <f t="shared" si="58"/>
+        <v>59520</v>
+      </c>
+      <c r="AG13" s="4">
+        <f t="shared" ref="AG13:AH13" si="59">SUM(AG8:AG12)</f>
+        <v>60489</v>
+      </c>
+      <c r="AH13" s="4">
         <f t="shared" si="59"/>
-        <v>57329</v>
-      </c>
-      <c r="AC13" s="4">
-        <f t="shared" ref="AC13" si="60">SUM(AC8:AC12)</f>
-        <v>56873</v>
-      </c>
-      <c r="AD13" s="4">
-        <f t="shared" ref="AD13" si="61">SUM(AD8:AD12)</f>
-        <v>64199</v>
-      </c>
-      <c r="AE13" s="4">
-        <f t="shared" ref="AE13:AF13" si="62">SUM(AE8:AE12)</f>
-        <v>55373</v>
-      </c>
-      <c r="AF13" s="4">
-        <f t="shared" si="62"/>
-        <v>59520</v>
-      </c>
-      <c r="AG13" s="4">
-        <f t="shared" ref="AG13:AH13" si="63">SUM(AG8:AG12)</f>
-        <v>60489</v>
-      </c>
-      <c r="AH13" s="4">
-        <f t="shared" si="63"/>
         <v>67696</v>
       </c>
       <c r="AI13" s="4">
-        <f t="shared" ref="AI13:AL13" si="64">SUM(AI8:AI12)</f>
+        <f t="shared" ref="AI13:AL13" si="60">SUM(AI8:AI12)</f>
         <v>60286</v>
       </c>
       <c r="AJ13" s="4">
-        <f t="shared" si="64"/>
+        <f t="shared" si="60"/>
         <v>67722</v>
       </c>
       <c r="AK13" s="4">
-        <f t="shared" si="64"/>
-        <v>70052.970249999998</v>
+        <f t="shared" si="60"/>
+        <v>74077</v>
       </c>
       <c r="AL13" s="4">
-        <f t="shared" si="64"/>
-        <v>75473.473299999998</v>
+        <f t="shared" si="60"/>
+        <v>78566.34689999999</v>
       </c>
       <c r="AM13" s="4"/>
       <c r="AN13" s="4">
-        <f t="shared" ref="AN13:AU13" si="65">SUM(AN8:AN12)</f>
+        <f t="shared" ref="AN13:AU13" si="61">SUM(AN8:AN12)</f>
         <v>26058</v>
       </c>
       <c r="AO13" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>33122</v>
       </c>
       <c r="AP13" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>43536</v>
       </c>
       <c r="AQ13" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>61825</v>
       </c>
       <c r="AR13" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>81311</v>
       </c>
       <c r="AS13" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>100446</v>
       </c>
       <c r="AT13" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>129858</v>
       </c>
       <c r="AU13" s="4">
-        <f t="shared" si="65"/>
+        <f t="shared" si="61"/>
         <v>172599</v>
       </c>
       <c r="AV13" s="4">
-        <f t="shared" ref="AV13:BE13" si="66">SUM(AV8:AV12)</f>
+        <f t="shared" ref="AV13:BE13" si="62">SUM(AV8:AV12)</f>
         <v>212904</v>
       </c>
       <c r="AW13" s="4">
-        <f t="shared" si="66"/>
+        <f t="shared" si="62"/>
         <v>233194</v>
       </c>
       <c r="AX13" s="4">
-        <f t="shared" ref="AX13" si="67">SUM(AX8:AX12)</f>
+        <f t="shared" ref="AX13" si="63">SUM(AX8:AX12)</f>
         <v>243078</v>
       </c>
       <c r="AY13" s="4">
-        <f t="shared" si="66"/>
-        <v>273534.44355000003</v>
+        <f t="shared" si="62"/>
+        <v>280651.3469</v>
       </c>
       <c r="AZ13" s="4">
-        <f t="shared" si="66"/>
-        <v>285648.49170299998</v>
+        <f t="shared" si="62"/>
+        <v>298834.77440200001</v>
       </c>
       <c r="BA13" s="4">
-        <f t="shared" si="66"/>
-        <v>300627.39168744005</v>
+        <f t="shared" si="62"/>
+        <v>316787.8172585601</v>
       </c>
       <c r="BB13" s="4">
-        <f t="shared" si="66"/>
-        <v>312601.75125642237</v>
+        <f t="shared" si="62"/>
+        <v>330563.33743458561</v>
       </c>
       <c r="BC13" s="4">
-        <f t="shared" si="66"/>
-        <v>321036.49657225702</v>
+        <f t="shared" si="62"/>
+        <v>340751.86260703858</v>
       </c>
       <c r="BD13" s="4">
-        <f t="shared" si="66"/>
-        <v>328474.21555734152</v>
+        <f t="shared" si="62"/>
+        <v>348616.76666478557</v>
       </c>
       <c r="BE13" s="4">
-        <f t="shared" si="66"/>
-        <v>334930.16156900855</v>
+        <f t="shared" si="62"/>
+        <v>355503.69766184804</v>
       </c>
       <c r="BF13" s="4">
-        <f t="shared" ref="BF13:BI13" si="68">SUM(BF8:BF12)</f>
-        <v>339488.90868384182</v>
+        <f t="shared" ref="BF13:BI13" si="64">SUM(BF8:BF12)</f>
+        <v>360336.40643718379</v>
       </c>
       <c r="BG13" s="4">
-        <f t="shared" si="68"/>
-        <v>342907.1501236874</v>
+        <f t="shared" si="64"/>
+        <v>364027.33161737933</v>
       </c>
       <c r="BH13" s="4">
-        <f t="shared" si="68"/>
-        <v>346360.27454852161</v>
+        <f t="shared" si="64"/>
+        <v>367757.79288285156</v>
       </c>
       <c r="BI13" s="4">
-        <f t="shared" si="68"/>
-        <v>349848.65180531208</v>
+        <f t="shared" si="64"/>
+        <v>371528.26439945743</v>
       </c>
     </row>
     <row r="14" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -3962,236 +3956,236 @@
         <v>42</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:R14" si="69">C7-C13</f>
+        <f t="shared" ref="C14:R14" si="65">C7-C13</f>
         <v>1005</v>
       </c>
       <c r="D14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>628</v>
       </c>
       <c r="E14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>347</v>
       </c>
       <c r="F14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>2127</v>
       </c>
       <c r="G14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>1927</v>
       </c>
       <c r="H14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>2983</v>
       </c>
       <c r="I14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>3724</v>
       </c>
       <c r="J14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>3786</v>
       </c>
       <c r="K14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>4420</v>
       </c>
       <c r="L14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>3084</v>
       </c>
       <c r="M14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>3157</v>
       </c>
       <c r="N14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>3879</v>
       </c>
       <c r="O14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>3989</v>
       </c>
       <c r="P14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>5843</v>
       </c>
       <c r="Q14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>6194</v>
       </c>
       <c r="R14" s="8">
-        <f t="shared" si="69"/>
+        <f t="shared" si="65"/>
         <v>6873</v>
       </c>
       <c r="S14" s="8">
-        <f t="shared" ref="S14:V14" si="70">S7-S13</f>
+        <f t="shared" ref="S14:V14" si="66">S7-S13</f>
         <v>8865</v>
       </c>
       <c r="T14" s="8">
-        <f t="shared" ref="T14:U14" si="71">T7-T13</f>
+        <f t="shared" ref="T14:U14" si="67">T7-T13</f>
         <v>7702</v>
       </c>
       <c r="U14" s="8">
+        <f t="shared" si="67"/>
+        <v>4852</v>
+      </c>
+      <c r="V14" s="8">
+        <f t="shared" si="66"/>
+        <v>3460</v>
+      </c>
+      <c r="W14" s="8">
+        <f t="shared" ref="W14:X14" si="68">W7-W13</f>
+        <v>3669</v>
+      </c>
+      <c r="X14" s="8">
+        <f t="shared" si="68"/>
+        <v>3317</v>
+      </c>
+      <c r="Y14" s="8">
+        <f t="shared" ref="Y14" si="69">Y7-Y13</f>
+        <v>2525</v>
+      </c>
+      <c r="Z14" s="8">
+        <f t="shared" ref="Z14" si="70">Z7-Z13</f>
+        <v>2737</v>
+      </c>
+      <c r="AA14" s="8">
+        <f t="shared" ref="AA14:AB14" si="71">AA7-AA13</f>
+        <v>4774</v>
+      </c>
+      <c r="AB14" s="8">
         <f t="shared" si="71"/>
-        <v>4852</v>
-      </c>
-      <c r="V14" s="8">
-        <f t="shared" si="70"/>
-        <v>3460</v>
-      </c>
-      <c r="W14" s="8">
-        <f t="shared" ref="W14:X14" si="72">W7-W13</f>
-        <v>3669</v>
-      </c>
-      <c r="X14" s="8">
-        <f t="shared" si="72"/>
-        <v>3317</v>
-      </c>
-      <c r="Y14" s="8">
-        <f t="shared" ref="Y14" si="73">Y7-Y13</f>
-        <v>2525</v>
-      </c>
-      <c r="Z14" s="8">
-        <f t="shared" ref="Z14" si="74">Z7-Z13</f>
-        <v>2737</v>
-      </c>
-      <c r="AA14" s="8">
-        <f t="shared" ref="AA14:AB14" si="75">AA7-AA13</f>
-        <v>4774</v>
-      </c>
-      <c r="AB14" s="8">
+        <v>7681</v>
+      </c>
+      <c r="AC14" s="8">
+        <f t="shared" ref="AC14" si="72">AC7-AC13</f>
+        <v>11188</v>
+      </c>
+      <c r="AD14" s="8">
+        <f t="shared" ref="AD14" si="73">AD7-AD13</f>
+        <v>13209</v>
+      </c>
+      <c r="AE14" s="8">
+        <f t="shared" ref="AE14:AF14" si="74">AE7-AE13</f>
+        <v>15307</v>
+      </c>
+      <c r="AF14" s="8">
+        <f t="shared" si="74"/>
+        <v>14672</v>
+      </c>
+      <c r="AG14" s="8">
+        <f t="shared" ref="AG14:AH14" si="75">AG7-AG13</f>
+        <v>17411</v>
+      </c>
+      <c r="AH14" s="8">
         <f t="shared" si="75"/>
-        <v>7681</v>
-      </c>
-      <c r="AC14" s="8">
-        <f t="shared" ref="AC14" si="76">AC7-AC13</f>
-        <v>11188</v>
-      </c>
-      <c r="AD14" s="8">
-        <f t="shared" ref="AD14" si="77">AD7-AD13</f>
-        <v>13209</v>
-      </c>
-      <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AF14" si="78">AE7-AE13</f>
-        <v>15307</v>
-      </c>
-      <c r="AF14" s="8">
+        <v>21203</v>
+      </c>
+      <c r="AI14" s="8">
+        <f t="shared" ref="AI14:AL14" si="76">AI7-AI13</f>
+        <v>18405</v>
+      </c>
+      <c r="AJ14" s="8">
+        <f t="shared" si="76"/>
+        <v>19171</v>
+      </c>
+      <c r="AK14" s="8">
+        <f t="shared" si="76"/>
+        <v>17422</v>
+      </c>
+      <c r="AL14" s="8">
+        <f t="shared" si="76"/>
+        <v>23399.546499999997</v>
+      </c>
+      <c r="AN14" s="8">
+        <f t="shared" ref="AN14:AU14" si="77">AN7-AN13</f>
+        <v>178</v>
+      </c>
+      <c r="AO14" s="8">
+        <f t="shared" si="77"/>
+        <v>2233</v>
+      </c>
+      <c r="AP14" s="8">
+        <f t="shared" si="77"/>
+        <v>4186</v>
+      </c>
+      <c r="AQ14" s="8">
+        <f t="shared" si="77"/>
+        <v>4107</v>
+      </c>
+      <c r="AR14" s="8">
+        <f t="shared" si="77"/>
+        <v>12420</v>
+      </c>
+      <c r="AS14" s="8">
+        <f t="shared" si="77"/>
+        <v>14540</v>
+      </c>
+      <c r="AT14" s="8">
+        <f t="shared" si="77"/>
+        <v>22899</v>
+      </c>
+      <c r="AU14" s="8">
+        <f t="shared" si="77"/>
+        <v>24879</v>
+      </c>
+      <c r="AV14" s="8">
+        <f t="shared" ref="AV14:BE14" si="78">AV7-AV13</f>
+        <v>12248</v>
+      </c>
+      <c r="AW14" s="8">
         <f t="shared" si="78"/>
-        <v>14672</v>
-      </c>
-      <c r="AG14" s="8">
-        <f t="shared" ref="AG14:AH14" si="79">AG7-AG13</f>
-        <v>17411</v>
-      </c>
-      <c r="AH14" s="8">
-        <f t="shared" si="79"/>
-        <v>21203</v>
-      </c>
-      <c r="AI14" s="8">
-        <f t="shared" ref="AI14:AL14" si="80">AI7-AI13</f>
-        <v>18405</v>
-      </c>
-      <c r="AJ14" s="8">
+        <v>36852</v>
+      </c>
+      <c r="AX14" s="8">
+        <f t="shared" ref="AX14" si="79">AX7-AX13</f>
+        <v>68593</v>
+      </c>
+      <c r="AY14" s="8">
+        <f t="shared" si="78"/>
+        <v>78397.546499999939</v>
+      </c>
+      <c r="AZ14" s="8">
+        <f t="shared" si="78"/>
+        <v>90741.672560000035</v>
+      </c>
+      <c r="BA14" s="8">
+        <f t="shared" si="78"/>
+        <v>105760.09436415997</v>
+      </c>
+      <c r="BB14" s="8">
+        <f t="shared" si="78"/>
+        <v>120827.54385807522</v>
+      </c>
+      <c r="BC14" s="8">
+        <f t="shared" si="78"/>
+        <v>125176.59851196426</v>
+      </c>
+      <c r="BD14" s="8">
+        <f t="shared" si="78"/>
+        <v>129495.34002085152</v>
+      </c>
+      <c r="BE14" s="8">
+        <f t="shared" si="78"/>
+        <v>132170.65115750179</v>
+      </c>
+      <c r="BF14" s="8">
+        <f t="shared" ref="BF14:BI14" si="80">BF7-BF13</f>
+        <v>135224.73507763294</v>
+      </c>
+      <c r="BG14" s="8">
         <f t="shared" si="80"/>
-        <v>19171</v>
-      </c>
-      <c r="AK14" s="8">
+        <v>136489.42131258547</v>
+      </c>
+      <c r="BH14" s="8">
         <f t="shared" si="80"/>
-        <v>17464.874750000003</v>
-      </c>
-      <c r="AL14" s="8">
+        <v>137764.12757641298</v>
+      </c>
+      <c r="BI14" s="8">
         <f t="shared" si="80"/>
-        <v>24880.790500000003</v>
-      </c>
-      <c r="AN14" s="8">
-        <f t="shared" ref="AN14:AU14" si="81">AN7-AN13</f>
-        <v>178</v>
-      </c>
-      <c r="AO14" s="8">
-        <f t="shared" si="81"/>
-        <v>2233</v>
-      </c>
-      <c r="AP14" s="8">
-        <f t="shared" si="81"/>
-        <v>4186</v>
-      </c>
-      <c r="AQ14" s="8">
-        <f t="shared" si="81"/>
-        <v>4107</v>
-      </c>
-      <c r="AR14" s="8">
-        <f t="shared" si="81"/>
-        <v>12420</v>
-      </c>
-      <c r="AS14" s="8">
-        <f t="shared" si="81"/>
-        <v>14540</v>
-      </c>
-      <c r="AT14" s="8">
-        <f t="shared" si="81"/>
-        <v>22899</v>
-      </c>
-      <c r="AU14" s="8">
-        <f t="shared" si="81"/>
-        <v>24879</v>
-      </c>
-      <c r="AV14" s="8">
-        <f t="shared" ref="AV14:BE14" si="82">AV7-AV13</f>
-        <v>12248</v>
-      </c>
-      <c r="AW14" s="8">
-        <f t="shared" si="82"/>
-        <v>36852</v>
-      </c>
-      <c r="AX14" s="8">
-        <f t="shared" ref="AX14" si="83">AX7-AX13</f>
-        <v>68593</v>
-      </c>
-      <c r="AY14" s="8">
-        <f t="shared" si="82"/>
-        <v>79921.665249999904</v>
-      </c>
-      <c r="AZ14" s="8">
-        <f t="shared" si="82"/>
-        <v>99375.837090000045</v>
-      </c>
-      <c r="BA14" s="8">
-        <f t="shared" si="82"/>
-        <v>117046.86773783999</v>
-      </c>
-      <c r="BB14" s="8">
-        <f t="shared" si="82"/>
-        <v>133634.24259256088</v>
-      </c>
-      <c r="BC14" s="8">
-        <f t="shared" si="82"/>
-        <v>139606.77984099259</v>
-      </c>
-      <c r="BD14" s="8">
-        <f t="shared" si="82"/>
-        <v>144232.85898156202</v>
-      </c>
-      <c r="BE14" s="8">
-        <f t="shared" si="82"/>
-        <v>147231.05446067313</v>
-      </c>
-      <c r="BF14" s="8">
-        <f t="shared" ref="BF14:BI14" si="84">BF7-BF13</f>
-        <v>150489.10929295362</v>
-      </c>
-      <c r="BG14" s="8">
-        <f t="shared" si="84"/>
-        <v>151970.64803287596</v>
-      </c>
-      <c r="BH14" s="8">
-        <f t="shared" si="84"/>
-        <v>153466.30158960744</v>
-      </c>
-      <c r="BI14" s="8">
-        <f t="shared" si="84"/>
-        <v>154976.19009419822</v>
+        <v>139048.87526439974</v>
       </c>
     </row>
     <row r="15" spans="2:61" x14ac:dyDescent="0.3">
@@ -4301,11 +4295,10 @@
         <v>-1085</v>
       </c>
       <c r="AK15" s="4">
-        <f t="shared" ref="AK15:AL15" si="85">AG15*1.05</f>
-        <v>-1318.8</v>
+        <v>-1100</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" si="85"/>
+        <f t="shared" ref="AK15:AL15" si="81">AH15*1.05</f>
         <v>-1310.4000000000001</v>
       </c>
       <c r="AN15" s="4">
@@ -4351,47 +4344,47 @@
       </c>
       <c r="AY15" s="4">
         <f>SUM(AI15:AL15)</f>
-        <v>-4780.2000000000007</v>
+        <v>-4561.3999999999996</v>
       </c>
       <c r="AZ15" s="4">
         <f>AY15*1.05</f>
-        <v>-5019.2100000000009</v>
+        <v>-4789.47</v>
       </c>
       <c r="BA15" s="4">
-        <f t="shared" ref="BA15:BI15" si="86">AZ15*1.05</f>
-        <v>-5270.1705000000011</v>
+        <f t="shared" ref="BA15:BI15" si="82">AZ15*1.05</f>
+        <v>-5028.9435000000003</v>
       </c>
       <c r="BB15" s="4">
-        <f t="shared" si="86"/>
-        <v>-5533.6790250000013</v>
+        <f t="shared" si="82"/>
+        <v>-5280.3906750000006</v>
       </c>
       <c r="BC15" s="4">
-        <f t="shared" si="86"/>
-        <v>-5810.3629762500013</v>
+        <f t="shared" si="82"/>
+        <v>-5544.4102087500005</v>
       </c>
       <c r="BD15" s="4">
-        <f t="shared" si="86"/>
-        <v>-6100.8811250625013</v>
+        <f t="shared" si="82"/>
+        <v>-5821.6307191875012</v>
       </c>
       <c r="BE15" s="4">
-        <f t="shared" si="86"/>
-        <v>-6405.925181315627</v>
+        <f t="shared" si="82"/>
+        <v>-6112.7122551468765</v>
       </c>
       <c r="BF15" s="4">
-        <f t="shared" si="86"/>
-        <v>-6726.2214403814087</v>
+        <f t="shared" si="82"/>
+        <v>-6418.3478679042209</v>
       </c>
       <c r="BG15" s="4">
-        <f t="shared" si="86"/>
-        <v>-7062.5325124004794</v>
+        <f t="shared" si="82"/>
+        <v>-6739.2652612994325</v>
       </c>
       <c r="BH15" s="4">
-        <f t="shared" si="86"/>
-        <v>-7415.6591380205036</v>
+        <f t="shared" si="82"/>
+        <v>-7076.2285243644046</v>
       </c>
       <c r="BI15" s="4">
-        <f t="shared" si="86"/>
-        <v>-7786.4420949215291</v>
+        <f t="shared" si="82"/>
+        <v>-7430.0399505826254</v>
       </c>
     </row>
     <row r="16" spans="2:61" x14ac:dyDescent="0.3">
@@ -4501,11 +4494,10 @@
         <v>516</v>
       </c>
       <c r="AK16" s="4">
-        <f t="shared" ref="AK16:AL16" si="87">AG16*0.98</f>
-        <v>590.93999999999994</v>
+        <v>538</v>
       </c>
       <c r="AL16" s="4">
-        <f t="shared" si="87"/>
+        <f t="shared" ref="AK16:AL16" si="83">AH16*0.98</f>
         <v>558.6</v>
       </c>
       <c r="AN16" s="4">
@@ -4551,47 +4543,47 @@
       </c>
       <c r="AY16" s="4">
         <f>SUM(AI16:AL16)</f>
-        <v>2206.54</v>
+        <v>2153.6</v>
       </c>
       <c r="AZ16" s="4">
-        <f t="shared" ref="AZ16:BI16" si="88">AY16*1.01</f>
-        <v>2228.6053999999999</v>
+        <f t="shared" ref="AZ16:BI16" si="84">AY16*1.01</f>
+        <v>2175.136</v>
       </c>
       <c r="BA16" s="4">
-        <f t="shared" si="88"/>
-        <v>2250.8914540000001</v>
+        <f t="shared" si="84"/>
+        <v>2196.8873600000002</v>
       </c>
       <c r="BB16" s="4">
-        <f t="shared" si="88"/>
-        <v>2273.4003685400003</v>
+        <f t="shared" si="84"/>
+        <v>2218.8562336</v>
       </c>
       <c r="BC16" s="4">
-        <f t="shared" si="88"/>
-        <v>2296.1343722254005</v>
+        <f t="shared" si="84"/>
+        <v>2241.0447959359999</v>
       </c>
       <c r="BD16" s="4">
-        <f t="shared" si="88"/>
-        <v>2319.0957159476548</v>
+        <f t="shared" si="84"/>
+        <v>2263.4552438953601</v>
       </c>
       <c r="BE16" s="4">
-        <f t="shared" si="88"/>
-        <v>2342.2866731071313</v>
+        <f t="shared" si="84"/>
+        <v>2286.0897963343136</v>
       </c>
       <c r="BF16" s="4">
-        <f t="shared" si="88"/>
-        <v>2365.7095398382025</v>
+        <f t="shared" si="84"/>
+        <v>2308.9506942976568</v>
       </c>
       <c r="BG16" s="4">
-        <f t="shared" si="88"/>
-        <v>2389.3666352365844</v>
+        <f t="shared" si="84"/>
+        <v>2332.0402012406335</v>
       </c>
       <c r="BH16" s="4">
-        <f t="shared" si="88"/>
-        <v>2413.2603015889504</v>
+        <f t="shared" si="84"/>
+        <v>2355.3606032530397</v>
       </c>
       <c r="BI16" s="4">
-        <f t="shared" si="88"/>
-        <v>2437.3929046048397</v>
+        <f t="shared" si="84"/>
+        <v>2378.91420928557</v>
       </c>
     </row>
     <row r="17" spans="2:153" x14ac:dyDescent="0.3">
@@ -4701,11 +4693,10 @@
         <v>-1117</v>
       </c>
       <c r="AK17" s="4">
-        <f t="shared" ref="AK17:AL17" si="89">AG17*1.01</f>
-        <v>27.27</v>
+        <v>-10186</v>
       </c>
       <c r="AL17" s="4">
-        <f t="shared" si="89"/>
+        <f t="shared" ref="AK17:AL17" si="85">AH17*1.01</f>
         <v>-472.68</v>
       </c>
       <c r="AN17" s="4">
@@ -4751,47 +4742,37 @@
       </c>
       <c r="AY17" s="4">
         <f>SUM(AI17:AL17)</f>
-        <v>-4311.41</v>
+        <v>-14524.68</v>
       </c>
       <c r="AZ17" s="4">
-        <f t="shared" ref="AZ17:BE17" si="90">AY17*1.01</f>
-        <v>-4354.5240999999996</v>
+        <v>0</v>
       </c>
       <c r="BA17" s="4">
-        <f t="shared" si="90"/>
-        <v>-4398.0693409999994</v>
+        <v>0</v>
       </c>
       <c r="BB17" s="4">
-        <f t="shared" si="90"/>
-        <v>-4442.0500344099992</v>
+        <v>0</v>
       </c>
       <c r="BC17" s="4">
-        <f t="shared" si="90"/>
-        <v>-4486.4705347540994</v>
+        <v>0</v>
       </c>
       <c r="BD17" s="4">
-        <f t="shared" si="90"/>
-        <v>-4531.33524010164</v>
+        <v>0</v>
       </c>
       <c r="BE17" s="4">
-        <f t="shared" si="90"/>
-        <v>-4576.6485925026564</v>
+        <v>0</v>
       </c>
       <c r="BF17" s="4">
-        <f t="shared" ref="BF17" si="91">BE17*1.01</f>
-        <v>-4622.4150784276826</v>
+        <v>0</v>
       </c>
       <c r="BG17" s="4">
-        <f t="shared" ref="BG17" si="92">BF17*1.01</f>
-        <v>-4668.6392292119599</v>
+        <v>0</v>
       </c>
       <c r="BH17" s="4">
-        <f t="shared" ref="BH17" si="93">BG17*1.01</f>
-        <v>-4715.3256215040792</v>
+        <v>0</v>
       </c>
       <c r="BI17" s="4">
-        <f t="shared" ref="BI17" si="94">BH17*1.01</f>
-        <v>-4762.4788777191197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -4799,236 +4780,236 @@
         <v>46</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:R18" si="95">C14-C15-C16-C17</f>
+        <f t="shared" ref="C18:R18" si="86">C14-C15-C16-C17</f>
         <v>953</v>
       </c>
       <c r="D18" s="8">
+        <f t="shared" si="86"/>
+        <v>666</v>
+      </c>
+      <c r="E18" s="8">
+        <f t="shared" si="86"/>
+        <v>316</v>
+      </c>
+      <c r="F18" s="8">
+        <f t="shared" si="86"/>
+        <v>1872</v>
+      </c>
+      <c r="G18" s="8">
+        <f t="shared" si="86"/>
+        <v>1916</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="86"/>
+        <v>2605</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="86"/>
+        <v>3390</v>
+      </c>
+      <c r="J18" s="8">
+        <f t="shared" si="86"/>
+        <v>3350</v>
+      </c>
+      <c r="K18" s="8">
+        <f t="shared" si="86"/>
+        <v>4401</v>
+      </c>
+      <c r="L18" s="8">
+        <f t="shared" si="86"/>
+        <v>2889</v>
+      </c>
+      <c r="M18" s="8">
+        <f t="shared" si="86"/>
+        <v>2632</v>
+      </c>
+      <c r="N18" s="8">
+        <f t="shared" si="86"/>
+        <v>4053</v>
+      </c>
+      <c r="O18" s="8">
+        <f t="shared" si="86"/>
+        <v>3383</v>
+      </c>
+      <c r="P18" s="8">
+        <f t="shared" si="86"/>
+        <v>6221</v>
+      </c>
+      <c r="Q18" s="8">
+        <f t="shared" si="86"/>
+        <v>6809</v>
+      </c>
+      <c r="R18" s="8">
+        <f t="shared" si="86"/>
+        <v>7765</v>
+      </c>
+      <c r="S18" s="8">
+        <f t="shared" ref="S18:V18" si="87">S14-S15-S16-S17</f>
+        <v>10268</v>
+      </c>
+      <c r="T18" s="8">
+        <f t="shared" ref="T18:U18" si="88">T14-T15-T16-T17</f>
+        <v>8634</v>
+      </c>
+      <c r="U18" s="8">
+        <f t="shared" si="88"/>
+        <v>4315</v>
+      </c>
+      <c r="V18" s="8">
+        <f t="shared" si="87"/>
+        <v>14934</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" ref="W18:X18" si="89">W14-W15-W16-W17</f>
+        <v>-5265</v>
+      </c>
+      <c r="X18" s="8">
+        <f t="shared" si="89"/>
+        <v>-2653</v>
+      </c>
+      <c r="Y18" s="8">
+        <f t="shared" ref="Y18" si="90">Y14-Y15-Y16-Y17</f>
+        <v>2944</v>
+      </c>
+      <c r="Z18" s="8">
+        <f t="shared" ref="Z18" si="91">Z14-Z15-Z16-Z17</f>
+        <v>-962</v>
+      </c>
+      <c r="AA18" s="8">
+        <f t="shared" ref="AA18:AB18" si="92">AA14-AA15-AA16-AA17</f>
+        <v>4119</v>
+      </c>
+      <c r="AB18" s="8">
+        <f t="shared" si="92"/>
+        <v>7563</v>
+      </c>
+      <c r="AC18" s="8">
+        <f t="shared" ref="AC18" si="93">AC14-AC15-AC16-AC17</f>
+        <v>12189</v>
+      </c>
+      <c r="AD18" s="8">
+        <f t="shared" ref="AD18" si="94">AD14-AD15-AD16-AD17</f>
+        <v>13686</v>
+      </c>
+      <c r="AE18" s="8">
+        <f t="shared" ref="AE18:AF18" si="95">AE14-AE15-AE16-AE17</f>
+        <v>12983</v>
+      </c>
+      <c r="AF18" s="8">
         <f t="shared" si="95"/>
-        <v>666</v>
-      </c>
-      <c r="E18" s="8">
-        <f t="shared" si="95"/>
-        <v>316</v>
-      </c>
-      <c r="F18" s="8">
-        <f t="shared" si="95"/>
-        <v>1872</v>
-      </c>
-      <c r="G18" s="8">
-        <f t="shared" si="95"/>
-        <v>1916</v>
-      </c>
-      <c r="H18" s="8">
-        <f t="shared" si="95"/>
-        <v>2605</v>
-      </c>
-      <c r="I18" s="8">
-        <f t="shared" si="95"/>
-        <v>3390</v>
-      </c>
-      <c r="J18" s="8">
-        <f t="shared" si="95"/>
-        <v>3350</v>
-      </c>
-      <c r="K18" s="8">
-        <f t="shared" si="95"/>
-        <v>4401</v>
-      </c>
-      <c r="L18" s="8">
-        <f t="shared" si="95"/>
-        <v>2889</v>
-      </c>
-      <c r="M18" s="8">
-        <f t="shared" si="95"/>
-        <v>2632</v>
-      </c>
-      <c r="N18" s="8">
-        <f t="shared" si="95"/>
-        <v>4053</v>
-      </c>
-      <c r="O18" s="8">
-        <f t="shared" si="95"/>
-        <v>3383</v>
-      </c>
-      <c r="P18" s="8">
-        <f t="shared" si="95"/>
-        <v>6221</v>
-      </c>
-      <c r="Q18" s="8">
-        <f t="shared" si="95"/>
-        <v>6809</v>
-      </c>
-      <c r="R18" s="8">
-        <f t="shared" si="95"/>
-        <v>7765</v>
-      </c>
-      <c r="S18" s="8">
-        <f t="shared" ref="S18:V18" si="96">S14-S15-S16-S17</f>
-        <v>10268</v>
-      </c>
-      <c r="T18" s="8">
-        <f t="shared" ref="T18:U18" si="97">T14-T15-T16-T17</f>
-        <v>8634</v>
-      </c>
-      <c r="U18" s="8">
+        <v>15245</v>
+      </c>
+      <c r="AG18" s="8">
+        <f t="shared" ref="AG18:AL18" si="96">AG14-AG15-AG16-AG17</f>
+        <v>18037</v>
+      </c>
+      <c r="AH18" s="8">
+        <f t="shared" si="96"/>
+        <v>22349</v>
+      </c>
+      <c r="AI18" s="8">
+        <f t="shared" si="96"/>
+        <v>21679</v>
+      </c>
+      <c r="AJ18" s="8">
+        <f t="shared" si="96"/>
+        <v>20857</v>
+      </c>
+      <c r="AK18" s="8">
+        <f t="shared" si="96"/>
+        <v>28170</v>
+      </c>
+      <c r="AL18" s="8">
+        <f t="shared" si="96"/>
+        <v>24624.0265</v>
+      </c>
+      <c r="AN18" s="8">
+        <f t="shared" ref="AN18:AU18" si="97">AN14-AN15-AN16-AN17</f>
+        <v>-111</v>
+      </c>
+      <c r="AO18" s="8">
         <f t="shared" si="97"/>
-        <v>4315</v>
-      </c>
-      <c r="V18" s="8">
-        <f t="shared" si="96"/>
-        <v>14934</v>
-      </c>
-      <c r="W18" s="8">
-        <f t="shared" ref="W18:X18" si="98">W14-W15-W16-W17</f>
-        <v>-5265</v>
-      </c>
-      <c r="X18" s="8">
+        <v>1568</v>
+      </c>
+      <c r="AP18" s="8">
+        <f t="shared" si="97"/>
+        <v>3892</v>
+      </c>
+      <c r="AQ18" s="8">
+        <f t="shared" si="97"/>
+        <v>3807</v>
+      </c>
+      <c r="AR18" s="8">
+        <f t="shared" si="97"/>
+        <v>11261</v>
+      </c>
+      <c r="AS18" s="8">
+        <f t="shared" si="97"/>
+        <v>13975</v>
+      </c>
+      <c r="AT18" s="8">
+        <f t="shared" si="97"/>
+        <v>24178</v>
+      </c>
+      <c r="AU18" s="8">
+        <f t="shared" si="97"/>
+        <v>38151</v>
+      </c>
+      <c r="AV18" s="8">
+        <f t="shared" ref="AV18:BE18" si="98">AV14-AV15-AV16-AV17</f>
+        <v>-5936</v>
+      </c>
+      <c r="AW18" s="8">
         <f t="shared" si="98"/>
-        <v>-2653</v>
-      </c>
-      <c r="Y18" s="8">
-        <f t="shared" ref="Y18" si="99">Y14-Y15-Y16-Y17</f>
-        <v>2944</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" ref="Z18" si="100">Z14-Z15-Z16-Z17</f>
-        <v>-962</v>
-      </c>
-      <c r="AA18" s="8">
-        <f t="shared" ref="AA18:AB18" si="101">AA14-AA15-AA16-AA17</f>
-        <v>4119</v>
-      </c>
-      <c r="AB18" s="8">
-        <f t="shared" si="101"/>
-        <v>7563</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" ref="AC18" si="102">AC14-AC15-AC16-AC17</f>
-        <v>12189</v>
-      </c>
-      <c r="AD18" s="8">
-        <f t="shared" ref="AD18" si="103">AD14-AD15-AD16-AD17</f>
-        <v>13686</v>
-      </c>
-      <c r="AE18" s="8">
-        <f t="shared" ref="AE18:AF18" si="104">AE14-AE15-AE16-AE17</f>
-        <v>12983</v>
-      </c>
-      <c r="AF18" s="8">
-        <f t="shared" si="104"/>
-        <v>15245</v>
-      </c>
-      <c r="AG18" s="8">
-        <f t="shared" ref="AG18:AL18" si="105">AG14-AG15-AG16-AG17</f>
-        <v>18037</v>
-      </c>
-      <c r="AH18" s="8">
-        <f t="shared" si="105"/>
-        <v>22349</v>
-      </c>
-      <c r="AI18" s="8">
-        <f t="shared" si="105"/>
-        <v>21679</v>
-      </c>
-      <c r="AJ18" s="8">
-        <f t="shared" si="105"/>
-        <v>20857</v>
-      </c>
-      <c r="AK18" s="8">
-        <f t="shared" si="105"/>
-        <v>18165.464750000003</v>
-      </c>
-      <c r="AL18" s="8">
-        <f t="shared" si="105"/>
-        <v>26105.270500000006</v>
-      </c>
-      <c r="AN18" s="8">
-        <f t="shared" ref="AN18:AU18" si="106">AN14-AN15-AN16-AN17</f>
-        <v>-111</v>
-      </c>
-      <c r="AO18" s="8">
-        <f t="shared" si="106"/>
-        <v>1568</v>
-      </c>
-      <c r="AP18" s="8">
-        <f t="shared" si="106"/>
-        <v>3892</v>
-      </c>
-      <c r="AQ18" s="8">
-        <f t="shared" si="106"/>
-        <v>3807</v>
-      </c>
-      <c r="AR18" s="8">
-        <f t="shared" si="106"/>
-        <v>11261</v>
-      </c>
-      <c r="AS18" s="8">
-        <f t="shared" si="106"/>
-        <v>13975</v>
-      </c>
-      <c r="AT18" s="8">
-        <f t="shared" si="106"/>
-        <v>24178</v>
-      </c>
-      <c r="AU18" s="8">
-        <f t="shared" si="106"/>
-        <v>38151</v>
-      </c>
-      <c r="AV18" s="8">
-        <f t="shared" ref="AV18:BE18" si="107">AV14-AV15-AV16-AV17</f>
-        <v>-5936</v>
-      </c>
-      <c r="AW18" s="8">
-        <f t="shared" si="107"/>
         <v>37557</v>
       </c>
       <c r="AX18" s="8">
-        <f t="shared" ref="AX18" si="108">AX14-AX15-AX16-AX17</f>
+        <f t="shared" ref="AX18" si="99">AX14-AX15-AX16-AX17</f>
         <v>68614</v>
       </c>
       <c r="AY18" s="8">
-        <f t="shared" si="107"/>
-        <v>86806.735249999911</v>
+        <f t="shared" si="98"/>
+        <v>95330.02649999992</v>
       </c>
       <c r="AZ18" s="8">
-        <f t="shared" si="107"/>
-        <v>106520.96579000005</v>
+        <f t="shared" si="98"/>
+        <v>93356.006560000038</v>
       </c>
       <c r="BA18" s="8">
-        <f t="shared" si="107"/>
-        <v>124464.21612483999</v>
+        <f t="shared" si="98"/>
+        <v>108592.15050415997</v>
       </c>
       <c r="BB18" s="8">
-        <f t="shared" si="107"/>
-        <v>141336.57128343088</v>
+        <f t="shared" si="98"/>
+        <v>123889.07829947522</v>
       </c>
       <c r="BC18" s="8">
-        <f t="shared" si="107"/>
-        <v>147607.47897977129</v>
+        <f t="shared" si="98"/>
+        <v>128479.96392477826</v>
       </c>
       <c r="BD18" s="8">
-        <f t="shared" si="107"/>
-        <v>152545.97963077851</v>
+        <f t="shared" si="98"/>
+        <v>133053.51549614366</v>
       </c>
       <c r="BE18" s="8">
-        <f t="shared" si="107"/>
-        <v>155871.3415613843</v>
+        <f t="shared" si="98"/>
+        <v>135997.27361631437</v>
       </c>
       <c r="BF18" s="8">
-        <f t="shared" ref="BF18:BI18" si="109">BF14-BF15-BF16-BF17</f>
-        <v>159472.0362719245</v>
+        <f t="shared" ref="BF18:BI18" si="100">BF14-BF15-BF16-BF17</f>
+        <v>139334.13225123953</v>
       </c>
       <c r="BG18" s="8">
-        <f t="shared" si="109"/>
-        <v>161312.4531392518</v>
+        <f t="shared" si="100"/>
+        <v>140896.64637264429</v>
       </c>
       <c r="BH18" s="8">
-        <f t="shared" si="109"/>
-        <v>163184.02604754307</v>
+        <f t="shared" si="100"/>
+        <v>142484.99549752436</v>
       </c>
       <c r="BI18" s="8">
-        <f t="shared" si="109"/>
-        <v>165087.71816223403</v>
+        <f t="shared" si="100"/>
+        <v>144100.0010056968</v>
       </c>
     </row>
     <row r="19" spans="2:153" x14ac:dyDescent="0.3">
@@ -5138,12 +5119,11 @@
         <v>2678</v>
       </c>
       <c r="AK19" s="4">
-        <f t="shared" ref="AK19:AL19" si="110">AK18*0.14</f>
-        <v>2543.1650650000006</v>
+        <v>6910</v>
       </c>
       <c r="AL19" s="4">
-        <f t="shared" si="110"/>
-        <v>3654.7378700000013</v>
+        <f t="shared" ref="AK19:AL19" si="101">AL18*0.14</f>
+        <v>3447.3637100000005</v>
       </c>
       <c r="AN19" s="4">
         <v>167</v>
@@ -5188,47 +5168,47 @@
       </c>
       <c r="AY19" s="4">
         <f>SUM(AI19:AL19)</f>
-        <v>13428.902935000002</v>
+        <v>17588.363710000001</v>
       </c>
       <c r="AZ19" s="4">
         <f>AZ18*0.15</f>
-        <v>15978.144868500007</v>
+        <v>14003.400984000005</v>
       </c>
       <c r="BA19" s="4">
-        <f t="shared" ref="BA19:BI19" si="111">BA18*0.15</f>
-        <v>18669.632418726</v>
+        <f t="shared" ref="BA19:BI19" si="102">BA18*0.15</f>
+        <v>16288.822575623995</v>
       </c>
       <c r="BB19" s="4">
-        <f t="shared" si="111"/>
-        <v>21200.485692514631</v>
+        <f t="shared" si="102"/>
+        <v>18583.361744921283</v>
       </c>
       <c r="BC19" s="4">
-        <f t="shared" si="111"/>
-        <v>22141.121846965692</v>
+        <f t="shared" si="102"/>
+        <v>19271.994588716738</v>
       </c>
       <c r="BD19" s="4">
-        <f t="shared" si="111"/>
-        <v>22881.896944616776</v>
+        <f t="shared" si="102"/>
+        <v>19958.02732442155</v>
       </c>
       <c r="BE19" s="4">
-        <f t="shared" si="111"/>
-        <v>23380.701234207645</v>
+        <f t="shared" si="102"/>
+        <v>20399.591042447155</v>
       </c>
       <c r="BF19" s="4">
-        <f t="shared" si="111"/>
-        <v>23920.805440788674</v>
+        <f t="shared" si="102"/>
+        <v>20900.119837685928</v>
       </c>
       <c r="BG19" s="4">
-        <f t="shared" si="111"/>
-        <v>24196.867970887768</v>
+        <f t="shared" si="102"/>
+        <v>21134.496955896644</v>
       </c>
       <c r="BH19" s="4">
-        <f t="shared" si="111"/>
-        <v>24477.603907131459</v>
+        <f t="shared" si="102"/>
+        <v>21372.749324628654</v>
       </c>
       <c r="BI19" s="4">
-        <f t="shared" si="111"/>
-        <v>24763.157724335102</v>
+        <f t="shared" si="102"/>
+        <v>21615.000150854521</v>
       </c>
     </row>
     <row r="20" spans="2:153" x14ac:dyDescent="0.3">
@@ -5338,12 +5318,11 @@
         <v>15</v>
       </c>
       <c r="AK20" s="4">
-        <f t="shared" ref="AK20:AL20" si="112">AK18*0.001</f>
-        <v>18.165464750000002</v>
+        <v>73</v>
       </c>
       <c r="AL20" s="4">
-        <f t="shared" si="112"/>
-        <v>26.105270500000007</v>
+        <f t="shared" ref="AK20:AL20" si="103">AL18*0.001</f>
+        <v>24.624026499999999</v>
       </c>
       <c r="AN20" s="4">
         <v>-37</v>
@@ -5388,47 +5367,47 @@
       </c>
       <c r="AY20" s="4">
         <f>SUM(AI20:AL20)</f>
-        <v>58.270735250000001</v>
+        <v>111.6240265</v>
       </c>
       <c r="AZ20" s="4">
-        <f t="shared" ref="AZ20:BI20" si="113">AZ18*0.001</f>
-        <v>106.52096579000005</v>
+        <f t="shared" ref="AZ20:BI20" si="104">AZ18*0.001</f>
+        <v>93.35600656000004</v>
       </c>
       <c r="BA20" s="4">
-        <f t="shared" si="113"/>
-        <v>124.46421612483999</v>
+        <f t="shared" si="104"/>
+        <v>108.59215050415997</v>
       </c>
       <c r="BB20" s="4">
-        <f t="shared" si="113"/>
-        <v>141.33657128343089</v>
+        <f t="shared" si="104"/>
+        <v>123.88907829947523</v>
       </c>
       <c r="BC20" s="4">
-        <f t="shared" si="113"/>
-        <v>147.60747897977129</v>
+        <f t="shared" si="104"/>
+        <v>128.47996392477827</v>
       </c>
       <c r="BD20" s="4">
-        <f t="shared" si="113"/>
-        <v>152.5459796307785</v>
+        <f t="shared" si="104"/>
+        <v>133.05351549614366</v>
       </c>
       <c r="BE20" s="4">
-        <f t="shared" si="113"/>
-        <v>155.8713415613843</v>
+        <f t="shared" si="104"/>
+        <v>135.99727361631437</v>
       </c>
       <c r="BF20" s="4">
-        <f t="shared" si="113"/>
-        <v>159.47203627192451</v>
+        <f t="shared" si="104"/>
+        <v>139.33413225123954</v>
       </c>
       <c r="BG20" s="4">
-        <f t="shared" si="113"/>
-        <v>161.3124531392518</v>
+        <f t="shared" si="104"/>
+        <v>140.89664637264428</v>
       </c>
       <c r="BH20" s="4">
-        <f t="shared" si="113"/>
-        <v>163.18402604754309</v>
+        <f t="shared" si="104"/>
+        <v>142.48499549752435</v>
       </c>
       <c r="BI20" s="4">
-        <f t="shared" si="113"/>
-        <v>165.08771816223404</v>
+        <f t="shared" si="104"/>
+        <v>144.10000100569681</v>
       </c>
     </row>
     <row r="21" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -5436,604 +5415,604 @@
         <v>49</v>
       </c>
       <c r="C21" s="8">
-        <f t="shared" ref="C21:R21" si="114">C18-C19-C20</f>
+        <f t="shared" ref="C21:R21" si="105">C18-C19-C20</f>
         <v>724</v>
       </c>
       <c r="D21" s="8">
+        <f t="shared" si="105"/>
+        <v>197</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="105"/>
+        <v>256</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="105"/>
+        <v>1856</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="105"/>
+        <v>1629</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="105"/>
+        <v>2534</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="105"/>
+        <v>2883</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="105"/>
+        <v>3027</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="105"/>
+        <v>3561</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="105"/>
+        <v>2625</v>
+      </c>
+      <c r="M21" s="8">
+        <f t="shared" si="105"/>
+        <v>2134</v>
+      </c>
+      <c r="N21" s="8">
+        <f t="shared" si="105"/>
+        <v>3268</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" si="105"/>
+        <v>2535</v>
+      </c>
+      <c r="P21" s="8">
+        <f t="shared" si="105"/>
+        <v>5243</v>
+      </c>
+      <c r="Q21" s="8">
+        <f t="shared" si="105"/>
+        <v>6331</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" si="105"/>
+        <v>7222</v>
+      </c>
+      <c r="S21" s="8">
+        <f t="shared" ref="S21:V21" si="106">S18-S19-S20</f>
+        <v>8107</v>
+      </c>
+      <c r="T21" s="8">
+        <f t="shared" ref="T21:U21" si="107">T18-T19-T20</f>
+        <v>7778</v>
+      </c>
+      <c r="U21" s="8">
+        <f t="shared" si="107"/>
+        <v>3156</v>
+      </c>
+      <c r="V21" s="8">
+        <f t="shared" si="106"/>
+        <v>14323</v>
+      </c>
+      <c r="W21" s="8">
+        <f t="shared" ref="W21:X21" si="108">W18-W19-W20</f>
+        <v>-3844</v>
+      </c>
+      <c r="X21" s="8">
+        <f t="shared" si="108"/>
+        <v>-2028</v>
+      </c>
+      <c r="Y21" s="8">
+        <f t="shared" ref="Y21" si="109">Y18-Y19-Y20</f>
+        <v>2872</v>
+      </c>
+      <c r="Z21" s="8">
+        <f t="shared" ref="Z21" si="110">Z18-Z19-Z20</f>
+        <v>278</v>
+      </c>
+      <c r="AA21" s="8">
+        <f t="shared" ref="AA21:AB21" si="111">AA18-AA19-AA20</f>
+        <v>3172</v>
+      </c>
+      <c r="AB21" s="8">
+        <f t="shared" si="111"/>
+        <v>6750</v>
+      </c>
+      <c r="AC21" s="8">
+        <f t="shared" ref="AC21" si="112">AC18-AC19-AC20</f>
+        <v>9879</v>
+      </c>
+      <c r="AD21" s="8">
+        <f t="shared" ref="AD21" si="113">AD18-AD19-AD20</f>
+        <v>10624</v>
+      </c>
+      <c r="AE21" s="8">
+        <f t="shared" ref="AE21:AF21" si="114">AE18-AE19-AE20</f>
+        <v>10431</v>
+      </c>
+      <c r="AF21" s="8">
         <f t="shared" si="114"/>
-        <v>197</v>
-      </c>
-      <c r="E21" s="8">
-        <f t="shared" si="114"/>
-        <v>256</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="114"/>
-        <v>1856</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="114"/>
-        <v>1629</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="114"/>
-        <v>2534</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" si="114"/>
-        <v>2883</v>
-      </c>
-      <c r="J21" s="8">
-        <f t="shared" si="114"/>
-        <v>3027</v>
-      </c>
-      <c r="K21" s="8">
-        <f t="shared" si="114"/>
-        <v>3561</v>
-      </c>
-      <c r="L21" s="8">
-        <f t="shared" si="114"/>
-        <v>2625</v>
-      </c>
-      <c r="M21" s="8">
-        <f t="shared" si="114"/>
-        <v>2134</v>
-      </c>
-      <c r="N21" s="8">
-        <f t="shared" si="114"/>
-        <v>3268</v>
-      </c>
-      <c r="O21" s="8">
-        <f t="shared" si="114"/>
-        <v>2535</v>
-      </c>
-      <c r="P21" s="8">
-        <f t="shared" si="114"/>
-        <v>5243</v>
-      </c>
-      <c r="Q21" s="8">
-        <f t="shared" si="114"/>
-        <v>6331</v>
-      </c>
-      <c r="R21" s="8">
-        <f t="shared" si="114"/>
-        <v>7222</v>
-      </c>
-      <c r="S21" s="8">
-        <f t="shared" ref="S21:V21" si="115">S18-S19-S20</f>
-        <v>8107</v>
-      </c>
-      <c r="T21" s="8">
-        <f t="shared" ref="T21:U21" si="116">T18-T19-T20</f>
-        <v>7778</v>
-      </c>
-      <c r="U21" s="8">
+        <v>13485</v>
+      </c>
+      <c r="AG21" s="8">
+        <f t="shared" ref="AG21:AH21" si="115">AG18-AG19-AG20</f>
+        <v>15328</v>
+      </c>
+      <c r="AH21" s="8">
+        <f t="shared" si="115"/>
+        <v>20004</v>
+      </c>
+      <c r="AI21" s="8">
+        <f t="shared" ref="AI21:AL21" si="116">AI18-AI19-AI20</f>
+        <v>17127</v>
+      </c>
+      <c r="AJ21" s="8">
         <f t="shared" si="116"/>
-        <v>3156</v>
-      </c>
-      <c r="V21" s="8">
-        <f t="shared" si="115"/>
-        <v>14323</v>
-      </c>
-      <c r="W21" s="8">
-        <f t="shared" ref="W21:X21" si="117">W18-W19-W20</f>
-        <v>-3844</v>
-      </c>
-      <c r="X21" s="8">
+        <v>18164</v>
+      </c>
+      <c r="AK21" s="8">
+        <f t="shared" si="116"/>
+        <v>21187</v>
+      </c>
+      <c r="AL21" s="8">
+        <f t="shared" si="116"/>
+        <v>21152.038763499997</v>
+      </c>
+      <c r="AN21" s="8">
+        <f t="shared" ref="AN21:AV21" si="117">AN18-AN19-AN20</f>
+        <v>-241</v>
+      </c>
+      <c r="AO21" s="8">
         <f t="shared" si="117"/>
-        <v>-2028</v>
-      </c>
-      <c r="Y21" s="8">
-        <f t="shared" ref="Y21" si="118">Y18-Y19-Y20</f>
-        <v>2872</v>
-      </c>
-      <c r="Z21" s="8">
-        <f t="shared" ref="Z21" si="119">Z18-Z19-Z20</f>
-        <v>278</v>
-      </c>
-      <c r="AA21" s="8">
-        <f t="shared" ref="AA21:AB21" si="120">AA18-AA19-AA20</f>
-        <v>3172</v>
-      </c>
-      <c r="AB21" s="8">
+        <v>596</v>
+      </c>
+      <c r="AP21" s="8">
+        <f t="shared" si="117"/>
+        <v>2371</v>
+      </c>
+      <c r="AQ21" s="8">
+        <f t="shared" si="117"/>
+        <v>3033</v>
+      </c>
+      <c r="AR21" s="8">
+        <f t="shared" si="117"/>
+        <v>10073</v>
+      </c>
+      <c r="AS21" s="8">
+        <f t="shared" si="117"/>
+        <v>11588</v>
+      </c>
+      <c r="AT21" s="8">
+        <f t="shared" si="117"/>
+        <v>21331</v>
+      </c>
+      <c r="AU21" s="8">
+        <f t="shared" si="117"/>
+        <v>33364</v>
+      </c>
+      <c r="AV21" s="8">
+        <f t="shared" si="117"/>
+        <v>-2722</v>
+      </c>
+      <c r="AW21" s="8">
+        <f t="shared" ref="AW21:BE21" si="118">AW18-AW19-AW20</f>
+        <v>30425</v>
+      </c>
+      <c r="AX21" s="8">
+        <f t="shared" ref="AX21" si="119">AX18-AX19-AX20</f>
+        <v>59248</v>
+      </c>
+      <c r="AY21" s="8">
+        <f t="shared" si="118"/>
+        <v>77630.038763499921</v>
+      </c>
+      <c r="AZ21" s="8">
+        <f t="shared" si="118"/>
+        <v>79259.249569440028</v>
+      </c>
+      <c r="BA21" s="8">
+        <f t="shared" si="118"/>
+        <v>92194.735778031813</v>
+      </c>
+      <c r="BB21" s="8">
+        <f t="shared" si="118"/>
+        <v>105181.82747625448</v>
+      </c>
+      <c r="BC21" s="8">
+        <f t="shared" si="118"/>
+        <v>109079.48937213674</v>
+      </c>
+      <c r="BD21" s="8">
+        <f t="shared" si="118"/>
+        <v>112962.43465622597</v>
+      </c>
+      <c r="BE21" s="8">
+        <f t="shared" si="118"/>
+        <v>115461.6853002509</v>
+      </c>
+      <c r="BF21" s="8">
+        <f t="shared" ref="BF21:BI21" si="120">BF18-BF19-BF20</f>
+        <v>118294.67828130236</v>
+      </c>
+      <c r="BG21" s="8">
         <f t="shared" si="120"/>
-        <v>6750</v>
-      </c>
-      <c r="AC21" s="8">
-        <f t="shared" ref="AC21" si="121">AC18-AC19-AC20</f>
-        <v>9879</v>
-      </c>
-      <c r="AD21" s="8">
-        <f t="shared" ref="AD21" si="122">AD18-AD19-AD20</f>
-        <v>10624</v>
-      </c>
-      <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AF21" si="123">AE18-AE19-AE20</f>
-        <v>10431</v>
-      </c>
-      <c r="AF21" s="8">
-        <f t="shared" si="123"/>
-        <v>13485</v>
-      </c>
-      <c r="AG21" s="8">
-        <f t="shared" ref="AG21:AH21" si="124">AG18-AG19-AG20</f>
-        <v>15328</v>
-      </c>
-      <c r="AH21" s="8">
-        <f t="shared" si="124"/>
-        <v>20004</v>
-      </c>
-      <c r="AI21" s="8">
-        <f t="shared" ref="AI21:AL21" si="125">AI18-AI19-AI20</f>
-        <v>17127</v>
-      </c>
-      <c r="AJ21" s="8">
-        <f t="shared" si="125"/>
-        <v>18164</v>
-      </c>
-      <c r="AK21" s="8">
-        <f t="shared" si="125"/>
-        <v>15604.134220250002</v>
-      </c>
-      <c r="AL21" s="8">
-        <f t="shared" si="125"/>
-        <v>22424.427359500005</v>
-      </c>
-      <c r="AN21" s="8">
-        <f t="shared" ref="AN21:AV21" si="126">AN18-AN19-AN20</f>
-        <v>-241</v>
-      </c>
-      <c r="AO21" s="8">
-        <f t="shared" si="126"/>
-        <v>596</v>
-      </c>
-      <c r="AP21" s="8">
-        <f t="shared" si="126"/>
-        <v>2371</v>
-      </c>
-      <c r="AQ21" s="8">
-        <f t="shared" si="126"/>
-        <v>3033</v>
-      </c>
-      <c r="AR21" s="8">
-        <f t="shared" si="126"/>
-        <v>10073</v>
-      </c>
-      <c r="AS21" s="8">
-        <f t="shared" si="126"/>
-        <v>11588</v>
-      </c>
-      <c r="AT21" s="8">
-        <f t="shared" si="126"/>
-        <v>21331</v>
-      </c>
-      <c r="AU21" s="8">
-        <f t="shared" si="126"/>
-        <v>33364</v>
-      </c>
-      <c r="AV21" s="8">
-        <f t="shared" si="126"/>
-        <v>-2722</v>
-      </c>
-      <c r="AW21" s="8">
-        <f t="shared" ref="AW21:BE21" si="127">AW18-AW19-AW20</f>
-        <v>30425</v>
-      </c>
-      <c r="AX21" s="8">
-        <f t="shared" ref="AX21" si="128">AX18-AX19-AX20</f>
-        <v>59248</v>
-      </c>
-      <c r="AY21" s="8">
-        <f t="shared" si="127"/>
-        <v>73319.561579749905</v>
-      </c>
-      <c r="AZ21" s="8">
-        <f t="shared" si="127"/>
-        <v>90436.299955710041</v>
-      </c>
-      <c r="BA21" s="8">
-        <f t="shared" si="127"/>
-        <v>105670.11948998916</v>
-      </c>
-      <c r="BB21" s="8">
-        <f t="shared" si="127"/>
-        <v>119994.74901963281</v>
-      </c>
-      <c r="BC21" s="8">
-        <f t="shared" si="127"/>
-        <v>125318.74965382583</v>
-      </c>
-      <c r="BD21" s="8">
-        <f t="shared" si="127"/>
-        <v>129511.53670653095</v>
-      </c>
-      <c r="BE21" s="8">
-        <f t="shared" si="127"/>
-        <v>132334.76898561529</v>
-      </c>
-      <c r="BF21" s="8">
-        <f t="shared" ref="BF21:BI21" si="129">BF18-BF19-BF20</f>
-        <v>135391.75879486388</v>
-      </c>
-      <c r="BG21" s="8">
-        <f t="shared" si="129"/>
-        <v>136954.27271522477</v>
+        <v>119621.25277037501</v>
       </c>
       <c r="BH21" s="8">
-        <f t="shared" si="129"/>
-        <v>138543.2381143641</v>
+        <f t="shared" si="120"/>
+        <v>120969.76117739819</v>
       </c>
       <c r="BI21" s="8">
-        <f t="shared" si="129"/>
-        <v>140159.47271973672</v>
+        <f t="shared" si="120"/>
+        <v>122340.90085383657</v>
       </c>
       <c r="BJ21" s="1">
         <f>BI21*(1+$BL$29)</f>
-        <v>138757.87799253935</v>
+        <v>121117.49184529821</v>
       </c>
       <c r="BK21" s="1">
-        <f t="shared" ref="BK21:DV21" si="130">BJ21*(1+$BL$29)</f>
-        <v>137370.29921261396</v>
+        <f t="shared" ref="BK21:DV21" si="121">BJ21*(1+$BL$29)</f>
+        <v>119906.31692684523</v>
       </c>
       <c r="BL21" s="1">
-        <f t="shared" si="130"/>
-        <v>135996.59622048782</v>
+        <f t="shared" si="121"/>
+        <v>118707.25375757678</v>
       </c>
       <c r="BM21" s="1">
-        <f t="shared" si="130"/>
-        <v>134636.63025828294</v>
+        <f t="shared" si="121"/>
+        <v>117520.181220001</v>
       </c>
       <c r="BN21" s="1">
-        <f t="shared" si="130"/>
-        <v>133290.26395570009</v>
+        <f t="shared" si="121"/>
+        <v>116344.97940780099</v>
       </c>
       <c r="BO21" s="1">
-        <f t="shared" si="130"/>
-        <v>131957.3613161431</v>
+        <f t="shared" si="121"/>
+        <v>115181.52961372297</v>
       </c>
       <c r="BP21" s="1">
-        <f t="shared" si="130"/>
-        <v>130637.78770298166</v>
+        <f t="shared" si="121"/>
+        <v>114029.71431758575</v>
       </c>
       <c r="BQ21" s="1">
-        <f t="shared" si="130"/>
-        <v>129331.40982595184</v>
+        <f t="shared" si="121"/>
+        <v>112889.41717440989</v>
       </c>
       <c r="BR21" s="1">
-        <f t="shared" si="130"/>
-        <v>128038.09572769231</v>
+        <f t="shared" si="121"/>
+        <v>111760.52300266578</v>
       </c>
       <c r="BS21" s="1">
-        <f t="shared" si="130"/>
-        <v>126757.71477041539</v>
+        <f t="shared" si="121"/>
+        <v>110642.91777263912</v>
       </c>
       <c r="BT21" s="1">
-        <f t="shared" si="130"/>
-        <v>125490.13762271123</v>
+        <f t="shared" si="121"/>
+        <v>109536.48859491273</v>
       </c>
       <c r="BU21" s="1">
-        <f t="shared" si="130"/>
-        <v>124235.23624648411</v>
+        <f t="shared" si="121"/>
+        <v>108441.12370896361</v>
       </c>
       <c r="BV21" s="1">
-        <f t="shared" si="130"/>
-        <v>122992.88388401928</v>
+        <f t="shared" si="121"/>
+        <v>107356.71247187398</v>
       </c>
       <c r="BW21" s="1">
-        <f t="shared" si="130"/>
-        <v>121762.95504517909</v>
+        <f t="shared" si="121"/>
+        <v>106283.14534715524</v>
       </c>
       <c r="BX21" s="1">
-        <f t="shared" si="130"/>
-        <v>120545.32549472729</v>
+        <f t="shared" si="121"/>
+        <v>105220.31389368369</v>
       </c>
       <c r="BY21" s="1">
-        <f t="shared" si="130"/>
-        <v>119339.87223978002</v>
+        <f t="shared" si="121"/>
+        <v>104168.11075474686</v>
       </c>
       <c r="BZ21" s="1">
-        <f t="shared" si="130"/>
-        <v>118146.47351738221</v>
+        <f t="shared" si="121"/>
+        <v>103126.42964719939</v>
       </c>
       <c r="CA21" s="1">
-        <f t="shared" si="130"/>
-        <v>116965.00878220839</v>
+        <f t="shared" si="121"/>
+        <v>102095.16535072739</v>
       </c>
       <c r="CB21" s="1">
-        <f t="shared" si="130"/>
-        <v>115795.3586943863</v>
+        <f t="shared" si="121"/>
+        <v>101074.21369722011</v>
       </c>
       <c r="CC21" s="1">
-        <f t="shared" si="130"/>
-        <v>114637.40510744244</v>
+        <f t="shared" si="121"/>
+        <v>100063.47156024791</v>
       </c>
       <c r="CD21" s="1">
-        <f t="shared" si="130"/>
-        <v>113491.03105636801</v>
+        <f t="shared" si="121"/>
+        <v>99062.836844645426</v>
       </c>
       <c r="CE21" s="1">
-        <f t="shared" si="130"/>
-        <v>112356.12074580434</v>
+        <f t="shared" si="121"/>
+        <v>98072.208476198968</v>
       </c>
       <c r="CF21" s="1">
-        <f t="shared" si="130"/>
-        <v>111232.55953834629</v>
+        <f t="shared" si="121"/>
+        <v>97091.486391436978</v>
       </c>
       <c r="CG21" s="1">
-        <f t="shared" si="130"/>
-        <v>110120.23394296283</v>
+        <f t="shared" si="121"/>
+        <v>96120.57152752261</v>
       </c>
       <c r="CH21" s="1">
-        <f t="shared" si="130"/>
-        <v>109019.03160353321</v>
+        <f t="shared" si="121"/>
+        <v>95159.365812247386</v>
       </c>
       <c r="CI21" s="1">
-        <f t="shared" si="130"/>
-        <v>107928.84128749787</v>
+        <f t="shared" si="121"/>
+        <v>94207.772154124905</v>
       </c>
       <c r="CJ21" s="1">
-        <f t="shared" si="130"/>
-        <v>106849.55287462288</v>
+        <f t="shared" si="121"/>
+        <v>93265.694432583652</v>
       </c>
       <c r="CK21" s="1">
-        <f t="shared" si="130"/>
-        <v>105781.05734587664</v>
+        <f t="shared" si="121"/>
+        <v>92333.037488257818</v>
       </c>
       <c r="CL21" s="1">
-        <f t="shared" si="130"/>
-        <v>104723.24677241787</v>
+        <f t="shared" si="121"/>
+        <v>91409.707113375232</v>
       </c>
       <c r="CM21" s="1">
-        <f t="shared" si="130"/>
-        <v>103676.01430469369</v>
+        <f t="shared" si="121"/>
+        <v>90495.610042241475</v>
       </c>
       <c r="CN21" s="1">
-        <f t="shared" si="130"/>
-        <v>102639.25416164675</v>
+        <f t="shared" si="121"/>
+        <v>89590.653941819066</v>
       </c>
       <c r="CO21" s="1">
-        <f t="shared" si="130"/>
-        <v>101612.86162003028</v>
+        <f t="shared" si="121"/>
+        <v>88694.74740240087</v>
       </c>
       <c r="CP21" s="1">
-        <f t="shared" si="130"/>
-        <v>100596.73300382997</v>
+        <f t="shared" si="121"/>
+        <v>87807.799928376859</v>
       </c>
       <c r="CQ21" s="1">
-        <f t="shared" si="130"/>
-        <v>99590.76567379167</v>
+        <f t="shared" si="121"/>
+        <v>86929.721929093095</v>
       </c>
       <c r="CR21" s="1">
-        <f t="shared" si="130"/>
-        <v>98594.858017053746</v>
+        <f t="shared" si="121"/>
+        <v>86060.424709802159</v>
       </c>
       <c r="CS21" s="1">
-        <f t="shared" si="130"/>
-        <v>97608.909436883201</v>
+        <f t="shared" si="121"/>
+        <v>85199.820462704141</v>
       </c>
       <c r="CT21" s="1">
-        <f t="shared" si="130"/>
-        <v>96632.820342514373</v>
+        <f t="shared" si="121"/>
+        <v>84347.822258077096</v>
       </c>
       <c r="CU21" s="1">
-        <f t="shared" si="130"/>
-        <v>95666.492139089227</v>
+        <f t="shared" si="121"/>
+        <v>83504.344035496324</v>
       </c>
       <c r="CV21" s="1">
-        <f t="shared" si="130"/>
-        <v>94709.82721769833</v>
+        <f t="shared" si="121"/>
+        <v>82669.300595141365</v>
       </c>
       <c r="CW21" s="1">
-        <f t="shared" si="130"/>
-        <v>93762.728945521347</v>
+        <f t="shared" si="121"/>
+        <v>81842.607589189953</v>
       </c>
       <c r="CX21" s="1">
-        <f t="shared" si="130"/>
-        <v>92825.101656066137</v>
+        <f t="shared" si="121"/>
+        <v>81024.181513298056</v>
       </c>
       <c r="CY21" s="1">
-        <f t="shared" si="130"/>
-        <v>91896.850639505472</v>
+        <f t="shared" si="121"/>
+        <v>80213.939698165079</v>
       </c>
       <c r="CZ21" s="1">
-        <f t="shared" si="130"/>
-        <v>90977.882133110412</v>
+        <f t="shared" si="121"/>
+        <v>79411.800301183423</v>
       </c>
       <c r="DA21" s="1">
-        <f t="shared" si="130"/>
-        <v>90068.103311779312</v>
+        <f t="shared" si="121"/>
+        <v>78617.682298171581</v>
       </c>
       <c r="DB21" s="1">
-        <f t="shared" si="130"/>
-        <v>89167.422278661514</v>
+        <f t="shared" si="121"/>
+        <v>77831.505475189872</v>
       </c>
       <c r="DC21" s="1">
-        <f t="shared" si="130"/>
-        <v>88275.748055874894</v>
+        <f t="shared" si="121"/>
+        <v>77053.190420437968</v>
       </c>
       <c r="DD21" s="1">
-        <f t="shared" si="130"/>
-        <v>87392.990575316144</v>
+        <f t="shared" si="121"/>
+        <v>76282.658516233583</v>
       </c>
       <c r="DE21" s="1">
-        <f t="shared" si="130"/>
-        <v>86519.060669562983</v>
+        <f t="shared" si="121"/>
+        <v>75519.83193107124</v>
       </c>
       <c r="DF21" s="1">
-        <f t="shared" si="130"/>
-        <v>85653.870062867354</v>
+        <f t="shared" si="121"/>
+        <v>74764.633611760524</v>
       </c>
       <c r="DG21" s="1">
-        <f t="shared" si="130"/>
-        <v>84797.331362238678</v>
+        <f t="shared" si="121"/>
+        <v>74016.987275642925</v>
       </c>
       <c r="DH21" s="1">
-        <f t="shared" si="130"/>
-        <v>83949.358048616297</v>
+        <f t="shared" si="121"/>
+        <v>73276.817402886489</v>
       </c>
       <c r="DI21" s="1">
-        <f t="shared" si="130"/>
-        <v>83109.864468130138</v>
+        <f t="shared" si="121"/>
+        <v>72544.049228857621</v>
       </c>
       <c r="DJ21" s="1">
-        <f t="shared" si="130"/>
-        <v>82278.765823448834</v>
+        <f t="shared" si="121"/>
+        <v>71818.608736569047</v>
       </c>
       <c r="DK21" s="1">
-        <f t="shared" si="130"/>
-        <v>81455.978165214343</v>
+        <f t="shared" si="121"/>
+        <v>71100.422649203363</v>
       </c>
       <c r="DL21" s="1">
-        <f t="shared" si="130"/>
-        <v>80641.418383562195</v>
+        <f t="shared" si="121"/>
+        <v>70389.418422711329</v>
       </c>
       <c r="DM21" s="1">
-        <f t="shared" si="130"/>
-        <v>79835.00419972658</v>
+        <f t="shared" si="121"/>
+        <v>69685.524238484213</v>
       </c>
       <c r="DN21" s="1">
-        <f t="shared" si="130"/>
-        <v>79036.65415772931</v>
+        <f t="shared" si="121"/>
+        <v>68988.668996099368</v>
       </c>
       <c r="DO21" s="1">
-        <f t="shared" si="130"/>
-        <v>78246.287616152011</v>
+        <f t="shared" si="121"/>
+        <v>68298.782306138368</v>
       </c>
       <c r="DP21" s="1">
-        <f t="shared" si="130"/>
-        <v>77463.824739990494</v>
+        <f t="shared" si="121"/>
+        <v>67615.794483076985</v>
       </c>
       <c r="DQ21" s="1">
-        <f t="shared" si="130"/>
-        <v>76689.186492590583</v>
+        <f t="shared" si="121"/>
+        <v>66939.63653824621</v>
       </c>
       <c r="DR21" s="1">
-        <f t="shared" si="130"/>
-        <v>75922.294627664684</v>
+        <f t="shared" si="121"/>
+        <v>66270.240172863749</v>
       </c>
       <c r="DS21" s="1">
-        <f t="shared" si="130"/>
-        <v>75163.071681388043</v>
+        <f t="shared" si="121"/>
+        <v>65607.537771135118</v>
       </c>
       <c r="DT21" s="1">
-        <f t="shared" si="130"/>
-        <v>74411.440964574154</v>
+        <f t="shared" si="121"/>
+        <v>64951.462393423768</v>
       </c>
       <c r="DU21" s="1">
-        <f t="shared" si="130"/>
-        <v>73667.326554928411</v>
+        <f t="shared" si="121"/>
+        <v>64301.947769489532</v>
       </c>
       <c r="DV21" s="1">
-        <f t="shared" si="130"/>
-        <v>72930.65328937913</v>
+        <f t="shared" si="121"/>
+        <v>63658.928291794633</v>
       </c>
       <c r="DW21" s="1">
-        <f t="shared" ref="DW21:EW21" si="131">DV21*(1+$BL$29)</f>
-        <v>72201.346756485334</v>
+        <f t="shared" ref="DW21:EW21" si="122">DV21*(1+$BL$29)</f>
+        <v>63022.339008876683</v>
       </c>
       <c r="DX21" s="1">
-        <f t="shared" si="131"/>
-        <v>71479.333288920476</v>
+        <f t="shared" si="122"/>
+        <v>62392.115618787917</v>
       </c>
       <c r="DY21" s="1">
-        <f t="shared" si="131"/>
-        <v>70764.539956031265</v>
+        <f t="shared" si="122"/>
+        <v>61768.19446260004</v>
       </c>
       <c r="DZ21" s="1">
-        <f t="shared" si="131"/>
-        <v>70056.894556470957</v>
+        <f t="shared" si="122"/>
+        <v>61150.512517974043</v>
       </c>
       <c r="EA21" s="1">
-        <f t="shared" si="131"/>
-        <v>69356.325610906249</v>
+        <f t="shared" si="122"/>
+        <v>60539.007392794301</v>
       </c>
       <c r="EB21" s="1">
-        <f t="shared" si="131"/>
-        <v>68662.762354797189</v>
+        <f t="shared" si="122"/>
+        <v>59933.61731886636</v>
       </c>
       <c r="EC21" s="1">
-        <f t="shared" si="131"/>
-        <v>67976.134731249214</v>
+        <f t="shared" si="122"/>
+        <v>59334.281145677698</v>
       </c>
       <c r="ED21" s="1">
-        <f t="shared" si="131"/>
-        <v>67296.37338393672</v>
+        <f t="shared" si="122"/>
+        <v>58740.938334220918</v>
       </c>
       <c r="EE21" s="1">
-        <f t="shared" si="131"/>
-        <v>66623.409650097354</v>
+        <f t="shared" si="122"/>
+        <v>58153.52895087871</v>
       </c>
       <c r="EF21" s="1">
-        <f t="shared" si="131"/>
-        <v>65957.175553596375</v>
+        <f t="shared" si="122"/>
+        <v>57571.993661369925</v>
       </c>
       <c r="EG21" s="1">
-        <f t="shared" si="131"/>
-        <v>65297.603798060409</v>
+        <f t="shared" si="122"/>
+        <v>56996.273724756225</v>
       </c>
       <c r="EH21" s="1">
-        <f t="shared" si="131"/>
-        <v>64644.627760079806</v>
+        <f t="shared" si="122"/>
+        <v>56426.310987508659</v>
       </c>
       <c r="EI21" s="1">
-        <f t="shared" si="131"/>
-        <v>63998.181482479005</v>
+        <f t="shared" si="122"/>
+        <v>55862.047877633573</v>
       </c>
       <c r="EJ21" s="1">
-        <f t="shared" si="131"/>
-        <v>63358.199667654211</v>
+        <f t="shared" si="122"/>
+        <v>55303.427398857239</v>
       </c>
       <c r="EK21" s="1">
-        <f t="shared" si="131"/>
-        <v>62724.61767097767</v>
+        <f t="shared" si="122"/>
+        <v>54750.393124868664</v>
       </c>
       <c r="EL21" s="1">
-        <f t="shared" si="131"/>
-        <v>62097.371494267893</v>
+        <f t="shared" si="122"/>
+        <v>54202.88919361998</v>
       </c>
       <c r="EM21" s="1">
-        <f t="shared" si="131"/>
-        <v>61476.397779325212</v>
+        <f t="shared" si="122"/>
+        <v>53660.860301683781</v>
       </c>
       <c r="EN21" s="1">
-        <f t="shared" si="131"/>
-        <v>60861.633801531963</v>
+        <f t="shared" si="122"/>
+        <v>53124.251698666943</v>
       </c>
       <c r="EO21" s="1">
-        <f t="shared" si="131"/>
-        <v>60253.01746351664</v>
+        <f t="shared" si="122"/>
+        <v>52593.009181680274</v>
       </c>
       <c r="EP21" s="1">
-        <f t="shared" si="131"/>
-        <v>59650.487288881472</v>
+        <f t="shared" si="122"/>
+        <v>52067.079089863473</v>
       </c>
       <c r="EQ21" s="1">
-        <f t="shared" si="131"/>
-        <v>59053.982415992657</v>
+        <f t="shared" si="122"/>
+        <v>51546.408298964838</v>
       </c>
       <c r="ER21" s="1">
-        <f t="shared" si="131"/>
-        <v>58463.442591832732</v>
+        <f t="shared" si="122"/>
+        <v>51030.944215975192</v>
       </c>
       <c r="ES21" s="1">
-        <f t="shared" si="131"/>
-        <v>57878.808165914408</v>
+        <f t="shared" si="122"/>
+        <v>50520.634773815444</v>
       </c>
       <c r="ET21" s="1">
-        <f t="shared" si="131"/>
-        <v>57300.020084255266</v>
+        <f t="shared" si="122"/>
+        <v>50015.428426077291</v>
       </c>
       <c r="EU21" s="1">
-        <f t="shared" si="131"/>
-        <v>56727.019883412715</v>
+        <f t="shared" si="122"/>
+        <v>49515.274141816517</v>
       </c>
       <c r="EV21" s="1">
-        <f t="shared" si="131"/>
-        <v>56159.749684578586</v>
+        <f t="shared" si="122"/>
+        <v>49020.121400398348</v>
       </c>
       <c r="EW21" s="1">
-        <f t="shared" si="131"/>
-        <v>55598.152187732798</v>
+        <f t="shared" si="122"/>
+        <v>48529.920186394367</v>
       </c>
     </row>
     <row r="22" spans="2:153" x14ac:dyDescent="0.3">
@@ -6144,10 +6123,12 @@
         <v>10637</v>
       </c>
       <c r="AK22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="AL22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="AN22" s="4">
         <v>503.6</v>
@@ -6184,37 +6165,48 @@
         <v>10515</v>
       </c>
       <c r="AY22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="AZ22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BA22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BB22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BC22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BD22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BE22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BF22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BG22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BH22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
       <c r="BI22" s="4">
-        <v>10637</v>
+        <f>10674</f>
+        <v>10674</v>
       </c>
     </row>
     <row r="23" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -6222,236 +6214,236 @@
         <v>50</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23:R23" si="132">C21/C22</f>
+        <f t="shared" ref="C23:R23" si="123">C21/C22</f>
         <v>1.437648927720413</v>
       </c>
       <c r="D23" s="6">
+        <f t="shared" si="123"/>
+        <v>0.39118347895154881</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="123"/>
+        <v>0.50833995234312945</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="123"/>
+        <v>3.6854646544876886</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="123"/>
+        <v>3.2347100873709294</v>
+      </c>
+      <c r="H23" s="6">
+        <f t="shared" si="123"/>
+        <v>5.0317712470214451</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="123"/>
+        <v>5.7247815726767275</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="123"/>
+        <v>6.0107227958697376</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="123"/>
+        <v>7.071088165210484</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="123"/>
+        <v>5.2124702144559167</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="123"/>
+        <v>4.2374900714853059</v>
+      </c>
+      <c r="N23" s="6">
+        <f t="shared" si="123"/>
+        <v>6.4892772041302615</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" si="123"/>
+        <v>5.0337569499602859</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="123"/>
+        <v>10.411040508339951</v>
+      </c>
+      <c r="Q23" s="6">
+        <f t="shared" si="123"/>
+        <v>12.571485305798252</v>
+      </c>
+      <c r="R23" s="6">
+        <f t="shared" si="123"/>
+        <v>14.340746624305003</v>
+      </c>
+      <c r="S23" s="6">
+        <f t="shared" ref="S23:V23" si="124">S21/S22</f>
+        <v>16.098093725178714</v>
+      </c>
+      <c r="T23" s="6">
+        <f t="shared" ref="T23:U23" si="125">T21/T22</f>
+        <v>15.401980198019801</v>
+      </c>
+      <c r="U23" s="6">
+        <f t="shared" si="125"/>
+        <v>6.21259842519685</v>
+      </c>
+      <c r="V23" s="6">
+        <f t="shared" si="124"/>
+        <v>28.194881889763778</v>
+      </c>
+      <c r="W23" s="6">
+        <f t="shared" ref="W23:X23" si="126">W21/W22</f>
+        <v>-7.5520628683693518</v>
+      </c>
+      <c r="X23" s="6">
+        <f t="shared" si="126"/>
+        <v>-0.19931203931203931</v>
+      </c>
+      <c r="Y23" s="6">
+        <f t="shared" ref="Y23" si="127">Y21/Y22</f>
+        <v>0.28181728976547932</v>
+      </c>
+      <c r="Z23" s="6">
+        <f t="shared" ref="Z23" si="128">Z21/Z22</f>
+        <v>2.7201565557729943E-2</v>
+      </c>
+      <c r="AA23" s="6">
+        <f t="shared" ref="AA23:AB23" si="129">AA21/AA22</f>
+        <v>0.30946341463414634</v>
+      </c>
+      <c r="AB23" s="6">
+        <f t="shared" si="129"/>
+        <v>0.65629557608167233</v>
+      </c>
+      <c r="AC23" s="6">
+        <f t="shared" ref="AC23" si="130">AC21/AC22</f>
+        <v>0.9570819608602984</v>
+      </c>
+      <c r="AD23" s="6">
+        <f t="shared" ref="AD23" si="131">AD21/AD22</f>
+        <v>1.0258787176516029</v>
+      </c>
+      <c r="AE23" s="6">
+        <f t="shared" ref="AE23:AF23" si="132">AE21/AE22</f>
+        <v>1.0036563071297988</v>
+      </c>
+      <c r="AF23" s="6">
         <f t="shared" si="132"/>
-        <v>0.39118347895154881</v>
-      </c>
-      <c r="E23" s="6">
-        <f t="shared" si="132"/>
-        <v>0.50833995234312945</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="132"/>
-        <v>3.6854646544876886</v>
-      </c>
-      <c r="G23" s="6">
-        <f t="shared" si="132"/>
-        <v>3.2347100873709294</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="132"/>
-        <v>5.0317712470214451</v>
-      </c>
-      <c r="I23" s="6">
-        <f t="shared" si="132"/>
-        <v>5.7247815726767275</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="132"/>
-        <v>6.0107227958697376</v>
-      </c>
-      <c r="K23" s="6">
-        <f t="shared" si="132"/>
-        <v>7.071088165210484</v>
-      </c>
-      <c r="L23" s="6">
-        <f t="shared" si="132"/>
-        <v>5.2124702144559167</v>
-      </c>
-      <c r="M23" s="6">
-        <f t="shared" si="132"/>
-        <v>4.2374900714853059</v>
-      </c>
-      <c r="N23" s="6">
-        <f t="shared" si="132"/>
-        <v>6.4892772041302615</v>
-      </c>
-      <c r="O23" s="6">
-        <f t="shared" si="132"/>
-        <v>5.0337569499602859</v>
-      </c>
-      <c r="P23" s="6">
-        <f t="shared" si="132"/>
-        <v>10.411040508339951</v>
-      </c>
-      <c r="Q23" s="6">
-        <f t="shared" si="132"/>
-        <v>12.571485305798252</v>
-      </c>
-      <c r="R23" s="6">
-        <f t="shared" si="132"/>
-        <v>14.340746624305003</v>
-      </c>
-      <c r="S23" s="6">
-        <f t="shared" ref="S23:V23" si="133">S21/S22</f>
-        <v>16.098093725178714</v>
-      </c>
-      <c r="T23" s="6">
-        <f t="shared" ref="T23:U23" si="134">T21/T22</f>
-        <v>15.401980198019801</v>
-      </c>
-      <c r="U23" s="6">
+        <v>1.2975079380352159</v>
+      </c>
+      <c r="AG23" s="6">
+        <f t="shared" ref="AG23:AH23" si="133">AG21/AG22</f>
+        <v>1.4577270565858298</v>
+      </c>
+      <c r="AH23" s="6">
+        <f t="shared" si="133"/>
+        <v>1.8957543593631538</v>
+      </c>
+      <c r="AI23" s="6">
+        <f t="shared" ref="AI23:AL23" si="134">AI21/AI22</f>
+        <v>1.6132587317734826</v>
+      </c>
+      <c r="AJ23" s="6">
         <f t="shared" si="134"/>
-        <v>6.21259842519685</v>
-      </c>
-      <c r="V23" s="6">
-        <f t="shared" si="133"/>
-        <v>28.194881889763778</v>
-      </c>
-      <c r="W23" s="6">
-        <f t="shared" ref="W23:X23" si="135">W21/W22</f>
-        <v>-7.5520628683693518</v>
-      </c>
-      <c r="X23" s="6">
+        <v>1.7076243301682805</v>
+      </c>
+      <c r="AK23" s="6">
+        <f t="shared" si="134"/>
+        <v>1.984916619823871</v>
+      </c>
+      <c r="AL23" s="6">
+        <f t="shared" si="134"/>
+        <v>1.9816412557148209</v>
+      </c>
+      <c r="AN23" s="6">
+        <f t="shared" ref="AN23:AV23" si="135">AN21/AN22</f>
+        <v>-0.4785544082605242</v>
+      </c>
+      <c r="AO23" s="6">
         <f t="shared" si="135"/>
-        <v>-0.19931203931203931</v>
-      </c>
-      <c r="Y23" s="6">
-        <f t="shared" ref="Y23" si="136">Y21/Y22</f>
-        <v>0.28181728976547932</v>
-      </c>
-      <c r="Z23" s="6">
-        <f t="shared" ref="Z23" si="137">Z21/Z22</f>
-        <v>2.7201565557729943E-2</v>
-      </c>
-      <c r="AA23" s="6">
-        <f t="shared" ref="AA23:AB23" si="138">AA21/AA22</f>
-        <v>0.30946341463414634</v>
-      </c>
-      <c r="AB23" s="6">
+        <v>1.1834789515488482</v>
+      </c>
+      <c r="AP23" s="6">
+        <f t="shared" si="135"/>
+        <v>4.7081016679904684</v>
+      </c>
+      <c r="AQ23" s="6">
+        <f t="shared" si="135"/>
+        <v>6.0226370135027798</v>
+      </c>
+      <c r="AR23" s="6">
+        <f t="shared" si="135"/>
+        <v>20.001985702938839</v>
+      </c>
+      <c r="AS23" s="6">
+        <f t="shared" si="135"/>
+        <v>23.010325655281967</v>
+      </c>
+      <c r="AT23" s="6">
+        <f t="shared" si="135"/>
+        <v>42.35702938840349</v>
+      </c>
+      <c r="AU23" s="6">
+        <f t="shared" si="135"/>
+        <v>66.25099285146942</v>
+      </c>
+      <c r="AV23" s="6">
+        <f t="shared" si="135"/>
+        <v>-0.26634050880626225</v>
+      </c>
+      <c r="AW23" s="6">
+        <f t="shared" ref="AW23:BE23" si="136">AW21/AW22</f>
+        <v>2.9379103901120125</v>
+      </c>
+      <c r="AX23" s="6">
+        <f t="shared" ref="AX23" si="137">AX21/AX22</f>
+        <v>5.6346172135045176</v>
+      </c>
+      <c r="AY23" s="6">
+        <f t="shared" si="136"/>
+        <v>7.2728160730279106</v>
+      </c>
+      <c r="AZ23" s="6">
+        <f t="shared" si="136"/>
+        <v>7.4254496505002834</v>
+      </c>
+      <c r="BA23" s="6">
+        <f t="shared" si="136"/>
+        <v>8.6373183228435266</v>
+      </c>
+      <c r="BB23" s="6">
+        <f t="shared" si="136"/>
+        <v>9.8540216859897392</v>
+      </c>
+      <c r="BC23" s="6">
+        <f t="shared" si="136"/>
+        <v>10.219176444831998</v>
+      </c>
+      <c r="BD23" s="6">
+        <f t="shared" si="136"/>
+        <v>10.582952469198611</v>
+      </c>
+      <c r="BE23" s="6">
+        <f t="shared" si="136"/>
+        <v>10.817096243231301</v>
+      </c>
+      <c r="BF23" s="6">
+        <f t="shared" ref="BF23:BI23" si="138">BF21/BF22</f>
+        <v>11.082506865402133</v>
+      </c>
+      <c r="BG23" s="6">
         <f t="shared" si="138"/>
-        <v>0.65629557608167233</v>
-      </c>
-      <c r="AC23" s="6">
-        <f t="shared" ref="AC23" si="139">AC21/AC22</f>
-        <v>0.9570819608602984</v>
-      </c>
-      <c r="AD23" s="6">
-        <f t="shared" ref="AD23" si="140">AD21/AD22</f>
-        <v>1.0258787176516029</v>
-      </c>
-      <c r="AE23" s="6">
-        <f t="shared" ref="AE23:AF23" si="141">AE21/AE22</f>
-        <v>1.0036563071297988</v>
-      </c>
-      <c r="AF23" s="6">
-        <f t="shared" si="141"/>
-        <v>1.2975079380352159</v>
-      </c>
-      <c r="AG23" s="6">
-        <f t="shared" ref="AG23:AH23" si="142">AG21/AG22</f>
-        <v>1.4577270565858298</v>
-      </c>
-      <c r="AH23" s="6">
-        <f t="shared" si="142"/>
-        <v>1.8957543593631538</v>
-      </c>
-      <c r="AI23" s="6">
-        <f t="shared" ref="AI23:AL23" si="143">AI21/AI22</f>
-        <v>1.6132587317734826</v>
-      </c>
-      <c r="AJ23" s="6">
-        <f t="shared" si="143"/>
-        <v>1.7076243301682805</v>
-      </c>
-      <c r="AK23" s="6">
-        <f t="shared" si="143"/>
-        <v>1.4669675867490835</v>
-      </c>
-      <c r="AL23" s="6">
-        <f t="shared" si="143"/>
-        <v>2.1081533665037138</v>
-      </c>
-      <c r="AN23" s="6">
-        <f t="shared" ref="AN23:AV23" si="144">AN21/AN22</f>
-        <v>-0.4785544082605242</v>
-      </c>
-      <c r="AO23" s="6">
-        <f t="shared" si="144"/>
-        <v>1.1834789515488482</v>
-      </c>
-      <c r="AP23" s="6">
-        <f t="shared" si="144"/>
-        <v>4.7081016679904684</v>
-      </c>
-      <c r="AQ23" s="6">
-        <f t="shared" si="144"/>
-        <v>6.0226370135027798</v>
-      </c>
-      <c r="AR23" s="6">
-        <f t="shared" si="144"/>
-        <v>20.001985702938839</v>
-      </c>
-      <c r="AS23" s="6">
-        <f t="shared" si="144"/>
-        <v>23.010325655281967</v>
-      </c>
-      <c r="AT23" s="6">
-        <f t="shared" si="144"/>
-        <v>42.35702938840349</v>
-      </c>
-      <c r="AU23" s="6">
-        <f t="shared" si="144"/>
-        <v>66.25099285146942</v>
-      </c>
-      <c r="AV23" s="6">
-        <f t="shared" si="144"/>
-        <v>-0.26634050880626225</v>
-      </c>
-      <c r="AW23" s="6">
-        <f t="shared" ref="AW23:BE23" si="145">AW21/AW22</f>
-        <v>2.9379103901120125</v>
-      </c>
-      <c r="AX23" s="6">
-        <f t="shared" ref="AX23" si="146">AX21/AX22</f>
-        <v>5.6346172135045176</v>
-      </c>
-      <c r="AY23" s="6">
-        <f t="shared" si="145"/>
-        <v>6.8928797198223091</v>
-      </c>
-      <c r="AZ23" s="6">
-        <f t="shared" si="145"/>
-        <v>8.5020494458691402</v>
-      </c>
-      <c r="BA23" s="6">
-        <f t="shared" si="145"/>
-        <v>9.9342032048499718</v>
-      </c>
-      <c r="BB23" s="6">
-        <f t="shared" si="145"/>
-        <v>11.280882675531899</v>
-      </c>
-      <c r="BC23" s="6">
-        <f t="shared" si="145"/>
-        <v>11.781399798235013</v>
-      </c>
-      <c r="BD23" s="6">
-        <f t="shared" si="145"/>
-        <v>12.175569869938043</v>
-      </c>
-      <c r="BE23" s="6">
-        <f t="shared" si="145"/>
-        <v>12.4409860849502</v>
-      </c>
-      <c r="BF23" s="6">
-        <f t="shared" ref="BF23:BI23" si="147">BF21/BF22</f>
-        <v>12.728378188856246</v>
-      </c>
-      <c r="BG23" s="6">
-        <f t="shared" si="147"/>
-        <v>12.875272418466182</v>
+        <v>11.206787780623479</v>
       </c>
       <c r="BH23" s="6">
-        <f t="shared" si="147"/>
-        <v>13.024653390463861</v>
+        <f t="shared" si="138"/>
+        <v>11.33312358791439</v>
       </c>
       <c r="BI23" s="6">
-        <f t="shared" si="147"/>
-        <v>13.176597980608886</v>
+        <f t="shared" si="138"/>
+        <v>11.461579619059076</v>
       </c>
     </row>
     <row r="25" spans="2:153" x14ac:dyDescent="0.3">
@@ -6467,128 +6459,128 @@
         <v>0.33163394286677339</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" ref="H25:V25" si="148">H3/D3-1</f>
+        <f t="shared" ref="H25:V25" si="139">H3/D3-1</f>
         <v>0.28769448373408779</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.17303948832035587</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>8.166969147005454E-2</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>8.4733428255022947E-2</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.12528245041426067</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.17720618739998817</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.13069351230425053</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.22045911968030807</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.40127175368139234</v>
       </c>
       <c r="Q25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.32844988168957356</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.40588025800324479</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.37403503740350375</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>0.15444630204601539</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>3.9830219426232549E-2</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="148"/>
+        <f t="shared" si="139"/>
         <v>5.0664264805224679E-3</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" ref="W25:W27" si="149">W3/S3-1</f>
+        <f t="shared" ref="W25:W27" si="140">W3/S3-1</f>
         <v>-1.8020211859247515E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" ref="X25:X27" si="150">X3/T3-1</f>
+        <f t="shared" ref="X25:X27" si="141">X3/T3-1</f>
         <v>-2.4636231984001111E-2</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" ref="Y25:Y27" si="151">Y3/U3-1</f>
+        <f t="shared" ref="Y25:Y27" si="142">Y3/U3-1</f>
         <v>8.1347036956046281E-2</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" ref="Z25:Z27" si="152">Z3/V3-1</f>
+        <f t="shared" ref="Z25:Z27" si="143">Z3/V3-1</f>
         <v>-1.2392181023860194E-2</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" ref="AA25:AA27" si="153">AA3/W3-1</f>
+        <f t="shared" ref="AA25:AA27" si="144">AA3/W3-1</f>
         <v>9.317155256398868E-3</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" ref="AB25:AB27" si="154">AB3/X3-1</f>
+        <f t="shared" ref="AB25:AB27" si="145">AB3/X3-1</f>
         <v>4.342907644719407E-2</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" ref="AC25:AC27" si="155">AC3/Y3-1</f>
+        <f t="shared" ref="AC25:AC27" si="146">AC3/Y3-1</f>
         <v>6.4560161779575242E-2</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" ref="AD25:AD27" si="156">AD3/Z3-1</f>
+        <f t="shared" ref="AD25:AD27" si="147">AD3/Z3-1</f>
         <v>8.7507620762501626E-2</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AE27" si="157">AE3/AA3-1</f>
+        <f t="shared" ref="AE25:AE27" si="148">AE3/AA3-1</f>
         <v>6.9040557378775347E-2</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" ref="AF25:AF27" si="158">AF3/AB3-1</f>
+        <f t="shared" ref="AF25:AF27" si="149">AF3/AB3-1</f>
         <v>4.2976690608483636E-2</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" ref="AG25:AG27" si="159">AG3/AC3-1</f>
+        <f t="shared" ref="AG25:AG27" si="150">AG3/AC3-1</f>
         <v>7.0127115290243847E-2</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" ref="AH25:AH27" si="160">AH3/AD3-1</f>
+        <f t="shared" ref="AH25:AH27" si="151">AH3/AD3-1</f>
         <v>7.200500632309037E-2</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" ref="AI25:AI27" si="161">AI3/AE3-1</f>
+        <f t="shared" ref="AI25:AI27" si="152">AI3/AE3-1</f>
         <v>5.0151850939834208E-2</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" ref="AJ25:AJ27" si="162">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ25:AJ27" si="153">AJ3/AF3-1</f>
         <v>0.10844743296139292</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" ref="AK25:AK27" si="163">AK3/AG3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <f t="shared" ref="AK25:AK27" si="154">AK3/AG3-1</f>
+        <v>9.5516338515702515E-2</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" ref="AL25:AL27" si="164">AL3/AH3-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AL25:AL27" si="155">AL3/AH3-1</f>
+        <v>8.0000000000000071E-2</v>
       </c>
       <c r="AN25" s="10"/>
       <c r="AO25" s="10">
@@ -6596,83 +6588,83 @@
         <v>0.131107305936073</v>
       </c>
       <c r="AP25" s="10">
-        <f t="shared" ref="AP25:BE25" si="165">AP3/AO3-1</f>
+        <f t="shared" ref="AP25:BE25" si="156">AP3/AO3-1</f>
         <v>0.19423979411616288</v>
       </c>
       <c r="AQ25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>0.25254317857708752</v>
       </c>
       <c r="AR25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>0.19686772593867019</v>
       </c>
       <c r="AS25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>0.13030335059718845</v>
       </c>
       <c r="AT25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>0.34604474867056934</v>
       </c>
       <c r="AU25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>0.11982493110714865</v>
       </c>
       <c r="AV25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>4.6073610243726471E-3</v>
       </c>
       <c r="AW25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>5.3462110077768354E-2</v>
       </c>
       <c r="AX25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>6.4184581475416946E-2</v>
       </c>
       <c r="AY25" s="10">
-        <f t="shared" si="165"/>
-        <v>6.0229259927068624E-2</v>
+        <f t="shared" si="156"/>
+        <v>8.360690533985049E-2</v>
       </c>
       <c r="AZ25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>5.0000000000000044E-2</v>
       </c>
       <c r="BA25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BB25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BC25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BD25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BE25" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="156"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF25" s="10">
-        <f t="shared" ref="BF25:BF27" si="166">BF3/BE3-1</f>
+        <f t="shared" ref="BF25:BF27" si="157">BF3/BE3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG25" s="10">
-        <f t="shared" ref="BG25:BG27" si="167">BG3/BF3-1</f>
+        <f t="shared" ref="BG25:BG27" si="158">BG3/BF3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH25" s="10">
-        <f t="shared" ref="BH25:BH27" si="168">BH3/BG3-1</f>
+        <f t="shared" ref="BH25:BH27" si="159">BH3/BG3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI25" s="10">
-        <f t="shared" ref="BI25:BI27" si="169">BI3/BH3-1</f>
+        <f t="shared" ref="BI25:BI27" si="160">BI3/BH3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -6689,212 +6681,212 @@
         <v>0.62245409015025044</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" ref="H26:V26" si="170">H4/D4-1</f>
+        <f t="shared" ref="H26:V26" si="161">H4/D4-1</f>
         <v>0.5913701741105224</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.52443910256410264</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.44725010455876202</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.30766064721922115</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.3104366853772238</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.32522996057818654</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.33276740237691005</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.32238265727662596</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.40365906780891536</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.43351512146752613</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.47713782355332701</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.5181636964089138</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.42433019551049966</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.28970971386410271</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="170"/>
+        <f t="shared" si="161"/>
         <v>0.21095799922934355</v>
       </c>
       <c r="W26" s="10">
+        <f t="shared" si="140"/>
+        <v>0.17563250827993016</v>
+      </c>
+      <c r="X26" s="10">
+        <f t="shared" si="141"/>
+        <v>0.17399593289273008</v>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" si="142"/>
+        <v>0.21140231693363853</v>
+      </c>
+      <c r="Z26" s="10">
+        <f t="shared" si="143"/>
+        <v>0.19208739923631746</v>
+      </c>
+      <c r="AA26" s="10">
+        <f t="shared" si="144"/>
+        <v>0.17316508026471511</v>
+      </c>
+      <c r="AB26" s="10">
+        <f t="shared" si="145"/>
+        <v>0.16535981069920669</v>
+      </c>
+      <c r="AC26" s="10">
+        <f t="shared" si="146"/>
+        <v>0.179321438585617</v>
+      </c>
+      <c r="AD26" s="10">
+        <f t="shared" si="147"/>
+        <v>0.1853876170986235</v>
+      </c>
+      <c r="AE26" s="10">
+        <f t="shared" si="148"/>
+        <v>0.17080864486977276</v>
+      </c>
+      <c r="AF26" s="10">
         <f t="shared" si="149"/>
-        <v>0.17563250827993016</v>
-      </c>
-      <c r="X26" s="10">
+        <v>0.14673992382317413</v>
+      </c>
+      <c r="AG26" s="10">
         <f t="shared" si="150"/>
-        <v>0.17399593289273008</v>
-      </c>
-      <c r="Y26" s="10">
+        <v>0.14220642706977671</v>
+      </c>
+      <c r="AH26" s="10">
         <f t="shared" si="151"/>
-        <v>0.21140231693363853</v>
-      </c>
-      <c r="Z26" s="10">
+        <v>0.13197795363400466</v>
+      </c>
+      <c r="AI26" s="10">
         <f t="shared" si="152"/>
-        <v>0.19208739923631746</v>
-      </c>
-      <c r="AA26" s="10">
+        <v>0.11285468093885775</v>
+      </c>
+      <c r="AJ26" s="10">
         <f t="shared" si="153"/>
-        <v>0.17316508026471511</v>
-      </c>
-      <c r="AB26" s="10">
+        <v>0.15100453661697988</v>
+      </c>
+      <c r="AK26" s="10">
         <f t="shared" si="154"/>
-        <v>0.16535981069920669</v>
-      </c>
-      <c r="AC26" s="10">
+        <v>0.16252903282352427</v>
+      </c>
+      <c r="AL26" s="10">
         <f t="shared" si="155"/>
-        <v>0.179321438585617</v>
-      </c>
-      <c r="AD26" s="10">
-        <f t="shared" si="156"/>
-        <v>0.1853876170986235</v>
-      </c>
-      <c r="AE26" s="10">
-        <f t="shared" si="157"/>
-        <v>0.17080864486977276</v>
-      </c>
-      <c r="AF26" s="10">
-        <f t="shared" si="158"/>
-        <v>0.14673992382317413</v>
-      </c>
-      <c r="AG26" s="10">
-        <f t="shared" si="159"/>
-        <v>0.14220642706977671</v>
-      </c>
-      <c r="AH26" s="10">
-        <f t="shared" si="160"/>
-        <v>0.13197795363400466</v>
-      </c>
-      <c r="AI26" s="10">
-        <f t="shared" si="161"/>
-        <v>0.11285468093885775</v>
-      </c>
-      <c r="AJ26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.15100453661697988</v>
-      </c>
-      <c r="AK26" s="10">
-        <f t="shared" si="163"/>
-        <v>0.1399999999999999</v>
-      </c>
-      <c r="AL26" s="10">
-        <f t="shared" si="164"/>
         <v>0.12999999999999989</v>
       </c>
       <c r="AN26" s="10"/>
       <c r="AO26" s="10">
-        <f t="shared" ref="AO26:BE26" si="171">AO4/AN4-1</f>
+        <f t="shared" ref="AO26:BE26" si="162">AO4/AN4-1</f>
         <v>0.46699809604400255</v>
       </c>
       <c r="AP26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.48972528661042602</v>
       </c>
       <c r="AQ26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.43492570543536124</v>
       </c>
       <c r="AR26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.53425304415286545</v>
       </c>
       <c r="AS26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.3203513168887131</v>
       </c>
       <c r="AT26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.41655080547808354</v>
       </c>
       <c r="AU26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.34020770030972858</v>
       </c>
       <c r="AV26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.18877365316727701</v>
       </c>
       <c r="AW26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.17638943197999124</v>
       </c>
       <c r="AX26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>0.14659859892504823</v>
       </c>
       <c r="AY26" s="10">
-        <f t="shared" si="171"/>
-        <v>0.13359630026692337</v>
+        <f t="shared" si="162"/>
+        <v>0.1392201789699381</v>
       </c>
       <c r="AZ26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>9.000000000000008E-2</v>
       </c>
       <c r="BA26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>8.0000000000000071E-2</v>
       </c>
       <c r="BB26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>6.0000000000000053E-2</v>
       </c>
       <c r="BC26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>4.0000000000000036E-2</v>
       </c>
       <c r="BD26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="BE26" s="10">
-        <f t="shared" si="171"/>
+        <f t="shared" si="162"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF26" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="157"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="BG26" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="158"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH26" s="10">
-        <f t="shared" si="168"/>
+        <f t="shared" si="159"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI26" s="10">
-        <f t="shared" si="169"/>
+        <f t="shared" si="160"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -6911,212 +6903,212 @@
         <v>0.42918743349946809</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" ref="H27:V27" si="172">H5/D5-1</f>
+        <f t="shared" ref="H27:V27" si="163">H5/D5-1</f>
         <v>0.39338690554604128</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.29334308705193846</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.19734339073329688</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.16962501469378166</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.1988806111258179</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.23693792420814486</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.20797701117665746</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.26385259631490787</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.40230900258658764</v>
       </c>
       <c r="Q27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.37387290836084075</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.43594816839553041</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.43823888034777081</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.27181932697498645</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>0.15255083467679031</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="163"/>
         <v>9.4436701047349692E-2</v>
       </c>
       <c r="W27" s="10">
+        <f t="shared" si="140"/>
+        <v>7.3038574245747334E-2</v>
+      </c>
+      <c r="X27" s="10">
+        <f t="shared" si="141"/>
+        <v>7.2108241952600016E-2</v>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" si="142"/>
+        <v>0.14699671515720314</v>
+      </c>
+      <c r="Z27" s="10">
+        <f t="shared" si="143"/>
+        <v>8.5814921549791867E-2</v>
+      </c>
+      <c r="AA27" s="10">
+        <f t="shared" si="144"/>
+        <v>9.3727456975026602E-2</v>
+      </c>
+      <c r="AB27" s="10">
+        <f t="shared" si="145"/>
+        <v>0.10845967302901816</v>
+      </c>
+      <c r="AC27" s="10">
+        <f t="shared" si="146"/>
+        <v>0.125742519728405</v>
+      </c>
+      <c r="AD27" s="10">
+        <f t="shared" si="147"/>
+        <v>0.13911825420230017</v>
+      </c>
+      <c r="AE27" s="10">
+        <f t="shared" si="148"/>
+        <v>0.12527677884388888</v>
+      </c>
+      <c r="AF27" s="10">
         <f t="shared" si="149"/>
-        <v>7.3038574245747334E-2</v>
-      </c>
-      <c r="X27" s="10">
+        <v>0.10115862869559389</v>
+      </c>
+      <c r="AG27" s="10">
         <f t="shared" si="150"/>
-        <v>7.2108241952600016E-2</v>
-      </c>
-      <c r="Y27" s="10">
+        <v>0.11038348371225104</v>
+      </c>
+      <c r="AH27" s="10">
         <f t="shared" si="151"/>
-        <v>0.14699671515720314</v>
-      </c>
-      <c r="Z27" s="10">
+        <v>0.10491230341078239</v>
+      </c>
+      <c r="AI27" s="10">
         <f t="shared" si="152"/>
-        <v>8.5814921549791867E-2</v>
-      </c>
-      <c r="AA27" s="10">
+        <v>8.6202926461660834E-2</v>
+      </c>
+      <c r="AJ27" s="10">
         <f t="shared" si="153"/>
-        <v>9.3727456975026602E-2</v>
-      </c>
-      <c r="AB27" s="10">
+        <v>0.13329774221669588</v>
+      </c>
+      <c r="AK27" s="10">
         <f t="shared" si="154"/>
-        <v>0.10845967302901816</v>
-      </c>
-      <c r="AC27" s="10">
+        <v>0.13401562214795093</v>
+      </c>
+      <c r="AL27" s="10">
         <f t="shared" si="155"/>
-        <v>0.125742519728405</v>
-      </c>
-      <c r="AD27" s="10">
-        <f t="shared" si="156"/>
-        <v>0.13911825420230017</v>
-      </c>
-      <c r="AE27" s="10">
-        <f t="shared" si="157"/>
-        <v>0.12527677884388888</v>
-      </c>
-      <c r="AF27" s="10">
-        <f t="shared" si="158"/>
-        <v>0.10115862869559389</v>
-      </c>
-      <c r="AG27" s="10">
-        <f t="shared" si="159"/>
-        <v>0.11038348371225104</v>
-      </c>
-      <c r="AH27" s="10">
-        <f t="shared" si="160"/>
-        <v>0.10491230341078239</v>
-      </c>
-      <c r="AI27" s="10">
-        <f t="shared" si="161"/>
-        <v>8.6202926461660834E-2</v>
-      </c>
-      <c r="AJ27" s="10">
-        <f t="shared" si="162"/>
-        <v>0.13329774221669588</v>
-      </c>
-      <c r="AK27" s="10">
-        <f t="shared" si="163"/>
-        <v>0.10170565909477136</v>
-      </c>
-      <c r="AL27" s="10">
-        <f t="shared" si="164"/>
-        <v>9.0592890005964044E-2</v>
+        <v>0.10810716111442442</v>
       </c>
       <c r="AN27" s="10"/>
       <c r="AO27" s="10">
-        <f t="shared" ref="AO27:BE27" si="173">AO5/AN5-1</f>
+        <f t="shared" ref="AO27:BE27" si="164">AO5/AN5-1</f>
         <v>0.20247673843664304</v>
       </c>
       <c r="AP27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.27083528026465808</v>
       </c>
       <c r="AQ27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.30796326119408479</v>
       </c>
       <c r="AR27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.3093396152159491</v>
       </c>
       <c r="AS27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.20454125820676983</v>
       </c>
       <c r="AT27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.37623430604373276</v>
       </c>
       <c r="AU27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.21695366571345676</v>
       </c>
       <c r="AV27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>9.399517263985091E-2</v>
       </c>
       <c r="AW27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.1182957412988368</v>
       </c>
       <c r="AX27" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="164"/>
         <v>0.1099089224666614</v>
       </c>
       <c r="AY27" s="10">
-        <f t="shared" si="173"/>
-        <v>0.10227978600505661</v>
+        <f t="shared" si="164"/>
+        <v>0.11548180995957402</v>
       </c>
       <c r="AZ27" s="10">
-        <f t="shared" si="173"/>
-        <v>7.3577459177837312E-2</v>
+        <f t="shared" si="164"/>
+        <v>7.3413999315320222E-2</v>
       </c>
       <c r="BA27" s="10">
-        <f t="shared" si="173"/>
-        <v>6.3938124151305731E-2</v>
+        <f t="shared" si="164"/>
+        <v>6.3775783872743963E-2</v>
       </c>
       <c r="BB27" s="10">
-        <f t="shared" si="173"/>
-        <v>4.8224631792403327E-2</v>
+        <f t="shared" si="164"/>
+        <v>4.8103800846839295E-2</v>
       </c>
       <c r="BC27" s="10">
-        <f t="shared" si="173"/>
-        <v>3.2286240381456333E-2</v>
+        <f t="shared" si="164"/>
+        <v>3.2206188535998548E-2</v>
       </c>
       <c r="BD27" s="10">
-        <f t="shared" si="173"/>
-        <v>2.6189024660443261E-2</v>
+        <f t="shared" si="164"/>
+        <v>2.6149176500987359E-2</v>
       </c>
       <c r="BE27" s="10">
-        <f t="shared" si="173"/>
-        <v>2.000000000000024E-2</v>
+        <f t="shared" si="164"/>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="BF27" s="10">
-        <f t="shared" si="166"/>
-        <v>1.6212008944810119E-2</v>
+        <f t="shared" si="157"/>
+        <v>1.6172252476597704E-2</v>
       </c>
       <c r="BG27" s="10">
-        <f t="shared" si="167"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="158"/>
+        <v>9.9999999999997868E-3</v>
       </c>
       <c r="BH27" s="10">
-        <f t="shared" si="168"/>
-        <v>1.0000000000000009E-2</v>
+        <f t="shared" si="159"/>
+        <v>1.0000000000000231E-2</v>
       </c>
       <c r="BI27" s="10">
-        <f t="shared" si="169"/>
+        <f t="shared" si="160"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -7125,19 +7117,19 @@
         <v>52</v>
       </c>
       <c r="C28" s="10">
-        <f t="shared" ref="C28:F28" si="174">C7/C5</f>
+        <f t="shared" ref="C28:F28" si="165">C7/C5</f>
         <v>0.37167497339978722</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="165"/>
         <v>0.38213674087735477</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="165"/>
         <v>0.37022220190197513</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="165"/>
         <v>0.36324086480406265</v>
       </c>
       <c r="G28" s="10">
@@ -7145,215 +7137,215 @@
         <v>0.39784883037498531</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" ref="H28:V28" si="175">H7/H5</f>
+        <f t="shared" ref="H28:V28" si="166">H7/H5</f>
         <v>0.4207918919941005</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.4166607748868778</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.38126355635991876</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.4318257956448911</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.42689735663365086</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.40981123447792972</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.38267552637899288</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.41344165827280921</v>
       </c>
       <c r="P28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.40772899046247973</v>
       </c>
       <c r="Q28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.40604295595194756</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.36853171916689897</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.42495254243535635</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.43247258577997877</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.43210121647475003</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="166"/>
         <v>0.39717783017494834</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" ref="W28:AE28" si="176">W7/W5</f>
+        <f t="shared" ref="W28:AE28" si="167">W7/W5</f>
         <v>0.42891862182680085</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.4521008957883102</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.44714833085498934</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.42602075011393797</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.46771306082067871</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.48376654785203488</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.47567495789157344</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.45544566106342044</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="167"/>
         <v>0.49318624269954575</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" ref="AF28:AH28" si="177">AF7/AF5</f>
+        <f t="shared" ref="AF28:AH28" si="168">AF7/AF5</f>
         <v>0.50137521371564497</v>
       </c>
       <c r="AG28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="168"/>
         <v>0.49031640829069029</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" si="177"/>
+        <f t="shared" si="168"/>
         <v>0.47339077276987307</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" ref="AI28:AL28" si="178">AI7/AI5</f>
+        <f t="shared" ref="AI28:AL28" si="169">AI7/AI5</f>
         <v>0.50550855351487467</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="178"/>
+        <f t="shared" si="169"/>
         <v>0.51813931855314788</v>
       </c>
       <c r="AK28" s="10">
-        <f t="shared" si="178"/>
-        <v>0.5</v>
+        <f t="shared" si="169"/>
+        <v>0.50785096215220149</v>
       </c>
       <c r="AL28" s="10">
-        <f t="shared" si="178"/>
+        <f t="shared" si="169"/>
         <v>0.49</v>
       </c>
       <c r="AN28" s="10">
-        <f t="shared" ref="AN28:BE28" si="179">AN7/AN5</f>
+        <f t="shared" ref="AN28:BE28" si="170">AN7/AN5</f>
         <v>0.29482626871038792</v>
       </c>
       <c r="AO28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.33040203353083003</v>
       </c>
       <c r="AP28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.35093060366064405</v>
       </c>
       <c r="AQ28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.3706835482891615</v>
       </c>
       <c r="AR28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.40247416128852193</v>
       </c>
       <c r="AS28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.40990011478600608</v>
       </c>
       <c r="AT28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.3956779186870571</v>
       </c>
       <c r="AU28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.42032514441639601</v>
       </c>
       <c r="AV28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.43805339865326287</v>
       </c>
       <c r="AW28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.46982088955000567</v>
       </c>
       <c r="AX28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.48854393464156787</v>
       </c>
       <c r="AY28" s="10">
-        <f t="shared" si="179"/>
-        <v>0.50263286303760679</v>
+        <f t="shared" si="170"/>
+        <v>0.50454316970664292</v>
       </c>
       <c r="AZ28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.51</v>
       </c>
       <c r="BA28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.52</v>
       </c>
       <c r="BB28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.53</v>
       </c>
       <c r="BC28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.53</v>
       </c>
       <c r="BD28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.53</v>
       </c>
       <c r="BE28" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="170"/>
         <v>0.53</v>
       </c>
       <c r="BF28" s="10">
-        <f t="shared" ref="BF28:BI28" si="180">BF7/BF5</f>
+        <f t="shared" ref="BF28:BI28" si="171">BF7/BF5</f>
         <v>0.53</v>
       </c>
       <c r="BG28" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="171"/>
         <v>0.53</v>
       </c>
       <c r="BH28" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="171"/>
         <v>0.53</v>
       </c>
       <c r="BI28" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="171"/>
         <v>0.53</v>
       </c>
     </row>
@@ -7362,19 +7354,19 @@
         <v>53</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:F29" si="181">C14/C5</f>
+        <f t="shared" ref="C29:F29" si="172">C14/C5</f>
         <v>2.8140225121800973E-2</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="172"/>
         <v>1.6545909629824794E-2</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="172"/>
         <v>7.932516459400147E-3</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="172"/>
         <v>3.5184358096372388E-2</v>
       </c>
       <c r="G29" s="10">
@@ -7382,216 +7374,216 @@
         <v>3.7753222836095765E-2</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" ref="H29:V29" si="182">H14/H5</f>
+        <f t="shared" ref="H29:V29" si="173">H14/H5</f>
         <v>5.6404341413606625E-2</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>6.5822963800904979E-2</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>5.230509926363925E-2</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>7.4036850921273031E-2</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>4.8640464324017411E-2</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>4.5112244752147014E-2</v>
       </c>
       <c r="N29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>4.4363370197971111E-2</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>5.2868048560674334E-2</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>6.5716663667446468E-2</v>
       </c>
       <c r="Q29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>6.4423526964480726E-2</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>5.4740950181195493E-2</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>8.1691516614755155E-2</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>6.8111071807569867E-2</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>4.3785871566256365E-2</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="173"/>
         <v>2.5179751404535267E-2</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" ref="W29:AE29" si="183">W14/W5</f>
+        <f t="shared" ref="W29:AE29" si="174">W14/W5</f>
         <v>3.1508708048504003E-2</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>2.7360311463780786E-2</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>1.986609074672898E-2</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>1.8344012224873328E-2</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>3.7484885126964934E-2</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>5.7157527365812637E-2</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>7.8192377850618167E-2</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>7.771782938438819E-2</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="174"/>
         <v>0.10680817511321374</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" ref="AF29:AH29" si="184">AF14/AF5</f>
+        <f t="shared" ref="AF29:AH29" si="175">AF14/AF5</f>
         <v>9.9150543665569649E-2</v>
       </c>
       <c r="AG29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="175"/>
         <v>0.1095879202150091</v>
       </c>
       <c r="AH29" s="10">
-        <f t="shared" si="184"/>
+        <f t="shared" si="175"/>
         <v>0.1129068330919315</v>
       </c>
       <c r="AI29" s="10">
-        <f t="shared" ref="AI29:AL29" si="185">AI14/AI5</f>
+        <f t="shared" ref="AI29:AL29" si="176">AI14/AI5</f>
         <v>0.11823315153500742</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="185"/>
+        <f t="shared" si="176"/>
         <v>0.11431586981669867</v>
       </c>
       <c r="AK29" s="10">
-        <f t="shared" si="185"/>
-        <v>9.9778935084610471E-2</v>
+        <f t="shared" si="176"/>
+        <v>9.6698100117112273E-2</v>
       </c>
       <c r="AL29" s="10">
-        <f t="shared" si="185"/>
-        <v>0.12148549432136835</v>
+        <f t="shared" si="176"/>
+        <v>0.11244718604113167</v>
       </c>
       <c r="AN29" s="10">
-        <f t="shared" ref="AN29:BE29" si="186">AN14/AN5</f>
+        <f t="shared" ref="AN29:BE29" si="177">AN14/AN5</f>
         <v>2.000269699285297E-3</v>
       </c>
       <c r="AO29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>2.0867988710913405E-2</v>
       </c>
       <c r="AP29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>3.0782354195621642E-2</v>
       </c>
       <c r="AQ29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>2.3090416380870993E-2</v>
       </c>
       <c r="AR29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>5.3330585219441187E-2</v>
       </c>
       <c r="AS29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>5.1831941879781268E-2</v>
       </c>
       <c r="AT29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>5.9313999751336569E-2</v>
       </c>
       <c r="AU29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>5.2954097509269465E-2</v>
       </c>
       <c r="AV29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>2.3829581912242232E-2</v>
       </c>
       <c r="AW29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>6.4114407996033296E-2</v>
       </c>
       <c r="AX29" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="177"/>
         <v>0.1075194487420038</v>
       </c>
       <c r="AY29" s="10">
-        <f t="shared" si="186"/>
-        <v>0.1136527405332559</v>
+        <f t="shared" si="177"/>
+        <v>0.1101659059126177</v>
       </c>
       <c r="AZ29" s="10">
-        <f t="shared" si="186"/>
-        <v>0.13163240119080352</v>
+        <f t="shared" si="177"/>
+        <v>0.1187911984065969</v>
       </c>
       <c r="BA29" s="10">
-        <f t="shared" si="186"/>
-        <v>0.14572210245234218</v>
+        <f t="shared" si="177"/>
+        <v>0.13015151076753337</v>
       </c>
       <c r="BB29" s="10">
-        <f t="shared" si="186"/>
-        <v>0.15871904003787402</v>
+        <f t="shared" si="177"/>
+        <v>0.14186949913873032</v>
       </c>
       <c r="BC29" s="10">
-        <f t="shared" si="186"/>
-        <v>0.16062666515368212</v>
+        <f t="shared" si="177"/>
+        <v>0.14239009364657859</v>
       </c>
       <c r="BD29" s="10">
-        <f t="shared" si="186"/>
-        <v>0.16171413413855437</v>
+        <f t="shared" si="177"/>
+        <v>0.1435490322276608</v>
       </c>
       <c r="BE29" s="10">
-        <f t="shared" si="186"/>
-        <v>0.16183893741331759</v>
+        <f t="shared" si="177"/>
+        <v>0.14364184887531348</v>
       </c>
       <c r="BF29" s="10">
-        <f t="shared" ref="BF29:BI29" si="187">BF14/BF5</f>
-        <v>0.16278123711468764</v>
+        <f t="shared" ref="BF29:BI29" si="178">BF14/BF5</f>
+        <v>0.14462213355161269</v>
       </c>
       <c r="BG29" s="10">
-        <f t="shared" si="187"/>
-        <v>0.16275622741099935</v>
+        <f t="shared" si="178"/>
+        <v>0.14452941459442506</v>
       </c>
       <c r="BH29" s="10">
-        <f t="shared" si="187"/>
-        <v>0.16273072246565398</v>
+        <f t="shared" si="178"/>
+        <v>0.14443485961828337</v>
       </c>
       <c r="BI29" s="10">
-        <f t="shared" si="187"/>
-        <v>0.16270471247188584</v>
+        <f t="shared" si="178"/>
+        <v>0.14433843226637644</v>
       </c>
       <c r="BK29" t="s">
         <v>61</v>
@@ -7605,19 +7597,19 @@
         <v>54</v>
       </c>
       <c r="C30" s="10">
-        <f t="shared" ref="C30:F30" si="188">C8/C5</f>
+        <f t="shared" ref="C30:F30" si="179">C8/C5</f>
         <v>0.1315170521364171</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="179"/>
         <v>0.13589777367935713</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="179"/>
         <v>0.1467629846378932</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="188"/>
+        <f t="shared" si="179"/>
         <v>0.14844590012075495</v>
       </c>
       <c r="G30" s="10">
@@ -7625,215 +7617,215 @@
         <v>0.15265859488264566</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" ref="H30:V30" si="189">H8/H5</f>
+        <f t="shared" ref="H30:V30" si="180">H8/H5</f>
         <v>0.1499829822637371</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.14626343325791855</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.13854081759529172</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.14407035175879396</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.14622105860828971</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.14528229090753206</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.13943753788441965</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.15282563749138525</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.15527712794673384</v>
       </c>
       <c r="Q30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.15294607103853555</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.1471387041535582</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.15232495991448422</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.15597806862398303</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.16693137927300292</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="189"/>
+        <f t="shared" si="180"/>
         <v>0.16334090181352429</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" ref="W30:AE30" si="190">W8/W5</f>
+        <f t="shared" ref="W30:AE30" si="181">W8/W5</f>
         <v>0.17408367970870117</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.1677912136859297</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.16194207756036538</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.15484169325219163</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.16414359521977417</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.15853939858464242</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.15595144077213924</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.15353522278640394</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="190"/>
+        <f t="shared" si="181"/>
         <v>0.15572209080823093</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" ref="AF30:AH30" si="191">AF8/AF5</f>
+        <f t="shared" ref="AF30:AH30" si="182">AF8/AF5</f>
         <v>0.1592544787365604</v>
       </c>
       <c r="AG30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="182"/>
         <v>0.15521441114824674</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" si="191"/>
+        <f t="shared" si="182"/>
         <v>0.14889878163074038</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" ref="AI30:AL30" si="192">AI8/AI5</f>
+        <f t="shared" ref="AI30:AL30" si="183">AI8/AI5</f>
         <v>0.15798467240969505</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="183"/>
         <v>0.15489379971616318</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="192"/>
-        <v>0.16</v>
+        <f t="shared" si="183"/>
+        <v>0.15362798261632135</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="192"/>
+        <f t="shared" si="183"/>
         <v>0.15</v>
       </c>
       <c r="AN30" s="10">
-        <f t="shared" ref="AN30:BE30" si="193">AN8/AN5</f>
+        <f t="shared" ref="AN30:BE30" si="184">AN8/AN5</f>
         <v>0.12098260439609836</v>
       </c>
       <c r="AO30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.1253200755097845</v>
       </c>
       <c r="AP30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.12956385536852788</v>
       </c>
       <c r="AQ30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.14195517974205302</v>
       </c>
       <c r="AR30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.14610948657503425</v>
       </c>
       <c r="AS30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.14341477673765338</v>
       </c>
       <c r="AT30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15157072402503211</v>
       </c>
       <c r="AU30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15987118525739535</v>
       </c>
       <c r="AV30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.16401126107283703</v>
       </c>
       <c r="AW30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.1576572109571405</v>
       </c>
       <c r="AX30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15440647439725749</v>
       </c>
       <c r="AY30" s="10">
-        <f t="shared" si="193"/>
-        <v>0.15542371502447827</v>
+        <f t="shared" si="184"/>
+        <v>0.15381840796684063</v>
       </c>
       <c r="AZ30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15</v>
       </c>
       <c r="BA30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15</v>
       </c>
       <c r="BB30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15</v>
       </c>
       <c r="BC30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15</v>
       </c>
       <c r="BD30" s="10">
-        <f t="shared" si="193"/>
-        <v>0.14999999999999997</v>
+        <f t="shared" si="184"/>
+        <v>0.15</v>
       </c>
       <c r="BE30" s="10">
-        <f t="shared" si="193"/>
+        <f t="shared" si="184"/>
         <v>0.15</v>
       </c>
       <c r="BF30" s="10">
-        <f t="shared" ref="BF30:BI30" si="194">BF8/BF5</f>
+        <f t="shared" ref="BF30:BI30" si="185">BF8/BF5</f>
         <v>0.15</v>
       </c>
       <c r="BG30" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="185"/>
         <v>0.15</v>
       </c>
       <c r="BH30" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="185"/>
         <v>0.15</v>
       </c>
       <c r="BI30" s="10">
-        <f t="shared" si="194"/>
+        <f t="shared" si="185"/>
         <v>0.15</v>
       </c>
       <c r="BK30" t="s">
@@ -7856,212 +7848,212 @@
         <v>0.4057291666666667</v>
       </c>
       <c r="H31" s="10">
-        <f t="shared" ref="H31:V31" si="195">H9/D9-1</f>
+        <f t="shared" ref="H31:V31" si="186">H9/D9-1</f>
         <v>0.30148048452220721</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.33239209358612354</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.42761627906976751</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>1.9370137087810302</v>
       </c>
       <c r="L31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>2.1247845570492934</v>
       </c>
       <c r="M31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>1.7853466545564638</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.98330278965587459</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.17635927841554189</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.14594594594594601</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.19304347826086965</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.23706365503080074</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.33919571045576413</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.33529072006160954</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.310131195335277</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="195"/>
+        <f t="shared" si="186"/>
         <v>0.27089385011204259</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" ref="W31" si="196">W9/S9-1</f>
+        <f t="shared" ref="W31" si="187">W9/S9-1</f>
         <v>0.18850096092248569</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" ref="X31" si="197">X9/T9-1</f>
+        <f t="shared" ref="X31" si="188">X9/T9-1</f>
         <v>0.3028620863672411</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" ref="Y31" si="198">Y9/U9-1</f>
+        <f t="shared" ref="Y31" si="189">Y9/U9-1</f>
         <v>0.35500695410292082</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" ref="Z31" si="199">Z9/V9-1</f>
+        <f t="shared" ref="Z31" si="190">Z9/V9-1</f>
         <v>0.35923724939593815</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" ref="AA31" si="200">AA9/W9-1</f>
+        <f t="shared" ref="AA31" si="191">AA9/W9-1</f>
         <v>0.37784665139469076</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" ref="AB31" si="201">AB9/X9-1</f>
+        <f t="shared" ref="AB31" si="192">AB9/X9-1</f>
         <v>0.21353474988933163</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" ref="AC31" si="202">AC9/Y9-1</f>
+        <f t="shared" ref="AC31" si="193">AC9/Y9-1</f>
         <v>8.8170387477546797E-2</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" ref="AD31" si="203">AD9/Z9-1</f>
+        <f t="shared" ref="AD31" si="194">AD9/Z9-1</f>
         <v>5.880657249927923E-2</v>
       </c>
       <c r="AE31" s="10">
-        <f t="shared" ref="AE31" si="204">AE9/AA9-1</f>
+        <f t="shared" ref="AE31" si="195">AE9/AA9-1</f>
         <v>-1.2713936430317485E-3</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" ref="AF31" si="205">AF9/AB9-1</f>
+        <f t="shared" ref="AF31" si="196">AF9/AB9-1</f>
         <v>1.7007888377182923E-2</v>
       </c>
       <c r="AG31" s="10">
-        <f t="shared" ref="AG31" si="206">AG9/AC9-1</f>
+        <f t="shared" ref="AG31" si="197">AG9/AC9-1</f>
         <v>4.9143989058152204E-2</v>
       </c>
       <c r="AH31" s="10">
-        <f t="shared" ref="AH31" si="207">AH9/AD9-1</f>
+        <f t="shared" ref="AH31" si="198">AH9/AD9-1</f>
         <v>6.9561666212905049E-2</v>
       </c>
       <c r="AI31" s="10">
-        <f t="shared" ref="AI31" si="208">AI9/AE9-1</f>
+        <f t="shared" ref="AI31" si="199">AI9/AE9-1</f>
         <v>0.12583235409322358</v>
       </c>
       <c r="AJ31" s="10">
-        <f t="shared" ref="AJ31" si="209">AJ9/AF9-1</f>
+        <f t="shared" ref="AJ31" si="200">AJ9/AF9-1</f>
         <v>0.21798780487804881</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" ref="AK31" si="210">AK9/AG9-1</f>
-        <v>0.24</v>
+        <f t="shared" ref="AK31" si="201">AK9/AG9-1</f>
+        <v>0.30195549561699253</v>
       </c>
       <c r="AL31" s="10">
-        <f t="shared" ref="AL31" si="211">AL9/AH9-1</f>
-        <v>0.19999999999999996</v>
+        <f t="shared" ref="AL31" si="202">AL9/AH9-1</f>
+        <v>0.30000000000000004</v>
       </c>
       <c r="AN31" s="10"/>
       <c r="AO31" s="10">
-        <f t="shared" ref="AO31:BE31" si="212">AO9/AN9-1</f>
+        <f t="shared" ref="AO31:BE31" si="203">AO9/AN9-1</f>
         <v>0.21283471837488466</v>
       </c>
       <c r="AP31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>0.37666539779215835</v>
       </c>
       <c r="AQ31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>0.3919535462463708</v>
       </c>
       <c r="AR31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>0.37206992451330945</v>
       </c>
       <c r="AS31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>1.6011292891269728</v>
       </c>
       <c r="AT31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>0.18941333630190349</v>
       </c>
       <c r="AU31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>0.31152604239786608</v>
       </c>
       <c r="AV31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>0.3061621351602084</v>
       </c>
       <c r="AW31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>0.16949175692841445</v>
       </c>
       <c r="AX31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
         <v>3.4126743126766446E-2</v>
       </c>
       <c r="AY31" s="10">
-        <f t="shared" si="212"/>
-        <v>0.19747244307914702</v>
+        <f t="shared" si="203"/>
+        <v>0.23965824900614385</v>
       </c>
       <c r="AZ31" s="10">
-        <f t="shared" si="212"/>
-        <v>8.0000000000000071E-2</v>
+        <f t="shared" si="203"/>
+        <v>0.12000000000000011</v>
       </c>
       <c r="BA31" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="203"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="BB31" s="10">
+        <f t="shared" si="203"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BB31" s="10">
-        <f t="shared" si="212"/>
+      <c r="BC31" s="10">
+        <f t="shared" si="203"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BC31" s="10">
-        <f t="shared" si="212"/>
+      <c r="BD31" s="10">
+        <f t="shared" si="203"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD31" s="10">
-        <f t="shared" si="212"/>
+      <c r="BE31" s="10">
+        <f t="shared" si="203"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE31" s="10">
-        <f t="shared" si="212"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BF31" s="10">
-        <f t="shared" ref="BF31" si="213">BF9/BE9-1</f>
+        <f t="shared" ref="BF31" si="204">BF9/BE9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG31" s="10">
-        <f t="shared" ref="BG31" si="214">BG9/BF9-1</f>
+        <f t="shared" ref="BG31" si="205">BG9/BF9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH31" s="10">
-        <f t="shared" ref="BH31" si="215">BH9/BG9-1</f>
+        <f t="shared" ref="BH31" si="206">BH9/BG9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI31" s="10">
-        <f t="shared" ref="BI31" si="216">BI9/BH9-1</f>
+        <f t="shared" ref="BI31" si="207">BI9/BH9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK31" t="s">
@@ -8069,7 +8061,7 @@
       </c>
       <c r="BL31" s="4">
         <f>NPV(BL30,AX21:EW21)</f>
-        <v>2269554.1773097329</v>
+        <v>2000973.7734789902</v>
       </c>
     </row>
     <row r="32" spans="2:153" x14ac:dyDescent="0.3">
@@ -8077,19 +8069,19 @@
         <v>56</v>
       </c>
       <c r="C32" s="10">
-        <f t="shared" ref="C32:F32" si="217">C10/C5</f>
+        <f t="shared" ref="C32:F32" si="208">C10/C5</f>
         <v>0.13476507812062496</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" si="217"/>
+        <f t="shared" si="208"/>
         <v>0.14619944671321303</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="217"/>
+        <f t="shared" si="208"/>
         <v>0.13588149231894661</v>
       </c>
       <c r="F32" s="10">
-        <f t="shared" si="217"/>
+        <f t="shared" si="208"/>
         <v>0.10444477527996957</v>
       </c>
       <c r="G32" s="10">
@@ -8097,215 +8089,215 @@
         <v>0.13242035970377336</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:V32" si="218">H10/H5</f>
+        <f t="shared" ref="H32:V32" si="209">H10/H5</f>
         <v>0.13703059410808152</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>0.12659078054298642</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>0.10595029219568131</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>6.137353433835846E-2</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>6.767711816289193E-2</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>6.7904145410897246E-2</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>7.0587966192801679E-2</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>6.3987700789906163E-2</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>4.8868544178513586E-2</v>
       </c>
       <c r="Q32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>5.6518799729575124E-2</v>
       </c>
       <c r="R32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>5.8962207797379637E-2</v>
       </c>
       <c r="S32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>5.7197884221972389E-2</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>6.6536964980544747E-2</v>
       </c>
       <c r="U32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>7.2284590116593869E-2</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="218"/>
+        <f t="shared" si="209"/>
         <v>7.8668529677175206E-2</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" ref="W32:AE32" si="219">W10/W5</f>
+        <f t="shared" ref="W32:AE32" si="210">W10/W5</f>
         <v>7.1450654391810656E-2</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>8.3194483395747074E-2</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>8.6655494449296225E-2</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>8.5909224953754595E-2</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>7.9869344681920251E-2</v>
       </c>
       <c r="AB32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>7.9958030405631667E-2</v>
       </c>
       <c r="AC32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>7.3740416401668965E-2</v>
       </c>
       <c r="AD32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>7.5911532645724603E-2</v>
       </c>
       <c r="AE32" s="10">
-        <f t="shared" si="219"/>
+        <f t="shared" si="210"/>
         <v>6.7418866397326138E-2</v>
       </c>
       <c r="AF32" s="10">
-        <f t="shared" ref="AF32:AH32" si="220">AF10/AF5</f>
+        <f t="shared" ref="AF32:AH32" si="211">AF10/AF5</f>
         <v>7.1038066726585886E-2</v>
       </c>
       <c r="AG32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="211"/>
         <v>6.6774926515480532E-2</v>
       </c>
       <c r="AH32" s="10">
-        <f t="shared" si="220"/>
+        <f t="shared" si="211"/>
         <v>6.9885831132316611E-2</v>
       </c>
       <c r="AI32" s="10">
-        <f t="shared" ref="AI32:AL32" si="221">AI10/AI5</f>
+        <f t="shared" ref="AI32:AL32" si="212">AI10/AI5</f>
         <v>6.2717210455652123E-2</v>
       </c>
       <c r="AJ32" s="10">
-        <f t="shared" si="221"/>
+        <f t="shared" si="212"/>
         <v>6.80731297181906E-2</v>
       </c>
       <c r="AK32" s="10">
-        <f t="shared" si="221"/>
+        <f t="shared" si="212"/>
+        <v>6.4861324645194229E-2</v>
+      </c>
+      <c r="AL32" s="10">
+        <f t="shared" si="212"/>
         <v>6.5000000000000002E-2</v>
       </c>
-      <c r="AL32" s="10">
-        <f t="shared" si="221"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
       <c r="AN32" s="10">
-        <f t="shared" ref="AN32:BE32" si="222">AN10/AN5</f>
+        <f t="shared" ref="AN32:BE32" si="213">AN10/AN5</f>
         <v>0.10422753629702881</v>
       </c>
       <c r="AO32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.11718969029774032</v>
       </c>
       <c r="AP32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.11828336532168517</v>
       </c>
       <c r="AQ32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.12717438970910686</v>
       </c>
       <c r="AR32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.12382400048091993</v>
       </c>
       <c r="AS32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>6.7299534439366607E-2</v>
       </c>
       <c r="AT32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>5.7011272742343237E-2</v>
       </c>
       <c r="AU32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>6.9283686161993263E-2</v>
       </c>
       <c r="AV32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>8.2177815219569517E-2</v>
       </c>
       <c r="AW32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>7.7194081265168718E-2</v>
       </c>
       <c r="AX32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>6.8824172086293947E-2</v>
       </c>
       <c r="AY32" s="10">
-        <f t="shared" si="222"/>
-        <v>6.5227549603972118E-2</v>
+        <f t="shared" si="213"/>
+        <v>6.5189747038517099E-2</v>
       </c>
       <c r="AZ32" s="10">
-        <f t="shared" si="222"/>
-        <v>5.9999999999999991E-2</v>
+        <f t="shared" si="213"/>
+        <v>0.06</v>
       </c>
       <c r="BA32" s="10">
-        <f t="shared" si="222"/>
-        <v>5.9999999999999991E-2</v>
+        <f t="shared" si="213"/>
+        <v>0.06</v>
       </c>
       <c r="BB32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.06</v>
       </c>
       <c r="BC32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.06</v>
       </c>
       <c r="BD32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.06</v>
       </c>
       <c r="BE32" s="10">
-        <f t="shared" si="222"/>
+        <f t="shared" si="213"/>
         <v>0.06</v>
       </c>
       <c r="BF32" s="10">
-        <f t="shared" ref="BF32:BI32" si="223">BF10/BF5</f>
+        <f t="shared" ref="BF32:BI32" si="214">BF10/BF5</f>
         <v>0.06</v>
       </c>
       <c r="BG32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="214"/>
         <v>0.06</v>
       </c>
       <c r="BH32" s="10">
-        <f t="shared" si="223"/>
-        <v>5.9999999999999991E-2</v>
+        <f t="shared" si="214"/>
+        <v>0.06</v>
       </c>
       <c r="BI32" s="10">
-        <f t="shared" si="223"/>
+        <f t="shared" si="214"/>
         <v>0.06</v>
       </c>
       <c r="BK32" t="s">
@@ -8329,212 +8321,212 @@
         <v>0.34213836477987414</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" ref="H33:V33" si="224">H11/D11-1</f>
+        <f t="shared" ref="H33:V33" si="215">H11/D11-1</f>
         <v>0.27116704805491998</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>8.4375000000000089E-2</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>6.9923371647509613E-2</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>9.9343955014058016E-2</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.14311431143114306</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.29490874159462055</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.26410026857654434</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.23785166240409206</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.24409448818897639</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.23738872403560829</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.39376770538243622</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.36845730027548207</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.36582278481012653</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.29076738609112707</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="224"/>
+        <f t="shared" si="215"/>
         <v>0.28302845528455278</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" ref="W33" si="225">W11/S11-1</f>
+        <f t="shared" ref="W33" si="216">W11/S11-1</f>
         <v>0.30548565676899853</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" ref="X33" si="226">X11/T11-1</f>
+        <f t="shared" ref="X33" si="217">X11/T11-1</f>
         <v>0.34522706209453191</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33" si="227">Y11/U11-1</f>
+        <f t="shared" ref="Y33" si="218">Y11/U11-1</f>
         <v>0.42173711100789602</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" ref="Z33" si="228">Z11/V11-1</f>
+        <f t="shared" ref="Z33" si="219">Z11/V11-1</f>
         <v>0.32000000000000006</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" ref="AA33" si="229">AA11/W11-1</f>
+        <f t="shared" ref="AA33" si="220">AA11/W11-1</f>
         <v>0.17309175019275247</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" ref="AB33" si="230">AB11/X11-1</f>
+        <f t="shared" ref="AB33" si="221">AB11/X11-1</f>
         <v>0.10299689975887016</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" ref="AC33" si="231">AC11/Y11-1</f>
+        <f t="shared" ref="AC33" si="222">AC11/Y11-1</f>
         <v>-0.16334531198954594</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" ref="AD33" si="232">AD11/Z11-1</f>
+        <f t="shared" ref="AD33" si="223">AD11/Z11-1</f>
         <v>-9.6909690969096962E-2</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" ref="AE33" si="233">AE11/AA11-1</f>
+        <f t="shared" ref="AE33" si="224">AE11/AA11-1</f>
         <v>-9.8915543871179734E-2</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" ref="AF33" si="234">AF11/AB11-1</f>
+        <f t="shared" ref="AF33" si="225">AF11/AB11-1</f>
         <v>-5.0281074328544673E-2</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" ref="AG33" si="235">AG11/AC11-1</f>
+        <f t="shared" ref="AG33" si="226">AG11/AC11-1</f>
         <v>5.9351815696993437E-2</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" ref="AH33" si="236">AH11/AD11-1</f>
+        <f t="shared" ref="AH33" si="227">AH11/AD11-1</f>
         <v>-4.8837209302325602E-2</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" ref="AI33" si="237">AI11/AE11-1</f>
+        <f t="shared" ref="AI33" si="228">AI11/AE11-1</f>
         <v>-4.1575492341356712E-2</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" ref="AJ33" si="238">AJ11/AF11-1</f>
+        <f t="shared" ref="AJ33" si="229">AJ11/AF11-1</f>
         <v>-2.4991779020059224E-2</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" ref="AK33" si="239">AK11/AG11-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AK33" si="230">AK11/AG11-1</f>
+        <v>5.9712495392554299E-2</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" ref="AL33" si="240">AL11/AH11-1</f>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" ref="AL33" si="231">AL11/AH11-1</f>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AN33" s="10"/>
       <c r="AO33" s="10">
-        <f t="shared" ref="AO33:BE33" si="241">AO11/AN11-1</f>
+        <f t="shared" ref="AO33:BE33" si="232">AO11/AN11-1</f>
         <v>0.12564432989690721</v>
       </c>
       <c r="AP33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>0.39210074413279905</v>
       </c>
       <c r="AQ33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>0.51027960526315796</v>
       </c>
       <c r="AR33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>0.18050639803974944</v>
       </c>
       <c r="AS33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>0.19995387453874547</v>
       </c>
       <c r="AT33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>0.28156832596578907</v>
       </c>
       <c r="AU33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>0.32318536292741462</v>
       </c>
       <c r="AV33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>0.34772753031848569</v>
       </c>
       <c r="AW33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>-6.3072912286603611E-3</v>
       </c>
       <c r="AX33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>-3.8676371022342559E-2</v>
       </c>
       <c r="AY33" s="10">
-        <f t="shared" si="241"/>
-        <v>2.9087067523549948E-3</v>
+        <f t="shared" si="232"/>
+        <v>1.0137336033101407E-2</v>
       </c>
       <c r="AZ33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="BA33" s="10">
+        <f t="shared" si="232"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BA33" s="10">
-        <f t="shared" si="241"/>
+      <c r="BB33" s="10">
+        <f t="shared" si="232"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB33" s="10">
-        <f t="shared" si="241"/>
+      <c r="BC33" s="10">
+        <f t="shared" si="232"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC33" s="10">
-        <f t="shared" si="241"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
       <c r="BD33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BE33" s="10">
-        <f t="shared" si="241"/>
+        <f t="shared" si="232"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BF33" s="10">
-        <f t="shared" ref="BF33" si="242">BF11/BE11-1</f>
+        <f t="shared" ref="BF33" si="233">BF11/BE11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BG33" s="10">
-        <f t="shared" ref="BG33" si="243">BG11/BF11-1</f>
+        <f t="shared" ref="BG33" si="234">BG11/BF11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BH33" s="10">
-        <f t="shared" ref="BH33" si="244">BH11/BG11-1</f>
+        <f t="shared" ref="BH33" si="235">BH11/BG11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BI33" s="10">
-        <f t="shared" ref="BI33" si="245">BI11/BH11-1</f>
+        <f t="shared" ref="BI33" si="236">BI11/BH11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BK33" t="s">
@@ -8542,7 +8534,7 @@
       </c>
       <c r="BL33" s="4">
         <f>BL31+BL32</f>
-        <v>2318133.1773097329</v>
+        <v>2049552.7734789902</v>
       </c>
     </row>
     <row r="34" spans="2:64" x14ac:dyDescent="0.3">
@@ -8550,235 +8542,235 @@
         <v>47</v>
       </c>
       <c r="C34" s="10">
-        <f t="shared" ref="C34:V34" si="246">C19/C18</f>
+        <f t="shared" ref="C34:V34" si="237">C19/C18</f>
         <v>0.2402938090241343</v>
       </c>
       <c r="D34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.70120120120120122</v>
       </c>
       <c r="E34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.18354430379746836</v>
       </c>
       <c r="F34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>8.5470085470085479E-3</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.14979123173277661</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>2.8406909788867563E-2</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.14985250737463127</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>9.7611940298507463E-2</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.18995682799363781</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>8.8958116995500172E-2</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.18768996960486323</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.19393042190969653</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.21992314513745195</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.1581739270213792</v>
       </c>
       <c r="Q34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>8.3565868703186955E-2</v>
       </c>
       <c r="R34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>7.2891178364455897E-2</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.20997273081417997</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.1005327773917072</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>0.26767091541135574</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="237"/>
         <v>4.0980313378867012E-2</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" ref="W34:AE34" si="247">W19/W18</f>
+        <f t="shared" ref="W34:AE34" si="238">W19/W18</f>
         <v>0.27008547008547007</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>0.24010554089709762</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>2.34375E-2</v>
       </c>
       <c r="Z34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>1.2754677754677755</v>
       </c>
       <c r="AA34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>0.23015294974508377</v>
       </c>
       <c r="AB34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>0.10630702102340341</v>
       </c>
       <c r="AC34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>0.18918697185987365</v>
       </c>
       <c r="AD34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>0.22373228116323249</v>
       </c>
       <c r="AE34" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="238"/>
         <v>0.1900177154740815</v>
       </c>
       <c r="AF34" s="10">
-        <f t="shared" ref="AF34:AH34" si="248">AF19/AF18</f>
+        <f t="shared" ref="AF34:AH34" si="239">AF19/AF18</f>
         <v>0.11590685470646113</v>
       </c>
       <c r="AG34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="239"/>
         <v>0.15002494871652713</v>
       </c>
       <c r="AH34" s="10">
-        <f t="shared" si="248"/>
+        <f t="shared" si="239"/>
         <v>0.10403150029084075</v>
       </c>
       <c r="AI34" s="10">
-        <f t="shared" ref="AI34:AL34" si="249">AI19/AI18</f>
+        <f t="shared" ref="AI34:AL34" si="240">AI19/AI18</f>
         <v>0.21001891231145348</v>
       </c>
       <c r="AJ34" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="240"/>
         <v>0.1283981397132857</v>
       </c>
       <c r="AK34" s="10">
-        <f t="shared" si="249"/>
+        <f t="shared" si="240"/>
+        <v>0.2452964146254881</v>
+      </c>
+      <c r="AL34" s="10">
+        <f t="shared" si="240"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AL34" s="10">
-        <f t="shared" si="249"/>
-        <v>0.14000000000000001</v>
-      </c>
       <c r="AN34" s="10">
-        <f t="shared" ref="AN34:BE34" si="250">AN19/AN18</f>
+        <f t="shared" ref="AN34:BE34" si="241">AN19/AN18</f>
         <v>-1.5045045045045045</v>
       </c>
       <c r="AO34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.60586734693877553</v>
       </c>
       <c r="AP34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.36613566289825283</v>
       </c>
       <c r="AQ34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.20225899658523772</v>
       </c>
       <c r="AR34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.106207264008525</v>
       </c>
       <c r="AS34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.16980322003577816</v>
       </c>
       <c r="AT34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.1184134337000579</v>
       </c>
       <c r="AU34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.12557993237398757</v>
       </c>
       <c r="AV34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.54194743935309975</v>
       </c>
       <c r="AW34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.18957850733551668</v>
       </c>
       <c r="AX34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.13503075174162707</v>
       </c>
       <c r="AY34" s="10">
-        <f t="shared" si="250"/>
-        <v>0.15469885944132447</v>
+        <f t="shared" si="241"/>
+        <v>0.18449972538295703</v>
       </c>
       <c r="AZ34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.15</v>
       </c>
       <c r="BA34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.15</v>
       </c>
       <c r="BB34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.15</v>
       </c>
       <c r="BC34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.15</v>
       </c>
       <c r="BD34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.15</v>
       </c>
       <c r="BE34" s="10">
-        <f t="shared" si="250"/>
+        <f t="shared" si="241"/>
         <v>0.15</v>
       </c>
       <c r="BF34" s="10">
-        <f t="shared" ref="BF34:BI34" si="251">BF19/BF18</f>
+        <f t="shared" ref="BF34:BI34" si="242">BF19/BF18</f>
         <v>0.15</v>
       </c>
       <c r="BG34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="242"/>
         <v>0.15</v>
       </c>
       <c r="BH34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="242"/>
         <v>0.15</v>
       </c>
       <c r="BI34" s="10">
-        <f t="shared" si="251"/>
+        <f t="shared" si="242"/>
         <v>0.15</v>
       </c>
       <c r="BK34" t="s">
@@ -8786,7 +8778,7 @@
       </c>
       <c r="BL34" s="3">
         <f>BL33/BE22</f>
-        <v>217.93110626207886</v>
+        <v>192.01356318896291</v>
       </c>
     </row>
     <row r="35" spans="2:64" x14ac:dyDescent="0.3">
@@ -8794,19 +8786,19 @@
         <v>58</v>
       </c>
       <c r="C35" s="10">
-        <f t="shared" ref="C35:F35" si="252">C21/C5</f>
+        <f t="shared" ref="C35:F35" si="243">C21/C5</f>
         <v>2.027216217729742E-2</v>
       </c>
       <c r="D35" s="10">
-        <f t="shared" si="252"/>
+        <f t="shared" si="243"/>
         <v>5.1903570017125542E-3</v>
       </c>
       <c r="E35" s="10">
-        <f t="shared" si="252"/>
+        <f t="shared" si="243"/>
         <v>5.8522311631309439E-3</v>
       </c>
       <c r="F35" s="10">
-        <f t="shared" si="252"/>
+        <f t="shared" si="243"/>
         <v>3.0701536731014178E-2</v>
       </c>
       <c r="G35" s="10">
@@ -8814,223 +8806,223 @@
         <v>3.1914893617021274E-2</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" ref="H35:V35" si="253">H21/H5</f>
+        <f t="shared" ref="H35:V35" si="244">H21/H5</f>
         <v>4.791438187800174E-2</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>5.0958003393665158E-2</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>4.1819211693353411E-2</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>5.9648241206030149E-2</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>4.1401173427544007E-2</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>3.0493991226189964E-2</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>3.7375481775449755E-2</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>3.3597518952446587E-2</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>5.896841821126507E-2</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>6.5848458058141351E-2</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>5.7520608498267692E-2</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>7.470650030409702E-2</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>6.8783162362928904E-2</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>2.8480669963541854E-2</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="253"/>
+        <f t="shared" si="244"/>
         <v>0.1042339824760574</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" ref="W35:AE35" si="254">W21/W5</f>
+        <f t="shared" ref="W35:AE35" si="245">W21/W5</f>
         <v>-3.3011576380062517E-2</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>-1.6727980599501788E-2</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>2.2596203019645794E-2</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>1.8632208251789495E-3</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>2.4906170008951147E-2</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>5.0229567728060844E-2</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>6.9043841686293975E-2</v>
       </c>
       <c r="AD35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>6.2508457822676972E-2</v>
       </c>
       <c r="AE35" s="10">
-        <f t="shared" si="254"/>
+        <f t="shared" si="245"/>
         <v>7.2784743882271671E-2</v>
       </c>
       <c r="AF35" s="10">
-        <f t="shared" ref="AF35:AH35" si="255">AF21/AF5</f>
+        <f t="shared" ref="AF35:AH35" si="246">AF21/AF5</f>
         <v>9.1129026808220201E-2</v>
       </c>
       <c r="AG35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="246"/>
         <v>9.6477148989469838E-2</v>
       </c>
       <c r="AH35" s="10">
-        <f t="shared" si="255"/>
+        <f t="shared" si="246"/>
         <v>0.10652210956803272</v>
       </c>
       <c r="AI35" s="10">
-        <f t="shared" ref="AI35:AL35" si="256">AI21/AI5</f>
+        <f t="shared" ref="AI35:AL35" si="247">AI21/AI5</f>
         <v>0.1100233190078822</v>
       </c>
       <c r="AJ35" s="10">
-        <f t="shared" si="256"/>
+        <f t="shared" si="247"/>
         <v>0.10831117100571251</v>
       </c>
       <c r="AK35" s="10">
-        <f t="shared" si="256"/>
-        <v>8.914830009953971E-2</v>
+        <f t="shared" si="247"/>
+        <v>0.11759514677885763</v>
       </c>
       <c r="AL35" s="10">
-        <f t="shared" si="256"/>
-        <v>0.10949180423517793</v>
+        <f t="shared" si="247"/>
+        <v>0.10164672370844936</v>
       </c>
       <c r="AN35" s="10">
-        <f t="shared" ref="AN35:BE35" si="257">AN21/AN5</f>
+        <f t="shared" ref="AN35:BE35" si="248">AN21/AN5</f>
         <v>-2.7082303231896437E-3</v>
       </c>
       <c r="AO35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>5.5697811337681999E-3</v>
       </c>
       <c r="AP35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>1.7435490157147373E-2</v>
       </c>
       <c r="AQ35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>1.7052162864178651E-2</v>
       </c>
       <c r="AR35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>4.3252736305590261E-2</v>
       </c>
       <c r="AS35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>4.1308703060722513E-2</v>
       </c>
       <c r="AT35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>5.5252496995316841E-2</v>
       </c>
       <c r="AU35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>7.1014128755145567E-2</v>
       </c>
       <c r="AV35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>-5.2958950004183018E-3</v>
       </c>
       <c r="AW35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>5.2932835755978319E-2</v>
       </c>
       <c r="AX35" s="10">
-        <f t="shared" si="257"/>
+        <f t="shared" si="248"/>
         <v>9.2871171971866534E-2</v>
       </c>
       <c r="AY35" s="10">
-        <f t="shared" si="257"/>
-        <v>0.10426420773602942</v>
+        <f t="shared" si="248"/>
+        <v>0.10908738765712016</v>
       </c>
       <c r="AZ35" s="10">
-        <f t="shared" si="257"/>
-        <v>0.1197911652024693</v>
+        <f t="shared" si="248"/>
+        <v>0.10375939714948236</v>
       </c>
       <c r="BA35" s="10">
-        <f t="shared" si="257"/>
-        <v>0.13155817217561713</v>
+        <f t="shared" si="248"/>
+        <v>0.11345757791221037</v>
       </c>
       <c r="BB35" s="10">
-        <f t="shared" si="257"/>
-        <v>0.1425192451013447</v>
+        <f t="shared" si="248"/>
+        <v>0.1234991021590255</v>
       </c>
       <c r="BC35" s="10">
-        <f t="shared" si="257"/>
-        <v>0.14418735867305338</v>
+        <f t="shared" si="248"/>
+        <v>0.12407941173713076</v>
       </c>
       <c r="BD35" s="10">
-        <f t="shared" si="257"/>
-        <v>0.14520856181688535</v>
+        <f t="shared" si="248"/>
+        <v>0.12522186644222519</v>
       </c>
       <c r="BE35" s="10">
-        <f t="shared" si="257"/>
-        <v>0.14546468117016378</v>
+        <f t="shared" si="248"/>
+        <v>0.1254826983565655</v>
       </c>
       <c r="BF35" s="10">
         <f>BJ21/BF5</f>
-        <v>0.15009178501458542</v>
+        <v>0.12953451209226577</v>
       </c>
       <c r="BG35" s="10">
-        <f t="shared" ref="BG35:BI35" si="258">BG21/BG5</f>
-        <v>0.14667411795286345</v>
+        <f t="shared" ref="BG35:BI35" si="249">BG21/BG5</f>
+        <v>0.12666761621297809</v>
       </c>
       <c r="BH35" s="10">
-        <f t="shared" si="258"/>
-        <v>0.14690678668579016</v>
+        <f t="shared" si="249"/>
+        <v>0.12682728647211533</v>
       </c>
       <c r="BI35" s="10">
-        <f t="shared" si="258"/>
-        <v>0.14714909880811181</v>
+        <f t="shared" si="249"/>
+        <v>0.12699486995289644</v>
       </c>
       <c r="BK35" t="s">
         <v>67</v>
       </c>
       <c r="BL35" s="3">
         <f>Main!D3</f>
-        <v>229.8</v>
+        <v>250.9</v>
       </c>
     </row>
     <row r="36" spans="2:64" x14ac:dyDescent="0.3">
@@ -9039,7 +9031,7 @@
       </c>
       <c r="BL36" s="13">
         <f>BL34/BL35-1</f>
-        <v>-5.1648797815148639E-2</v>
+        <v>-0.2347008242767521</v>
       </c>
     </row>
     <row r="37" spans="2:64" x14ac:dyDescent="0.3">

--- a/Financial Analysis/AMZN.xlsx
+++ b/Financial Analysis/AMZN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFD34FDC-F226-4C2B-B318-3C2DA63574EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F3771C-65D6-4991-85BA-A8A11EA26AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{EA1D195A-C8DC-4C80-AD05-94F317AC85A7}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="93">
   <si>
     <t>AMZN</t>
   </si>
@@ -289,7 +289,22 @@
     <t>Q425</t>
   </si>
   <si>
-    <t>Slightly overvalued</t>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>Q425 8K</t>
+  </si>
+  <si>
+    <t>Fairly valued</t>
   </si>
 </sst>
 </file>
@@ -402,14 +417,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>160020</xdr:rowOff>
     </xdr:to>
@@ -426,7 +441,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23461980" y="0"/>
+          <a:off x="24048720" y="0"/>
           <a:ext cx="0" cy="6743700"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -452,14 +467,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>30480</xdr:colOff>
+      <xdr:col>55</xdr:col>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>68580</xdr:rowOff>
     </xdr:to>
@@ -476,7 +491,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="31386780" y="0"/>
+          <a:off x="34427160" y="0"/>
           <a:ext cx="0" cy="6652260"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -877,17 +892,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="3">
-        <v>250.9</v>
+        <v>205.61</v>
       </c>
       <c r="E3" s="2">
-        <v>45961</v>
+        <v>46059</v>
       </c>
       <c r="F3" s="2">
         <f ca="1">TODAY()</f>
-        <v>45961</v>
+        <v>46059</v>
       </c>
       <c r="G3" s="2">
-        <v>46051</v>
+        <v>46135</v>
       </c>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -906,11 +921,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4"/>
@@ -930,7 +944,7 @@
       </c>
       <c r="D5" s="4">
         <f>D3*D4</f>
-        <v>2678106.6</v>
+        <v>2169596.7200000002</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4"/>
@@ -951,11 +965,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
-        <f>78779+22423</f>
-        <v>101202</v>
+        <f>86810+36219</f>
+        <v>123029</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -974,11 +988,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="4">
-        <f>52623</f>
-        <v>52623</v>
+        <f>65648</f>
+        <v>65648</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -998,7 +1012,7 @@
       </c>
       <c r="D8" s="4">
         <f>D6-D7</f>
-        <v>48579</v>
+        <v>57381</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -1018,7 +1032,7 @@
       </c>
       <c r="D9" s="4">
         <f>D5-D8</f>
-        <v>2629527.6</v>
+        <v>2112215.7200000002</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -1462,16 +1476,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D602CD1E-E9A8-4C9A-BF94-D3B3F3A20110}">
-  <dimension ref="B2:EW37"/>
+  <dimension ref="B2:FA37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="59" max="60" width="8.88671875" customWidth="1"/>
-    <col min="63" max="63" width="12" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="8.88671875" customWidth="1"/>
+    <col min="67" max="67" width="12" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="17.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:65" x14ac:dyDescent="0.3">
       <c r="C2" s="5" t="s">
         <v>13</v>
       </c>
@@ -1580,74 +1594,86 @@
       <c r="AL2" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AN2">
+      <c r="AM2" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="AN2" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AO2" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="AP2" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="AR2">
         <v>2014</v>
       </c>
-      <c r="AO2">
+      <c r="AS2">
         <v>2015</v>
       </c>
-      <c r="AP2">
+      <c r="AT2">
         <v>2016</v>
       </c>
-      <c r="AQ2">
+      <c r="AU2">
         <v>2017</v>
       </c>
-      <c r="AR2">
+      <c r="AV2">
         <v>2018</v>
       </c>
-      <c r="AS2">
+      <c r="AW2">
         <v>2019</v>
       </c>
-      <c r="AT2">
+      <c r="AX2">
         <v>2020</v>
       </c>
-      <c r="AU2">
+      <c r="AY2">
         <v>2021</v>
       </c>
-      <c r="AV2">
+      <c r="AZ2">
         <v>2022</v>
       </c>
-      <c r="AW2">
+      <c r="BA2">
         <v>2023</v>
       </c>
-      <c r="AX2">
+      <c r="BB2">
         <v>2024</v>
       </c>
-      <c r="AY2">
+      <c r="BC2">
         <v>2025</v>
       </c>
-      <c r="AZ2">
+      <c r="BD2">
         <v>2026</v>
       </c>
-      <c r="BA2">
+      <c r="BE2">
         <v>2027</v>
       </c>
-      <c r="BB2">
+      <c r="BF2">
         <v>2028</v>
       </c>
-      <c r="BC2">
+      <c r="BG2">
         <v>2029</v>
       </c>
-      <c r="BD2">
+      <c r="BH2">
         <v>2030</v>
       </c>
-      <c r="BE2">
+      <c r="BI2">
         <v>2031</v>
       </c>
-      <c r="BF2">
+      <c r="BJ2">
         <v>2032</v>
       </c>
-      <c r="BG2">
+      <c r="BK2">
         <v>2033</v>
       </c>
-      <c r="BH2">
+      <c r="BL2">
         <v>2034</v>
       </c>
-      <c r="BI2">
+      <c r="BM2">
         <v>2035</v>
       </c>
     </row>
-    <row r="3" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>33</v>
       </c>
@@ -1757,96 +1783,99 @@
         <v>74058</v>
       </c>
       <c r="AL3" s="4">
-        <f>AH3*1.08</f>
-        <v>88804.08</v>
-      </c>
-      <c r="AN3" s="4">
+        <v>89992</v>
+      </c>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="4"/>
+      <c r="AR3" s="4">
         <v>70080</v>
       </c>
-      <c r="AO3" s="4">
+      <c r="AS3" s="4">
         <v>79268</v>
       </c>
-      <c r="AP3" s="4">
+      <c r="AT3" s="4">
         <v>94665</v>
       </c>
-      <c r="AQ3" s="4">
+      <c r="AU3" s="4">
         <f>SUM(C3:F3)</f>
         <v>118572</v>
       </c>
-      <c r="AR3" s="4">
+      <c r="AV3" s="4">
         <f>SUM(G3:J3)</f>
         <v>141915</v>
       </c>
-      <c r="AS3" s="4">
+      <c r="AW3" s="4">
         <f>SUM(K3:N3)</f>
         <v>160407</v>
       </c>
-      <c r="AT3" s="4">
+      <c r="AX3" s="4">
         <f>SUM(O3:R3)</f>
         <v>215915</v>
       </c>
-      <c r="AU3" s="4">
+      <c r="AY3" s="4">
         <f>SUM(S3:V3)</f>
         <v>241787</v>
       </c>
-      <c r="AV3" s="4">
+      <c r="AZ3" s="4">
         <f>SUM(W3:Z3)</f>
         <v>242901</v>
       </c>
-      <c r="AW3" s="4">
+      <c r="BA3" s="4">
         <f>SUM(AA3:AD3)</f>
         <v>255887</v>
       </c>
-      <c r="AX3" s="4">
+      <c r="BB3" s="4">
         <f>SUM(AE3:AH3)</f>
         <v>272311</v>
       </c>
-      <c r="AY3" s="4">
+      <c r="BC3" s="4">
         <f>SUM(AI3:AL3)</f>
-        <v>295078.08</v>
-      </c>
-      <c r="AZ3" s="4">
-        <f>AY3*1.05</f>
-        <v>309831.98400000005</v>
-      </c>
-      <c r="BA3" s="4">
-        <f>AZ3*1.04</f>
-        <v>322225.26336000004</v>
-      </c>
-      <c r="BB3" s="4">
-        <f>BA3*1.03</f>
-        <v>331892.02126080007</v>
-      </c>
-      <c r="BC3" s="4">
-        <f t="shared" ref="BC3:BD3" si="0">BB3*1.02</f>
-        <v>338529.86168601608</v>
+        <v>296266</v>
       </c>
       <c r="BD3" s="4">
+        <f>BC3*1.05</f>
+        <v>311079.3</v>
+      </c>
+      <c r="BE3" s="4">
+        <f>BD3*1.04</f>
+        <v>323522.47200000001</v>
+      </c>
+      <c r="BF3" s="4">
+        <f>BE3*1.03</f>
+        <v>333228.14616</v>
+      </c>
+      <c r="BG3" s="4">
+        <f t="shared" ref="BG3:BH3" si="0">BF3*1.02</f>
+        <v>339892.70908320002</v>
+      </c>
+      <c r="BH3" s="4">
         <f t="shared" si="0"/>
-        <v>345300.45891973644</v>
-      </c>
-      <c r="BE3" s="4">
-        <f>BD3*1.02</f>
-        <v>352206.46809813118</v>
-      </c>
-      <c r="BF3" s="4">
-        <f>BE3*1.01</f>
-        <v>355728.53277911252</v>
-      </c>
-      <c r="BG3" s="4">
-        <f t="shared" ref="BG3:BI3" si="1">BF3*1.01</f>
-        <v>359285.81810690364</v>
-      </c>
-      <c r="BH3" s="4">
+        <v>346690.56326486403</v>
+      </c>
+      <c r="BI3" s="4">
+        <f>BH3*1.02</f>
+        <v>353624.37453016132</v>
+      </c>
+      <c r="BJ3" s="4">
+        <f>BI3*1.01</f>
+        <v>357160.61827546294</v>
+      </c>
+      <c r="BK3" s="4">
+        <f t="shared" ref="BK3:BM3" si="1">BJ3*1.01</f>
+        <v>360732.22445821756</v>
+      </c>
+      <c r="BL3" s="4">
         <f t="shared" si="1"/>
-        <v>362878.67628797266</v>
-      </c>
-      <c r="BI3" s="4">
+        <v>364339.54670279974</v>
+      </c>
+      <c r="BM3" s="4">
         <f t="shared" si="1"/>
-        <v>366507.46305085241</v>
+        <v>367982.94216982776</v>
       </c>
     </row>
-    <row r="4" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>34</v>
       </c>
@@ -1956,96 +1985,99 @@
         <v>106111</v>
       </c>
       <c r="AL4" s="4">
-        <f>AH4*1.13</f>
-        <v>119289.57999999999</v>
-      </c>
-      <c r="AN4" s="4">
+        <v>123394</v>
+      </c>
+      <c r="AM4" s="4"/>
+      <c r="AN4" s="4"/>
+      <c r="AO4" s="4"/>
+      <c r="AP4" s="4"/>
+      <c r="AR4" s="4">
         <v>18908</v>
       </c>
-      <c r="AO4" s="4">
+      <c r="AS4" s="4">
         <v>27738</v>
       </c>
-      <c r="AP4" s="4">
+      <c r="AT4" s="4">
         <v>41322</v>
       </c>
-      <c r="AQ4" s="4">
+      <c r="AU4" s="4">
         <f>SUM(C4:F4)</f>
         <v>59294</v>
       </c>
-      <c r="AR4" s="4">
+      <c r="AV4" s="4">
         <f>SUM(G4:J4)</f>
         <v>90972</v>
       </c>
-      <c r="AS4" s="4">
+      <c r="AW4" s="4">
         <f>SUM(K4:N4)</f>
         <v>120115</v>
       </c>
-      <c r="AT4" s="4">
+      <c r="AX4" s="4">
         <f>SUM(O4:R4)</f>
         <v>170149</v>
       </c>
-      <c r="AU4" s="4">
+      <c r="AY4" s="4">
         <f>SUM(S4:V4)</f>
         <v>228035</v>
       </c>
-      <c r="AV4" s="4">
+      <c r="AZ4" s="4">
         <f>SUM(W4:Z4)</f>
         <v>271082</v>
       </c>
-      <c r="AW4" s="4">
+      <c r="BA4" s="4">
         <f>SUM(AA4:AD4)</f>
         <v>318898</v>
       </c>
-      <c r="AX4" s="4">
+      <c r="BB4" s="4">
         <f>SUM(AE4:AH4)</f>
         <v>365648</v>
       </c>
-      <c r="AY4" s="4">
+      <c r="BC4" s="4">
         <f>SUM(AI4:AL4)</f>
-        <v>416553.57999999996</v>
-      </c>
-      <c r="AZ4" s="4">
-        <f>AY4*1.09</f>
-        <v>454043.40220000001</v>
-      </c>
-      <c r="BA4" s="4">
-        <f>AZ4*1.08</f>
-        <v>490366.87437600002</v>
-      </c>
-      <c r="BB4" s="4">
-        <f>BA4*1.06</f>
-        <v>519788.88683856005</v>
-      </c>
-      <c r="BC4" s="4">
-        <f>BB4*1.04</f>
-        <v>540580.44231210242</v>
+        <v>420658</v>
       </c>
       <c r="BD4" s="4">
-        <f t="shared" ref="BD4" si="2">BC4*1.03</f>
-        <v>556797.85558146553</v>
+        <f>BC4*1.09</f>
+        <v>458517.22000000003</v>
       </c>
       <c r="BE4" s="4">
-        <f>BD4*1.02</f>
-        <v>567933.81269309483</v>
+        <f>BD4*1.08</f>
+        <v>495198.59760000004</v>
       </c>
       <c r="BF4" s="4">
-        <f t="shared" ref="BF4" si="3">BE4*1.02</f>
-        <v>579292.4889469567</v>
+        <f>BE4*1.06</f>
+        <v>524910.51345600002</v>
       </c>
       <c r="BG4" s="4">
-        <f>BF4*1.01</f>
-        <v>585085.41383642622</v>
+        <f>BF4*1.04</f>
+        <v>545906.93399424001</v>
       </c>
       <c r="BH4" s="4">
-        <f t="shared" ref="BH4:BI4" si="4">BG4*1.01</f>
-        <v>590936.26797479053</v>
+        <f t="shared" ref="BH4" si="2">BG4*1.03</f>
+        <v>562284.14201406727</v>
       </c>
       <c r="BI4" s="4">
+        <f>BH4*1.02</f>
+        <v>573529.82485434867</v>
+      </c>
+      <c r="BJ4" s="4">
+        <f t="shared" ref="BJ4" si="3">BI4*1.02</f>
+        <v>585000.42135143571</v>
+      </c>
+      <c r="BK4" s="4">
+        <f>BJ4*1.01</f>
+        <v>590850.4255649501</v>
+      </c>
+      <c r="BL4" s="4">
+        <f t="shared" ref="BL4:BM4" si="4">BK4*1.01</f>
+        <v>596758.92982059962</v>
+      </c>
+      <c r="BM4" s="4">
         <f t="shared" si="4"/>
-        <v>596845.6306545384</v>
+        <v>602726.51911880565</v>
       </c>
     </row>
-    <row r="5" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:65" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>35</v>
       </c>
@@ -2191,98 +2223,102 @@
       </c>
       <c r="AL5" s="8">
         <f t="shared" si="14"/>
-        <v>208093.65999999997</v>
-      </c>
-      <c r="AN5" s="8">
-        <f t="shared" ref="AN5:AU5" si="15">AN3+AN4</f>
+        <v>213386</v>
+      </c>
+      <c r="AM5" s="8"/>
+      <c r="AN5" s="8"/>
+      <c r="AO5" s="8"/>
+      <c r="AP5" s="8"/>
+      <c r="AR5" s="8">
+        <f t="shared" ref="AR5:AY5" si="15">AR3+AR4</f>
         <v>88988</v>
       </c>
-      <c r="AO5" s="8">
+      <c r="AS5" s="8">
         <f t="shared" si="15"/>
         <v>107006</v>
       </c>
-      <c r="AP5" s="8">
+      <c r="AT5" s="8">
         <f t="shared" si="15"/>
         <v>135987</v>
       </c>
-      <c r="AQ5" s="8">
+      <c r="AU5" s="8">
         <f t="shared" si="15"/>
         <v>177866</v>
       </c>
-      <c r="AR5" s="8">
+      <c r="AV5" s="8">
         <f t="shared" si="15"/>
         <v>232887</v>
       </c>
-      <c r="AS5" s="8">
+      <c r="AW5" s="8">
         <f t="shared" si="15"/>
         <v>280522</v>
       </c>
-      <c r="AT5" s="8">
+      <c r="AX5" s="8">
         <f t="shared" si="15"/>
         <v>386064</v>
       </c>
-      <c r="AU5" s="8">
+      <c r="AY5" s="8">
         <f t="shared" si="15"/>
         <v>469822</v>
       </c>
-      <c r="AV5" s="8">
-        <f t="shared" ref="AV5:BE5" si="16">AV3+AV4</f>
+      <c r="AZ5" s="8">
+        <f t="shared" ref="AZ5:BI5" si="16">AZ3+AZ4</f>
         <v>513983</v>
       </c>
-      <c r="AW5" s="8">
+      <c r="BA5" s="8">
         <f t="shared" si="16"/>
         <v>574785</v>
       </c>
-      <c r="AX5" s="8">
-        <f t="shared" ref="AX5" si="17">AX3+AX4</f>
+      <c r="BB5" s="8">
+        <f t="shared" ref="BB5" si="17">BB3+BB4</f>
         <v>637959</v>
-      </c>
-      <c r="AY5" s="8">
-        <f t="shared" si="16"/>
-        <v>711631.65999999992</v>
-      </c>
-      <c r="AZ5" s="8">
-        <f t="shared" si="16"/>
-        <v>763875.38620000007</v>
-      </c>
-      <c r="BA5" s="8">
-        <f t="shared" si="16"/>
-        <v>812592.13773600012</v>
-      </c>
-      <c r="BB5" s="8">
-        <f t="shared" si="16"/>
-        <v>851680.90809936007</v>
       </c>
       <c r="BC5" s="8">
         <f t="shared" si="16"/>
-        <v>879110.3039981185</v>
+        <v>716924</v>
       </c>
       <c r="BD5" s="8">
         <f t="shared" si="16"/>
-        <v>902098.31450120197</v>
+        <v>769596.52</v>
       </c>
       <c r="BE5" s="8">
         <f t="shared" si="16"/>
-        <v>920140.28079122608</v>
+        <v>818721.06960000005</v>
       </c>
       <c r="BF5" s="8">
-        <f t="shared" ref="BF5:BI5" si="18">BF3+BF4</f>
-        <v>935021.02172606927</v>
+        <f t="shared" si="16"/>
+        <v>858138.65961600002</v>
       </c>
       <c r="BG5" s="8">
+        <f t="shared" si="16"/>
+        <v>885799.64307744009</v>
+      </c>
+      <c r="BH5" s="8">
+        <f t="shared" si="16"/>
+        <v>908974.7052789313</v>
+      </c>
+      <c r="BI5" s="8">
+        <f t="shared" si="16"/>
+        <v>927154.19938451005</v>
+      </c>
+      <c r="BJ5" s="8">
+        <f t="shared" ref="BJ5:BM5" si="18">BJ3+BJ4</f>
+        <v>942161.03962689871</v>
+      </c>
+      <c r="BK5" s="8">
         <f t="shared" si="18"/>
-        <v>944371.2319433298</v>
-      </c>
-      <c r="BH5" s="8">
+        <v>951582.65002316772</v>
+      </c>
+      <c r="BL5" s="8">
         <f t="shared" si="18"/>
-        <v>953814.94426276325</v>
-      </c>
-      <c r="BI5" s="8">
+        <v>961098.47652339935</v>
+      </c>
+      <c r="BM5" s="8">
         <f t="shared" si="18"/>
-        <v>963353.09370539081</v>
+        <v>970709.46128863341</v>
       </c>
     </row>
-    <row r="6" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>31</v>
       </c>
@@ -2392,96 +2428,99 @@
         <v>88670</v>
       </c>
       <c r="AL6" s="4">
-        <f>AL5-AL7</f>
-        <v>106127.76659999999</v>
-      </c>
-      <c r="AN6" s="4">
+        <v>109959</v>
+      </c>
+      <c r="AM6" s="4"/>
+      <c r="AN6" s="4"/>
+      <c r="AO6" s="4"/>
+      <c r="AP6" s="4"/>
+      <c r="AR6" s="4">
         <v>62752</v>
       </c>
-      <c r="AO6" s="4">
+      <c r="AS6" s="4">
         <v>71651</v>
       </c>
-      <c r="AP6" s="4">
+      <c r="AT6" s="4">
         <v>88265</v>
       </c>
-      <c r="AQ6" s="4">
+      <c r="AU6" s="4">
         <f>SUM(C6:F6)</f>
         <v>111934</v>
       </c>
-      <c r="AR6" s="4">
+      <c r="AV6" s="4">
         <f>SUM(G6:J6)</f>
         <v>139156</v>
       </c>
-      <c r="AS6" s="4">
+      <c r="AW6" s="4">
         <f>SUM(K6:N6)</f>
         <v>165536</v>
       </c>
-      <c r="AT6" s="4">
+      <c r="AX6" s="4">
         <f>SUM(O6:R6)</f>
         <v>233307</v>
       </c>
-      <c r="AU6" s="4">
+      <c r="AY6" s="4">
         <f>SUM(S6:V6)</f>
         <v>272344</v>
       </c>
-      <c r="AV6" s="4">
+      <c r="AZ6" s="4">
         <f>SUM(W6:Z6)</f>
         <v>288831</v>
       </c>
-      <c r="AW6" s="4">
+      <c r="BA6" s="4">
         <f>SUM(AA6:AD6)</f>
         <v>304739</v>
       </c>
-      <c r="AX6" s="4">
+      <c r="BB6" s="4">
         <f>SUM(AE6:AH6)</f>
         <v>326288</v>
       </c>
-      <c r="AY6" s="4">
+      <c r="BC6" s="4">
         <f>SUM(AI6:AL6)</f>
-        <v>352582.76659999997</v>
-      </c>
-      <c r="AZ6" s="4">
-        <f t="shared" ref="AZ6:BE6" si="19">AZ5-AZ7</f>
-        <v>374298.93923800002</v>
-      </c>
-      <c r="BA6" s="4">
-        <f t="shared" si="19"/>
-        <v>390044.22611328005</v>
-      </c>
-      <c r="BB6" s="4">
-        <f t="shared" si="19"/>
-        <v>400290.02680669923</v>
-      </c>
-      <c r="BC6" s="4">
-        <f t="shared" si="19"/>
-        <v>413181.84287911566</v>
+        <v>356414</v>
       </c>
       <c r="BD6" s="4">
-        <f t="shared" si="19"/>
-        <v>423986.20781556488</v>
+        <f t="shared" ref="BD6:BI6" si="19">BD5-BD7</f>
+        <v>377102.29479999997</v>
       </c>
       <c r="BE6" s="4">
         <f t="shared" si="19"/>
-        <v>432465.93197187624</v>
+        <v>392986.11340800003</v>
       </c>
       <c r="BF6" s="4">
-        <f t="shared" ref="BF6:BI6" si="20">BF5-BF7</f>
-        <v>439459.88021125254</v>
+        <f t="shared" si="19"/>
+        <v>403325.17001951998</v>
       </c>
       <c r="BG6" s="4">
+        <f t="shared" si="19"/>
+        <v>416325.83224639681</v>
+      </c>
+      <c r="BH6" s="4">
+        <f t="shared" si="19"/>
+        <v>427218.1114810977</v>
+      </c>
+      <c r="BI6" s="4">
+        <f t="shared" si="19"/>
+        <v>435762.47371071967</v>
+      </c>
+      <c r="BJ6" s="4">
+        <f t="shared" ref="BJ6:BM6" si="20">BJ5-BJ7</f>
+        <v>442815.68862464238</v>
+      </c>
+      <c r="BK6" s="4">
         <f t="shared" si="20"/>
-        <v>443854.47901336499</v>
-      </c>
-      <c r="BH6" s="4">
+        <v>447243.84551088879</v>
+      </c>
+      <c r="BL6" s="4">
         <f t="shared" si="20"/>
-        <v>448293.02380349871</v>
-      </c>
-      <c r="BI6" s="4">
+        <v>451716.28396599769</v>
+      </c>
+      <c r="BM6" s="4">
         <f t="shared" si="20"/>
-        <v>452775.95404153364</v>
+        <v>456233.4468056577</v>
       </c>
     </row>
-    <row r="7" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:65" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
@@ -2598,7 +2637,7 @@
         <v>77408</v>
       </c>
       <c r="AE7" s="8">
-        <f t="shared" ref="AE7:AK7" si="29">AE5-AE6</f>
+        <f t="shared" ref="AE7:AL7" si="29">AE5-AE6</f>
         <v>70680</v>
       </c>
       <c r="AF7" s="8">
@@ -2626,99 +2665,103 @@
         <v>91499</v>
       </c>
       <c r="AL7" s="8">
-        <f>AL5*0.49</f>
-        <v>101965.89339999999</v>
-      </c>
-      <c r="AN7" s="8">
-        <f t="shared" ref="AN7:AW7" si="30">AN5-AN6</f>
+        <f t="shared" si="29"/>
+        <v>103427</v>
+      </c>
+      <c r="AM7" s="8"/>
+      <c r="AN7" s="8"/>
+      <c r="AO7" s="8"/>
+      <c r="AP7" s="8"/>
+      <c r="AR7" s="8">
+        <f t="shared" ref="AR7:BA7" si="30">AR5-AR6</f>
         <v>26236</v>
       </c>
-      <c r="AO7" s="8">
+      <c r="AS7" s="8">
         <f t="shared" si="30"/>
         <v>35355</v>
       </c>
-      <c r="AP7" s="8">
+      <c r="AT7" s="8">
         <f t="shared" si="30"/>
         <v>47722</v>
       </c>
-      <c r="AQ7" s="8">
+      <c r="AU7" s="8">
         <f t="shared" si="30"/>
         <v>65932</v>
       </c>
-      <c r="AR7" s="8">
+      <c r="AV7" s="8">
         <f t="shared" si="30"/>
         <v>93731</v>
       </c>
-      <c r="AS7" s="8">
+      <c r="AW7" s="8">
         <f t="shared" si="30"/>
         <v>114986</v>
       </c>
-      <c r="AT7" s="8">
+      <c r="AX7" s="8">
         <f t="shared" si="30"/>
         <v>152757</v>
       </c>
-      <c r="AU7" s="8">
+      <c r="AY7" s="8">
         <f t="shared" si="30"/>
         <v>197478</v>
       </c>
-      <c r="AV7" s="8">
+      <c r="AZ7" s="8">
         <f t="shared" si="30"/>
         <v>225152</v>
       </c>
-      <c r="AW7" s="8">
+      <c r="BA7" s="8">
         <f t="shared" si="30"/>
         <v>270046</v>
       </c>
-      <c r="AX7" s="8">
-        <f t="shared" ref="AX7:AY7" si="31">AX5-AX6</f>
+      <c r="BB7" s="8">
+        <f t="shared" ref="BB7:BC7" si="31">BB5-BB6</f>
         <v>311671</v>
       </c>
-      <c r="AY7" s="8">
+      <c r="BC7" s="8">
         <f t="shared" si="31"/>
-        <v>359048.89339999994</v>
-      </c>
-      <c r="AZ7" s="8">
-        <f>AZ5*0.51</f>
-        <v>389576.44696200005</v>
-      </c>
-      <c r="BA7" s="8">
-        <f>BA5*0.52</f>
-        <v>422547.91162272007</v>
-      </c>
-      <c r="BB7" s="8">
-        <f>BB5*0.53</f>
-        <v>451390.88129266084</v>
-      </c>
-      <c r="BC7" s="8">
-        <f t="shared" ref="BC7:BI7" si="32">BC5*0.53</f>
-        <v>465928.46111900284</v>
+        <v>360510</v>
       </c>
       <c r="BD7" s="8">
-        <f t="shared" si="32"/>
-        <v>478112.10668563709</v>
+        <f>BD5*0.51</f>
+        <v>392494.22520000004</v>
       </c>
       <c r="BE7" s="8">
-        <f t="shared" si="32"/>
-        <v>487674.34881934983</v>
+        <f>BE5*0.52</f>
+        <v>425734.95619200001</v>
       </c>
       <c r="BF7" s="8">
-        <f t="shared" si="32"/>
-        <v>495561.14151481673</v>
+        <f>BF5*0.53</f>
+        <v>454813.48959648004</v>
       </c>
       <c r="BG7" s="8">
-        <f t="shared" si="32"/>
-        <v>500516.7529299648</v>
+        <f t="shared" ref="BG7:BM7" si="32">BG5*0.53</f>
+        <v>469473.81083104329</v>
       </c>
       <c r="BH7" s="8">
         <f t="shared" si="32"/>
-        <v>505521.92045926454</v>
+        <v>481756.5937978336</v>
       </c>
       <c r="BI7" s="8">
         <f t="shared" si="32"/>
-        <v>510577.13966385718</v>
+        <v>491391.72567379038</v>
+      </c>
+      <c r="BJ7" s="8">
+        <f t="shared" si="32"/>
+        <v>499345.35100225633</v>
+      </c>
+      <c r="BK7" s="8">
+        <f t="shared" si="32"/>
+        <v>504338.80451227893</v>
+      </c>
+      <c r="BL7" s="8">
+        <f t="shared" si="32"/>
+        <v>509382.19255740166</v>
+      </c>
+      <c r="BM7" s="8">
+        <f t="shared" si="32"/>
+        <v>514476.0144829757</v>
       </c>
     </row>
-    <row r="8" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>36</v>
       </c>
@@ -2828,96 +2871,99 @@
         <v>27679</v>
       </c>
       <c r="AL8" s="4">
-        <f>AL5*0.15</f>
-        <v>31214.048999999995</v>
-      </c>
-      <c r="AN8" s="4">
+        <v>30826</v>
+      </c>
+      <c r="AM8" s="4"/>
+      <c r="AN8" s="4"/>
+      <c r="AO8" s="4"/>
+      <c r="AP8" s="4"/>
+      <c r="AR8" s="4">
         <v>10766</v>
       </c>
-      <c r="AO8" s="4">
+      <c r="AS8" s="4">
         <v>13410</v>
       </c>
-      <c r="AP8" s="4">
+      <c r="AT8" s="4">
         <v>17619</v>
       </c>
-      <c r="AQ8" s="4">
+      <c r="AU8" s="4">
         <f>SUM(C8:F8)</f>
         <v>25249</v>
       </c>
-      <c r="AR8" s="4">
+      <c r="AV8" s="4">
         <f>SUM(G8:J8)</f>
         <v>34027</v>
       </c>
-      <c r="AS8" s="4">
+      <c r="AW8" s="4">
         <f>SUM(K8:N8)</f>
         <v>40231</v>
       </c>
-      <c r="AT8" s="4">
+      <c r="AX8" s="4">
         <f>SUM(O8:R8)</f>
         <v>58516</v>
       </c>
-      <c r="AU8" s="4">
+      <c r="AY8" s="4">
         <f>SUM(S8:V8)</f>
         <v>75111</v>
       </c>
-      <c r="AV8" s="4">
+      <c r="AZ8" s="4">
         <f>SUM(W8:Z8)</f>
         <v>84299</v>
       </c>
-      <c r="AW8" s="4">
+      <c r="BA8" s="4">
         <f>SUM(AA8:AD8)</f>
         <v>90619</v>
       </c>
-      <c r="AX8" s="4">
+      <c r="BB8" s="4">
         <f>SUM(AE8:AH8)</f>
         <v>98505</v>
       </c>
-      <c r="AY8" s="4">
+      <c r="BC8" s="4">
         <f>SUM(AI8:AL8)</f>
-        <v>109462.049</v>
-      </c>
-      <c r="AZ8" s="4">
-        <f t="shared" ref="AZ8:BE8" si="33">AZ5*0.15</f>
-        <v>114581.30793000001</v>
-      </c>
-      <c r="BA8" s="4">
-        <f t="shared" si="33"/>
-        <v>121888.82066040002</v>
-      </c>
-      <c r="BB8" s="4">
-        <f t="shared" si="33"/>
-        <v>127752.13621490401</v>
-      </c>
-      <c r="BC8" s="4">
-        <f t="shared" si="33"/>
-        <v>131866.54559971776</v>
+        <v>109074</v>
       </c>
       <c r="BD8" s="4">
-        <f t="shared" si="33"/>
-        <v>135314.7471751803</v>
+        <f t="shared" ref="BD8:BI8" si="33">BD5*0.15</f>
+        <v>115439.478</v>
       </c>
       <c r="BE8" s="4">
         <f t="shared" si="33"/>
-        <v>138021.04211868389</v>
+        <v>122808.16044000001</v>
       </c>
       <c r="BF8" s="4">
-        <f t="shared" ref="BF8:BI8" si="34">BF5*0.15</f>
-        <v>140253.15325891037</v>
+        <f t="shared" si="33"/>
+        <v>128720.7989424</v>
       </c>
       <c r="BG8" s="4">
+        <f t="shared" si="33"/>
+        <v>132869.946461616</v>
+      </c>
+      <c r="BH8" s="4">
+        <f t="shared" si="33"/>
+        <v>136346.20579183969</v>
+      </c>
+      <c r="BI8" s="4">
+        <f t="shared" si="33"/>
+        <v>139073.12990767651</v>
+      </c>
+      <c r="BJ8" s="4">
+        <f t="shared" ref="BJ8:BM8" si="34">BJ5*0.15</f>
+        <v>141324.15594403481</v>
+      </c>
+      <c r="BK8" s="4">
         <f t="shared" si="34"/>
-        <v>141655.68479149946</v>
-      </c>
-      <c r="BH8" s="4">
+        <v>142737.39750347516</v>
+      </c>
+      <c r="BL8" s="4">
         <f t="shared" si="34"/>
-        <v>143072.24163941448</v>
-      </c>
-      <c r="BI8" s="4">
+        <v>144164.77147850991</v>
+      </c>
+      <c r="BM8" s="4">
         <f t="shared" si="34"/>
-        <v>144502.96405580861</v>
+        <v>145606.41919329501</v>
       </c>
     </row>
-    <row r="9" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>37</v>
       </c>
@@ -3027,96 +3073,99 @@
         <v>28962</v>
       </c>
       <c r="AL9" s="4">
-        <f>AH9*1.3</f>
-        <v>30642.3</v>
-      </c>
-      <c r="AN9" s="4">
+        <v>29399</v>
+      </c>
+      <c r="AM9" s="4"/>
+      <c r="AN9" s="4"/>
+      <c r="AO9" s="4"/>
+      <c r="AP9" s="4"/>
+      <c r="AR9" s="4">
         <v>4332</v>
       </c>
-      <c r="AO9" s="4">
+      <c r="AS9" s="4">
         <v>5254</v>
       </c>
-      <c r="AP9" s="4">
+      <c r="AT9" s="4">
         <v>7233</v>
       </c>
-      <c r="AQ9" s="4">
+      <c r="AU9" s="4">
         <f>SUM(C9:F9)</f>
         <v>10068</v>
       </c>
-      <c r="AR9" s="4">
+      <c r="AV9" s="4">
         <f>SUM(G9:J9)</f>
         <v>13814</v>
       </c>
-      <c r="AS9" s="4">
+      <c r="AW9" s="4">
         <f>SUM(K9:N9)</f>
         <v>35932</v>
       </c>
-      <c r="AT9" s="4">
+      <c r="AX9" s="4">
         <f>SUM(O9:R9)</f>
         <v>42738</v>
       </c>
-      <c r="AU9" s="4">
+      <c r="AY9" s="4">
         <f>SUM(S9:V9)</f>
         <v>56052</v>
       </c>
-      <c r="AV9" s="4">
+      <c r="AZ9" s="4">
         <f>SUM(W9:Z9)</f>
         <v>73213</v>
       </c>
-      <c r="AW9" s="4">
+      <c r="BA9" s="4">
         <f>SUM(AA9:AD9)</f>
         <v>85622</v>
       </c>
-      <c r="AX9" s="4">
+      <c r="BB9" s="4">
         <f>SUM(AE9:AH9)</f>
         <v>88544</v>
       </c>
-      <c r="AY9" s="4">
+      <c r="BC9" s="4">
         <f>SUM(AI9:AL9)</f>
-        <v>109764.3</v>
-      </c>
-      <c r="AZ9" s="4">
-        <f>AY9*1.12</f>
-        <v>122936.01600000002</v>
-      </c>
-      <c r="BA9" s="4">
-        <f>AZ9*1.06</f>
-        <v>130312.17696000003</v>
-      </c>
-      <c r="BB9" s="4">
-        <f>BA9*1.04</f>
-        <v>135524.66403840002</v>
-      </c>
-      <c r="BC9" s="4">
-        <f>BB9*1.03</f>
-        <v>139590.40395955203</v>
+        <v>108521</v>
       </c>
       <c r="BD9" s="4">
-        <f t="shared" ref="BC9:BE9" si="35">BC9*1.02</f>
-        <v>142382.21203874308</v>
+        <f>BC9*1.12</f>
+        <v>121543.52000000002</v>
       </c>
       <c r="BE9" s="4">
+        <f>BD9*1.06</f>
+        <v>128836.13120000003</v>
+      </c>
+      <c r="BF9" s="4">
+        <f>BE9*1.04</f>
+        <v>133989.57644800004</v>
+      </c>
+      <c r="BG9" s="4">
+        <f>BF9*1.03</f>
+        <v>138009.26374144005</v>
+      </c>
+      <c r="BH9" s="4">
+        <f t="shared" ref="BH9:BI9" si="35">BG9*1.02</f>
+        <v>140769.44901626886</v>
+      </c>
+      <c r="BI9" s="4">
         <f t="shared" si="35"/>
-        <v>145229.85627951793</v>
-      </c>
-      <c r="BF9" s="4">
-        <f>BE9*1.01</f>
-        <v>146682.15484231312</v>
-      </c>
-      <c r="BG9" s="4">
-        <f t="shared" ref="BG9:BI9" si="36">BF9*1.01</f>
-        <v>148148.97639073624</v>
-      </c>
-      <c r="BH9" s="4">
+        <v>143584.83799659423</v>
+      </c>
+      <c r="BJ9" s="4">
+        <f>BI9*1.01</f>
+        <v>145020.68637656016</v>
+      </c>
+      <c r="BK9" s="4">
+        <f t="shared" ref="BK9:BM9" si="36">BJ9*1.01</f>
+        <v>146470.89324032576</v>
+      </c>
+      <c r="BL9" s="4">
         <f t="shared" si="36"/>
-        <v>149630.4661546436</v>
-      </c>
-      <c r="BI9" s="4">
+        <v>147935.60217272904</v>
+      </c>
+      <c r="BM9" s="4">
         <f t="shared" si="36"/>
-        <v>151126.77081619002</v>
+        <v>149414.95819445633</v>
       </c>
     </row>
-    <row r="10" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>38</v>
       </c>
@@ -3226,96 +3275,99 @@
         <v>11686</v>
       </c>
       <c r="AL10" s="4">
-        <f>AL5*0.065</f>
-        <v>13526.087899999999</v>
-      </c>
-      <c r="AN10" s="4">
+        <v>14264</v>
+      </c>
+      <c r="AM10" s="4"/>
+      <c r="AN10" s="4"/>
+      <c r="AO10" s="4"/>
+      <c r="AP10" s="4"/>
+      <c r="AR10" s="4">
         <v>9275</v>
       </c>
-      <c r="AO10" s="4">
+      <c r="AS10" s="4">
         <v>12540</v>
       </c>
-      <c r="AP10" s="4">
+      <c r="AT10" s="4">
         <v>16085</v>
       </c>
-      <c r="AQ10" s="4">
+      <c r="AU10" s="4">
         <f>SUM(C10:F10)</f>
         <v>22620</v>
       </c>
-      <c r="AR10" s="4">
+      <c r="AV10" s="4">
         <f>SUM(G10:J10)</f>
         <v>28837</v>
       </c>
-      <c r="AS10" s="4">
+      <c r="AW10" s="4">
         <f>SUM(K10:N10)</f>
         <v>18879</v>
       </c>
-      <c r="AT10" s="4">
+      <c r="AX10" s="4">
         <f>SUM(O10:R10)</f>
         <v>22010</v>
       </c>
-      <c r="AU10" s="4">
+      <c r="AY10" s="4">
         <f>SUM(S10:V10)</f>
         <v>32551</v>
       </c>
-      <c r="AV10" s="4">
+      <c r="AZ10" s="4">
         <f>SUM(W10:Z10)</f>
         <v>42238</v>
       </c>
-      <c r="AW10" s="4">
+      <c r="BA10" s="4">
         <f>SUM(AA10:AD10)</f>
         <v>44370</v>
       </c>
-      <c r="AX10" s="4">
+      <c r="BB10" s="4">
         <f>SUM(AE10:AH10)</f>
         <v>43907</v>
       </c>
-      <c r="AY10" s="4">
+      <c r="BC10" s="4">
         <f>SUM(AI10:AL10)</f>
-        <v>46391.087899999999</v>
-      </c>
-      <c r="AZ10" s="4">
-        <f>AZ5*0.06</f>
-        <v>45832.523172000001</v>
-      </c>
-      <c r="BA10" s="4">
-        <f t="shared" ref="BA10:BI10" si="37">BA5*0.06</f>
-        <v>48755.528264160006</v>
-      </c>
-      <c r="BB10" s="4">
-        <f t="shared" si="37"/>
-        <v>51100.854485961601</v>
-      </c>
-      <c r="BC10" s="4">
-        <f t="shared" si="37"/>
-        <v>52746.61823988711</v>
+        <v>47129</v>
       </c>
       <c r="BD10" s="4">
-        <f t="shared" si="37"/>
-        <v>54125.898870072117</v>
+        <f>BD5*0.06</f>
+        <v>46175.7912</v>
       </c>
       <c r="BE10" s="4">
-        <f t="shared" si="37"/>
-        <v>55208.416847473563</v>
+        <f t="shared" ref="BE10:BM10" si="37">BE5*0.06</f>
+        <v>49123.264176000004</v>
       </c>
       <c r="BF10" s="4">
         <f t="shared" si="37"/>
-        <v>56101.261303564155</v>
+        <v>51488.319576959999</v>
       </c>
       <c r="BG10" s="4">
         <f t="shared" si="37"/>
-        <v>56662.273916599785</v>
+        <v>53147.9785846464</v>
       </c>
       <c r="BH10" s="4">
         <f t="shared" si="37"/>
-        <v>57228.896655765791</v>
+        <v>54538.482316735877</v>
       </c>
       <c r="BI10" s="4">
         <f t="shared" si="37"/>
-        <v>57801.18562232345</v>
+        <v>55629.251963070601</v>
+      </c>
+      <c r="BJ10" s="4">
+        <f t="shared" si="37"/>
+        <v>56529.662377613924</v>
+      </c>
+      <c r="BK10" s="4">
+        <f t="shared" si="37"/>
+        <v>57094.95900139006</v>
+      </c>
+      <c r="BL10" s="4">
+        <f t="shared" si="37"/>
+        <v>57665.908591403961</v>
+      </c>
+      <c r="BM10" s="4">
+        <f t="shared" si="37"/>
+        <v>58242.567677318002</v>
       </c>
     </row>
-    <row r="11" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>39</v>
       </c>
@@ -3425,96 +3477,99 @@
         <v>2875</v>
       </c>
       <c r="AL11" s="4">
-        <f>AH11*1.05</f>
-        <v>3006.15</v>
-      </c>
-      <c r="AN11" s="4">
+        <v>2704</v>
+      </c>
+      <c r="AM11" s="4"/>
+      <c r="AN11" s="4"/>
+      <c r="AO11" s="4"/>
+      <c r="AP11" s="4"/>
+      <c r="AR11" s="4">
         <v>1552</v>
       </c>
-      <c r="AO11" s="4">
+      <c r="AS11" s="4">
         <v>1747</v>
       </c>
-      <c r="AP11" s="4">
+      <c r="AT11" s="4">
         <v>2432</v>
       </c>
-      <c r="AQ11" s="4">
+      <c r="AU11" s="4">
         <f>SUM(C11:F11)</f>
         <v>3673</v>
       </c>
-      <c r="AR11" s="4">
+      <c r="AV11" s="4">
         <f>SUM(G11:J11)</f>
         <v>4336</v>
       </c>
-      <c r="AS11" s="4">
+      <c r="AW11" s="4">
         <f>SUM(K11:N11)</f>
         <v>5203</v>
       </c>
-      <c r="AT11" s="4">
+      <c r="AX11" s="4">
         <f>SUM(O11:R11)</f>
         <v>6668</v>
       </c>
-      <c r="AU11" s="4">
+      <c r="AY11" s="4">
         <f>SUM(S11:V11)</f>
         <v>8823</v>
       </c>
-      <c r="AV11" s="4">
+      <c r="AZ11" s="4">
         <f>SUM(W11:Z11)</f>
         <v>11891</v>
       </c>
-      <c r="AW11" s="4">
+      <c r="BA11" s="4">
         <f>SUM(AA11:AD11)</f>
         <v>11816</v>
       </c>
-      <c r="AX11" s="4">
+      <c r="BB11" s="4">
         <f>SUM(AE11:AH11)</f>
         <v>11359</v>
       </c>
-      <c r="AY11" s="4">
+      <c r="BC11" s="4">
         <f>SUM(AI11:AL11)</f>
-        <v>11474.15</v>
-      </c>
-      <c r="AZ11" s="4">
-        <f>AY11*1.03</f>
-        <v>11818.3745</v>
-      </c>
-      <c r="BA11" s="4">
-        <f>AZ11*1.02</f>
-        <v>12054.74199</v>
-      </c>
-      <c r="BB11" s="4">
-        <f>BA11*1.02</f>
-        <v>12295.8368298</v>
-      </c>
-      <c r="BC11" s="4">
-        <f>BB11*1.02</f>
-        <v>12541.753566396001</v>
+        <v>11172</v>
       </c>
       <c r="BD11" s="4">
-        <f t="shared" ref="BD11:BE11" si="38">BC11*1.01</f>
-        <v>12667.171102059961</v>
+        <f>BC11*1.03</f>
+        <v>11507.16</v>
       </c>
       <c r="BE11" s="4">
+        <f>BD11*1.02</f>
+        <v>11737.3032</v>
+      </c>
+      <c r="BF11" s="4">
+        <f>BE11*1.02</f>
+        <v>11972.049264000001</v>
+      </c>
+      <c r="BG11" s="4">
+        <f>BF11*1.02</f>
+        <v>12211.490249280001</v>
+      </c>
+      <c r="BH11" s="4">
+        <f t="shared" ref="BH11:BI11" si="38">BG11*1.01</f>
+        <v>12333.605151772801</v>
+      </c>
+      <c r="BI11" s="4">
         <f t="shared" si="38"/>
-        <v>12793.842813080561</v>
-      </c>
-      <c r="BF11" s="4">
-        <f t="shared" ref="BF11" si="39">BE11*1.01</f>
-        <v>12921.781241211365</v>
-      </c>
-      <c r="BG11" s="4">
-        <f t="shared" ref="BG11" si="40">BF11*1.01</f>
-        <v>13050.99905362348</v>
-      </c>
-      <c r="BH11" s="4">
-        <f t="shared" ref="BH11" si="41">BG11*1.01</f>
-        <v>13181.509044159715</v>
-      </c>
-      <c r="BI11" s="4">
-        <f t="shared" ref="BI11" si="42">BH11*1.01</f>
-        <v>13313.324134601313</v>
+        <v>12456.941203290529</v>
+      </c>
+      <c r="BJ11" s="4">
+        <f t="shared" ref="BJ11" si="39">BI11*1.01</f>
+        <v>12581.510615323436</v>
+      </c>
+      <c r="BK11" s="4">
+        <f t="shared" ref="BK11" si="40">BJ11*1.01</f>
+        <v>12707.325721476671</v>
+      </c>
+      <c r="BL11" s="4">
+        <f t="shared" ref="BL11" si="41">BK11*1.01</f>
+        <v>12834.398978691437</v>
+      </c>
+      <c r="BM11" s="4">
+        <f t="shared" ref="BM11" si="42">BL11*1.01</f>
+        <v>12962.742968478351</v>
       </c>
     </row>
-    <row r="12" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>41</v>
       </c>
@@ -3624,571 +3679,582 @@
         <v>2875</v>
       </c>
       <c r="AL12" s="4">
-        <f t="shared" ref="AK12:AL12" si="43">AH12*1.01</f>
-        <v>177.76</v>
-      </c>
-      <c r="AN12" s="4">
+        <v>1257</v>
+      </c>
+      <c r="AM12" s="4"/>
+      <c r="AN12" s="4"/>
+      <c r="AO12" s="4"/>
+      <c r="AP12" s="4"/>
+      <c r="AR12" s="4">
         <v>133</v>
       </c>
-      <c r="AO12" s="4">
+      <c r="AS12" s="4">
         <v>171</v>
       </c>
-      <c r="AP12" s="4">
+      <c r="AT12" s="4">
         <v>167</v>
       </c>
-      <c r="AQ12" s="4">
+      <c r="AU12" s="4">
         <f>SUM(C12:F12)</f>
         <v>215</v>
       </c>
-      <c r="AR12" s="4">
+      <c r="AV12" s="4">
         <f>SUM(G12:J12)</f>
         <v>297</v>
       </c>
-      <c r="AS12" s="4">
+      <c r="AW12" s="4">
         <f>SUM(K12:N12)</f>
         <v>201</v>
       </c>
-      <c r="AT12" s="4">
+      <c r="AX12" s="4">
         <f>SUM(O12:R12)</f>
         <v>-74</v>
       </c>
-      <c r="AU12" s="4">
+      <c r="AY12" s="4">
         <f>SUM(S12:V12)</f>
         <v>62</v>
       </c>
-      <c r="AV12" s="4">
+      <c r="AZ12" s="4">
         <f>SUM(W12:Z12)</f>
         <v>1263</v>
       </c>
-      <c r="AW12" s="4">
+      <c r="BA12" s="4">
         <f>SUM(AA12:AD12)</f>
         <v>767</v>
       </c>
-      <c r="AX12" s="4">
+      <c r="BB12" s="4">
         <f>SUM(AE12:AH12)</f>
         <v>763</v>
       </c>
-      <c r="AY12" s="4">
+      <c r="BC12" s="4">
         <f>SUM(AI12:AL12)</f>
-        <v>3559.76</v>
-      </c>
-      <c r="AZ12" s="4">
-        <f t="shared" ref="AZ12:BE12" si="44">AY12*1.03</f>
-        <v>3666.5528000000004</v>
-      </c>
-      <c r="BA12" s="4">
-        <f t="shared" si="44"/>
-        <v>3776.5493840000004</v>
-      </c>
-      <c r="BB12" s="4">
-        <f t="shared" si="44"/>
-        <v>3889.8458655200006</v>
-      </c>
-      <c r="BC12" s="4">
-        <f t="shared" si="44"/>
-        <v>4006.5412414856009</v>
+        <v>4639</v>
       </c>
       <c r="BD12" s="4">
-        <f t="shared" si="44"/>
-        <v>4126.7374787301687</v>
+        <f t="shared" ref="BD12:BI12" si="43">BC12*1.03</f>
+        <v>4778.17</v>
       </c>
       <c r="BE12" s="4">
-        <f t="shared" si="44"/>
-        <v>4250.5396030920738</v>
+        <f t="shared" si="43"/>
+        <v>4921.5151000000005</v>
       </c>
       <c r="BF12" s="4">
-        <f t="shared" ref="BF12" si="45">BE12*1.03</f>
-        <v>4378.0557911848364</v>
+        <f t="shared" si="43"/>
+        <v>5069.1605530000006</v>
       </c>
       <c r="BG12" s="4">
-        <f t="shared" ref="BG12" si="46">BF12*1.03</f>
-        <v>4509.3974649203819</v>
+        <f t="shared" si="43"/>
+        <v>5221.235369590001</v>
       </c>
       <c r="BH12" s="4">
-        <f t="shared" ref="BH12" si="47">BG12*1.03</f>
-        <v>4644.6793888679931</v>
+        <f t="shared" si="43"/>
+        <v>5377.8724306777012</v>
       </c>
       <c r="BI12" s="4">
-        <f t="shared" ref="BI12" si="48">BH12*1.03</f>
-        <v>4784.0197705340333</v>
+        <f t="shared" si="43"/>
+        <v>5539.2086035980328</v>
+      </c>
+      <c r="BJ12" s="4">
+        <f t="shared" ref="BJ12" si="44">BI12*1.03</f>
+        <v>5705.3848617059739</v>
+      </c>
+      <c r="BK12" s="4">
+        <f t="shared" ref="BK12" si="45">BJ12*1.03</f>
+        <v>5876.5464075571535</v>
+      </c>
+      <c r="BL12" s="4">
+        <f t="shared" ref="BL12" si="46">BK12*1.03</f>
+        <v>6052.842799783868</v>
+      </c>
+      <c r="BM12" s="4">
+        <f t="shared" ref="BM12" si="47">BL12*1.03</f>
+        <v>6234.428083777384</v>
       </c>
     </row>
-    <row r="13" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="4">
-        <f t="shared" ref="C13:R13" si="49">SUM(C8:C12)</f>
+        <f t="shared" ref="C13:R13" si="48">SUM(C8:C12)</f>
         <v>12269</v>
       </c>
       <c r="D13" s="4">
+        <f t="shared" si="48"/>
+        <v>13876</v>
+      </c>
+      <c r="E13" s="4">
+        <f t="shared" si="48"/>
+        <v>15848</v>
+      </c>
+      <c r="F13" s="4">
+        <f t="shared" si="48"/>
+        <v>19832</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="48"/>
+        <v>18380</v>
+      </c>
+      <c r="H13" s="4">
+        <f t="shared" si="48"/>
+        <v>19271</v>
+      </c>
+      <c r="I13" s="4">
+        <f t="shared" si="48"/>
+        <v>19849</v>
+      </c>
+      <c r="J13" s="4">
+        <f t="shared" si="48"/>
+        <v>23811</v>
+      </c>
+      <c r="K13" s="4">
+        <f t="shared" si="48"/>
+        <v>21360</v>
+      </c>
+      <c r="L13" s="4">
+        <f t="shared" si="48"/>
+        <v>23983</v>
+      </c>
+      <c r="M13" s="4">
+        <f t="shared" si="48"/>
+        <v>25522</v>
+      </c>
+      <c r="N13" s="4">
+        <f t="shared" si="48"/>
+        <v>29581</v>
+      </c>
+      <c r="O13" s="4">
+        <f t="shared" si="48"/>
+        <v>27206</v>
+      </c>
+      <c r="P13" s="4">
+        <f t="shared" si="48"/>
+        <v>30409</v>
+      </c>
+      <c r="Q13" s="4">
+        <f t="shared" si="48"/>
+        <v>32845</v>
+      </c>
+      <c r="R13" s="4">
+        <f t="shared" si="48"/>
+        <v>39398</v>
+      </c>
+      <c r="S13" s="4">
+        <f t="shared" ref="S13:V13" si="49">SUM(S8:S12)</f>
+        <v>37250</v>
+      </c>
+      <c r="T13" s="4">
+        <f t="shared" ref="T13:U13" si="50">SUM(T8:T12)</f>
+        <v>41202</v>
+      </c>
+      <c r="U13" s="4">
+        <f t="shared" si="50"/>
+        <v>43030</v>
+      </c>
+      <c r="V13" s="4">
         <f t="shared" si="49"/>
-        <v>13876</v>
-      </c>
-      <c r="E13" s="4">
-        <f t="shared" si="49"/>
-        <v>15848</v>
-      </c>
-      <c r="F13" s="4">
-        <f t="shared" si="49"/>
-        <v>19832</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="49"/>
-        <v>18380</v>
-      </c>
-      <c r="H13" s="4">
-        <f t="shared" si="49"/>
-        <v>19271</v>
-      </c>
-      <c r="I13" s="4">
-        <f t="shared" si="49"/>
-        <v>19849</v>
-      </c>
-      <c r="J13" s="4">
-        <f t="shared" si="49"/>
-        <v>23811</v>
-      </c>
-      <c r="K13" s="4">
-        <f t="shared" si="49"/>
-        <v>21360</v>
-      </c>
-      <c r="L13" s="4">
-        <f t="shared" si="49"/>
-        <v>23983</v>
-      </c>
-      <c r="M13" s="4">
-        <f t="shared" si="49"/>
-        <v>25522</v>
-      </c>
-      <c r="N13" s="4">
-        <f t="shared" si="49"/>
-        <v>29581</v>
-      </c>
-      <c r="O13" s="4">
-        <f t="shared" si="49"/>
-        <v>27206</v>
-      </c>
-      <c r="P13" s="4">
-        <f t="shared" si="49"/>
-        <v>30409</v>
-      </c>
-      <c r="Q13" s="4">
-        <f t="shared" si="49"/>
-        <v>32845</v>
-      </c>
-      <c r="R13" s="4">
-        <f t="shared" si="49"/>
-        <v>39398</v>
-      </c>
-      <c r="S13" s="4">
-        <f t="shared" ref="S13:V13" si="50">SUM(S8:S12)</f>
-        <v>37250</v>
-      </c>
-      <c r="T13" s="4">
-        <f t="shared" ref="T13:U13" si="51">SUM(T8:T12)</f>
-        <v>41202</v>
-      </c>
-      <c r="U13" s="4">
+        <v>51117</v>
+      </c>
+      <c r="W13" s="4">
+        <f t="shared" ref="W13:X13" si="51">SUM(W8:W12)</f>
+        <v>46276</v>
+      </c>
+      <c r="X13" s="4">
         <f t="shared" si="51"/>
-        <v>43030</v>
-      </c>
-      <c r="V13" s="4">
-        <f t="shared" si="50"/>
-        <v>51117</v>
-      </c>
-      <c r="W13" s="4">
-        <f t="shared" ref="W13:X13" si="52">SUM(W8:W12)</f>
-        <v>46276</v>
-      </c>
-      <c r="X13" s="4">
-        <f t="shared" si="52"/>
         <v>51493</v>
       </c>
       <c r="Y13" s="4">
-        <f t="shared" ref="Y13" si="53">SUM(Y8:Y12)</f>
+        <f t="shared" ref="Y13" si="52">SUM(Y8:Y12)</f>
         <v>54308</v>
       </c>
       <c r="Z13" s="4">
-        <f t="shared" ref="Z13" si="54">SUM(Z8:Z12)</f>
+        <f t="shared" ref="Z13" si="53">SUM(Z8:Z12)</f>
         <v>60827</v>
       </c>
       <c r="AA13" s="4">
-        <f t="shared" ref="AA13:AB13" si="55">SUM(AA8:AA12)</f>
+        <f t="shared" ref="AA13:AB13" si="54">SUM(AA8:AA12)</f>
         <v>54793</v>
       </c>
       <c r="AB13" s="4">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>57329</v>
       </c>
       <c r="AC13" s="4">
-        <f t="shared" ref="AC13" si="56">SUM(AC8:AC12)</f>
+        <f t="shared" ref="AC13" si="55">SUM(AC8:AC12)</f>
         <v>56873</v>
       </c>
       <c r="AD13" s="4">
-        <f t="shared" ref="AD13" si="57">SUM(AD8:AD12)</f>
+        <f t="shared" ref="AD13" si="56">SUM(AD8:AD12)</f>
         <v>64199</v>
       </c>
       <c r="AE13" s="4">
-        <f t="shared" ref="AE13:AF13" si="58">SUM(AE8:AE12)</f>
+        <f t="shared" ref="AE13:AF13" si="57">SUM(AE8:AE12)</f>
         <v>55373</v>
       </c>
       <c r="AF13" s="4">
+        <f t="shared" si="57"/>
+        <v>59520</v>
+      </c>
+      <c r="AG13" s="4">
+        <f t="shared" ref="AG13:AH13" si="58">SUM(AG8:AG12)</f>
+        <v>60489</v>
+      </c>
+      <c r="AH13" s="4">
         <f t="shared" si="58"/>
-        <v>59520</v>
-      </c>
-      <c r="AG13" s="4">
-        <f t="shared" ref="AG13:AH13" si="59">SUM(AG8:AG12)</f>
-        <v>60489</v>
-      </c>
-      <c r="AH13" s="4">
+        <v>67696</v>
+      </c>
+      <c r="AI13" s="4">
+        <f t="shared" ref="AI13:AL13" si="59">SUM(AI8:AI12)</f>
+        <v>60286</v>
+      </c>
+      <c r="AJ13" s="4">
         <f t="shared" si="59"/>
-        <v>67696</v>
-      </c>
-      <c r="AI13" s="4">
-        <f t="shared" ref="AI13:AL13" si="60">SUM(AI8:AI12)</f>
-        <v>60286</v>
-      </c>
-      <c r="AJ13" s="4">
+        <v>67722</v>
+      </c>
+      <c r="AK13" s="4">
+        <f t="shared" si="59"/>
+        <v>74077</v>
+      </c>
+      <c r="AL13" s="4">
+        <f t="shared" si="59"/>
+        <v>78450</v>
+      </c>
+      <c r="AM13" s="4"/>
+      <c r="AN13" s="4"/>
+      <c r="AO13" s="4"/>
+      <c r="AP13" s="4"/>
+      <c r="AQ13" s="4"/>
+      <c r="AR13" s="4">
+        <f t="shared" ref="AR13:AY13" si="60">SUM(AR8:AR12)</f>
+        <v>26058</v>
+      </c>
+      <c r="AS13" s="4">
         <f t="shared" si="60"/>
-        <v>67722</v>
-      </c>
-      <c r="AK13" s="4">
+        <v>33122</v>
+      </c>
+      <c r="AT13" s="4">
         <f t="shared" si="60"/>
-        <v>74077</v>
-      </c>
-      <c r="AL13" s="4">
+        <v>43536</v>
+      </c>
+      <c r="AU13" s="4">
         <f t="shared" si="60"/>
-        <v>78566.34689999999</v>
-      </c>
-      <c r="AM13" s="4"/>
-      <c r="AN13" s="4">
-        <f t="shared" ref="AN13:AU13" si="61">SUM(AN8:AN12)</f>
-        <v>26058</v>
-      </c>
-      <c r="AO13" s="4">
+        <v>61825</v>
+      </c>
+      <c r="AV13" s="4">
+        <f t="shared" si="60"/>
+        <v>81311</v>
+      </c>
+      <c r="AW13" s="4">
+        <f t="shared" si="60"/>
+        <v>100446</v>
+      </c>
+      <c r="AX13" s="4">
+        <f t="shared" si="60"/>
+        <v>129858</v>
+      </c>
+      <c r="AY13" s="4">
+        <f t="shared" si="60"/>
+        <v>172599</v>
+      </c>
+      <c r="AZ13" s="4">
+        <f t="shared" ref="AZ13:BI13" si="61">SUM(AZ8:AZ12)</f>
+        <v>212904</v>
+      </c>
+      <c r="BA13" s="4">
         <f t="shared" si="61"/>
-        <v>33122</v>
-      </c>
-      <c r="AP13" s="4">
+        <v>233194</v>
+      </c>
+      <c r="BB13" s="4">
+        <f t="shared" ref="BB13" si="62">SUM(BB8:BB12)</f>
+        <v>243078</v>
+      </c>
+      <c r="BC13" s="4">
         <f t="shared" si="61"/>
-        <v>43536</v>
-      </c>
-      <c r="AQ13" s="4">
+        <v>280535</v>
+      </c>
+      <c r="BD13" s="4">
         <f t="shared" si="61"/>
-        <v>61825</v>
-      </c>
-      <c r="AR13" s="4">
+        <v>299444.11919999996</v>
+      </c>
+      <c r="BE13" s="4">
         <f t="shared" si="61"/>
-        <v>81311</v>
-      </c>
-      <c r="AS13" s="4">
+        <v>317426.37411600008</v>
+      </c>
+      <c r="BF13" s="4">
         <f t="shared" si="61"/>
-        <v>100446</v>
-      </c>
-      <c r="AT13" s="4">
+        <v>331239.90478436003</v>
+      </c>
+      <c r="BG13" s="4">
         <f t="shared" si="61"/>
-        <v>129858</v>
-      </c>
-      <c r="AU13" s="4">
+        <v>341459.91440657247</v>
+      </c>
+      <c r="BH13" s="4">
         <f t="shared" si="61"/>
-        <v>172599</v>
-      </c>
-      <c r="AV13" s="4">
-        <f t="shared" ref="AV13:BE13" si="62">SUM(AV8:AV12)</f>
-        <v>212904</v>
-      </c>
-      <c r="AW13" s="4">
-        <f t="shared" si="62"/>
-        <v>233194</v>
-      </c>
-      <c r="AX13" s="4">
-        <f t="shared" ref="AX13" si="63">SUM(AX8:AX12)</f>
-        <v>243078</v>
-      </c>
-      <c r="AY13" s="4">
-        <f t="shared" si="62"/>
-        <v>280651.3469</v>
-      </c>
-      <c r="AZ13" s="4">
-        <f t="shared" si="62"/>
-        <v>298834.77440200001</v>
-      </c>
-      <c r="BA13" s="4">
-        <f t="shared" si="62"/>
-        <v>316787.8172585601</v>
-      </c>
-      <c r="BB13" s="4">
-        <f t="shared" si="62"/>
-        <v>330563.33743458561</v>
-      </c>
-      <c r="BC13" s="4">
-        <f t="shared" si="62"/>
-        <v>340751.86260703858</v>
-      </c>
-      <c r="BD13" s="4">
-        <f t="shared" si="62"/>
-        <v>348616.76666478557</v>
-      </c>
-      <c r="BE13" s="4">
-        <f t="shared" si="62"/>
-        <v>355503.69766184804</v>
-      </c>
-      <c r="BF13" s="4">
-        <f t="shared" ref="BF13:BI13" si="64">SUM(BF8:BF12)</f>
-        <v>360336.40643718379</v>
-      </c>
-      <c r="BG13" s="4">
-        <f t="shared" si="64"/>
-        <v>364027.33161737933</v>
-      </c>
-      <c r="BH13" s="4">
-        <f t="shared" si="64"/>
-        <v>367757.79288285156</v>
+        <v>349365.61470729497</v>
       </c>
       <c r="BI13" s="4">
-        <f t="shared" si="64"/>
-        <v>371528.26439945743</v>
+        <f t="shared" si="61"/>
+        <v>356283.36967422994</v>
+      </c>
+      <c r="BJ13" s="4">
+        <f t="shared" ref="BJ13:BM13" si="63">SUM(BJ8:BJ12)</f>
+        <v>361161.40017523832</v>
+      </c>
+      <c r="BK13" s="4">
+        <f t="shared" si="63"/>
+        <v>364887.1218742248</v>
+      </c>
+      <c r="BL13" s="4">
+        <f t="shared" si="63"/>
+        <v>368653.52402111824</v>
+      </c>
+      <c r="BM13" s="4">
+        <f t="shared" si="63"/>
+        <v>372461.11611732509</v>
       </c>
     </row>
-    <row r="14" spans="2:61" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:65" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B14" s="1" t="s">
         <v>42</v>
       </c>
       <c r="C14" s="8">
-        <f t="shared" ref="C14:R14" si="65">C7-C13</f>
+        <f t="shared" ref="C14:R14" si="64">C7-C13</f>
         <v>1005</v>
       </c>
       <c r="D14" s="8">
+        <f t="shared" si="64"/>
+        <v>628</v>
+      </c>
+      <c r="E14" s="8">
+        <f t="shared" si="64"/>
+        <v>347</v>
+      </c>
+      <c r="F14" s="8">
+        <f t="shared" si="64"/>
+        <v>2127</v>
+      </c>
+      <c r="G14" s="8">
+        <f t="shared" si="64"/>
+        <v>1927</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="64"/>
+        <v>2983</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="64"/>
+        <v>3724</v>
+      </c>
+      <c r="J14" s="8">
+        <f t="shared" si="64"/>
+        <v>3786</v>
+      </c>
+      <c r="K14" s="8">
+        <f t="shared" si="64"/>
+        <v>4420</v>
+      </c>
+      <c r="L14" s="8">
+        <f t="shared" si="64"/>
+        <v>3084</v>
+      </c>
+      <c r="M14" s="8">
+        <f t="shared" si="64"/>
+        <v>3157</v>
+      </c>
+      <c r="N14" s="8">
+        <f t="shared" si="64"/>
+        <v>3879</v>
+      </c>
+      <c r="O14" s="8">
+        <f t="shared" si="64"/>
+        <v>3989</v>
+      </c>
+      <c r="P14" s="8">
+        <f t="shared" si="64"/>
+        <v>5843</v>
+      </c>
+      <c r="Q14" s="8">
+        <f t="shared" si="64"/>
+        <v>6194</v>
+      </c>
+      <c r="R14" s="8">
+        <f t="shared" si="64"/>
+        <v>6873</v>
+      </c>
+      <c r="S14" s="8">
+        <f t="shared" ref="S14:V14" si="65">S7-S13</f>
+        <v>8865</v>
+      </c>
+      <c r="T14" s="8">
+        <f t="shared" ref="T14:U14" si="66">T7-T13</f>
+        <v>7702</v>
+      </c>
+      <c r="U14" s="8">
+        <f t="shared" si="66"/>
+        <v>4852</v>
+      </c>
+      <c r="V14" s="8">
         <f t="shared" si="65"/>
-        <v>628</v>
-      </c>
-      <c r="E14" s="8">
-        <f t="shared" si="65"/>
-        <v>347</v>
-      </c>
-      <c r="F14" s="8">
-        <f t="shared" si="65"/>
-        <v>2127</v>
-      </c>
-      <c r="G14" s="8">
-        <f t="shared" si="65"/>
-        <v>1927</v>
-      </c>
-      <c r="H14" s="8">
-        <f t="shared" si="65"/>
-        <v>2983</v>
-      </c>
-      <c r="I14" s="8">
-        <f t="shared" si="65"/>
-        <v>3724</v>
-      </c>
-      <c r="J14" s="8">
-        <f t="shared" si="65"/>
-        <v>3786</v>
-      </c>
-      <c r="K14" s="8">
-        <f t="shared" si="65"/>
-        <v>4420</v>
-      </c>
-      <c r="L14" s="8">
-        <f t="shared" si="65"/>
-        <v>3084</v>
-      </c>
-      <c r="M14" s="8">
-        <f t="shared" si="65"/>
-        <v>3157</v>
-      </c>
-      <c r="N14" s="8">
-        <f t="shared" si="65"/>
-        <v>3879</v>
-      </c>
-      <c r="O14" s="8">
-        <f t="shared" si="65"/>
-        <v>3989</v>
-      </c>
-      <c r="P14" s="8">
-        <f t="shared" si="65"/>
-        <v>5843</v>
-      </c>
-      <c r="Q14" s="8">
-        <f t="shared" si="65"/>
-        <v>6194</v>
-      </c>
-      <c r="R14" s="8">
-        <f t="shared" si="65"/>
-        <v>6873</v>
-      </c>
-      <c r="S14" s="8">
-        <f t="shared" ref="S14:V14" si="66">S7-S13</f>
-        <v>8865</v>
-      </c>
-      <c r="T14" s="8">
-        <f t="shared" ref="T14:U14" si="67">T7-T13</f>
-        <v>7702</v>
-      </c>
-      <c r="U14" s="8">
+        <v>3460</v>
+      </c>
+      <c r="W14" s="8">
+        <f t="shared" ref="W14:X14" si="67">W7-W13</f>
+        <v>3669</v>
+      </c>
+      <c r="X14" s="8">
         <f t="shared" si="67"/>
-        <v>4852</v>
-      </c>
-      <c r="V14" s="8">
-        <f t="shared" si="66"/>
-        <v>3460</v>
-      </c>
-      <c r="W14" s="8">
-        <f t="shared" ref="W14:X14" si="68">W7-W13</f>
-        <v>3669</v>
-      </c>
-      <c r="X14" s="8">
-        <f t="shared" si="68"/>
         <v>3317</v>
       </c>
       <c r="Y14" s="8">
-        <f t="shared" ref="Y14" si="69">Y7-Y13</f>
+        <f t="shared" ref="Y14" si="68">Y7-Y13</f>
         <v>2525</v>
       </c>
       <c r="Z14" s="8">
-        <f t="shared" ref="Z14" si="70">Z7-Z13</f>
+        <f t="shared" ref="Z14" si="69">Z7-Z13</f>
         <v>2737</v>
       </c>
       <c r="AA14" s="8">
-        <f t="shared" ref="AA14:AB14" si="71">AA7-AA13</f>
+        <f t="shared" ref="AA14:AB14" si="70">AA7-AA13</f>
         <v>4774</v>
       </c>
       <c r="AB14" s="8">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>7681</v>
       </c>
       <c r="AC14" s="8">
-        <f t="shared" ref="AC14" si="72">AC7-AC13</f>
+        <f t="shared" ref="AC14" si="71">AC7-AC13</f>
         <v>11188</v>
       </c>
       <c r="AD14" s="8">
-        <f t="shared" ref="AD14" si="73">AD7-AD13</f>
+        <f t="shared" ref="AD14" si="72">AD7-AD13</f>
         <v>13209</v>
       </c>
       <c r="AE14" s="8">
-        <f t="shared" ref="AE14:AF14" si="74">AE7-AE13</f>
+        <f t="shared" ref="AE14:AF14" si="73">AE7-AE13</f>
         <v>15307</v>
       </c>
       <c r="AF14" s="8">
+        <f t="shared" si="73"/>
+        <v>14672</v>
+      </c>
+      <c r="AG14" s="8">
+        <f t="shared" ref="AG14:AH14" si="74">AG7-AG13</f>
+        <v>17411</v>
+      </c>
+      <c r="AH14" s="8">
         <f t="shared" si="74"/>
-        <v>14672</v>
-      </c>
-      <c r="AG14" s="8">
-        <f t="shared" ref="AG14:AH14" si="75">AG7-AG13</f>
-        <v>17411</v>
-      </c>
-      <c r="AH14" s="8">
+        <v>21203</v>
+      </c>
+      <c r="AI14" s="8">
+        <f t="shared" ref="AI14:AL14" si="75">AI7-AI13</f>
+        <v>18405</v>
+      </c>
+      <c r="AJ14" s="8">
         <f t="shared" si="75"/>
-        <v>21203</v>
-      </c>
-      <c r="AI14" s="8">
-        <f t="shared" ref="AI14:AL14" si="76">AI7-AI13</f>
-        <v>18405</v>
-      </c>
-      <c r="AJ14" s="8">
+        <v>19171</v>
+      </c>
+      <c r="AK14" s="8">
+        <f t="shared" si="75"/>
+        <v>17422</v>
+      </c>
+      <c r="AL14" s="8">
+        <f t="shared" si="75"/>
+        <v>24977</v>
+      </c>
+      <c r="AM14" s="8"/>
+      <c r="AN14" s="8"/>
+      <c r="AO14" s="8"/>
+      <c r="AP14" s="8"/>
+      <c r="AR14" s="8">
+        <f t="shared" ref="AR14:AY14" si="76">AR7-AR13</f>
+        <v>178</v>
+      </c>
+      <c r="AS14" s="8">
         <f t="shared" si="76"/>
-        <v>19171</v>
-      </c>
-      <c r="AK14" s="8">
+        <v>2233</v>
+      </c>
+      <c r="AT14" s="8">
         <f t="shared" si="76"/>
-        <v>17422</v>
-      </c>
-      <c r="AL14" s="8">
+        <v>4186</v>
+      </c>
+      <c r="AU14" s="8">
         <f t="shared" si="76"/>
-        <v>23399.546499999997</v>
-      </c>
-      <c r="AN14" s="8">
-        <f t="shared" ref="AN14:AU14" si="77">AN7-AN13</f>
-        <v>178</v>
-      </c>
-      <c r="AO14" s="8">
+        <v>4107</v>
+      </c>
+      <c r="AV14" s="8">
+        <f t="shared" si="76"/>
+        <v>12420</v>
+      </c>
+      <c r="AW14" s="8">
+        <f t="shared" si="76"/>
+        <v>14540</v>
+      </c>
+      <c r="AX14" s="8">
+        <f t="shared" si="76"/>
+        <v>22899</v>
+      </c>
+      <c r="AY14" s="8">
+        <f t="shared" si="76"/>
+        <v>24879</v>
+      </c>
+      <c r="AZ14" s="8">
+        <f t="shared" ref="AZ14:BI14" si="77">AZ7-AZ13</f>
+        <v>12248</v>
+      </c>
+      <c r="BA14" s="8">
         <f t="shared" si="77"/>
-        <v>2233</v>
-      </c>
-      <c r="AP14" s="8">
+        <v>36852</v>
+      </c>
+      <c r="BB14" s="8">
+        <f t="shared" ref="BB14" si="78">BB7-BB13</f>
+        <v>68593</v>
+      </c>
+      <c r="BC14" s="8">
         <f t="shared" si="77"/>
-        <v>4186</v>
-      </c>
-      <c r="AQ14" s="8">
+        <v>79975</v>
+      </c>
+      <c r="BD14" s="8">
         <f t="shared" si="77"/>
-        <v>4107</v>
-      </c>
-      <c r="AR14" s="8">
+        <v>93050.106000000087</v>
+      </c>
+      <c r="BE14" s="8">
         <f t="shared" si="77"/>
-        <v>12420</v>
-      </c>
-      <c r="AS14" s="8">
+        <v>108308.58207599993</v>
+      </c>
+      <c r="BF14" s="8">
         <f t="shared" si="77"/>
-        <v>14540</v>
-      </c>
-      <c r="AT14" s="8">
+        <v>123573.58481212001</v>
+      </c>
+      <c r="BG14" s="8">
         <f t="shared" si="77"/>
-        <v>22899</v>
-      </c>
-      <c r="AU14" s="8">
+        <v>128013.89642447082</v>
+      </c>
+      <c r="BH14" s="8">
         <f t="shared" si="77"/>
-        <v>24879</v>
-      </c>
-      <c r="AV14" s="8">
-        <f t="shared" ref="AV14:BE14" si="78">AV7-AV13</f>
-        <v>12248</v>
-      </c>
-      <c r="AW14" s="8">
-        <f t="shared" si="78"/>
-        <v>36852</v>
-      </c>
-      <c r="AX14" s="8">
-        <f t="shared" ref="AX14" si="79">AX7-AX13</f>
-        <v>68593</v>
-      </c>
-      <c r="AY14" s="8">
-        <f t="shared" si="78"/>
-        <v>78397.546499999939</v>
-      </c>
-      <c r="AZ14" s="8">
-        <f t="shared" si="78"/>
-        <v>90741.672560000035</v>
-      </c>
-      <c r="BA14" s="8">
-        <f t="shared" si="78"/>
-        <v>105760.09436415997</v>
-      </c>
-      <c r="BB14" s="8">
-        <f t="shared" si="78"/>
-        <v>120827.54385807522</v>
-      </c>
-      <c r="BC14" s="8">
-        <f t="shared" si="78"/>
-        <v>125176.59851196426</v>
-      </c>
-      <c r="BD14" s="8">
-        <f t="shared" si="78"/>
-        <v>129495.34002085152</v>
-      </c>
-      <c r="BE14" s="8">
-        <f t="shared" si="78"/>
-        <v>132170.65115750179</v>
-      </c>
-      <c r="BF14" s="8">
-        <f t="shared" ref="BF14:BI14" si="80">BF7-BF13</f>
-        <v>135224.73507763294</v>
-      </c>
-      <c r="BG14" s="8">
-        <f t="shared" si="80"/>
-        <v>136489.42131258547</v>
-      </c>
-      <c r="BH14" s="8">
-        <f t="shared" si="80"/>
-        <v>137764.12757641298</v>
+        <v>132390.97909053863</v>
       </c>
       <c r="BI14" s="8">
-        <f t="shared" si="80"/>
-        <v>139048.87526439974</v>
+        <f t="shared" si="77"/>
+        <v>135108.35599956044</v>
+      </c>
+      <c r="BJ14" s="8">
+        <f t="shared" ref="BJ14:BM14" si="79">BJ7-BJ13</f>
+        <v>138183.95082701801</v>
+      </c>
+      <c r="BK14" s="8">
+        <f t="shared" si="79"/>
+        <v>139451.68263805413</v>
+      </c>
+      <c r="BL14" s="8">
+        <f t="shared" si="79"/>
+        <v>140728.66853628343</v>
+      </c>
+      <c r="BM14" s="8">
+        <f t="shared" si="79"/>
+        <v>142014.89836565062</v>
       </c>
     </row>
-    <row r="15" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>43</v>
       </c>
@@ -4298,96 +4364,99 @@
         <v>-1100</v>
       </c>
       <c r="AL15" s="4">
-        <f t="shared" ref="AK15:AL15" si="81">AH15*1.05</f>
-        <v>-1310.4000000000001</v>
-      </c>
-      <c r="AN15" s="4">
+        <v>-1130</v>
+      </c>
+      <c r="AM15" s="4"/>
+      <c r="AN15" s="4"/>
+      <c r="AO15" s="4"/>
+      <c r="AP15" s="4"/>
+      <c r="AR15" s="4">
         <v>-39</v>
       </c>
-      <c r="AO15" s="4">
+      <c r="AS15" s="4">
         <v>-50</v>
       </c>
-      <c r="AP15" s="4">
+      <c r="AT15" s="4">
         <v>-100</v>
       </c>
-      <c r="AQ15" s="4">
+      <c r="AU15" s="4">
         <f>SUM(C15:F15)</f>
         <v>-203</v>
       </c>
-      <c r="AR15" s="4">
+      <c r="AV15" s="4">
         <f>SUM(G15:J15)</f>
         <v>-441</v>
       </c>
-      <c r="AS15" s="4">
+      <c r="AW15" s="4">
         <f>SUM(K15:N15)</f>
         <v>-833</v>
       </c>
-      <c r="AT15" s="4">
+      <c r="AX15" s="4">
         <f>SUM(O15:R15)</f>
         <v>-555</v>
       </c>
-      <c r="AU15" s="4">
+      <c r="AY15" s="4">
         <f>SUM(S15:V15)</f>
         <v>-448</v>
       </c>
-      <c r="AV15" s="4">
+      <c r="AZ15" s="4">
         <f>SUM(W15:Z15)</f>
         <v>-989</v>
       </c>
-      <c r="AW15" s="4">
+      <c r="BA15" s="4">
         <f>SUM(AA15:AD15)</f>
         <v>-2949</v>
       </c>
-      <c r="AX15" s="4">
+      <c r="BB15" s="4">
         <f>SUM(AE15:AH15)</f>
         <v>-4677</v>
       </c>
-      <c r="AY15" s="4">
+      <c r="BC15" s="4">
         <f>SUM(AI15:AL15)</f>
-        <v>-4561.3999999999996</v>
-      </c>
-      <c r="AZ15" s="4">
-        <f>AY15*1.05</f>
-        <v>-4789.47</v>
-      </c>
-      <c r="BA15" s="4">
-        <f t="shared" ref="BA15:BI15" si="82">AZ15*1.05</f>
-        <v>-5028.9435000000003</v>
-      </c>
-      <c r="BB15" s="4">
-        <f t="shared" si="82"/>
-        <v>-5280.3906750000006</v>
-      </c>
-      <c r="BC15" s="4">
-        <f t="shared" si="82"/>
-        <v>-5544.4102087500005</v>
+        <v>-4381</v>
       </c>
       <c r="BD15" s="4">
-        <f t="shared" si="82"/>
-        <v>-5821.6307191875012</v>
+        <f>BC15*1.05</f>
+        <v>-4600.05</v>
       </c>
       <c r="BE15" s="4">
-        <f t="shared" si="82"/>
-        <v>-6112.7122551468765</v>
+        <f t="shared" ref="BE15:BM15" si="80">BD15*1.05</f>
+        <v>-4830.0525000000007</v>
       </c>
       <c r="BF15" s="4">
-        <f t="shared" si="82"/>
-        <v>-6418.3478679042209</v>
+        <f t="shared" si="80"/>
+        <v>-5071.5551250000008</v>
       </c>
       <c r="BG15" s="4">
-        <f t="shared" si="82"/>
-        <v>-6739.2652612994325</v>
+        <f t="shared" si="80"/>
+        <v>-5325.1328812500014</v>
       </c>
       <c r="BH15" s="4">
-        <f t="shared" si="82"/>
-        <v>-7076.2285243644046</v>
+        <f t="shared" si="80"/>
+        <v>-5591.389525312502</v>
       </c>
       <c r="BI15" s="4">
-        <f t="shared" si="82"/>
-        <v>-7430.0399505826254</v>
+        <f t="shared" si="80"/>
+        <v>-5870.9590015781278</v>
+      </c>
+      <c r="BJ15" s="4">
+        <f t="shared" si="80"/>
+        <v>-6164.5069516570347</v>
+      </c>
+      <c r="BK15" s="4">
+        <f t="shared" si="80"/>
+        <v>-6472.7322992398867</v>
+      </c>
+      <c r="BL15" s="4">
+        <f t="shared" si="80"/>
+        <v>-6796.3689142018811</v>
+      </c>
+      <c r="BM15" s="4">
+        <f t="shared" si="80"/>
+        <v>-7136.1873599119754</v>
       </c>
     </row>
-    <row r="16" spans="2:61" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:65" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>44</v>
       </c>
@@ -4497,96 +4566,99 @@
         <v>538</v>
       </c>
       <c r="AL16" s="4">
-        <f t="shared" ref="AK16:AL16" si="83">AH16*0.98</f>
-        <v>558.6</v>
-      </c>
-      <c r="AN16" s="4">
+        <v>679</v>
+      </c>
+      <c r="AM16" s="4"/>
+      <c r="AN16" s="4"/>
+      <c r="AO16" s="4"/>
+      <c r="AP16" s="4"/>
+      <c r="AR16" s="4">
         <v>210</v>
       </c>
-      <c r="AO16" s="4">
+      <c r="AS16" s="4">
         <v>459</v>
       </c>
-      <c r="AP16" s="4">
+      <c r="AT16" s="4">
         <v>484</v>
       </c>
-      <c r="AQ16" s="4">
+      <c r="AU16" s="4">
         <f>SUM(C16:F16)</f>
         <v>849</v>
       </c>
-      <c r="AR16" s="4">
+      <c r="AV16" s="4">
         <f>SUM(G16:J16)</f>
         <v>1418</v>
       </c>
-      <c r="AS16" s="4">
+      <c r="AW16" s="4">
         <f>SUM(K16:N16)</f>
         <v>1600</v>
       </c>
-      <c r="AT16" s="4">
+      <c r="AX16" s="4">
         <f>SUM(O16:R16)</f>
         <v>1647</v>
       </c>
-      <c r="AU16" s="4">
+      <c r="AY16" s="4">
         <f>SUM(S16:V16)</f>
         <v>1809</v>
       </c>
-      <c r="AV16" s="4">
+      <c r="AZ16" s="4">
         <f>SUM(W16:Z16)</f>
         <v>2367</v>
       </c>
-      <c r="AW16" s="4">
+      <c r="BA16" s="4">
         <f>SUM(AA16:AD16)</f>
         <v>3182</v>
       </c>
-      <c r="AX16" s="4">
+      <c r="BB16" s="4">
         <f>SUM(AE16:AH16)</f>
         <v>2406</v>
       </c>
-      <c r="AY16" s="4">
+      <c r="BC16" s="4">
         <f>SUM(AI16:AL16)</f>
-        <v>2153.6</v>
-      </c>
-      <c r="AZ16" s="4">
-        <f t="shared" ref="AZ16:BI16" si="84">AY16*1.01</f>
-        <v>2175.136</v>
-      </c>
-      <c r="BA16" s="4">
-        <f t="shared" si="84"/>
-        <v>2196.8873600000002</v>
-      </c>
-      <c r="BB16" s="4">
-        <f t="shared" si="84"/>
-        <v>2218.8562336</v>
-      </c>
-      <c r="BC16" s="4">
-        <f t="shared" si="84"/>
-        <v>2241.0447959359999</v>
+        <v>2274</v>
       </c>
       <c r="BD16" s="4">
-        <f t="shared" si="84"/>
-        <v>2263.4552438953601</v>
+        <f t="shared" ref="BD16:BM16" si="81">BC16*1.01</f>
+        <v>2296.7400000000002</v>
       </c>
       <c r="BE16" s="4">
-        <f t="shared" si="84"/>
-        <v>2286.0897963343136</v>
+        <f t="shared" si="81"/>
+        <v>2319.7074000000002</v>
       </c>
       <c r="BF16" s="4">
-        <f t="shared" si="84"/>
-        <v>2308.9506942976568</v>
+        <f t="shared" si="81"/>
+        <v>2342.9044740000004</v>
       </c>
       <c r="BG16" s="4">
-        <f t="shared" si="84"/>
-        <v>2332.0402012406335</v>
+        <f t="shared" si="81"/>
+        <v>2366.3335187400003</v>
       </c>
       <c r="BH16" s="4">
-        <f t="shared" si="84"/>
-        <v>2355.3606032530397</v>
+        <f t="shared" si="81"/>
+        <v>2389.9968539274005</v>
       </c>
       <c r="BI16" s="4">
-        <f t="shared" si="84"/>
-        <v>2378.91420928557</v>
+        <f t="shared" si="81"/>
+        <v>2413.8968224666746</v>
+      </c>
+      <c r="BJ16" s="4">
+        <f t="shared" si="81"/>
+        <v>2438.0357906913414</v>
+      </c>
+      <c r="BK16" s="4">
+        <f t="shared" si="81"/>
+        <v>2462.4161485982549</v>
+      </c>
+      <c r="BL16" s="4">
+        <f t="shared" si="81"/>
+        <v>2487.0403100842377</v>
+      </c>
+      <c r="BM16" s="4">
+        <f t="shared" si="81"/>
+        <v>2511.9107131850801</v>
       </c>
     </row>
-    <row r="17" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>45</v>
       </c>
@@ -4696,65 +4768,56 @@
         <v>-10186</v>
       </c>
       <c r="AL17" s="4">
-        <f t="shared" ref="AK17:AL17" si="85">AH17*1.01</f>
-        <v>-472.68</v>
-      </c>
-      <c r="AN17" s="4">
+        <v>-1177</v>
+      </c>
+      <c r="AM17" s="4"/>
+      <c r="AN17" s="4"/>
+      <c r="AO17" s="4"/>
+      <c r="AP17" s="4"/>
+      <c r="AR17" s="4">
         <v>118</v>
       </c>
-      <c r="AO17" s="4">
+      <c r="AS17" s="4">
         <v>256</v>
       </c>
-      <c r="AP17" s="4">
+      <c r="AT17" s="4">
         <v>-90</v>
       </c>
-      <c r="AQ17" s="4">
+      <c r="AU17" s="4">
         <f>SUM(C17:F17)</f>
         <v>-346</v>
       </c>
-      <c r="AR17" s="4">
+      <c r="AV17" s="4">
         <f>SUM(G17:J17)</f>
         <v>182</v>
       </c>
-      <c r="AS17" s="4">
+      <c r="AW17" s="4">
         <f>SUM(K17:N17)</f>
         <v>-202</v>
       </c>
-      <c r="AT17" s="4">
+      <c r="AX17" s="4">
         <f>SUM(O17:R17)</f>
         <v>-2371</v>
       </c>
-      <c r="AU17" s="4">
+      <c r="AY17" s="4">
         <f>SUM(S17:V17)</f>
         <v>-14633</v>
       </c>
-      <c r="AV17" s="4">
+      <c r="AZ17" s="4">
         <f>SUM(W17:Z17)</f>
         <v>16806</v>
       </c>
-      <c r="AW17" s="4">
+      <c r="BA17" s="4">
         <f>SUM(AA17:AD17)</f>
         <v>-938</v>
       </c>
-      <c r="AX17" s="4">
+      <c r="BB17" s="4">
         <f>SUM(AE17:AH17)</f>
         <v>2250</v>
       </c>
-      <c r="AY17" s="4">
+      <c r="BC17" s="4">
         <f>SUM(AI17:AL17)</f>
-        <v>-14524.68</v>
-      </c>
-      <c r="AZ17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BA17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BB17" s="4">
-        <v>0</v>
-      </c>
-      <c r="BC17" s="4">
-        <v>0</v>
+        <v>-15229</v>
       </c>
       <c r="BD17" s="4">
         <v>0</v>
@@ -4774,245 +4837,261 @@
       <c r="BI17" s="4">
         <v>0</v>
       </c>
+      <c r="BJ17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BK17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BL17" s="4">
+        <v>0</v>
+      </c>
+      <c r="BM17" s="4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="18" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:157" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="1" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:R18" si="86">C14-C15-C16-C17</f>
+        <f t="shared" ref="C18:R18" si="82">C14-C15-C16-C17</f>
         <v>953</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>666</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>316</v>
       </c>
       <c r="F18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>1872</v>
       </c>
       <c r="G18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>1916</v>
       </c>
       <c r="H18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>2605</v>
       </c>
       <c r="I18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>3390</v>
       </c>
       <c r="J18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>3350</v>
       </c>
       <c r="K18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>4401</v>
       </c>
       <c r="L18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>2889</v>
       </c>
       <c r="M18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>2632</v>
       </c>
       <c r="N18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>4053</v>
       </c>
       <c r="O18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>3383</v>
       </c>
       <c r="P18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>6221</v>
       </c>
       <c r="Q18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>6809</v>
       </c>
       <c r="R18" s="8">
-        <f t="shared" si="86"/>
+        <f t="shared" si="82"/>
         <v>7765</v>
       </c>
       <c r="S18" s="8">
-        <f t="shared" ref="S18:V18" si="87">S14-S15-S16-S17</f>
+        <f t="shared" ref="S18:V18" si="83">S14-S15-S16-S17</f>
         <v>10268</v>
       </c>
       <c r="T18" s="8">
-        <f t="shared" ref="T18:U18" si="88">T14-T15-T16-T17</f>
+        <f t="shared" ref="T18:U18" si="84">T14-T15-T16-T17</f>
         <v>8634</v>
       </c>
       <c r="U18" s="8">
+        <f t="shared" si="84"/>
+        <v>4315</v>
+      </c>
+      <c r="V18" s="8">
+        <f t="shared" si="83"/>
+        <v>14934</v>
+      </c>
+      <c r="W18" s="8">
+        <f t="shared" ref="W18:X18" si="85">W14-W15-W16-W17</f>
+        <v>-5265</v>
+      </c>
+      <c r="X18" s="8">
+        <f t="shared" si="85"/>
+        <v>-2653</v>
+      </c>
+      <c r="Y18" s="8">
+        <f t="shared" ref="Y18" si="86">Y14-Y15-Y16-Y17</f>
+        <v>2944</v>
+      </c>
+      <c r="Z18" s="8">
+        <f t="shared" ref="Z18" si="87">Z14-Z15-Z16-Z17</f>
+        <v>-962</v>
+      </c>
+      <c r="AA18" s="8">
+        <f t="shared" ref="AA18:AB18" si="88">AA14-AA15-AA16-AA17</f>
+        <v>4119</v>
+      </c>
+      <c r="AB18" s="8">
         <f t="shared" si="88"/>
-        <v>4315</v>
-      </c>
-      <c r="V18" s="8">
-        <f t="shared" si="87"/>
-        <v>14934</v>
-      </c>
-      <c r="W18" s="8">
-        <f t="shared" ref="W18:X18" si="89">W14-W15-W16-W17</f>
-        <v>-5265</v>
-      </c>
-      <c r="X18" s="8">
-        <f t="shared" si="89"/>
-        <v>-2653</v>
-      </c>
-      <c r="Y18" s="8">
-        <f t="shared" ref="Y18" si="90">Y14-Y15-Y16-Y17</f>
-        <v>2944</v>
-      </c>
-      <c r="Z18" s="8">
-        <f t="shared" ref="Z18" si="91">Z14-Z15-Z16-Z17</f>
-        <v>-962</v>
-      </c>
-      <c r="AA18" s="8">
-        <f t="shared" ref="AA18:AB18" si="92">AA14-AA15-AA16-AA17</f>
-        <v>4119</v>
-      </c>
-      <c r="AB18" s="8">
+        <v>7563</v>
+      </c>
+      <c r="AC18" s="8">
+        <f t="shared" ref="AC18" si="89">AC14-AC15-AC16-AC17</f>
+        <v>12189</v>
+      </c>
+      <c r="AD18" s="8">
+        <f t="shared" ref="AD18" si="90">AD14-AD15-AD16-AD17</f>
+        <v>13686</v>
+      </c>
+      <c r="AE18" s="8">
+        <f t="shared" ref="AE18:AF18" si="91">AE14-AE15-AE16-AE17</f>
+        <v>12983</v>
+      </c>
+      <c r="AF18" s="8">
+        <f t="shared" si="91"/>
+        <v>15245</v>
+      </c>
+      <c r="AG18" s="8">
+        <f t="shared" ref="AG18:AL18" si="92">AG14-AG15-AG16-AG17</f>
+        <v>18037</v>
+      </c>
+      <c r="AH18" s="8">
         <f t="shared" si="92"/>
-        <v>7563</v>
-      </c>
-      <c r="AC18" s="8">
-        <f t="shared" ref="AC18" si="93">AC14-AC15-AC16-AC17</f>
-        <v>12189</v>
-      </c>
-      <c r="AD18" s="8">
-        <f t="shared" ref="AD18" si="94">AD14-AD15-AD16-AD17</f>
-        <v>13686</v>
-      </c>
-      <c r="AE18" s="8">
-        <f t="shared" ref="AE18:AF18" si="95">AE14-AE15-AE16-AE17</f>
-        <v>12983</v>
-      </c>
-      <c r="AF18" s="8">
-        <f t="shared" si="95"/>
-        <v>15245</v>
-      </c>
-      <c r="AG18" s="8">
-        <f t="shared" ref="AG18:AL18" si="96">AG14-AG15-AG16-AG17</f>
-        <v>18037</v>
-      </c>
-      <c r="AH18" s="8">
+        <v>22349</v>
+      </c>
+      <c r="AI18" s="8">
+        <f t="shared" si="92"/>
+        <v>21679</v>
+      </c>
+      <c r="AJ18" s="8">
+        <f t="shared" si="92"/>
+        <v>20857</v>
+      </c>
+      <c r="AK18" s="8">
+        <f t="shared" si="92"/>
+        <v>28170</v>
+      </c>
+      <c r="AL18" s="8">
+        <f t="shared" si="92"/>
+        <v>26605</v>
+      </c>
+      <c r="AM18" s="8"/>
+      <c r="AN18" s="8"/>
+      <c r="AO18" s="8"/>
+      <c r="AP18" s="8"/>
+      <c r="AR18" s="8">
+        <f t="shared" ref="AR18:AY18" si="93">AR14-AR15-AR16-AR17</f>
+        <v>-111</v>
+      </c>
+      <c r="AS18" s="8">
+        <f t="shared" si="93"/>
+        <v>1568</v>
+      </c>
+      <c r="AT18" s="8">
+        <f t="shared" si="93"/>
+        <v>3892</v>
+      </c>
+      <c r="AU18" s="8">
+        <f t="shared" si="93"/>
+        <v>3807</v>
+      </c>
+      <c r="AV18" s="8">
+        <f t="shared" si="93"/>
+        <v>11261</v>
+      </c>
+      <c r="AW18" s="8">
+        <f t="shared" si="93"/>
+        <v>13975</v>
+      </c>
+      <c r="AX18" s="8">
+        <f t="shared" si="93"/>
+        <v>24178</v>
+      </c>
+      <c r="AY18" s="8">
+        <f t="shared" si="93"/>
+        <v>38151</v>
+      </c>
+      <c r="AZ18" s="8">
+        <f t="shared" ref="AZ18:BI18" si="94">AZ14-AZ15-AZ16-AZ17</f>
+        <v>-5936</v>
+      </c>
+      <c r="BA18" s="8">
+        <f t="shared" si="94"/>
+        <v>37557</v>
+      </c>
+      <c r="BB18" s="8">
+        <f t="shared" ref="BB18" si="95">BB14-BB15-BB16-BB17</f>
+        <v>68614</v>
+      </c>
+      <c r="BC18" s="8">
+        <f t="shared" si="94"/>
+        <v>97311</v>
+      </c>
+      <c r="BD18" s="8">
+        <f t="shared" si="94"/>
+        <v>95353.416000000085</v>
+      </c>
+      <c r="BE18" s="8">
+        <f t="shared" si="94"/>
+        <v>110818.92717599994</v>
+      </c>
+      <c r="BF18" s="8">
+        <f t="shared" si="94"/>
+        <v>126302.23546312001</v>
+      </c>
+      <c r="BG18" s="8">
+        <f t="shared" si="94"/>
+        <v>130972.69578698082</v>
+      </c>
+      <c r="BH18" s="8">
+        <f t="shared" si="94"/>
+        <v>135592.37176192371</v>
+      </c>
+      <c r="BI18" s="8">
+        <f t="shared" si="94"/>
+        <v>138565.41817867191</v>
+      </c>
+      <c r="BJ18" s="8">
+        <f t="shared" ref="BJ18:BM18" si="96">BJ14-BJ15-BJ16-BJ17</f>
+        <v>141910.42198798369</v>
+      </c>
+      <c r="BK18" s="8">
         <f t="shared" si="96"/>
-        <v>22349</v>
-      </c>
-      <c r="AI18" s="8">
+        <v>143461.99878869578</v>
+      </c>
+      <c r="BL18" s="8">
         <f t="shared" si="96"/>
-        <v>21679</v>
-      </c>
-      <c r="AJ18" s="8">
+        <v>145037.99714040107</v>
+      </c>
+      <c r="BM18" s="8">
         <f t="shared" si="96"/>
-        <v>20857</v>
-      </c>
-      <c r="AK18" s="8">
-        <f t="shared" si="96"/>
-        <v>28170</v>
-      </c>
-      <c r="AL18" s="8">
-        <f t="shared" si="96"/>
-        <v>24624.0265</v>
-      </c>
-      <c r="AN18" s="8">
-        <f t="shared" ref="AN18:AU18" si="97">AN14-AN15-AN16-AN17</f>
-        <v>-111</v>
-      </c>
-      <c r="AO18" s="8">
-        <f t="shared" si="97"/>
-        <v>1568</v>
-      </c>
-      <c r="AP18" s="8">
-        <f t="shared" si="97"/>
-        <v>3892</v>
-      </c>
-      <c r="AQ18" s="8">
-        <f t="shared" si="97"/>
-        <v>3807</v>
-      </c>
-      <c r="AR18" s="8">
-        <f t="shared" si="97"/>
-        <v>11261</v>
-      </c>
-      <c r="AS18" s="8">
-        <f t="shared" si="97"/>
-        <v>13975</v>
-      </c>
-      <c r="AT18" s="8">
-        <f t="shared" si="97"/>
-        <v>24178</v>
-      </c>
-      <c r="AU18" s="8">
-        <f t="shared" si="97"/>
-        <v>38151</v>
-      </c>
-      <c r="AV18" s="8">
-        <f t="shared" ref="AV18:BE18" si="98">AV14-AV15-AV16-AV17</f>
-        <v>-5936</v>
-      </c>
-      <c r="AW18" s="8">
-        <f t="shared" si="98"/>
-        <v>37557</v>
-      </c>
-      <c r="AX18" s="8">
-        <f t="shared" ref="AX18" si="99">AX14-AX15-AX16-AX17</f>
-        <v>68614</v>
-      </c>
-      <c r="AY18" s="8">
-        <f t="shared" si="98"/>
-        <v>95330.02649999992</v>
-      </c>
-      <c r="AZ18" s="8">
-        <f t="shared" si="98"/>
-        <v>93356.006560000038</v>
-      </c>
-      <c r="BA18" s="8">
-        <f t="shared" si="98"/>
-        <v>108592.15050415997</v>
-      </c>
-      <c r="BB18" s="8">
-        <f t="shared" si="98"/>
-        <v>123889.07829947522</v>
-      </c>
-      <c r="BC18" s="8">
-        <f t="shared" si="98"/>
-        <v>128479.96392477826</v>
-      </c>
-      <c r="BD18" s="8">
-        <f t="shared" si="98"/>
-        <v>133053.51549614366</v>
-      </c>
-      <c r="BE18" s="8">
-        <f t="shared" si="98"/>
-        <v>135997.27361631437</v>
-      </c>
-      <c r="BF18" s="8">
-        <f t="shared" ref="BF18:BI18" si="100">BF14-BF15-BF16-BF17</f>
-        <v>139334.13225123953</v>
-      </c>
-      <c r="BG18" s="8">
-        <f t="shared" si="100"/>
-        <v>140896.64637264429</v>
-      </c>
-      <c r="BH18" s="8">
-        <f t="shared" si="100"/>
-        <v>142484.99549752436</v>
-      </c>
-      <c r="BI18" s="8">
-        <f t="shared" si="100"/>
-        <v>144100.0010056968</v>
+        <v>146639.1750123775</v>
       </c>
     </row>
-    <row r="19" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>47</v>
       </c>
@@ -5122,96 +5201,99 @@
         <v>6910</v>
       </c>
       <c r="AL19" s="4">
-        <f t="shared" ref="AK19:AL19" si="101">AL18*0.14</f>
-        <v>3447.3637100000005</v>
-      </c>
-      <c r="AN19" s="4">
+        <v>4946</v>
+      </c>
+      <c r="AM19" s="4"/>
+      <c r="AN19" s="4"/>
+      <c r="AO19" s="4"/>
+      <c r="AP19" s="4"/>
+      <c r="AR19" s="4">
         <v>167</v>
       </c>
-      <c r="AO19" s="4">
+      <c r="AS19" s="4">
         <v>950</v>
       </c>
-      <c r="AP19" s="4">
+      <c r="AT19" s="4">
         <v>1425</v>
       </c>
-      <c r="AQ19" s="4">
+      <c r="AU19" s="4">
         <f>SUM(C19:F19)</f>
         <v>770</v>
       </c>
-      <c r="AR19" s="4">
+      <c r="AV19" s="4">
         <f>SUM(G19:J19)</f>
         <v>1196</v>
       </c>
-      <c r="AS19" s="4">
+      <c r="AW19" s="4">
         <f>SUM(K19:N19)</f>
         <v>2373</v>
       </c>
-      <c r="AT19" s="4">
+      <c r="AX19" s="4">
         <f>SUM(O19:R19)</f>
         <v>2863</v>
       </c>
-      <c r="AU19" s="4">
+      <c r="AY19" s="4">
         <f>SUM(S19:V19)</f>
         <v>4791</v>
       </c>
-      <c r="AV19" s="4">
+      <c r="AZ19" s="4">
         <f>SUM(W19:Z19)</f>
         <v>-3217</v>
       </c>
-      <c r="AW19" s="4">
+      <c r="BA19" s="4">
         <f>SUM(AA19:AD19)</f>
         <v>7120</v>
       </c>
-      <c r="AX19" s="4">
+      <c r="BB19" s="4">
         <f>SUM(AE19:AH19)</f>
         <v>9265</v>
       </c>
-      <c r="AY19" s="4">
+      <c r="BC19" s="4">
         <f>SUM(AI19:AL19)</f>
-        <v>17588.363710000001</v>
-      </c>
-      <c r="AZ19" s="4">
-        <f>AZ18*0.15</f>
-        <v>14003.400984000005</v>
-      </c>
-      <c r="BA19" s="4">
-        <f t="shared" ref="BA19:BI19" si="102">BA18*0.15</f>
-        <v>16288.822575623995</v>
-      </c>
-      <c r="BB19" s="4">
-        <f t="shared" si="102"/>
-        <v>18583.361744921283</v>
-      </c>
-      <c r="BC19" s="4">
-        <f t="shared" si="102"/>
-        <v>19271.994588716738</v>
+        <v>19087</v>
       </c>
       <c r="BD19" s="4">
-        <f t="shared" si="102"/>
-        <v>19958.02732442155</v>
+        <f>BD18*0.15</f>
+        <v>14303.012400000012</v>
       </c>
       <c r="BE19" s="4">
-        <f t="shared" si="102"/>
-        <v>20399.591042447155</v>
+        <f t="shared" ref="BE19:BM19" si="97">BE18*0.15</f>
+        <v>16622.839076399989</v>
       </c>
       <c r="BF19" s="4">
-        <f t="shared" si="102"/>
-        <v>20900.119837685928</v>
+        <f t="shared" si="97"/>
+        <v>18945.335319468002</v>
       </c>
       <c r="BG19" s="4">
-        <f t="shared" si="102"/>
-        <v>21134.496955896644</v>
+        <f t="shared" si="97"/>
+        <v>19645.904368047122</v>
       </c>
       <c r="BH19" s="4">
-        <f t="shared" si="102"/>
-        <v>21372.749324628654</v>
+        <f t="shared" si="97"/>
+        <v>20338.855764288557</v>
       </c>
       <c r="BI19" s="4">
-        <f t="shared" si="102"/>
-        <v>21615.000150854521</v>
+        <f t="shared" si="97"/>
+        <v>20784.812726800785</v>
+      </c>
+      <c r="BJ19" s="4">
+        <f t="shared" si="97"/>
+        <v>21286.563298197554</v>
+      </c>
+      <c r="BK19" s="4">
+        <f t="shared" si="97"/>
+        <v>21519.299818304367</v>
+      </c>
+      <c r="BL19" s="4">
+        <f t="shared" si="97"/>
+        <v>21755.699571060159</v>
+      </c>
+      <c r="BM19" s="4">
+        <f t="shared" si="97"/>
+        <v>21995.876251856625</v>
       </c>
     </row>
-    <row r="20" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B20" t="s">
         <v>48</v>
       </c>
@@ -5321,701 +5403,708 @@
         <v>73</v>
       </c>
       <c r="AL20" s="4">
-        <f t="shared" ref="AK20:AL20" si="103">AL18*0.001</f>
-        <v>24.624026499999999</v>
-      </c>
-      <c r="AN20" s="4">
+        <v>467</v>
+      </c>
+      <c r="AM20" s="4"/>
+      <c r="AN20" s="4"/>
+      <c r="AO20" s="4"/>
+      <c r="AP20" s="4"/>
+      <c r="AR20" s="4">
         <v>-37</v>
       </c>
-      <c r="AO20" s="4">
+      <c r="AS20" s="4">
         <v>22</v>
       </c>
-      <c r="AP20" s="4">
+      <c r="AT20" s="4">
         <v>96</v>
       </c>
-      <c r="AQ20" s="4">
+      <c r="AU20" s="4">
         <f>SUM(C20:F20)</f>
         <v>4</v>
       </c>
-      <c r="AR20" s="4">
+      <c r="AV20" s="4">
         <f>SUM(G20:J20)</f>
         <v>-8</v>
       </c>
-      <c r="AS20" s="4">
+      <c r="AW20" s="4">
         <f>SUM(K20:N20)</f>
         <v>14</v>
       </c>
-      <c r="AT20" s="4">
+      <c r="AX20" s="4">
         <f>SUM(O20:R20)</f>
         <v>-16</v>
       </c>
-      <c r="AU20" s="4">
+      <c r="AY20" s="4">
         <f>SUM(S20:V20)</f>
         <v>-4</v>
       </c>
-      <c r="AV20" s="4">
+      <c r="AZ20" s="4">
         <f>SUM(W20:Z20)</f>
         <v>3</v>
       </c>
-      <c r="AW20" s="4">
+      <c r="BA20" s="4">
         <f>SUM(AA20:AD20)</f>
         <v>12</v>
       </c>
-      <c r="AX20" s="4">
+      <c r="BB20" s="4">
         <f>SUM(AE20:AH20)</f>
         <v>101</v>
       </c>
-      <c r="AY20" s="4">
+      <c r="BC20" s="4">
         <f>SUM(AI20:AL20)</f>
-        <v>111.6240265</v>
-      </c>
-      <c r="AZ20" s="4">
-        <f t="shared" ref="AZ20:BI20" si="104">AZ18*0.001</f>
-        <v>93.35600656000004</v>
-      </c>
-      <c r="BA20" s="4">
-        <f t="shared" si="104"/>
-        <v>108.59215050415997</v>
-      </c>
-      <c r="BB20" s="4">
-        <f t="shared" si="104"/>
-        <v>123.88907829947523</v>
-      </c>
-      <c r="BC20" s="4">
-        <f t="shared" si="104"/>
-        <v>128.47996392477827</v>
+        <v>554</v>
       </c>
       <c r="BD20" s="4">
-        <f t="shared" si="104"/>
-        <v>133.05351549614366</v>
+        <f t="shared" ref="BD20:BM20" si="98">BD18*0.001</f>
+        <v>95.353416000000081</v>
       </c>
       <c r="BE20" s="4">
-        <f t="shared" si="104"/>
-        <v>135.99727361631437</v>
+        <f t="shared" si="98"/>
+        <v>110.81892717599995</v>
       </c>
       <c r="BF20" s="4">
-        <f t="shared" si="104"/>
-        <v>139.33413225123954</v>
+        <f t="shared" si="98"/>
+        <v>126.30223546312001</v>
       </c>
       <c r="BG20" s="4">
-        <f t="shared" si="104"/>
-        <v>140.89664637264428</v>
+        <f t="shared" si="98"/>
+        <v>130.97269578698084</v>
       </c>
       <c r="BH20" s="4">
-        <f t="shared" si="104"/>
-        <v>142.48499549752435</v>
+        <f t="shared" si="98"/>
+        <v>135.59237176192372</v>
       </c>
       <c r="BI20" s="4">
-        <f t="shared" si="104"/>
-        <v>144.10000100569681</v>
+        <f t="shared" si="98"/>
+        <v>138.56541817867191</v>
+      </c>
+      <c r="BJ20" s="4">
+        <f t="shared" si="98"/>
+        <v>141.91042198798368</v>
+      </c>
+      <c r="BK20" s="4">
+        <f t="shared" si="98"/>
+        <v>143.46199878869578</v>
+      </c>
+      <c r="BL20" s="4">
+        <f t="shared" si="98"/>
+        <v>145.03799714040107</v>
+      </c>
+      <c r="BM20" s="4">
+        <f t="shared" si="98"/>
+        <v>146.63917501237751</v>
       </c>
     </row>
-    <row r="21" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:157" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B21" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C21" s="8">
-        <f t="shared" ref="C21:R21" si="105">C18-C19-C20</f>
+        <f t="shared" ref="C21:R21" si="99">C18-C19-C20</f>
         <v>724</v>
       </c>
       <c r="D21" s="8">
+        <f t="shared" si="99"/>
+        <v>197</v>
+      </c>
+      <c r="E21" s="8">
+        <f t="shared" si="99"/>
+        <v>256</v>
+      </c>
+      <c r="F21" s="8">
+        <f t="shared" si="99"/>
+        <v>1856</v>
+      </c>
+      <c r="G21" s="8">
+        <f t="shared" si="99"/>
+        <v>1629</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="99"/>
+        <v>2534</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="99"/>
+        <v>2883</v>
+      </c>
+      <c r="J21" s="8">
+        <f t="shared" si="99"/>
+        <v>3027</v>
+      </c>
+      <c r="K21" s="8">
+        <f t="shared" si="99"/>
+        <v>3561</v>
+      </c>
+      <c r="L21" s="8">
+        <f t="shared" si="99"/>
+        <v>2625</v>
+      </c>
+      <c r="M21" s="8">
+        <f t="shared" si="99"/>
+        <v>2134</v>
+      </c>
+      <c r="N21" s="8">
+        <f t="shared" si="99"/>
+        <v>3268</v>
+      </c>
+      <c r="O21" s="8">
+        <f t="shared" si="99"/>
+        <v>2535</v>
+      </c>
+      <c r="P21" s="8">
+        <f t="shared" si="99"/>
+        <v>5243</v>
+      </c>
+      <c r="Q21" s="8">
+        <f t="shared" si="99"/>
+        <v>6331</v>
+      </c>
+      <c r="R21" s="8">
+        <f t="shared" si="99"/>
+        <v>7222</v>
+      </c>
+      <c r="S21" s="8">
+        <f t="shared" ref="S21:V21" si="100">S18-S19-S20</f>
+        <v>8107</v>
+      </c>
+      <c r="T21" s="8">
+        <f t="shared" ref="T21:U21" si="101">T18-T19-T20</f>
+        <v>7778</v>
+      </c>
+      <c r="U21" s="8">
+        <f t="shared" si="101"/>
+        <v>3156</v>
+      </c>
+      <c r="V21" s="8">
+        <f t="shared" si="100"/>
+        <v>14323</v>
+      </c>
+      <c r="W21" s="8">
+        <f t="shared" ref="W21:X21" si="102">W18-W19-W20</f>
+        <v>-3844</v>
+      </c>
+      <c r="X21" s="8">
+        <f t="shared" si="102"/>
+        <v>-2028</v>
+      </c>
+      <c r="Y21" s="8">
+        <f t="shared" ref="Y21" si="103">Y18-Y19-Y20</f>
+        <v>2872</v>
+      </c>
+      <c r="Z21" s="8">
+        <f t="shared" ref="Z21" si="104">Z18-Z19-Z20</f>
+        <v>278</v>
+      </c>
+      <c r="AA21" s="8">
+        <f t="shared" ref="AA21:AB21" si="105">AA18-AA19-AA20</f>
+        <v>3172</v>
+      </c>
+      <c r="AB21" s="8">
         <f t="shared" si="105"/>
-        <v>197</v>
-      </c>
-      <c r="E21" s="8">
-        <f t="shared" si="105"/>
-        <v>256</v>
-      </c>
-      <c r="F21" s="8">
-        <f t="shared" si="105"/>
-        <v>1856</v>
-      </c>
-      <c r="G21" s="8">
-        <f t="shared" si="105"/>
-        <v>1629</v>
-      </c>
-      <c r="H21" s="8">
-        <f t="shared" si="105"/>
-        <v>2534</v>
-      </c>
-      <c r="I21" s="8">
-        <f t="shared" si="105"/>
-        <v>2883</v>
-      </c>
-      <c r="J21" s="8">
-        <f t="shared" si="105"/>
-        <v>3027</v>
-      </c>
-      <c r="K21" s="8">
-        <f t="shared" si="105"/>
-        <v>3561</v>
-      </c>
-      <c r="L21" s="8">
-        <f t="shared" si="105"/>
-        <v>2625</v>
-      </c>
-      <c r="M21" s="8">
-        <f t="shared" si="105"/>
-        <v>2134</v>
-      </c>
-      <c r="N21" s="8">
-        <f t="shared" si="105"/>
-        <v>3268</v>
-      </c>
-      <c r="O21" s="8">
-        <f t="shared" si="105"/>
-        <v>2535</v>
-      </c>
-      <c r="P21" s="8">
-        <f t="shared" si="105"/>
-        <v>5243</v>
-      </c>
-      <c r="Q21" s="8">
-        <f t="shared" si="105"/>
-        <v>6331</v>
-      </c>
-      <c r="R21" s="8">
-        <f t="shared" si="105"/>
-        <v>7222</v>
-      </c>
-      <c r="S21" s="8">
-        <f t="shared" ref="S21:V21" si="106">S18-S19-S20</f>
-        <v>8107</v>
-      </c>
-      <c r="T21" s="8">
-        <f t="shared" ref="T21:U21" si="107">T18-T19-T20</f>
-        <v>7778</v>
-      </c>
-      <c r="U21" s="8">
-        <f t="shared" si="107"/>
-        <v>3156</v>
-      </c>
-      <c r="V21" s="8">
-        <f t="shared" si="106"/>
-        <v>14323</v>
-      </c>
-      <c r="W21" s="8">
-        <f t="shared" ref="W21:X21" si="108">W18-W19-W20</f>
-        <v>-3844</v>
-      </c>
-      <c r="X21" s="8">
+        <v>6750</v>
+      </c>
+      <c r="AC21" s="8">
+        <f t="shared" ref="AC21" si="106">AC18-AC19-AC20</f>
+        <v>9879</v>
+      </c>
+      <c r="AD21" s="8">
+        <f t="shared" ref="AD21" si="107">AD18-AD19-AD20</f>
+        <v>10624</v>
+      </c>
+      <c r="AE21" s="8">
+        <f t="shared" ref="AE21:AF21" si="108">AE18-AE19-AE20</f>
+        <v>10431</v>
+      </c>
+      <c r="AF21" s="8">
         <f t="shared" si="108"/>
-        <v>-2028</v>
-      </c>
-      <c r="Y21" s="8">
-        <f t="shared" ref="Y21" si="109">Y18-Y19-Y20</f>
-        <v>2872</v>
-      </c>
-      <c r="Z21" s="8">
-        <f t="shared" ref="Z21" si="110">Z18-Z19-Z20</f>
-        <v>278</v>
-      </c>
-      <c r="AA21" s="8">
-        <f t="shared" ref="AA21:AB21" si="111">AA18-AA19-AA20</f>
-        <v>3172</v>
-      </c>
-      <c r="AB21" s="8">
+        <v>13485</v>
+      </c>
+      <c r="AG21" s="8">
+        <f t="shared" ref="AG21:AH21" si="109">AG18-AG19-AG20</f>
+        <v>15328</v>
+      </c>
+      <c r="AH21" s="8">
+        <f t="shared" si="109"/>
+        <v>20004</v>
+      </c>
+      <c r="AI21" s="8">
+        <f t="shared" ref="AI21:AL21" si="110">AI18-AI19-AI20</f>
+        <v>17127</v>
+      </c>
+      <c r="AJ21" s="8">
+        <f t="shared" si="110"/>
+        <v>18164</v>
+      </c>
+      <c r="AK21" s="8">
+        <f t="shared" si="110"/>
+        <v>21187</v>
+      </c>
+      <c r="AL21" s="8">
+        <f t="shared" si="110"/>
+        <v>21192</v>
+      </c>
+      <c r="AM21" s="8"/>
+      <c r="AN21" s="8"/>
+      <c r="AO21" s="8"/>
+      <c r="AP21" s="8"/>
+      <c r="AR21" s="8">
+        <f t="shared" ref="AR21:AZ21" si="111">AR18-AR19-AR20</f>
+        <v>-241</v>
+      </c>
+      <c r="AS21" s="8">
         <f t="shared" si="111"/>
-        <v>6750</v>
-      </c>
-      <c r="AC21" s="8">
-        <f t="shared" ref="AC21" si="112">AC18-AC19-AC20</f>
-        <v>9879</v>
-      </c>
-      <c r="AD21" s="8">
-        <f t="shared" ref="AD21" si="113">AD18-AD19-AD20</f>
-        <v>10624</v>
-      </c>
-      <c r="AE21" s="8">
-        <f t="shared" ref="AE21:AF21" si="114">AE18-AE19-AE20</f>
-        <v>10431</v>
-      </c>
-      <c r="AF21" s="8">
+        <v>596</v>
+      </c>
+      <c r="AT21" s="8">
+        <f t="shared" si="111"/>
+        <v>2371</v>
+      </c>
+      <c r="AU21" s="8">
+        <f t="shared" si="111"/>
+        <v>3033</v>
+      </c>
+      <c r="AV21" s="8">
+        <f t="shared" si="111"/>
+        <v>10073</v>
+      </c>
+      <c r="AW21" s="8">
+        <f t="shared" si="111"/>
+        <v>11588</v>
+      </c>
+      <c r="AX21" s="8">
+        <f t="shared" si="111"/>
+        <v>21331</v>
+      </c>
+      <c r="AY21" s="8">
+        <f t="shared" si="111"/>
+        <v>33364</v>
+      </c>
+      <c r="AZ21" s="8">
+        <f t="shared" si="111"/>
+        <v>-2722</v>
+      </c>
+      <c r="BA21" s="8">
+        <f t="shared" ref="BA21:BI21" si="112">BA18-BA19-BA20</f>
+        <v>30425</v>
+      </c>
+      <c r="BB21" s="8">
+        <f t="shared" ref="BB21" si="113">BB18-BB19-BB20</f>
+        <v>59248</v>
+      </c>
+      <c r="BC21" s="8">
+        <f t="shared" si="112"/>
+        <v>77670</v>
+      </c>
+      <c r="BD21" s="8">
+        <f t="shared" si="112"/>
+        <v>80955.05018400008</v>
+      </c>
+      <c r="BE21" s="8">
+        <f t="shared" si="112"/>
+        <v>94085.269172423941</v>
+      </c>
+      <c r="BF21" s="8">
+        <f t="shared" si="112"/>
+        <v>107230.59790818889</v>
+      </c>
+      <c r="BG21" s="8">
+        <f t="shared" si="112"/>
+        <v>111195.81872314672</v>
+      </c>
+      <c r="BH21" s="8">
+        <f t="shared" si="112"/>
+        <v>115117.92362587323</v>
+      </c>
+      <c r="BI21" s="8">
+        <f t="shared" si="112"/>
+        <v>117642.04003369246</v>
+      </c>
+      <c r="BJ21" s="8">
+        <f t="shared" ref="BJ21:BM21" si="114">BJ18-BJ19-BJ20</f>
+        <v>120481.94826779816</v>
+      </c>
+      <c r="BK21" s="8">
         <f t="shared" si="114"/>
-        <v>13485</v>
-      </c>
-      <c r="AG21" s="8">
-        <f t="shared" ref="AG21:AH21" si="115">AG18-AG19-AG20</f>
-        <v>15328</v>
-      </c>
-      <c r="AH21" s="8">
+        <v>121799.23697160272</v>
+      </c>
+      <c r="BL21" s="8">
+        <f t="shared" si="114"/>
+        <v>123137.25957220051</v>
+      </c>
+      <c r="BM21" s="8">
+        <f t="shared" si="114"/>
+        <v>124496.6595855085</v>
+      </c>
+      <c r="BN21" s="1">
+        <f>BM21*(1+$BP$29)</f>
+        <v>123251.69298965341</v>
+      </c>
+      <c r="BO21" s="1">
+        <f t="shared" ref="BO21:DZ21" si="115">BN21*(1+$BP$29)</f>
+        <v>122019.17605975688</v>
+      </c>
+      <c r="BP21" s="1">
         <f t="shared" si="115"/>
-        <v>20004</v>
-      </c>
-      <c r="AI21" s="8">
-        <f t="shared" ref="AI21:AL21" si="116">AI18-AI19-AI20</f>
-        <v>17127</v>
-      </c>
-      <c r="AJ21" s="8">
+        <v>120798.9842991593</v>
+      </c>
+      <c r="BQ21" s="1">
+        <f t="shared" si="115"/>
+        <v>119590.99445616771</v>
+      </c>
+      <c r="BR21" s="1">
+        <f t="shared" si="115"/>
+        <v>118395.08451160604</v>
+      </c>
+      <c r="BS21" s="1">
+        <f t="shared" si="115"/>
+        <v>117211.13366648997</v>
+      </c>
+      <c r="BT21" s="1">
+        <f t="shared" si="115"/>
+        <v>116039.02232982506</v>
+      </c>
+      <c r="BU21" s="1">
+        <f t="shared" si="115"/>
+        <v>114878.63210652681</v>
+      </c>
+      <c r="BV21" s="1">
+        <f t="shared" si="115"/>
+        <v>113729.84578546154</v>
+      </c>
+      <c r="BW21" s="1">
+        <f t="shared" si="115"/>
+        <v>112592.54732760692</v>
+      </c>
+      <c r="BX21" s="1">
+        <f t="shared" si="115"/>
+        <v>111466.62185433085</v>
+      </c>
+      <c r="BY21" s="1">
+        <f t="shared" si="115"/>
+        <v>110351.95563578754</v>
+      </c>
+      <c r="BZ21" s="1">
+        <f t="shared" si="115"/>
+        <v>109248.43607942967</v>
+      </c>
+      <c r="CA21" s="1">
+        <f t="shared" si="115"/>
+        <v>108155.95171863536</v>
+      </c>
+      <c r="CB21" s="1">
+        <f t="shared" si="115"/>
+        <v>107074.39220144901</v>
+      </c>
+      <c r="CC21" s="1">
+        <f t="shared" si="115"/>
+        <v>106003.64827943452</v>
+      </c>
+      <c r="CD21" s="1">
+        <f t="shared" si="115"/>
+        <v>104943.61179664018</v>
+      </c>
+      <c r="CE21" s="1">
+        <f t="shared" si="115"/>
+        <v>103894.17567867378</v>
+      </c>
+      <c r="CF21" s="1">
+        <f t="shared" si="115"/>
+        <v>102855.23392188705</v>
+      </c>
+      <c r="CG21" s="1">
+        <f t="shared" si="115"/>
+        <v>101826.68158266817</v>
+      </c>
+      <c r="CH21" s="1">
+        <f t="shared" si="115"/>
+        <v>100808.41476684148</v>
+      </c>
+      <c r="CI21" s="1">
+        <f t="shared" si="115"/>
+        <v>99800.330619173066</v>
+      </c>
+      <c r="CJ21" s="1">
+        <f t="shared" si="115"/>
+        <v>98802.327312981331</v>
+      </c>
+      <c r="CK21" s="1">
+        <f t="shared" si="115"/>
+        <v>97814.304039851515</v>
+      </c>
+      <c r="CL21" s="1">
+        <f t="shared" si="115"/>
+        <v>96836.160999453001</v>
+      </c>
+      <c r="CM21" s="1">
+        <f t="shared" si="115"/>
+        <v>95867.799389458465</v>
+      </c>
+      <c r="CN21" s="1">
+        <f t="shared" si="115"/>
+        <v>94909.121395563881</v>
+      </c>
+      <c r="CO21" s="1">
+        <f t="shared" si="115"/>
+        <v>93960.030181608236</v>
+      </c>
+      <c r="CP21" s="1">
+        <f t="shared" si="115"/>
+        <v>93020.429879792151</v>
+      </c>
+      <c r="CQ21" s="1">
+        <f t="shared" si="115"/>
+        <v>92090.225580994229</v>
+      </c>
+      <c r="CR21" s="1">
+        <f t="shared" si="115"/>
+        <v>91169.32332518429</v>
+      </c>
+      <c r="CS21" s="1">
+        <f t="shared" si="115"/>
+        <v>90257.630091932442</v>
+      </c>
+      <c r="CT21" s="1">
+        <f t="shared" si="115"/>
+        <v>89355.05379101311</v>
+      </c>
+      <c r="CU21" s="1">
+        <f t="shared" si="115"/>
+        <v>88461.503253102972</v>
+      </c>
+      <c r="CV21" s="1">
+        <f t="shared" si="115"/>
+        <v>87576.888220571942</v>
+      </c>
+      <c r="CW21" s="1">
+        <f t="shared" si="115"/>
+        <v>86701.119338366218</v>
+      </c>
+      <c r="CX21" s="1">
+        <f t="shared" si="115"/>
+        <v>85834.108144982558</v>
+      </c>
+      <c r="CY21" s="1">
+        <f t="shared" si="115"/>
+        <v>84975.767063532738</v>
+      </c>
+      <c r="CZ21" s="1">
+        <f t="shared" si="115"/>
+        <v>84126.009392897409</v>
+      </c>
+      <c r="DA21" s="1">
+        <f t="shared" si="115"/>
+        <v>83284.74929896844</v>
+      </c>
+      <c r="DB21" s="1">
+        <f t="shared" si="115"/>
+        <v>82451.901805978749</v>
+      </c>
+      <c r="DC21" s="1">
+        <f t="shared" si="115"/>
+        <v>81627.382787918963</v>
+      </c>
+      <c r="DD21" s="1">
+        <f t="shared" si="115"/>
+        <v>80811.108960039768</v>
+      </c>
+      <c r="DE21" s="1">
+        <f t="shared" si="115"/>
+        <v>80002.997870439372</v>
+      </c>
+      <c r="DF21" s="1">
+        <f t="shared" si="115"/>
+        <v>79202.967891734981</v>
+      </c>
+      <c r="DG21" s="1">
+        <f t="shared" si="115"/>
+        <v>78410.938212817637</v>
+      </c>
+      <c r="DH21" s="1">
+        <f t="shared" si="115"/>
+        <v>77626.828830689454</v>
+      </c>
+      <c r="DI21" s="1">
+        <f t="shared" si="115"/>
+        <v>76850.560542382562</v>
+      </c>
+      <c r="DJ21" s="1">
+        <f t="shared" si="115"/>
+        <v>76082.054936958739</v>
+      </c>
+      <c r="DK21" s="1">
+        <f t="shared" si="115"/>
+        <v>75321.234387589153</v>
+      </c>
+      <c r="DL21" s="1">
+        <f t="shared" si="115"/>
+        <v>74568.022043713267</v>
+      </c>
+      <c r="DM21" s="1">
+        <f t="shared" si="115"/>
+        <v>73822.341823276132</v>
+      </c>
+      <c r="DN21" s="1">
+        <f t="shared" si="115"/>
+        <v>73084.118405043366</v>
+      </c>
+      <c r="DO21" s="1">
+        <f t="shared" si="115"/>
+        <v>72353.277220992924</v>
+      </c>
+      <c r="DP21" s="1">
+        <f t="shared" si="115"/>
+        <v>71629.744448782993</v>
+      </c>
+      <c r="DQ21" s="1">
+        <f t="shared" si="115"/>
+        <v>70913.447004295158</v>
+      </c>
+      <c r="DR21" s="1">
+        <f t="shared" si="115"/>
+        <v>70204.312534252211</v>
+      </c>
+      <c r="DS21" s="1">
+        <f t="shared" si="115"/>
+        <v>69502.269408909691</v>
+      </c>
+      <c r="DT21" s="1">
+        <f t="shared" si="115"/>
+        <v>68807.246714820591</v>
+      </c>
+      <c r="DU21" s="1">
+        <f t="shared" si="115"/>
+        <v>68119.174247672388</v>
+      </c>
+      <c r="DV21" s="1">
+        <f t="shared" si="115"/>
+        <v>67437.982505195658</v>
+      </c>
+      <c r="DW21" s="1">
+        <f t="shared" si="115"/>
+        <v>66763.602680143696</v>
+      </c>
+      <c r="DX21" s="1">
+        <f t="shared" si="115"/>
+        <v>66095.966653342257</v>
+      </c>
+      <c r="DY21" s="1">
+        <f t="shared" si="115"/>
+        <v>65435.006986808832</v>
+      </c>
+      <c r="DZ21" s="1">
+        <f t="shared" si="115"/>
+        <v>64780.656916940745</v>
+      </c>
+      <c r="EA21" s="1">
+        <f t="shared" ref="EA21:FA21" si="116">DZ21*(1+$BP$29)</f>
+        <v>64132.850347771338</v>
+      </c>
+      <c r="EB21" s="1">
         <f t="shared" si="116"/>
-        <v>18164</v>
-      </c>
-      <c r="AK21" s="8">
+        <v>63491.521844293624</v>
+      </c>
+      <c r="EC21" s="1">
         <f t="shared" si="116"/>
-        <v>21187</v>
-      </c>
-      <c r="AL21" s="8">
+        <v>62856.606625850683</v>
+      </c>
+      <c r="ED21" s="1">
         <f t="shared" si="116"/>
-        <v>21152.038763499997</v>
-      </c>
-      <c r="AN21" s="8">
-        <f t="shared" ref="AN21:AV21" si="117">AN18-AN19-AN20</f>
-        <v>-241</v>
-      </c>
-      <c r="AO21" s="8">
-        <f t="shared" si="117"/>
-        <v>596</v>
-      </c>
-      <c r="AP21" s="8">
-        <f t="shared" si="117"/>
-        <v>2371</v>
-      </c>
-      <c r="AQ21" s="8">
-        <f t="shared" si="117"/>
-        <v>3033</v>
-      </c>
-      <c r="AR21" s="8">
-        <f t="shared" si="117"/>
-        <v>10073</v>
-      </c>
-      <c r="AS21" s="8">
-        <f t="shared" si="117"/>
-        <v>11588</v>
-      </c>
-      <c r="AT21" s="8">
-        <f t="shared" si="117"/>
-        <v>21331</v>
-      </c>
-      <c r="AU21" s="8">
-        <f t="shared" si="117"/>
-        <v>33364</v>
-      </c>
-      <c r="AV21" s="8">
-        <f t="shared" si="117"/>
-        <v>-2722</v>
-      </c>
-      <c r="AW21" s="8">
-        <f t="shared" ref="AW21:BE21" si="118">AW18-AW19-AW20</f>
-        <v>30425</v>
-      </c>
-      <c r="AX21" s="8">
-        <f t="shared" ref="AX21" si="119">AX18-AX19-AX20</f>
-        <v>59248</v>
-      </c>
-      <c r="AY21" s="8">
-        <f t="shared" si="118"/>
-        <v>77630.038763499921</v>
-      </c>
-      <c r="AZ21" s="8">
-        <f t="shared" si="118"/>
-        <v>79259.249569440028</v>
-      </c>
-      <c r="BA21" s="8">
-        <f t="shared" si="118"/>
-        <v>92194.735778031813</v>
-      </c>
-      <c r="BB21" s="8">
-        <f t="shared" si="118"/>
-        <v>105181.82747625448</v>
-      </c>
-      <c r="BC21" s="8">
-        <f t="shared" si="118"/>
-        <v>109079.48937213674</v>
-      </c>
-      <c r="BD21" s="8">
-        <f t="shared" si="118"/>
-        <v>112962.43465622597</v>
-      </c>
-      <c r="BE21" s="8">
-        <f t="shared" si="118"/>
-        <v>115461.6853002509</v>
-      </c>
-      <c r="BF21" s="8">
-        <f t="shared" ref="BF21:BI21" si="120">BF18-BF19-BF20</f>
-        <v>118294.67828130236</v>
-      </c>
-      <c r="BG21" s="8">
-        <f t="shared" si="120"/>
-        <v>119621.25277037501</v>
-      </c>
-      <c r="BH21" s="8">
-        <f t="shared" si="120"/>
-        <v>120969.76117739819</v>
-      </c>
-      <c r="BI21" s="8">
-        <f t="shared" si="120"/>
-        <v>122340.90085383657</v>
-      </c>
-      <c r="BJ21" s="1">
-        <f>BI21*(1+$BL$29)</f>
-        <v>121117.49184529821</v>
-      </c>
-      <c r="BK21" s="1">
-        <f t="shared" ref="BK21:DV21" si="121">BJ21*(1+$BL$29)</f>
-        <v>119906.31692684523</v>
-      </c>
-      <c r="BL21" s="1">
-        <f t="shared" si="121"/>
-        <v>118707.25375757678</v>
-      </c>
-      <c r="BM21" s="1">
-        <f t="shared" si="121"/>
-        <v>117520.181220001</v>
-      </c>
-      <c r="BN21" s="1">
-        <f t="shared" si="121"/>
-        <v>116344.97940780099</v>
-      </c>
-      <c r="BO21" s="1">
-        <f t="shared" si="121"/>
-        <v>115181.52961372297</v>
-      </c>
-      <c r="BP21" s="1">
-        <f t="shared" si="121"/>
-        <v>114029.71431758575</v>
-      </c>
-      <c r="BQ21" s="1">
-        <f t="shared" si="121"/>
-        <v>112889.41717440989</v>
-      </c>
-      <c r="BR21" s="1">
-        <f t="shared" si="121"/>
-        <v>111760.52300266578</v>
-      </c>
-      <c r="BS21" s="1">
-        <f t="shared" si="121"/>
-        <v>110642.91777263912</v>
-      </c>
-      <c r="BT21" s="1">
-        <f t="shared" si="121"/>
-        <v>109536.48859491273</v>
-      </c>
-      <c r="BU21" s="1">
-        <f t="shared" si="121"/>
-        <v>108441.12370896361</v>
-      </c>
-      <c r="BV21" s="1">
-        <f t="shared" si="121"/>
-        <v>107356.71247187398</v>
-      </c>
-      <c r="BW21" s="1">
-        <f t="shared" si="121"/>
-        <v>106283.14534715524</v>
-      </c>
-      <c r="BX21" s="1">
-        <f t="shared" si="121"/>
-        <v>105220.31389368369</v>
-      </c>
-      <c r="BY21" s="1">
-        <f t="shared" si="121"/>
-        <v>104168.11075474686</v>
-      </c>
-      <c r="BZ21" s="1">
-        <f t="shared" si="121"/>
-        <v>103126.42964719939</v>
-      </c>
-      <c r="CA21" s="1">
-        <f t="shared" si="121"/>
-        <v>102095.16535072739</v>
-      </c>
-      <c r="CB21" s="1">
-        <f t="shared" si="121"/>
-        <v>101074.21369722011</v>
-      </c>
-      <c r="CC21" s="1">
-        <f t="shared" si="121"/>
-        <v>100063.47156024791</v>
-      </c>
-      <c r="CD21" s="1">
-        <f t="shared" si="121"/>
-        <v>99062.836844645426</v>
-      </c>
-      <c r="CE21" s="1">
-        <f t="shared" si="121"/>
-        <v>98072.208476198968</v>
-      </c>
-      <c r="CF21" s="1">
-        <f t="shared" si="121"/>
-        <v>97091.486391436978</v>
-      </c>
-      <c r="CG21" s="1">
-        <f t="shared" si="121"/>
-        <v>96120.57152752261</v>
-      </c>
-      <c r="CH21" s="1">
-        <f t="shared" si="121"/>
-        <v>95159.365812247386</v>
-      </c>
-      <c r="CI21" s="1">
-        <f t="shared" si="121"/>
-        <v>94207.772154124905</v>
-      </c>
-      <c r="CJ21" s="1">
-        <f t="shared" si="121"/>
-        <v>93265.694432583652</v>
-      </c>
-      <c r="CK21" s="1">
-        <f t="shared" si="121"/>
-        <v>92333.037488257818</v>
-      </c>
-      <c r="CL21" s="1">
-        <f t="shared" si="121"/>
-        <v>91409.707113375232</v>
-      </c>
-      <c r="CM21" s="1">
-        <f t="shared" si="121"/>
-        <v>90495.610042241475</v>
-      </c>
-      <c r="CN21" s="1">
-        <f t="shared" si="121"/>
-        <v>89590.653941819066</v>
-      </c>
-      <c r="CO21" s="1">
-        <f t="shared" si="121"/>
-        <v>88694.74740240087</v>
-      </c>
-      <c r="CP21" s="1">
-        <f t="shared" si="121"/>
-        <v>87807.799928376859</v>
-      </c>
-      <c r="CQ21" s="1">
-        <f t="shared" si="121"/>
-        <v>86929.721929093095</v>
-      </c>
-      <c r="CR21" s="1">
-        <f t="shared" si="121"/>
-        <v>86060.424709802159</v>
-      </c>
-      <c r="CS21" s="1">
-        <f t="shared" si="121"/>
-        <v>85199.820462704141</v>
-      </c>
-      <c r="CT21" s="1">
-        <f t="shared" si="121"/>
-        <v>84347.822258077096</v>
-      </c>
-      <c r="CU21" s="1">
-        <f t="shared" si="121"/>
-        <v>83504.344035496324</v>
-      </c>
-      <c r="CV21" s="1">
-        <f t="shared" si="121"/>
-        <v>82669.300595141365</v>
-      </c>
-      <c r="CW21" s="1">
-        <f t="shared" si="121"/>
-        <v>81842.607589189953</v>
-      </c>
-      <c r="CX21" s="1">
-        <f t="shared" si="121"/>
-        <v>81024.181513298056</v>
-      </c>
-      <c r="CY21" s="1">
-        <f t="shared" si="121"/>
-        <v>80213.939698165079</v>
-      </c>
-      <c r="CZ21" s="1">
-        <f t="shared" si="121"/>
-        <v>79411.800301183423</v>
-      </c>
-      <c r="DA21" s="1">
-        <f t="shared" si="121"/>
-        <v>78617.682298171581</v>
-      </c>
-      <c r="DB21" s="1">
-        <f t="shared" si="121"/>
-        <v>77831.505475189872</v>
-      </c>
-      <c r="DC21" s="1">
-        <f t="shared" si="121"/>
-        <v>77053.190420437968</v>
-      </c>
-      <c r="DD21" s="1">
-        <f t="shared" si="121"/>
-        <v>76282.658516233583</v>
-      </c>
-      <c r="DE21" s="1">
-        <f t="shared" si="121"/>
-        <v>75519.83193107124</v>
-      </c>
-      <c r="DF21" s="1">
-        <f t="shared" si="121"/>
-        <v>74764.633611760524</v>
-      </c>
-      <c r="DG21" s="1">
-        <f t="shared" si="121"/>
-        <v>74016.987275642925</v>
-      </c>
-      <c r="DH21" s="1">
-        <f t="shared" si="121"/>
-        <v>73276.817402886489</v>
-      </c>
-      <c r="DI21" s="1">
-        <f t="shared" si="121"/>
-        <v>72544.049228857621</v>
-      </c>
-      <c r="DJ21" s="1">
-        <f t="shared" si="121"/>
-        <v>71818.608736569047</v>
-      </c>
-      <c r="DK21" s="1">
-        <f t="shared" si="121"/>
-        <v>71100.422649203363</v>
-      </c>
-      <c r="DL21" s="1">
-        <f t="shared" si="121"/>
-        <v>70389.418422711329</v>
-      </c>
-      <c r="DM21" s="1">
-        <f t="shared" si="121"/>
-        <v>69685.524238484213</v>
-      </c>
-      <c r="DN21" s="1">
-        <f t="shared" si="121"/>
-        <v>68988.668996099368</v>
-      </c>
-      <c r="DO21" s="1">
-        <f t="shared" si="121"/>
-        <v>68298.782306138368</v>
-      </c>
-      <c r="DP21" s="1">
-        <f t="shared" si="121"/>
-        <v>67615.794483076985</v>
-      </c>
-      <c r="DQ21" s="1">
-        <f t="shared" si="121"/>
-        <v>66939.63653824621</v>
-      </c>
-      <c r="DR21" s="1">
-        <f t="shared" si="121"/>
-        <v>66270.240172863749</v>
-      </c>
-      <c r="DS21" s="1">
-        <f t="shared" si="121"/>
-        <v>65607.537771135118</v>
-      </c>
-      <c r="DT21" s="1">
-        <f t="shared" si="121"/>
-        <v>64951.462393423768</v>
-      </c>
-      <c r="DU21" s="1">
-        <f t="shared" si="121"/>
-        <v>64301.947769489532</v>
-      </c>
-      <c r="DV21" s="1">
-        <f t="shared" si="121"/>
-        <v>63658.928291794633</v>
-      </c>
-      <c r="DW21" s="1">
-        <f t="shared" ref="DW21:EW21" si="122">DV21*(1+$BL$29)</f>
-        <v>63022.339008876683</v>
-      </c>
-      <c r="DX21" s="1">
-        <f t="shared" si="122"/>
-        <v>62392.115618787917</v>
-      </c>
-      <c r="DY21" s="1">
-        <f t="shared" si="122"/>
-        <v>61768.19446260004</v>
-      </c>
-      <c r="DZ21" s="1">
-        <f t="shared" si="122"/>
-        <v>61150.512517974043</v>
-      </c>
-      <c r="EA21" s="1">
-        <f t="shared" si="122"/>
-        <v>60539.007392794301</v>
-      </c>
-      <c r="EB21" s="1">
-        <f t="shared" si="122"/>
-        <v>59933.61731886636</v>
-      </c>
-      <c r="EC21" s="1">
-        <f t="shared" si="122"/>
-        <v>59334.281145677698</v>
-      </c>
-      <c r="ED21" s="1">
-        <f t="shared" si="122"/>
-        <v>58740.938334220918</v>
+        <v>62228.040559592177</v>
       </c>
       <c r="EE21" s="1">
-        <f t="shared" si="122"/>
-        <v>58153.52895087871</v>
+        <f t="shared" si="116"/>
+        <v>61605.760153996256</v>
       </c>
       <c r="EF21" s="1">
-        <f t="shared" si="122"/>
-        <v>57571.993661369925</v>
+        <f t="shared" si="116"/>
+        <v>60989.702552456292</v>
       </c>
       <c r="EG21" s="1">
-        <f t="shared" si="122"/>
-        <v>56996.273724756225</v>
+        <f t="shared" si="116"/>
+        <v>60379.805526931726</v>
       </c>
       <c r="EH21" s="1">
-        <f t="shared" si="122"/>
-        <v>56426.310987508659</v>
+        <f t="shared" si="116"/>
+        <v>59776.007471662408</v>
       </c>
       <c r="EI21" s="1">
-        <f t="shared" si="122"/>
-        <v>55862.047877633573</v>
+        <f t="shared" si="116"/>
+        <v>59178.247396945786</v>
       </c>
       <c r="EJ21" s="1">
-        <f t="shared" si="122"/>
-        <v>55303.427398857239</v>
+        <f t="shared" si="116"/>
+        <v>58586.464922976331</v>
       </c>
       <c r="EK21" s="1">
-        <f t="shared" si="122"/>
-        <v>54750.393124868664</v>
+        <f t="shared" si="116"/>
+        <v>58000.600273746568</v>
       </c>
       <c r="EL21" s="1">
-        <f t="shared" si="122"/>
-        <v>54202.88919361998</v>
+        <f t="shared" si="116"/>
+        <v>57420.594271009104</v>
       </c>
       <c r="EM21" s="1">
-        <f t="shared" si="122"/>
-        <v>53660.860301683781</v>
+        <f t="shared" si="116"/>
+        <v>56846.388328299014</v>
       </c>
       <c r="EN21" s="1">
-        <f t="shared" si="122"/>
-        <v>53124.251698666943</v>
+        <f t="shared" si="116"/>
+        <v>56277.924445016026</v>
       </c>
       <c r="EO21" s="1">
-        <f t="shared" si="122"/>
-        <v>52593.009181680274</v>
+        <f t="shared" si="116"/>
+        <v>55715.145200565865</v>
       </c>
       <c r="EP21" s="1">
-        <f t="shared" si="122"/>
-        <v>52067.079089863473</v>
+        <f t="shared" si="116"/>
+        <v>55157.993748560206</v>
       </c>
       <c r="EQ21" s="1">
-        <f t="shared" si="122"/>
-        <v>51546.408298964838</v>
+        <f t="shared" si="116"/>
+        <v>54606.413811074606</v>
       </c>
       <c r="ER21" s="1">
-        <f t="shared" si="122"/>
-        <v>51030.944215975192</v>
+        <f t="shared" si="116"/>
+        <v>54060.349672963857</v>
       </c>
       <c r="ES21" s="1">
-        <f t="shared" si="122"/>
-        <v>50520.634773815444</v>
+        <f t="shared" si="116"/>
+        <v>53519.746176234221</v>
       </c>
       <c r="ET21" s="1">
-        <f t="shared" si="122"/>
-        <v>50015.428426077291</v>
+        <f t="shared" si="116"/>
+        <v>52984.548714471879</v>
       </c>
       <c r="EU21" s="1">
-        <f t="shared" si="122"/>
-        <v>49515.274141816517</v>
+        <f t="shared" si="116"/>
+        <v>52454.703227327162</v>
       </c>
       <c r="EV21" s="1">
-        <f t="shared" si="122"/>
-        <v>49020.121400398348</v>
+        <f t="shared" si="116"/>
+        <v>51930.156195053889</v>
       </c>
       <c r="EW21" s="1">
-        <f t="shared" si="122"/>
-        <v>48529.920186394367</v>
+        <f t="shared" si="116"/>
+        <v>51410.85463310335</v>
+      </c>
+      <c r="EX21" s="1">
+        <f t="shared" si="116"/>
+        <v>50896.746086772313</v>
+      </c>
+      <c r="EY21" s="1">
+        <f t="shared" si="116"/>
+        <v>50387.77862590459</v>
+      </c>
+      <c r="EZ21" s="1">
+        <f t="shared" si="116"/>
+        <v>49883.900839645547</v>
+      </c>
+      <c r="FA21" s="1">
+        <f t="shared" si="116"/>
+        <v>49385.061831249091</v>
       </c>
     </row>
-    <row r="22" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>2</v>
       </c>
@@ -6127,21 +6216,12 @@
         <v>10674</v>
       </c>
       <c r="AL22" s="4">
-        <f>10674</f>
-        <v>10674</v>
-      </c>
-      <c r="AN22" s="4">
-        <v>503.6</v>
-      </c>
-      <c r="AO22" s="4">
-        <v>503.6</v>
-      </c>
-      <c r="AP22" s="4">
-        <v>503.6</v>
-      </c>
-      <c r="AQ22" s="4">
-        <v>503.6</v>
-      </c>
+        <v>10552</v>
+      </c>
+      <c r="AM22" s="4"/>
+      <c r="AN22" s="4"/>
+      <c r="AO22" s="4"/>
+      <c r="AP22" s="4"/>
       <c r="AR22" s="4">
         <v>503.6</v>
       </c>
@@ -6155,298 +6235,303 @@
         <v>503.6</v>
       </c>
       <c r="AV22" s="4">
+        <v>503.6</v>
+      </c>
+      <c r="AW22" s="4">
+        <v>503.6</v>
+      </c>
+      <c r="AX22" s="4">
+        <v>503.6</v>
+      </c>
+      <c r="AY22" s="4">
+        <v>503.6</v>
+      </c>
+      <c r="AZ22" s="4">
         <v>10220</v>
       </c>
-      <c r="AW22" s="4">
+      <c r="BA22" s="4">
         <f>AD22</f>
         <v>10356</v>
       </c>
-      <c r="AX22" s="4">
+      <c r="BB22" s="4">
         <v>10515</v>
       </c>
-      <c r="AY22" s="4">
-        <f>10674</f>
-        <v>10674</v>
-      </c>
-      <c r="AZ22" s="4">
-        <f>10674</f>
-        <v>10674</v>
-      </c>
-      <c r="BA22" s="4">
-        <f>10674</f>
-        <v>10674</v>
-      </c>
-      <c r="BB22" s="4">
-        <f>10674</f>
-        <v>10674</v>
-      </c>
       <c r="BC22" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
       </c>
       <c r="BD22" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
       </c>
       <c r="BE22" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
       </c>
       <c r="BF22" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
       </c>
       <c r="BG22" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
       </c>
       <c r="BH22" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
       </c>
       <c r="BI22" s="4">
-        <f>10674</f>
-        <v>10674</v>
+        <v>10552</v>
+      </c>
+      <c r="BJ22" s="4">
+        <v>10552</v>
+      </c>
+      <c r="BK22" s="4">
+        <v>10552</v>
+      </c>
+      <c r="BL22" s="4">
+        <v>10552</v>
+      </c>
+      <c r="BM22" s="4">
+        <v>10552</v>
       </c>
     </row>
-    <row r="23" spans="2:153" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:157" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23:R23" si="123">C21/C22</f>
+        <f t="shared" ref="C23:R23" si="117">C21/C22</f>
         <v>1.437648927720413</v>
       </c>
       <c r="D23" s="6">
+        <f t="shared" si="117"/>
+        <v>0.39118347895154881</v>
+      </c>
+      <c r="E23" s="6">
+        <f t="shared" si="117"/>
+        <v>0.50833995234312945</v>
+      </c>
+      <c r="F23" s="6">
+        <f t="shared" si="117"/>
+        <v>3.6854646544876886</v>
+      </c>
+      <c r="G23" s="6">
+        <f t="shared" si="117"/>
+        <v>3.2347100873709294</v>
+      </c>
+      <c r="H23" s="6">
+        <f t="shared" si="117"/>
+        <v>5.0317712470214451</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="117"/>
+        <v>5.7247815726767275</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="117"/>
+        <v>6.0107227958697376</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="117"/>
+        <v>7.071088165210484</v>
+      </c>
+      <c r="L23" s="6">
+        <f t="shared" si="117"/>
+        <v>5.2124702144559167</v>
+      </c>
+      <c r="M23" s="6">
+        <f t="shared" si="117"/>
+        <v>4.2374900714853059</v>
+      </c>
+      <c r="N23" s="6">
+        <f t="shared" si="117"/>
+        <v>6.4892772041302615</v>
+      </c>
+      <c r="O23" s="6">
+        <f t="shared" si="117"/>
+        <v>5.0337569499602859</v>
+      </c>
+      <c r="P23" s="6">
+        <f t="shared" si="117"/>
+        <v>10.411040508339951</v>
+      </c>
+      <c r="Q23" s="6">
+        <f t="shared" si="117"/>
+        <v>12.571485305798252</v>
+      </c>
+      <c r="R23" s="6">
+        <f t="shared" si="117"/>
+        <v>14.340746624305003</v>
+      </c>
+      <c r="S23" s="6">
+        <f t="shared" ref="S23:V23" si="118">S21/S22</f>
+        <v>16.098093725178714</v>
+      </c>
+      <c r="T23" s="6">
+        <f t="shared" ref="T23:U23" si="119">T21/T22</f>
+        <v>15.401980198019801</v>
+      </c>
+      <c r="U23" s="6">
+        <f t="shared" si="119"/>
+        <v>6.21259842519685</v>
+      </c>
+      <c r="V23" s="6">
+        <f t="shared" si="118"/>
+        <v>28.194881889763778</v>
+      </c>
+      <c r="W23" s="6">
+        <f t="shared" ref="W23:X23" si="120">W21/W22</f>
+        <v>-7.5520628683693518</v>
+      </c>
+      <c r="X23" s="6">
+        <f t="shared" si="120"/>
+        <v>-0.19931203931203931</v>
+      </c>
+      <c r="Y23" s="6">
+        <f t="shared" ref="Y23" si="121">Y21/Y22</f>
+        <v>0.28181728976547932</v>
+      </c>
+      <c r="Z23" s="6">
+        <f t="shared" ref="Z23" si="122">Z21/Z22</f>
+        <v>2.7201565557729943E-2</v>
+      </c>
+      <c r="AA23" s="6">
+        <f t="shared" ref="AA23:AB23" si="123">AA21/AA22</f>
+        <v>0.30946341463414634</v>
+      </c>
+      <c r="AB23" s="6">
         <f t="shared" si="123"/>
-        <v>0.39118347895154881</v>
-      </c>
-      <c r="E23" s="6">
-        <f t="shared" si="123"/>
-        <v>0.50833995234312945</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="123"/>
-        <v>3.6854646544876886</v>
-      </c>
-      <c r="G23" s="6">
-        <f t="shared" si="123"/>
-        <v>3.2347100873709294</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="123"/>
-        <v>5.0317712470214451</v>
-      </c>
-      <c r="I23" s="6">
-        <f t="shared" si="123"/>
-        <v>5.7247815726767275</v>
-      </c>
-      <c r="J23" s="6">
-        <f t="shared" si="123"/>
-        <v>6.0107227958697376</v>
-      </c>
-      <c r="K23" s="6">
-        <f t="shared" si="123"/>
-        <v>7.071088165210484</v>
-      </c>
-      <c r="L23" s="6">
-        <f t="shared" si="123"/>
-        <v>5.2124702144559167</v>
-      </c>
-      <c r="M23" s="6">
-        <f t="shared" si="123"/>
-        <v>4.2374900714853059</v>
-      </c>
-      <c r="N23" s="6">
-        <f t="shared" si="123"/>
-        <v>6.4892772041302615</v>
-      </c>
-      <c r="O23" s="6">
-        <f t="shared" si="123"/>
-        <v>5.0337569499602859</v>
-      </c>
-      <c r="P23" s="6">
-        <f t="shared" si="123"/>
-        <v>10.411040508339951</v>
-      </c>
-      <c r="Q23" s="6">
-        <f t="shared" si="123"/>
-        <v>12.571485305798252</v>
-      </c>
-      <c r="R23" s="6">
-        <f t="shared" si="123"/>
-        <v>14.340746624305003</v>
-      </c>
-      <c r="S23" s="6">
-        <f t="shared" ref="S23:V23" si="124">S21/S22</f>
-        <v>16.098093725178714</v>
-      </c>
-      <c r="T23" s="6">
-        <f t="shared" ref="T23:U23" si="125">T21/T22</f>
-        <v>15.401980198019801</v>
-      </c>
-      <c r="U23" s="6">
-        <f t="shared" si="125"/>
-        <v>6.21259842519685</v>
-      </c>
-      <c r="V23" s="6">
-        <f t="shared" si="124"/>
-        <v>28.194881889763778</v>
-      </c>
-      <c r="W23" s="6">
-        <f t="shared" ref="W23:X23" si="126">W21/W22</f>
-        <v>-7.5520628683693518</v>
-      </c>
-      <c r="X23" s="6">
+        <v>0.65629557608167233</v>
+      </c>
+      <c r="AC23" s="6">
+        <f t="shared" ref="AC23" si="124">AC21/AC22</f>
+        <v>0.9570819608602984</v>
+      </c>
+      <c r="AD23" s="6">
+        <f t="shared" ref="AD23" si="125">AD21/AD22</f>
+        <v>1.0258787176516029</v>
+      </c>
+      <c r="AE23" s="6">
+        <f t="shared" ref="AE23:AF23" si="126">AE21/AE22</f>
+        <v>1.0036563071297988</v>
+      </c>
+      <c r="AF23" s="6">
         <f t="shared" si="126"/>
-        <v>-0.19931203931203931</v>
-      </c>
-      <c r="Y23" s="6">
-        <f t="shared" ref="Y23" si="127">Y21/Y22</f>
-        <v>0.28181728976547932</v>
-      </c>
-      <c r="Z23" s="6">
-        <f t="shared" ref="Z23" si="128">Z21/Z22</f>
-        <v>2.7201565557729943E-2</v>
-      </c>
-      <c r="AA23" s="6">
-        <f t="shared" ref="AA23:AB23" si="129">AA21/AA22</f>
-        <v>0.30946341463414634</v>
-      </c>
-      <c r="AB23" s="6">
+        <v>1.2975079380352159</v>
+      </c>
+      <c r="AG23" s="6">
+        <f t="shared" ref="AG23:AH23" si="127">AG21/AG22</f>
+        <v>1.4577270565858298</v>
+      </c>
+      <c r="AH23" s="6">
+        <f t="shared" si="127"/>
+        <v>1.8957543593631538</v>
+      </c>
+      <c r="AI23" s="6">
+        <f t="shared" ref="AI23:AL23" si="128">AI21/AI22</f>
+        <v>1.6132587317734826</v>
+      </c>
+      <c r="AJ23" s="6">
+        <f t="shared" si="128"/>
+        <v>1.7076243301682805</v>
+      </c>
+      <c r="AK23" s="6">
+        <f t="shared" si="128"/>
+        <v>1.984916619823871</v>
+      </c>
+      <c r="AL23" s="6">
+        <f t="shared" si="128"/>
+        <v>2.0083396512509477</v>
+      </c>
+      <c r="AM23" s="6"/>
+      <c r="AN23" s="6"/>
+      <c r="AO23" s="6"/>
+      <c r="AP23" s="6"/>
+      <c r="AR23" s="6">
+        <f t="shared" ref="AR23:AZ23" si="129">AR21/AR22</f>
+        <v>-0.4785544082605242</v>
+      </c>
+      <c r="AS23" s="6">
         <f t="shared" si="129"/>
-        <v>0.65629557608167233</v>
-      </c>
-      <c r="AC23" s="6">
-        <f t="shared" ref="AC23" si="130">AC21/AC22</f>
-        <v>0.9570819608602984</v>
-      </c>
-      <c r="AD23" s="6">
-        <f t="shared" ref="AD23" si="131">AD21/AD22</f>
-        <v>1.0258787176516029</v>
-      </c>
-      <c r="AE23" s="6">
-        <f t="shared" ref="AE23:AF23" si="132">AE21/AE22</f>
-        <v>1.0036563071297988</v>
-      </c>
-      <c r="AF23" s="6">
+        <v>1.1834789515488482</v>
+      </c>
+      <c r="AT23" s="6">
+        <f t="shared" si="129"/>
+        <v>4.7081016679904684</v>
+      </c>
+      <c r="AU23" s="6">
+        <f t="shared" si="129"/>
+        <v>6.0226370135027798</v>
+      </c>
+      <c r="AV23" s="6">
+        <f t="shared" si="129"/>
+        <v>20.001985702938839</v>
+      </c>
+      <c r="AW23" s="6">
+        <f t="shared" si="129"/>
+        <v>23.010325655281967</v>
+      </c>
+      <c r="AX23" s="6">
+        <f t="shared" si="129"/>
+        <v>42.35702938840349</v>
+      </c>
+      <c r="AY23" s="6">
+        <f t="shared" si="129"/>
+        <v>66.25099285146942</v>
+      </c>
+      <c r="AZ23" s="6">
+        <f t="shared" si="129"/>
+        <v>-0.26634050880626225</v>
+      </c>
+      <c r="BA23" s="6">
+        <f t="shared" ref="BA23:BI23" si="130">BA21/BA22</f>
+        <v>2.9379103901120125</v>
+      </c>
+      <c r="BB23" s="6">
+        <f t="shared" ref="BB23" si="131">BB21/BB22</f>
+        <v>5.6346172135045176</v>
+      </c>
+      <c r="BC23" s="6">
+        <f t="shared" si="130"/>
+        <v>7.3606899166034871</v>
+      </c>
+      <c r="BD23" s="6">
+        <f t="shared" si="130"/>
+        <v>7.6720100629264669</v>
+      </c>
+      <c r="BE23" s="6">
+        <f t="shared" si="130"/>
+        <v>8.9163446903358548</v>
+      </c>
+      <c r="BF23" s="6">
+        <f t="shared" si="130"/>
+        <v>10.162111249828364</v>
+      </c>
+      <c r="BG23" s="6">
+        <f t="shared" si="130"/>
+        <v>10.53789032630276</v>
+      </c>
+      <c r="BH23" s="6">
+        <f t="shared" si="130"/>
+        <v>10.909583361056978</v>
+      </c>
+      <c r="BI23" s="6">
+        <f t="shared" si="130"/>
+        <v>11.148790753761606</v>
+      </c>
+      <c r="BJ23" s="6">
+        <f t="shared" ref="BJ23:BM23" si="132">BJ21/BJ22</f>
+        <v>11.417925347592698</v>
+      </c>
+      <c r="BK23" s="6">
         <f t="shared" si="132"/>
-        <v>1.2975079380352159</v>
-      </c>
-      <c r="AG23" s="6">
-        <f t="shared" ref="AG23:AH23" si="133">AG21/AG22</f>
-        <v>1.4577270565858298</v>
-      </c>
-      <c r="AH23" s="6">
-        <f t="shared" si="133"/>
-        <v>1.8957543593631538</v>
-      </c>
-      <c r="AI23" s="6">
-        <f t="shared" ref="AI23:AL23" si="134">AI21/AI22</f>
-        <v>1.6132587317734826</v>
-      </c>
-      <c r="AJ23" s="6">
-        <f t="shared" si="134"/>
-        <v>1.7076243301682805</v>
-      </c>
-      <c r="AK23" s="6">
-        <f t="shared" si="134"/>
-        <v>1.984916619823871</v>
-      </c>
-      <c r="AL23" s="6">
-        <f t="shared" si="134"/>
-        <v>1.9816412557148209</v>
-      </c>
-      <c r="AN23" s="6">
-        <f t="shared" ref="AN23:AV23" si="135">AN21/AN22</f>
-        <v>-0.4785544082605242</v>
-      </c>
-      <c r="AO23" s="6">
-        <f t="shared" si="135"/>
-        <v>1.1834789515488482</v>
-      </c>
-      <c r="AP23" s="6">
-        <f t="shared" si="135"/>
-        <v>4.7081016679904684</v>
-      </c>
-      <c r="AQ23" s="6">
-        <f t="shared" si="135"/>
-        <v>6.0226370135027798</v>
-      </c>
-      <c r="AR23" s="6">
-        <f t="shared" si="135"/>
-        <v>20.001985702938839</v>
-      </c>
-      <c r="AS23" s="6">
-        <f t="shared" si="135"/>
-        <v>23.010325655281967</v>
-      </c>
-      <c r="AT23" s="6">
-        <f t="shared" si="135"/>
-        <v>42.35702938840349</v>
-      </c>
-      <c r="AU23" s="6">
-        <f t="shared" si="135"/>
-        <v>66.25099285146942</v>
-      </c>
-      <c r="AV23" s="6">
-        <f t="shared" si="135"/>
-        <v>-0.26634050880626225</v>
-      </c>
-      <c r="AW23" s="6">
-        <f t="shared" ref="AW23:BE23" si="136">AW21/AW22</f>
-        <v>2.9379103901120125</v>
-      </c>
-      <c r="AX23" s="6">
-        <f t="shared" ref="AX23" si="137">AX21/AX22</f>
-        <v>5.6346172135045176</v>
-      </c>
-      <c r="AY23" s="6">
-        <f t="shared" si="136"/>
-        <v>7.2728160730279106</v>
-      </c>
-      <c r="AZ23" s="6">
-        <f t="shared" si="136"/>
-        <v>7.4254496505002834</v>
-      </c>
-      <c r="BA23" s="6">
-        <f t="shared" si="136"/>
-        <v>8.6373183228435266</v>
-      </c>
-      <c r="BB23" s="6">
-        <f t="shared" si="136"/>
-        <v>9.8540216859897392</v>
-      </c>
-      <c r="BC23" s="6">
-        <f t="shared" si="136"/>
-        <v>10.219176444831998</v>
-      </c>
-      <c r="BD23" s="6">
-        <f t="shared" si="136"/>
-        <v>10.582952469198611</v>
-      </c>
-      <c r="BE23" s="6">
-        <f t="shared" si="136"/>
-        <v>10.817096243231301</v>
-      </c>
-      <c r="BF23" s="6">
-        <f t="shared" ref="BF23:BI23" si="138">BF21/BF22</f>
-        <v>11.082506865402133</v>
-      </c>
-      <c r="BG23" s="6">
-        <f t="shared" si="138"/>
-        <v>11.206787780623479</v>
-      </c>
-      <c r="BH23" s="6">
-        <f t="shared" si="138"/>
-        <v>11.33312358791439</v>
-      </c>
-      <c r="BI23" s="6">
-        <f t="shared" si="138"/>
-        <v>11.461579619059076</v>
+        <v>11.542763170167051</v>
+      </c>
+      <c r="BL23" s="6">
+        <f t="shared" si="132"/>
+        <v>11.669565918517865</v>
+      </c>
+      <c r="BM23" s="6">
+        <f t="shared" si="132"/>
+        <v>11.798394577853346</v>
       </c>
     </row>
-    <row r="25" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B25" t="s">
         <v>59</v>
       </c>
@@ -6459,216 +6544,220 @@
         <v>0.33163394286677339</v>
       </c>
       <c r="H25" s="10">
-        <f t="shared" ref="H25:V25" si="139">H3/D3-1</f>
+        <f t="shared" ref="H25:V25" si="133">H3/D3-1</f>
         <v>0.28769448373408779</v>
       </c>
       <c r="I25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.17303948832035587</v>
       </c>
       <c r="J25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>8.166969147005454E-2</v>
       </c>
       <c r="K25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>8.4733428255022947E-2</v>
       </c>
       <c r="L25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.12528245041426067</v>
       </c>
       <c r="M25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.17720618739998817</v>
       </c>
       <c r="N25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.13069351230425053</v>
       </c>
       <c r="O25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.22045911968030807</v>
       </c>
       <c r="P25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.40127175368139234</v>
       </c>
       <c r="Q25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.32844988168957356</v>
       </c>
       <c r="R25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.40588025800324479</v>
       </c>
       <c r="S25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.37403503740350375</v>
       </c>
       <c r="T25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>0.15444630204601539</v>
       </c>
       <c r="U25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>3.9830219426232549E-2</v>
       </c>
       <c r="V25" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="133"/>
         <v>5.0664264805224679E-3</v>
       </c>
       <c r="W25" s="10">
-        <f t="shared" ref="W25:W27" si="140">W3/S3-1</f>
+        <f t="shared" ref="W25:W27" si="134">W3/S3-1</f>
         <v>-1.8020211859247515E-2</v>
       </c>
       <c r="X25" s="10">
-        <f t="shared" ref="X25:X27" si="141">X3/T3-1</f>
+        <f t="shared" ref="X25:X27" si="135">X3/T3-1</f>
         <v>-2.4636231984001111E-2</v>
       </c>
       <c r="Y25" s="10">
-        <f t="shared" ref="Y25:Y27" si="142">Y3/U3-1</f>
+        <f t="shared" ref="Y25:Y27" si="136">Y3/U3-1</f>
         <v>8.1347036956046281E-2</v>
       </c>
       <c r="Z25" s="10">
-        <f t="shared" ref="Z25:Z27" si="143">Z3/V3-1</f>
+        <f t="shared" ref="Z25:Z27" si="137">Z3/V3-1</f>
         <v>-1.2392181023860194E-2</v>
       </c>
       <c r="AA25" s="10">
-        <f t="shared" ref="AA25:AA27" si="144">AA3/W3-1</f>
+        <f t="shared" ref="AA25:AA27" si="138">AA3/W3-1</f>
         <v>9.317155256398868E-3</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" ref="AB25:AB27" si="145">AB3/X3-1</f>
+        <f t="shared" ref="AB25:AB27" si="139">AB3/X3-1</f>
         <v>4.342907644719407E-2</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" ref="AC25:AC27" si="146">AC3/Y3-1</f>
+        <f t="shared" ref="AC25:AC27" si="140">AC3/Y3-1</f>
         <v>6.4560161779575242E-2</v>
       </c>
       <c r="AD25" s="10">
-        <f t="shared" ref="AD25:AD27" si="147">AD3/Z3-1</f>
+        <f t="shared" ref="AD25:AD27" si="141">AD3/Z3-1</f>
         <v>8.7507620762501626E-2</v>
       </c>
       <c r="AE25" s="10">
-        <f t="shared" ref="AE25:AE27" si="148">AE3/AA3-1</f>
+        <f t="shared" ref="AE25:AE27" si="142">AE3/AA3-1</f>
         <v>6.9040557378775347E-2</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" ref="AF25:AF27" si="149">AF3/AB3-1</f>
+        <f t="shared" ref="AF25:AF27" si="143">AF3/AB3-1</f>
         <v>4.2976690608483636E-2</v>
       </c>
       <c r="AG25" s="10">
-        <f t="shared" ref="AG25:AG27" si="150">AG3/AC3-1</f>
+        <f t="shared" ref="AG25:AG27" si="144">AG3/AC3-1</f>
         <v>7.0127115290243847E-2</v>
       </c>
       <c r="AH25" s="10">
-        <f t="shared" ref="AH25:AH27" si="151">AH3/AD3-1</f>
+        <f t="shared" ref="AH25:AH27" si="145">AH3/AD3-1</f>
         <v>7.200500632309037E-2</v>
       </c>
       <c r="AI25" s="10">
-        <f t="shared" ref="AI25:AI27" si="152">AI3/AE3-1</f>
+        <f t="shared" ref="AI25:AI27" si="146">AI3/AE3-1</f>
         <v>5.0151850939834208E-2</v>
       </c>
       <c r="AJ25" s="10">
-        <f t="shared" ref="AJ25:AJ27" si="153">AJ3/AF3-1</f>
+        <f t="shared" ref="AJ25:AJ27" si="147">AJ3/AF3-1</f>
         <v>0.10844743296139292</v>
       </c>
       <c r="AK25" s="10">
-        <f t="shared" ref="AK25:AK27" si="154">AK3/AG3-1</f>
+        <f t="shared" ref="AK25:AK27" si="148">AK3/AG3-1</f>
         <v>9.5516338515702515E-2</v>
       </c>
       <c r="AL25" s="10">
-        <f t="shared" ref="AL25:AL27" si="155">AL3/AH3-1</f>
-        <v>8.0000000000000071E-2</v>
-      </c>
+        <f t="shared" ref="AL25:AL27" si="149">AL3/AH3-1</f>
+        <v>9.4447011894048138E-2</v>
+      </c>
+      <c r="AM25" s="10"/>
       <c r="AN25" s="10"/>
-      <c r="AO25" s="10">
-        <f>AO3/AN3-1</f>
+      <c r="AO25" s="10"/>
+      <c r="AP25" s="10"/>
+      <c r="AR25" s="10"/>
+      <c r="AS25" s="10">
+        <f>AS3/AR3-1</f>
         <v>0.131107305936073</v>
       </c>
-      <c r="AP25" s="10">
-        <f t="shared" ref="AP25:BE25" si="156">AP3/AO3-1</f>
+      <c r="AT25" s="10">
+        <f t="shared" ref="AT25:BI25" si="150">AT3/AS3-1</f>
         <v>0.19423979411616288</v>
       </c>
-      <c r="AQ25" s="10">
-        <f t="shared" si="156"/>
+      <c r="AU25" s="10">
+        <f t="shared" si="150"/>
         <v>0.25254317857708752</v>
       </c>
-      <c r="AR25" s="10">
-        <f t="shared" si="156"/>
+      <c r="AV25" s="10">
+        <f t="shared" si="150"/>
         <v>0.19686772593867019</v>
       </c>
-      <c r="AS25" s="10">
-        <f t="shared" si="156"/>
+      <c r="AW25" s="10">
+        <f t="shared" si="150"/>
         <v>0.13030335059718845</v>
       </c>
-      <c r="AT25" s="10">
-        <f t="shared" si="156"/>
+      <c r="AX25" s="10">
+        <f t="shared" si="150"/>
         <v>0.34604474867056934</v>
       </c>
-      <c r="AU25" s="10">
-        <f t="shared" si="156"/>
+      <c r="AY25" s="10">
+        <f t="shared" si="150"/>
         <v>0.11982493110714865</v>
       </c>
-      <c r="AV25" s="10">
-        <f t="shared" si="156"/>
+      <c r="AZ25" s="10">
+        <f t="shared" si="150"/>
         <v>4.6073610243726471E-3</v>
       </c>
-      <c r="AW25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BA25" s="10">
+        <f t="shared" si="150"/>
         <v>5.3462110077768354E-2</v>
       </c>
-      <c r="AX25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BB25" s="10">
+        <f t="shared" si="150"/>
         <v>6.4184581475416946E-2</v>
       </c>
-      <c r="AY25" s="10">
-        <f t="shared" si="156"/>
-        <v>8.360690533985049E-2</v>
-      </c>
-      <c r="AZ25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BC25" s="10">
+        <f t="shared" si="150"/>
+        <v>8.7969270429765878E-2</v>
+      </c>
+      <c r="BD25" s="10">
+        <f t="shared" si="150"/>
         <v>5.0000000000000044E-2</v>
       </c>
-      <c r="BA25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BE25" s="10">
+        <f t="shared" si="150"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BB25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BF25" s="10">
+        <f t="shared" si="150"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BC25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BG25" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BH25" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE25" s="10">
-        <f t="shared" si="156"/>
+      <c r="BI25" s="10">
+        <f t="shared" si="150"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF25" s="10">
-        <f t="shared" ref="BF25:BF27" si="157">BF3/BE3-1</f>
+      <c r="BJ25" s="10">
+        <f t="shared" ref="BJ25:BJ27" si="151">BJ3/BI3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BG25" s="10">
-        <f t="shared" ref="BG25:BG27" si="158">BG3/BF3-1</f>
+      <c r="BK25" s="10">
+        <f t="shared" ref="BK25:BK27" si="152">BK3/BJ3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH25" s="10">
-        <f t="shared" ref="BH25:BH27" si="159">BH3/BG3-1</f>
+      <c r="BL25" s="10">
+        <f t="shared" ref="BL25:BL27" si="153">BL3/BK3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BI25" s="10">
-        <f t="shared" ref="BI25:BI27" si="160">BI3/BH3-1</f>
+      <c r="BM25" s="10">
+        <f t="shared" ref="BM25:BM27" si="154">BM3/BL3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
-    <row r="26" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B26" t="s">
         <v>60</v>
       </c>
@@ -6681,216 +6770,220 @@
         <v>0.62245409015025044</v>
       </c>
       <c r="H26" s="10">
-        <f t="shared" ref="H26:V26" si="161">H4/D4-1</f>
+        <f t="shared" ref="H26:V26" si="155">H4/D4-1</f>
         <v>0.5913701741105224</v>
       </c>
       <c r="I26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.52443910256410264</v>
       </c>
       <c r="J26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.44725010455876202</v>
       </c>
       <c r="K26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.30766064721922115</v>
       </c>
       <c r="L26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.3104366853772238</v>
       </c>
       <c r="M26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.32522996057818654</v>
       </c>
       <c r="N26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.33276740237691005</v>
       </c>
       <c r="O26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.32238265727662596</v>
       </c>
       <c r="P26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.40365906780891536</v>
       </c>
       <c r="Q26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.43351512146752613</v>
       </c>
       <c r="R26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.47713782355332701</v>
       </c>
       <c r="S26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.5181636964089138</v>
       </c>
       <c r="T26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.42433019551049966</v>
       </c>
       <c r="U26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.28970971386410271</v>
       </c>
       <c r="V26" s="10">
-        <f t="shared" si="161"/>
+        <f t="shared" si="155"/>
         <v>0.21095799922934355</v>
       </c>
       <c r="W26" s="10">
+        <f t="shared" si="134"/>
+        <v>0.17563250827993016</v>
+      </c>
+      <c r="X26" s="10">
+        <f t="shared" si="135"/>
+        <v>0.17399593289273008</v>
+      </c>
+      <c r="Y26" s="10">
+        <f t="shared" si="136"/>
+        <v>0.21140231693363853</v>
+      </c>
+      <c r="Z26" s="10">
+        <f t="shared" si="137"/>
+        <v>0.19208739923631746</v>
+      </c>
+      <c r="AA26" s="10">
+        <f t="shared" si="138"/>
+        <v>0.17316508026471511</v>
+      </c>
+      <c r="AB26" s="10">
+        <f t="shared" si="139"/>
+        <v>0.16535981069920669</v>
+      </c>
+      <c r="AC26" s="10">
         <f t="shared" si="140"/>
-        <v>0.17563250827993016</v>
-      </c>
-      <c r="X26" s="10">
+        <v>0.179321438585617</v>
+      </c>
+      <c r="AD26" s="10">
         <f t="shared" si="141"/>
-        <v>0.17399593289273008</v>
-      </c>
-      <c r="Y26" s="10">
+        <v>0.1853876170986235</v>
+      </c>
+      <c r="AE26" s="10">
         <f t="shared" si="142"/>
-        <v>0.21140231693363853</v>
-      </c>
-      <c r="Z26" s="10">
+        <v>0.17080864486977276</v>
+      </c>
+      <c r="AF26" s="10">
         <f t="shared" si="143"/>
-        <v>0.19208739923631746</v>
-      </c>
-      <c r="AA26" s="10">
+        <v>0.14673992382317413</v>
+      </c>
+      <c r="AG26" s="10">
         <f t="shared" si="144"/>
-        <v>0.17316508026471511</v>
-      </c>
-      <c r="AB26" s="10">
+        <v>0.14220642706977671</v>
+      </c>
+      <c r="AH26" s="10">
         <f t="shared" si="145"/>
-        <v>0.16535981069920669</v>
-      </c>
-      <c r="AC26" s="10">
+        <v>0.13197795363400466</v>
+      </c>
+      <c r="AI26" s="10">
         <f t="shared" si="146"/>
-        <v>0.179321438585617</v>
-      </c>
-      <c r="AD26" s="10">
+        <v>0.11285468093885775</v>
+      </c>
+      <c r="AJ26" s="10">
         <f t="shared" si="147"/>
-        <v>0.1853876170986235</v>
-      </c>
-      <c r="AE26" s="10">
+        <v>0.15100453661697988</v>
+      </c>
+      <c r="AK26" s="10">
         <f t="shared" si="148"/>
-        <v>0.17080864486977276</v>
-      </c>
-      <c r="AF26" s="10">
+        <v>0.16252903282352427</v>
+      </c>
+      <c r="AL26" s="10">
         <f t="shared" si="149"/>
-        <v>0.14673992382317413</v>
-      </c>
-      <c r="AG26" s="10">
-        <f t="shared" si="150"/>
-        <v>0.14220642706977671</v>
-      </c>
-      <c r="AH26" s="10">
+        <v>0.168880131860637</v>
+      </c>
+      <c r="AM26" s="10"/>
+      <c r="AN26" s="10"/>
+      <c r="AO26" s="10"/>
+      <c r="AP26" s="10"/>
+      <c r="AR26" s="10"/>
+      <c r="AS26" s="10">
+        <f t="shared" ref="AS26:BI26" si="156">AS4/AR4-1</f>
+        <v>0.46699809604400255</v>
+      </c>
+      <c r="AT26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.48972528661042602</v>
+      </c>
+      <c r="AU26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.43492570543536124</v>
+      </c>
+      <c r="AV26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.53425304415286545</v>
+      </c>
+      <c r="AW26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.3203513168887131</v>
+      </c>
+      <c r="AX26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.41655080547808354</v>
+      </c>
+      <c r="AY26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.34020770030972858</v>
+      </c>
+      <c r="AZ26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.18877365316727701</v>
+      </c>
+      <c r="BA26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.17638943197999124</v>
+      </c>
+      <c r="BB26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.14659859892504823</v>
+      </c>
+      <c r="BC26" s="10">
+        <f t="shared" si="156"/>
+        <v>0.15044523694919709</v>
+      </c>
+      <c r="BD26" s="10">
+        <f t="shared" si="156"/>
+        <v>9.000000000000008E-2</v>
+      </c>
+      <c r="BE26" s="10">
+        <f t="shared" si="156"/>
+        <v>8.0000000000000071E-2</v>
+      </c>
+      <c r="BF26" s="10">
+        <f t="shared" si="156"/>
+        <v>6.0000000000000053E-2</v>
+      </c>
+      <c r="BG26" s="10">
+        <f t="shared" si="156"/>
+        <v>4.0000000000000036E-2</v>
+      </c>
+      <c r="BH26" s="10">
+        <f t="shared" si="156"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="BI26" s="10">
+        <f t="shared" si="156"/>
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BJ26" s="10">
         <f t="shared" si="151"/>
-        <v>0.13197795363400466</v>
-      </c>
-      <c r="AI26" s="10">
+        <v>2.0000000000000018E-2</v>
+      </c>
+      <c r="BK26" s="10">
         <f t="shared" si="152"/>
-        <v>0.11285468093885775</v>
-      </c>
-      <c r="AJ26" s="10">
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BL26" s="10">
         <f t="shared" si="153"/>
-        <v>0.15100453661697988</v>
-      </c>
-      <c r="AK26" s="10">
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BM26" s="10">
         <f t="shared" si="154"/>
-        <v>0.16252903282352427</v>
-      </c>
-      <c r="AL26" s="10">
-        <f t="shared" si="155"/>
-        <v>0.12999999999999989</v>
-      </c>
-      <c r="AN26" s="10"/>
-      <c r="AO26" s="10">
-        <f t="shared" ref="AO26:BE26" si="162">AO4/AN4-1</f>
-        <v>0.46699809604400255</v>
-      </c>
-      <c r="AP26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.48972528661042602</v>
-      </c>
-      <c r="AQ26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.43492570543536124</v>
-      </c>
-      <c r="AR26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.53425304415286545</v>
-      </c>
-      <c r="AS26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.3203513168887131</v>
-      </c>
-      <c r="AT26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.41655080547808354</v>
-      </c>
-      <c r="AU26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.34020770030972858</v>
-      </c>
-      <c r="AV26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.18877365316727701</v>
-      </c>
-      <c r="AW26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.17638943197999124</v>
-      </c>
-      <c r="AX26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.14659859892504823</v>
-      </c>
-      <c r="AY26" s="10">
-        <f t="shared" si="162"/>
-        <v>0.1392201789699381</v>
-      </c>
-      <c r="AZ26" s="10">
-        <f t="shared" si="162"/>
-        <v>9.000000000000008E-2</v>
-      </c>
-      <c r="BA26" s="10">
-        <f t="shared" si="162"/>
-        <v>8.0000000000000071E-2</v>
-      </c>
-      <c r="BB26" s="10">
-        <f t="shared" si="162"/>
-        <v>6.0000000000000053E-2</v>
-      </c>
-      <c r="BC26" s="10">
-        <f t="shared" si="162"/>
-        <v>4.0000000000000036E-2</v>
-      </c>
-      <c r="BD26" s="10">
-        <f t="shared" si="162"/>
-        <v>3.0000000000000027E-2</v>
-      </c>
-      <c r="BE26" s="10">
-        <f t="shared" si="162"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BF26" s="10">
-        <f t="shared" si="157"/>
-        <v>2.0000000000000018E-2</v>
-      </c>
-      <c r="BG26" s="10">
-        <f t="shared" si="158"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH26" s="10">
-        <f t="shared" si="159"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="BI26" s="10">
-        <f t="shared" si="160"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
     </row>
-    <row r="27" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B27" s="1" t="s">
         <v>51</v>
       </c>
@@ -6903,233 +6996,237 @@
         <v>0.42918743349946809</v>
       </c>
       <c r="H27" s="10">
-        <f t="shared" ref="H27:V27" si="163">H5/D5-1</f>
+        <f t="shared" ref="H27:V27" si="157">H5/D5-1</f>
         <v>0.39338690554604128</v>
       </c>
       <c r="I27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.29334308705193846</v>
       </c>
       <c r="J27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.19734339073329688</v>
       </c>
       <c r="K27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.16962501469378166</v>
       </c>
       <c r="L27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.1988806111258179</v>
       </c>
       <c r="M27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.23693792420814486</v>
       </c>
       <c r="N27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.20797701117665746</v>
       </c>
       <c r="O27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.26385259631490787</v>
       </c>
       <c r="P27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.40230900258658764</v>
       </c>
       <c r="Q27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.37387290836084075</v>
       </c>
       <c r="R27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.43594816839553041</v>
       </c>
       <c r="S27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.43823888034777081</v>
       </c>
       <c r="T27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.27181932697498645</v>
       </c>
       <c r="U27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>0.15255083467679031</v>
       </c>
       <c r="V27" s="10">
-        <f t="shared" si="163"/>
+        <f t="shared" si="157"/>
         <v>9.4436701047349692E-2</v>
       </c>
       <c r="W27" s="10">
+        <f t="shared" si="134"/>
+        <v>7.3038574245747334E-2</v>
+      </c>
+      <c r="X27" s="10">
+        <f t="shared" si="135"/>
+        <v>7.2108241952600016E-2</v>
+      </c>
+      <c r="Y27" s="10">
+        <f t="shared" si="136"/>
+        <v>0.14699671515720314</v>
+      </c>
+      <c r="Z27" s="10">
+        <f t="shared" si="137"/>
+        <v>8.5814921549791867E-2</v>
+      </c>
+      <c r="AA27" s="10">
+        <f t="shared" si="138"/>
+        <v>9.3727456975026602E-2</v>
+      </c>
+      <c r="AB27" s="10">
+        <f t="shared" si="139"/>
+        <v>0.10845967302901816</v>
+      </c>
+      <c r="AC27" s="10">
         <f t="shared" si="140"/>
-        <v>7.3038574245747334E-2</v>
-      </c>
-      <c r="X27" s="10">
+        <v>0.125742519728405</v>
+      </c>
+      <c r="AD27" s="10">
         <f t="shared" si="141"/>
-        <v>7.2108241952600016E-2</v>
-      </c>
-      <c r="Y27" s="10">
+        <v>0.13911825420230017</v>
+      </c>
+      <c r="AE27" s="10">
         <f t="shared" si="142"/>
-        <v>0.14699671515720314</v>
-      </c>
-      <c r="Z27" s="10">
+        <v>0.12527677884388888</v>
+      </c>
+      <c r="AF27" s="10">
         <f t="shared" si="143"/>
-        <v>8.5814921549791867E-2</v>
-      </c>
-      <c r="AA27" s="10">
+        <v>0.10115862869559389</v>
+      </c>
+      <c r="AG27" s="10">
         <f t="shared" si="144"/>
-        <v>9.3727456975026602E-2</v>
-      </c>
-      <c r="AB27" s="10">
+        <v>0.11038348371225104</v>
+      </c>
+      <c r="AH27" s="10">
         <f t="shared" si="145"/>
-        <v>0.10845967302901816</v>
-      </c>
-      <c r="AC27" s="10">
+        <v>0.10491230341078239</v>
+      </c>
+      <c r="AI27" s="10">
         <f t="shared" si="146"/>
-        <v>0.125742519728405</v>
-      </c>
-      <c r="AD27" s="10">
+        <v>8.6202926461660834E-2</v>
+      </c>
+      <c r="AJ27" s="10">
         <f t="shared" si="147"/>
-        <v>0.13911825420230017</v>
-      </c>
-      <c r="AE27" s="10">
+        <v>0.13329774221669588</v>
+      </c>
+      <c r="AK27" s="10">
         <f t="shared" si="148"/>
-        <v>0.12527677884388888</v>
-      </c>
-      <c r="AF27" s="10">
+        <v>0.13401562214795093</v>
+      </c>
+      <c r="AL27" s="10">
         <f t="shared" si="149"/>
-        <v>0.10115862869559389</v>
-      </c>
-      <c r="AG27" s="10">
-        <f t="shared" si="150"/>
-        <v>0.11038348371225104</v>
-      </c>
-      <c r="AH27" s="10">
-        <f t="shared" si="151"/>
-        <v>0.10491230341078239</v>
-      </c>
-      <c r="AI27" s="10">
-        <f t="shared" si="152"/>
-        <v>8.6202926461660834E-2</v>
-      </c>
-      <c r="AJ27" s="10">
-        <f t="shared" si="153"/>
-        <v>0.13329774221669588</v>
-      </c>
-      <c r="AK27" s="10">
-        <f t="shared" si="154"/>
-        <v>0.13401562214795093</v>
-      </c>
-      <c r="AL27" s="10">
-        <f t="shared" si="155"/>
-        <v>0.10810716111442442</v>
-      </c>
+        <v>0.13628908579705201</v>
+      </c>
+      <c r="AM27" s="10"/>
       <c r="AN27" s="10"/>
-      <c r="AO27" s="10">
-        <f t="shared" ref="AO27:BE27" si="164">AO5/AN5-1</f>
+      <c r="AO27" s="10"/>
+      <c r="AP27" s="10"/>
+      <c r="AR27" s="10"/>
+      <c r="AS27" s="10">
+        <f t="shared" ref="AS27:BI27" si="158">AS5/AR5-1</f>
         <v>0.20247673843664304</v>
       </c>
-      <c r="AP27" s="10">
-        <f t="shared" si="164"/>
+      <c r="AT27" s="10">
+        <f t="shared" si="158"/>
         <v>0.27083528026465808</v>
       </c>
-      <c r="AQ27" s="10">
-        <f t="shared" si="164"/>
+      <c r="AU27" s="10">
+        <f t="shared" si="158"/>
         <v>0.30796326119408479</v>
       </c>
-      <c r="AR27" s="10">
-        <f t="shared" si="164"/>
+      <c r="AV27" s="10">
+        <f t="shared" si="158"/>
         <v>0.3093396152159491</v>
       </c>
-      <c r="AS27" s="10">
-        <f t="shared" si="164"/>
+      <c r="AW27" s="10">
+        <f t="shared" si="158"/>
         <v>0.20454125820676983</v>
       </c>
-      <c r="AT27" s="10">
-        <f t="shared" si="164"/>
+      <c r="AX27" s="10">
+        <f t="shared" si="158"/>
         <v>0.37623430604373276</v>
       </c>
-      <c r="AU27" s="10">
-        <f t="shared" si="164"/>
+      <c r="AY27" s="10">
+        <f t="shared" si="158"/>
         <v>0.21695366571345676</v>
       </c>
-      <c r="AV27" s="10">
-        <f t="shared" si="164"/>
+      <c r="AZ27" s="10">
+        <f t="shared" si="158"/>
         <v>9.399517263985091E-2</v>
       </c>
-      <c r="AW27" s="10">
-        <f t="shared" si="164"/>
+      <c r="BA27" s="10">
+        <f t="shared" si="158"/>
         <v>0.1182957412988368</v>
       </c>
-      <c r="AX27" s="10">
-        <f t="shared" si="164"/>
+      <c r="BB27" s="10">
+        <f t="shared" si="158"/>
         <v>0.1099089224666614</v>
       </c>
-      <c r="AY27" s="10">
-        <f t="shared" si="164"/>
-        <v>0.11548180995957402</v>
-      </c>
-      <c r="AZ27" s="10">
-        <f t="shared" si="164"/>
-        <v>7.3413999315320222E-2</v>
-      </c>
-      <c r="BA27" s="10">
-        <f t="shared" si="164"/>
-        <v>6.3775783872743963E-2</v>
-      </c>
-      <c r="BB27" s="10">
-        <f t="shared" si="164"/>
-        <v>4.8103800846839295E-2</v>
-      </c>
       <c r="BC27" s="10">
-        <f t="shared" si="164"/>
-        <v>3.2206188535998548E-2</v>
+        <f t="shared" si="158"/>
+        <v>0.12377754683294695</v>
       </c>
       <c r="BD27" s="10">
-        <f t="shared" si="164"/>
-        <v>2.6149176500987359E-2</v>
+        <f t="shared" si="158"/>
+        <v>7.3470158622113368E-2</v>
       </c>
       <c r="BE27" s="10">
-        <f t="shared" si="164"/>
-        <v>2.0000000000000018E-2</v>
+        <f t="shared" si="158"/>
+        <v>6.3831564103226546E-2</v>
       </c>
       <c r="BF27" s="10">
-        <f t="shared" si="157"/>
-        <v>1.6172252476597704E-2</v>
+        <f t="shared" si="158"/>
+        <v>4.8145322600843921E-2</v>
       </c>
       <c r="BG27" s="10">
         <f t="shared" si="158"/>
-        <v>9.9999999999997868E-3</v>
+        <v>3.223369924135322E-2</v>
       </c>
       <c r="BH27" s="10">
-        <f t="shared" si="159"/>
-        <v>1.0000000000000231E-2</v>
+        <f t="shared" si="158"/>
+        <v>2.6162871460386317E-2</v>
       </c>
       <c r="BI27" s="10">
-        <f t="shared" si="160"/>
+        <f t="shared" si="158"/>
+        <v>2.000000000000024E-2</v>
+      </c>
+      <c r="BJ27" s="10">
+        <f t="shared" si="151"/>
+        <v>1.6185916271911349E-2</v>
+      </c>
+      <c r="BK27" s="10">
+        <f t="shared" si="152"/>
         <v>1.0000000000000009E-2</v>
       </c>
+      <c r="BL27" s="10">
+        <f t="shared" si="153"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="BM27" s="10">
+        <f t="shared" si="154"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
     </row>
-    <row r="28" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B28" s="1" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="10">
-        <f t="shared" ref="C28:F28" si="165">C7/C5</f>
+        <f t="shared" ref="C28:F28" si="159">C7/C5</f>
         <v>0.37167497339978722</v>
       </c>
       <c r="D28" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="159"/>
         <v>0.38213674087735477</v>
       </c>
       <c r="E28" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="159"/>
         <v>0.37022220190197513</v>
       </c>
       <c r="F28" s="10">
-        <f t="shared" si="165"/>
+        <f t="shared" si="159"/>
         <v>0.36324086480406265</v>
       </c>
       <c r="G28" s="10">
@@ -7137,236 +7234,240 @@
         <v>0.39784883037498531</v>
       </c>
       <c r="H28" s="10">
-        <f t="shared" ref="H28:V28" si="166">H7/H5</f>
+        <f t="shared" ref="H28:V28" si="160">H7/H5</f>
         <v>0.4207918919941005</v>
       </c>
       <c r="I28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.4166607748868778</v>
       </c>
       <c r="J28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.38126355635991876</v>
       </c>
       <c r="K28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.4318257956448911</v>
       </c>
       <c r="L28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.42689735663365086</v>
       </c>
       <c r="M28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.40981123447792972</v>
       </c>
       <c r="N28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.38267552637899288</v>
       </c>
       <c r="O28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.41344165827280921</v>
       </c>
       <c r="P28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.40772899046247973</v>
       </c>
       <c r="Q28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.40604295595194756</v>
       </c>
       <c r="R28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.36853171916689897</v>
       </c>
       <c r="S28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.42495254243535635</v>
       </c>
       <c r="T28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.43247258577997877</v>
       </c>
       <c r="U28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.43210121647475003</v>
       </c>
       <c r="V28" s="10">
-        <f t="shared" si="166"/>
+        <f t="shared" si="160"/>
         <v>0.39717783017494834</v>
       </c>
       <c r="W28" s="10">
-        <f t="shared" ref="W28:AE28" si="167">W7/W5</f>
+        <f t="shared" ref="W28:AE28" si="161">W7/W5</f>
         <v>0.42891862182680085</v>
       </c>
       <c r="X28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.4521008957883102</v>
       </c>
       <c r="Y28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.44714833085498934</v>
       </c>
       <c r="Z28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.42602075011393797</v>
       </c>
       <c r="AA28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.46771306082067871</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.48376654785203488</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.47567495789157344</v>
       </c>
       <c r="AD28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.45544566106342044</v>
       </c>
       <c r="AE28" s="10">
-        <f t="shared" si="167"/>
+        <f t="shared" si="161"/>
         <v>0.49318624269954575</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" ref="AF28:AH28" si="168">AF7/AF5</f>
+        <f t="shared" ref="AF28:AH28" si="162">AF7/AF5</f>
         <v>0.50137521371564497</v>
       </c>
       <c r="AG28" s="10">
-        <f t="shared" si="168"/>
+        <f t="shared" si="162"/>
         <v>0.49031640829069029</v>
       </c>
       <c r="AH28" s="10">
-        <f t="shared" si="168"/>
+        <f t="shared" si="162"/>
         <v>0.47339077276987307</v>
       </c>
       <c r="AI28" s="10">
-        <f t="shared" ref="AI28:AL28" si="169">AI7/AI5</f>
+        <f t="shared" ref="AI28:AL28" si="163">AI7/AI5</f>
         <v>0.50550855351487467</v>
       </c>
       <c r="AJ28" s="10">
-        <f t="shared" si="169"/>
+        <f t="shared" si="163"/>
         <v>0.51813931855314788</v>
       </c>
       <c r="AK28" s="10">
-        <f t="shared" si="169"/>
+        <f t="shared" si="163"/>
         <v>0.50785096215220149</v>
       </c>
       <c r="AL28" s="10">
-        <f t="shared" si="169"/>
-        <v>0.49</v>
-      </c>
-      <c r="AN28" s="10">
-        <f t="shared" ref="AN28:BE28" si="170">AN7/AN5</f>
+        <f t="shared" si="163"/>
+        <v>0.48469440356911886</v>
+      </c>
+      <c r="AM28" s="10"/>
+      <c r="AN28" s="10"/>
+      <c r="AO28" s="10"/>
+      <c r="AP28" s="10"/>
+      <c r="AR28" s="10">
+        <f t="shared" ref="AR28:BI28" si="164">AR7/AR5</f>
         <v>0.29482626871038792</v>
       </c>
-      <c r="AO28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AS28" s="10">
+        <f t="shared" si="164"/>
         <v>0.33040203353083003</v>
       </c>
-      <c r="AP28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AT28" s="10">
+        <f t="shared" si="164"/>
         <v>0.35093060366064405</v>
       </c>
-      <c r="AQ28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AU28" s="10">
+        <f t="shared" si="164"/>
         <v>0.3706835482891615</v>
       </c>
-      <c r="AR28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AV28" s="10">
+        <f t="shared" si="164"/>
         <v>0.40247416128852193</v>
       </c>
-      <c r="AS28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AW28" s="10">
+        <f t="shared" si="164"/>
         <v>0.40990011478600608</v>
       </c>
-      <c r="AT28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AX28" s="10">
+        <f t="shared" si="164"/>
         <v>0.3956779186870571</v>
       </c>
-      <c r="AU28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AY28" s="10">
+        <f t="shared" si="164"/>
         <v>0.42032514441639601</v>
       </c>
-      <c r="AV28" s="10">
-        <f t="shared" si="170"/>
+      <c r="AZ28" s="10">
+        <f t="shared" si="164"/>
         <v>0.43805339865326287</v>
       </c>
-      <c r="AW28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BA28" s="10">
+        <f t="shared" si="164"/>
         <v>0.46982088955000567</v>
       </c>
-      <c r="AX28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BB28" s="10">
+        <f t="shared" si="164"/>
         <v>0.48854393464156787</v>
       </c>
-      <c r="AY28" s="10">
-        <f t="shared" si="170"/>
-        <v>0.50454316970664292</v>
-      </c>
-      <c r="AZ28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BC28" s="10">
+        <f t="shared" si="164"/>
+        <v>0.50285664868242663</v>
+      </c>
+      <c r="BD28" s="10">
+        <f t="shared" si="164"/>
         <v>0.51</v>
       </c>
-      <c r="BA28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BE28" s="10">
+        <f t="shared" si="164"/>
         <v>0.52</v>
       </c>
-      <c r="BB28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BF28" s="10">
+        <f t="shared" si="164"/>
         <v>0.53</v>
       </c>
-      <c r="BC28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BG28" s="10">
+        <f t="shared" si="164"/>
         <v>0.53</v>
       </c>
-      <c r="BD28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BH28" s="10">
+        <f t="shared" si="164"/>
         <v>0.53</v>
       </c>
-      <c r="BE28" s="10">
-        <f t="shared" si="170"/>
+      <c r="BI28" s="10">
+        <f t="shared" si="164"/>
         <v>0.53</v>
       </c>
-      <c r="BF28" s="10">
-        <f t="shared" ref="BF28:BI28" si="171">BF7/BF5</f>
+      <c r="BJ28" s="10">
+        <f t="shared" ref="BJ28:BM28" si="165">BJ7/BJ5</f>
         <v>0.53</v>
       </c>
-      <c r="BG28" s="10">
-        <f t="shared" si="171"/>
+      <c r="BK28" s="10">
+        <f t="shared" si="165"/>
         <v>0.53</v>
       </c>
-      <c r="BH28" s="10">
-        <f t="shared" si="171"/>
+      <c r="BL28" s="10">
+        <f t="shared" si="165"/>
         <v>0.53</v>
       </c>
-      <c r="BI28" s="10">
-        <f t="shared" si="171"/>
+      <c r="BM28" s="10">
+        <f t="shared" si="165"/>
         <v>0.53</v>
       </c>
     </row>
-    <row r="29" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>53</v>
       </c>
       <c r="C29" s="10">
-        <f t="shared" ref="C29:F29" si="172">C14/C5</f>
+        <f t="shared" ref="C29:F29" si="166">C14/C5</f>
         <v>2.8140225121800973E-2</v>
       </c>
       <c r="D29" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="166"/>
         <v>1.6545909629824794E-2</v>
       </c>
       <c r="E29" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="166"/>
         <v>7.932516459400147E-3</v>
       </c>
       <c r="F29" s="10">
-        <f t="shared" si="172"/>
+        <f t="shared" si="166"/>
         <v>3.5184358096372388E-2</v>
       </c>
       <c r="G29" s="10">
@@ -7374,242 +7475,246 @@
         <v>3.7753222836095765E-2</v>
       </c>
       <c r="H29" s="10">
-        <f t="shared" ref="H29:V29" si="173">H14/H5</f>
+        <f t="shared" ref="H29:V29" si="167">H14/H5</f>
         <v>5.6404341413606625E-2</v>
       </c>
       <c r="I29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>6.5822963800904979E-2</v>
       </c>
       <c r="J29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>5.230509926363925E-2</v>
       </c>
       <c r="K29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>7.4036850921273031E-2</v>
       </c>
       <c r="L29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>4.8640464324017411E-2</v>
       </c>
       <c r="M29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>4.5112244752147014E-2</v>
       </c>
       <c r="N29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>4.4363370197971111E-2</v>
       </c>
       <c r="O29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>5.2868048560674334E-2</v>
       </c>
       <c r="P29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>6.5716663667446468E-2</v>
       </c>
       <c r="Q29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>6.4423526964480726E-2</v>
       </c>
       <c r="R29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>5.4740950181195493E-2</v>
       </c>
       <c r="S29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>8.1691516614755155E-2</v>
       </c>
       <c r="T29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>6.8111071807569867E-2</v>
       </c>
       <c r="U29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>4.3785871566256365E-2</v>
       </c>
       <c r="V29" s="10">
-        <f t="shared" si="173"/>
+        <f t="shared" si="167"/>
         <v>2.5179751404535267E-2</v>
       </c>
       <c r="W29" s="10">
-        <f t="shared" ref="W29:AE29" si="174">W14/W5</f>
+        <f t="shared" ref="W29:AE29" si="168">W14/W5</f>
         <v>3.1508708048504003E-2</v>
       </c>
       <c r="X29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>2.7360311463780786E-2</v>
       </c>
       <c r="Y29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>1.986609074672898E-2</v>
       </c>
       <c r="Z29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>1.8344012224873328E-2</v>
       </c>
       <c r="AA29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>3.7484885126964934E-2</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>5.7157527365812637E-2</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>7.8192377850618167E-2</v>
       </c>
       <c r="AD29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>7.771782938438819E-2</v>
       </c>
       <c r="AE29" s="10">
-        <f t="shared" si="174"/>
+        <f t="shared" si="168"/>
         <v>0.10680817511321374</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" ref="AF29:AH29" si="175">AF14/AF5</f>
+        <f t="shared" ref="AF29:AH29" si="169">AF14/AF5</f>
         <v>9.9150543665569649E-2</v>
       </c>
       <c r="AG29" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="169"/>
         <v>0.1095879202150091</v>
       </c>
       <c r="AH29" s="10">
-        <f t="shared" si="175"/>
+        <f t="shared" si="169"/>
         <v>0.1129068330919315</v>
       </c>
       <c r="AI29" s="10">
-        <f t="shared" ref="AI29:AL29" si="176">AI14/AI5</f>
+        <f t="shared" ref="AI29:AL29" si="170">AI14/AI5</f>
         <v>0.11823315153500742</v>
       </c>
       <c r="AJ29" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="170"/>
         <v>0.11431586981669867</v>
       </c>
       <c r="AK29" s="10">
-        <f t="shared" si="176"/>
+        <f t="shared" si="170"/>
         <v>9.6698100117112273E-2</v>
       </c>
       <c r="AL29" s="10">
-        <f t="shared" si="176"/>
-        <v>0.11244718604113167</v>
-      </c>
-      <c r="AN29" s="10">
-        <f t="shared" ref="AN29:BE29" si="177">AN14/AN5</f>
+        <f t="shared" si="170"/>
+        <v>0.11705079058607407</v>
+      </c>
+      <c r="AM29" s="10"/>
+      <c r="AN29" s="10"/>
+      <c r="AO29" s="10"/>
+      <c r="AP29" s="10"/>
+      <c r="AR29" s="10">
+        <f t="shared" ref="AR29:BI29" si="171">AR14/AR5</f>
         <v>2.000269699285297E-3</v>
       </c>
-      <c r="AO29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AS29" s="10">
+        <f t="shared" si="171"/>
         <v>2.0867988710913405E-2</v>
       </c>
-      <c r="AP29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AT29" s="10">
+        <f t="shared" si="171"/>
         <v>3.0782354195621642E-2</v>
       </c>
-      <c r="AQ29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AU29" s="10">
+        <f t="shared" si="171"/>
         <v>2.3090416380870993E-2</v>
       </c>
-      <c r="AR29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AV29" s="10">
+        <f t="shared" si="171"/>
         <v>5.3330585219441187E-2</v>
       </c>
-      <c r="AS29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AW29" s="10">
+        <f t="shared" si="171"/>
         <v>5.1831941879781268E-2</v>
       </c>
-      <c r="AT29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AX29" s="10">
+        <f t="shared" si="171"/>
         <v>5.9313999751336569E-2</v>
       </c>
-      <c r="AU29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AY29" s="10">
+        <f t="shared" si="171"/>
         <v>5.2954097509269465E-2</v>
       </c>
-      <c r="AV29" s="10">
-        <f t="shared" si="177"/>
+      <c r="AZ29" s="10">
+        <f t="shared" si="171"/>
         <v>2.3829581912242232E-2</v>
       </c>
-      <c r="AW29" s="10">
-        <f t="shared" si="177"/>
+      <c r="BA29" s="10">
+        <f t="shared" si="171"/>
         <v>6.4114407996033296E-2</v>
       </c>
-      <c r="AX29" s="10">
-        <f t="shared" si="177"/>
+      <c r="BB29" s="10">
+        <f t="shared" si="171"/>
         <v>0.1075194487420038</v>
       </c>
-      <c r="AY29" s="10">
-        <f t="shared" si="177"/>
-        <v>0.1101659059126177</v>
-      </c>
-      <c r="AZ29" s="10">
-        <f t="shared" si="177"/>
-        <v>0.1187911984065969</v>
-      </c>
-      <c r="BA29" s="10">
-        <f t="shared" si="177"/>
-        <v>0.13015151076753337</v>
-      </c>
-      <c r="BB29" s="10">
-        <f t="shared" si="177"/>
-        <v>0.14186949913873032</v>
-      </c>
       <c r="BC29" s="10">
-        <f t="shared" si="177"/>
-        <v>0.14239009364657859</v>
+        <f t="shared" si="171"/>
+        <v>0.11155296795755199</v>
       </c>
       <c r="BD29" s="10">
-        <f t="shared" si="177"/>
-        <v>0.1435490322276608</v>
+        <f t="shared" si="171"/>
+        <v>0.12090764911462969</v>
       </c>
       <c r="BE29" s="10">
-        <f t="shared" si="177"/>
-        <v>0.14364184887531348</v>
+        <f t="shared" si="171"/>
+        <v>0.13228996552991595</v>
       </c>
       <c r="BF29" s="10">
-        <f t="shared" ref="BF29:BI29" si="178">BF14/BF5</f>
-        <v>0.14462213355161269</v>
+        <f t="shared" si="171"/>
+        <v>0.14400188527506352</v>
       </c>
       <c r="BG29" s="10">
-        <f t="shared" si="178"/>
-        <v>0.14452941459442506</v>
+        <f t="shared" si="171"/>
+        <v>0.14451789117878358</v>
       </c>
       <c r="BH29" s="10">
-        <f t="shared" si="178"/>
-        <v>0.14443485961828337</v>
+        <f t="shared" si="171"/>
+        <v>0.14564869442644462</v>
       </c>
       <c r="BI29" s="10">
-        <f t="shared" si="178"/>
-        <v>0.14433843226637644</v>
-      </c>
-      <c r="BK29" t="s">
+        <f t="shared" si="171"/>
+        <v>0.14572371681997659</v>
+      </c>
+      <c r="BJ29" s="10">
+        <f t="shared" ref="BJ29:BM29" si="172">BJ14/BJ5</f>
+        <v>0.14666701871024052</v>
+      </c>
+      <c r="BK29" s="10">
+        <f t="shared" si="172"/>
+        <v>0.14654710511447322</v>
+      </c>
+      <c r="BL29" s="10">
+        <f t="shared" si="172"/>
+        <v>0.14642481699205687</v>
+      </c>
+      <c r="BM29" s="10">
+        <f t="shared" si="172"/>
+        <v>0.14630010732266213</v>
+      </c>
+      <c r="BO29" t="s">
         <v>61</v>
       </c>
-      <c r="BL29" s="10">
+      <c r="BP29" s="10">
         <v>-0.01</v>
       </c>
     </row>
-    <row r="30" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
         <v>54</v>
       </c>
       <c r="C30" s="10">
-        <f t="shared" ref="C30:F30" si="179">C8/C5</f>
+        <f t="shared" ref="C30:F30" si="173">C8/C5</f>
         <v>0.1315170521364171</v>
       </c>
       <c r="D30" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="173"/>
         <v>0.13589777367935713</v>
       </c>
       <c r="E30" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="173"/>
         <v>0.1467629846378932</v>
       </c>
       <c r="F30" s="10">
-        <f t="shared" si="179"/>
+        <f t="shared" si="173"/>
         <v>0.14844590012075495</v>
       </c>
       <c r="G30" s="10">
@@ -7617,225 +7722,229 @@
         <v>0.15265859488264566</v>
       </c>
       <c r="H30" s="10">
-        <f t="shared" ref="H30:V30" si="180">H8/H5</f>
+        <f t="shared" ref="H30:V30" si="174">H8/H5</f>
         <v>0.1499829822637371</v>
       </c>
       <c r="I30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.14626343325791855</v>
       </c>
       <c r="J30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.13854081759529172</v>
       </c>
       <c r="K30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.14407035175879396</v>
       </c>
       <c r="L30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.14622105860828971</v>
       </c>
       <c r="M30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.14528229090753206</v>
       </c>
       <c r="N30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.13943753788441965</v>
       </c>
       <c r="O30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.15282563749138525</v>
       </c>
       <c r="P30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.15527712794673384</v>
       </c>
       <c r="Q30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.15294607103853555</v>
       </c>
       <c r="R30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.1471387041535582</v>
       </c>
       <c r="S30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.15232495991448422</v>
       </c>
       <c r="T30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.15597806862398303</v>
       </c>
       <c r="U30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.16693137927300292</v>
       </c>
       <c r="V30" s="10">
-        <f t="shared" si="180"/>
+        <f t="shared" si="174"/>
         <v>0.16334090181352429</v>
       </c>
       <c r="W30" s="10">
-        <f t="shared" ref="W30:AE30" si="181">W8/W5</f>
+        <f t="shared" ref="W30:AE30" si="175">W8/W5</f>
         <v>0.17408367970870117</v>
       </c>
       <c r="X30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.1677912136859297</v>
       </c>
       <c r="Y30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.16194207756036538</v>
       </c>
       <c r="Z30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.15484169325219163</v>
       </c>
       <c r="AA30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.16414359521977417</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.15853939858464242</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.15595144077213924</v>
       </c>
       <c r="AD30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.15353522278640394</v>
       </c>
       <c r="AE30" s="10">
-        <f t="shared" si="181"/>
+        <f t="shared" si="175"/>
         <v>0.15572209080823093</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" ref="AF30:AH30" si="182">AF8/AF5</f>
+        <f t="shared" ref="AF30:AH30" si="176">AF8/AF5</f>
         <v>0.1592544787365604</v>
       </c>
       <c r="AG30" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="176"/>
         <v>0.15521441114824674</v>
       </c>
       <c r="AH30" s="10">
-        <f t="shared" si="182"/>
+        <f t="shared" si="176"/>
         <v>0.14889878163074038</v>
       </c>
       <c r="AI30" s="10">
-        <f t="shared" ref="AI30:AL30" si="183">AI8/AI5</f>
+        <f t="shared" ref="AI30:AL30" si="177">AI8/AI5</f>
         <v>0.15798467240969505</v>
       </c>
       <c r="AJ30" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="177"/>
         <v>0.15489379971616318</v>
       </c>
       <c r="AK30" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="177"/>
         <v>0.15362798261632135</v>
       </c>
       <c r="AL30" s="10">
-        <f t="shared" si="183"/>
+        <f t="shared" si="177"/>
+        <v>0.14446121113850019</v>
+      </c>
+      <c r="AM30" s="10"/>
+      <c r="AN30" s="10"/>
+      <c r="AO30" s="10"/>
+      <c r="AP30" s="10"/>
+      <c r="AR30" s="10">
+        <f t="shared" ref="AR30:BI30" si="178">AR8/AR5</f>
+        <v>0.12098260439609836</v>
+      </c>
+      <c r="AS30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.1253200755097845</v>
+      </c>
+      <c r="AT30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.12956385536852788</v>
+      </c>
+      <c r="AU30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.14195517974205302</v>
+      </c>
+      <c r="AV30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.14610948657503425</v>
+      </c>
+      <c r="AW30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.14341477673765338</v>
+      </c>
+      <c r="AX30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.15157072402503211</v>
+      </c>
+      <c r="AY30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.15987118525739535</v>
+      </c>
+      <c r="AZ30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.16401126107283703</v>
+      </c>
+      <c r="BA30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.1576572109571405</v>
+      </c>
+      <c r="BB30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.15440647439725749</v>
+      </c>
+      <c r="BC30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.15214164960302626</v>
+      </c>
+      <c r="BD30" s="10">
+        <f t="shared" si="178"/>
         <v>0.15</v>
       </c>
-      <c r="AN30" s="10">
-        <f t="shared" ref="AN30:BE30" si="184">AN8/AN5</f>
-        <v>0.12098260439609836</v>
-      </c>
-      <c r="AO30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.1253200755097845</v>
-      </c>
-      <c r="AP30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.12956385536852788</v>
-      </c>
-      <c r="AQ30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.14195517974205302</v>
-      </c>
-      <c r="AR30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.14610948657503425</v>
-      </c>
-      <c r="AS30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.14341477673765338</v>
-      </c>
-      <c r="AT30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.15157072402503211</v>
-      </c>
-      <c r="AU30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.15987118525739535</v>
-      </c>
-      <c r="AV30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.16401126107283703</v>
-      </c>
-      <c r="AW30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.1576572109571405</v>
-      </c>
-      <c r="AX30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.15440647439725749</v>
-      </c>
-      <c r="AY30" s="10">
-        <f t="shared" si="184"/>
-        <v>0.15381840796684063</v>
-      </c>
-      <c r="AZ30" s="10">
-        <f t="shared" si="184"/>
+      <c r="BE30" s="10">
+        <f t="shared" si="178"/>
         <v>0.15</v>
       </c>
-      <c r="BA30" s="10">
-        <f t="shared" si="184"/>
+      <c r="BF30" s="10">
+        <f t="shared" si="178"/>
         <v>0.15</v>
       </c>
-      <c r="BB30" s="10">
-        <f t="shared" si="184"/>
+      <c r="BG30" s="10">
+        <f t="shared" si="178"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="BH30" s="10">
+        <f t="shared" si="178"/>
         <v>0.15</v>
       </c>
-      <c r="BC30" s="10">
-        <f t="shared" si="184"/>
+      <c r="BI30" s="10">
+        <f t="shared" si="178"/>
         <v>0.15</v>
       </c>
-      <c r="BD30" s="10">
-        <f t="shared" si="184"/>
+      <c r="BJ30" s="10">
+        <f t="shared" ref="BJ30:BM30" si="179">BJ8/BJ5</f>
         <v>0.15</v>
       </c>
-      <c r="BE30" s="10">
-        <f t="shared" si="184"/>
+      <c r="BK30" s="10">
+        <f t="shared" si="179"/>
         <v>0.15</v>
       </c>
-      <c r="BF30" s="10">
-        <f t="shared" ref="BF30:BI30" si="185">BF8/BF5</f>
+      <c r="BL30" s="10">
+        <f t="shared" si="179"/>
         <v>0.15</v>
       </c>
-      <c r="BG30" s="10">
-        <f t="shared" si="185"/>
+      <c r="BM30" s="10">
+        <f t="shared" si="179"/>
         <v>0.15</v>
       </c>
-      <c r="BH30" s="10">
-        <f t="shared" si="185"/>
-        <v>0.15</v>
-      </c>
-      <c r="BI30" s="10">
-        <f t="shared" si="185"/>
-        <v>0.15</v>
-      </c>
-      <c r="BK30" t="s">
+      <c r="BO30" t="s">
         <v>62</v>
       </c>
-      <c r="BL30" s="10">
+      <c r="BP30" s="10">
         <v>0.05</v>
       </c>
     </row>
-    <row r="31" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
         <v>55</v>
       </c>
@@ -7848,240 +7957,244 @@
         <v>0.4057291666666667</v>
       </c>
       <c r="H31" s="10">
-        <f t="shared" ref="H31:V31" si="186">H9/D9-1</f>
+        <f t="shared" ref="H31:V31" si="180">H9/D9-1</f>
         <v>0.30148048452220721</v>
       </c>
       <c r="I31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.33239209358612354</v>
       </c>
       <c r="J31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.42761627906976751</v>
       </c>
       <c r="K31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>1.9370137087810302</v>
       </c>
       <c r="L31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>2.1247845570492934</v>
       </c>
       <c r="M31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>1.7853466545564638</v>
       </c>
       <c r="N31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.98330278965587459</v>
       </c>
       <c r="O31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.17635927841554189</v>
       </c>
       <c r="P31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.14594594594594601</v>
       </c>
       <c r="Q31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.19304347826086965</v>
       </c>
       <c r="R31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.23706365503080074</v>
       </c>
       <c r="S31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.33919571045576413</v>
       </c>
       <c r="T31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.33529072006160954</v>
       </c>
       <c r="U31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.310131195335277</v>
       </c>
       <c r="V31" s="10">
-        <f t="shared" si="186"/>
+        <f t="shared" si="180"/>
         <v>0.27089385011204259</v>
       </c>
       <c r="W31" s="10">
-        <f t="shared" ref="W31" si="187">W9/S9-1</f>
+        <f t="shared" ref="W31" si="181">W9/S9-1</f>
         <v>0.18850096092248569</v>
       </c>
       <c r="X31" s="10">
-        <f t="shared" ref="X31" si="188">X9/T9-1</f>
+        <f t="shared" ref="X31" si="182">X9/T9-1</f>
         <v>0.3028620863672411</v>
       </c>
       <c r="Y31" s="10">
-        <f t="shared" ref="Y31" si="189">Y9/U9-1</f>
+        <f t="shared" ref="Y31" si="183">Y9/U9-1</f>
         <v>0.35500695410292082</v>
       </c>
       <c r="Z31" s="10">
-        <f t="shared" ref="Z31" si="190">Z9/V9-1</f>
+        <f t="shared" ref="Z31" si="184">Z9/V9-1</f>
         <v>0.35923724939593815</v>
       </c>
       <c r="AA31" s="10">
-        <f t="shared" ref="AA31" si="191">AA9/W9-1</f>
+        <f t="shared" ref="AA31" si="185">AA9/W9-1</f>
         <v>0.37784665139469076</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" ref="AB31" si="192">AB9/X9-1</f>
+        <f t="shared" ref="AB31" si="186">AB9/X9-1</f>
         <v>0.21353474988933163</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" ref="AC31" si="193">AC9/Y9-1</f>
+        <f t="shared" ref="AC31" si="187">AC9/Y9-1</f>
         <v>8.8170387477546797E-2</v>
       </c>
       <c r="AD31" s="10">
-        <f t="shared" ref="AD31" si="194">AD9/Z9-1</f>
+        <f t="shared" ref="AD31" si="188">AD9/Z9-1</f>
         <v>5.880657249927923E-2</v>
       </c>
       <c r="AE31" s="10">
-        <f t="shared" ref="AE31" si="195">AE9/AA9-1</f>
+        <f t="shared" ref="AE31" si="189">AE9/AA9-1</f>
         <v>-1.2713936430317485E-3</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" ref="AF31" si="196">AF9/AB9-1</f>
+        <f t="shared" ref="AF31" si="190">AF9/AB9-1</f>
         <v>1.7007888377182923E-2</v>
       </c>
       <c r="AG31" s="10">
-        <f t="shared" ref="AG31" si="197">AG9/AC9-1</f>
+        <f t="shared" ref="AG31" si="191">AG9/AC9-1</f>
         <v>4.9143989058152204E-2</v>
       </c>
       <c r="AH31" s="10">
-        <f t="shared" ref="AH31" si="198">AH9/AD9-1</f>
+        <f t="shared" ref="AH31" si="192">AH9/AD9-1</f>
         <v>6.9561666212905049E-2</v>
       </c>
       <c r="AI31" s="10">
-        <f t="shared" ref="AI31" si="199">AI9/AE9-1</f>
+        <f t="shared" ref="AI31" si="193">AI9/AE9-1</f>
         <v>0.12583235409322358</v>
       </c>
       <c r="AJ31" s="10">
-        <f t="shared" ref="AJ31" si="200">AJ9/AF9-1</f>
+        <f t="shared" ref="AJ31" si="194">AJ9/AF9-1</f>
         <v>0.21798780487804881</v>
       </c>
       <c r="AK31" s="10">
-        <f t="shared" ref="AK31" si="201">AK9/AG9-1</f>
+        <f t="shared" ref="AK31" si="195">AK9/AG9-1</f>
         <v>0.30195549561699253</v>
       </c>
       <c r="AL31" s="10">
-        <f t="shared" ref="AL31" si="202">AL9/AH9-1</f>
-        <v>0.30000000000000004</v>
-      </c>
+        <f t="shared" ref="AL31" si="196">AL9/AH9-1</f>
+        <v>0.24725298035721854</v>
+      </c>
+      <c r="AM31" s="10"/>
       <c r="AN31" s="10"/>
-      <c r="AO31" s="10">
-        <f t="shared" ref="AO31:BE31" si="203">AO9/AN9-1</f>
+      <c r="AO31" s="10"/>
+      <c r="AP31" s="10"/>
+      <c r="AR31" s="10"/>
+      <c r="AS31" s="10">
+        <f t="shared" ref="AS31:BI31" si="197">AS9/AR9-1</f>
         <v>0.21283471837488466</v>
       </c>
-      <c r="AP31" s="10">
-        <f t="shared" si="203"/>
+      <c r="AT31" s="10">
+        <f t="shared" si="197"/>
         <v>0.37666539779215835</v>
       </c>
-      <c r="AQ31" s="10">
-        <f t="shared" si="203"/>
+      <c r="AU31" s="10">
+        <f t="shared" si="197"/>
         <v>0.3919535462463708</v>
       </c>
-      <c r="AR31" s="10">
-        <f t="shared" si="203"/>
+      <c r="AV31" s="10">
+        <f t="shared" si="197"/>
         <v>0.37206992451330945</v>
       </c>
-      <c r="AS31" s="10">
-        <f t="shared" si="203"/>
+      <c r="AW31" s="10">
+        <f t="shared" si="197"/>
         <v>1.6011292891269728</v>
       </c>
-      <c r="AT31" s="10">
-        <f t="shared" si="203"/>
+      <c r="AX31" s="10">
+        <f t="shared" si="197"/>
         <v>0.18941333630190349</v>
       </c>
-      <c r="AU31" s="10">
-        <f t="shared" si="203"/>
+      <c r="AY31" s="10">
+        <f t="shared" si="197"/>
         <v>0.31152604239786608</v>
       </c>
-      <c r="AV31" s="10">
-        <f t="shared" si="203"/>
+      <c r="AZ31" s="10">
+        <f t="shared" si="197"/>
         <v>0.3061621351602084</v>
       </c>
-      <c r="AW31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BA31" s="10">
+        <f t="shared" si="197"/>
         <v>0.16949175692841445</v>
       </c>
-      <c r="AX31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BB31" s="10">
+        <f t="shared" si="197"/>
         <v>3.4126743126766446E-2</v>
       </c>
-      <c r="AY31" s="10">
-        <f t="shared" si="203"/>
-        <v>0.23965824900614385</v>
-      </c>
-      <c r="AZ31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BC31" s="10">
+        <f t="shared" si="197"/>
+        <v>0.22561664257318403</v>
+      </c>
+      <c r="BD31" s="10">
+        <f t="shared" si="197"/>
         <v>0.12000000000000011</v>
       </c>
-      <c r="BA31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BE31" s="10">
+        <f t="shared" si="197"/>
         <v>6.0000000000000053E-2</v>
       </c>
-      <c r="BB31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BF31" s="10">
+        <f t="shared" si="197"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="BC31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BG31" s="10">
+        <f t="shared" si="197"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BD31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BH31" s="10">
+        <f t="shared" si="197"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BE31" s="10">
-        <f t="shared" si="203"/>
+      <c r="BI31" s="10">
+        <f t="shared" si="197"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BF31" s="10">
-        <f t="shared" ref="BF31" si="204">BF9/BE9-1</f>
+      <c r="BJ31" s="10">
+        <f t="shared" ref="BJ31" si="198">BJ9/BI9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BG31" s="10">
-        <f t="shared" ref="BG31" si="205">BG9/BF9-1</f>
+      <c r="BK31" s="10">
+        <f t="shared" ref="BK31" si="199">BK9/BJ9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH31" s="10">
-        <f t="shared" ref="BH31" si="206">BH9/BG9-1</f>
+      <c r="BL31" s="10">
+        <f t="shared" ref="BL31" si="200">BL9/BK9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BI31" s="10">
-        <f t="shared" ref="BI31" si="207">BI9/BH9-1</f>
+      <c r="BM31" s="10">
+        <f t="shared" ref="BM31" si="201">BM9/BL9-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BK31" t="s">
+      <c r="BO31" t="s">
         <v>63</v>
       </c>
-      <c r="BL31" s="4">
-        <f>NPV(BL30,AX21:EW21)</f>
-        <v>2000973.7734789902</v>
+      <c r="BP31" s="4">
+        <f>NPV(BP30,BD21:FA21)</f>
+        <v>2103878.5934383585</v>
       </c>
     </row>
-    <row r="32" spans="2:153" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:157" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
         <v>56</v>
       </c>
       <c r="C32" s="10">
-        <f t="shared" ref="C32:F32" si="208">C10/C5</f>
+        <f t="shared" ref="C32:F32" si="202">C10/C5</f>
         <v>0.13476507812062496</v>
       </c>
       <c r="D32" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="202"/>
         <v>0.14619944671321303</v>
       </c>
       <c r="E32" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="202"/>
         <v>0.13588149231894661</v>
       </c>
       <c r="F32" s="10">
-        <f t="shared" si="208"/>
+        <f t="shared" si="202"/>
         <v>0.10444477527996957</v>
       </c>
       <c r="G32" s="10">
@@ -8089,226 +8202,230 @@
         <v>0.13242035970377336</v>
       </c>
       <c r="H32" s="10">
-        <f t="shared" ref="H32:V32" si="209">H10/H5</f>
+        <f t="shared" ref="H32:V32" si="203">H10/H5</f>
         <v>0.13703059410808152</v>
       </c>
       <c r="I32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>0.12659078054298642</v>
       </c>
       <c r="J32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>0.10595029219568131</v>
       </c>
       <c r="K32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>6.137353433835846E-2</v>
       </c>
       <c r="L32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>6.767711816289193E-2</v>
       </c>
       <c r="M32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>6.7904145410897246E-2</v>
       </c>
       <c r="N32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>7.0587966192801679E-2</v>
       </c>
       <c r="O32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>6.3987700789906163E-2</v>
       </c>
       <c r="P32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>4.8868544178513586E-2</v>
       </c>
       <c r="Q32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>5.6518799729575124E-2</v>
       </c>
       <c r="R32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>5.8962207797379637E-2</v>
       </c>
       <c r="S32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>5.7197884221972389E-2</v>
       </c>
       <c r="T32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>6.6536964980544747E-2</v>
       </c>
       <c r="U32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>7.2284590116593869E-2</v>
       </c>
       <c r="V32" s="10">
-        <f t="shared" si="209"/>
+        <f t="shared" si="203"/>
         <v>7.8668529677175206E-2</v>
       </c>
       <c r="W32" s="10">
-        <f t="shared" ref="W32:AE32" si="210">W10/W5</f>
+        <f t="shared" ref="W32:AE32" si="204">W10/W5</f>
         <v>7.1450654391810656E-2</v>
       </c>
       <c r="X32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>8.3194483395747074E-2</v>
       </c>
       <c r="Y32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>8.6655494449296225E-2</v>
       </c>
       <c r="Z32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>8.5909224953754595E-2</v>
       </c>
       <c r="AA32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>7.9869344681920251E-2</v>
       </c>
       <c r="AB32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>7.9958030405631667E-2</v>
       </c>
       <c r="AC32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>7.3740416401668965E-2</v>
       </c>
       <c r="AD32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>7.5911532645724603E-2</v>
       </c>
       <c r="AE32" s="10">
-        <f t="shared" si="210"/>
+        <f t="shared" si="204"/>
         <v>6.7418866397326138E-2</v>
       </c>
       <c r="AF32" s="10">
-        <f t="shared" ref="AF32:AH32" si="211">AF10/AF5</f>
+        <f t="shared" ref="AF32:AH32" si="205">AF10/AF5</f>
         <v>7.1038066726585886E-2</v>
       </c>
       <c r="AG32" s="10">
-        <f t="shared" si="211"/>
+        <f t="shared" si="205"/>
         <v>6.6774926515480532E-2</v>
       </c>
       <c r="AH32" s="10">
-        <f t="shared" si="211"/>
+        <f t="shared" si="205"/>
         <v>6.9885831132316611E-2</v>
       </c>
       <c r="AI32" s="10">
-        <f t="shared" ref="AI32:AL32" si="212">AI10/AI5</f>
+        <f t="shared" ref="AI32:AL32" si="206">AI10/AI5</f>
         <v>6.2717210455652123E-2</v>
       </c>
       <c r="AJ32" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="206"/>
         <v>6.80731297181906E-2</v>
       </c>
       <c r="AK32" s="10">
-        <f t="shared" si="212"/>
+        <f t="shared" si="206"/>
         <v>6.4861324645194229E-2</v>
       </c>
       <c r="AL32" s="10">
-        <f t="shared" si="212"/>
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="AN32" s="10">
-        <f t="shared" ref="AN32:BE32" si="213">AN10/AN5</f>
+        <f t="shared" si="206"/>
+        <v>6.6845997394393258E-2</v>
+      </c>
+      <c r="AM32" s="10"/>
+      <c r="AN32" s="10"/>
+      <c r="AO32" s="10"/>
+      <c r="AP32" s="10"/>
+      <c r="AR32" s="10">
+        <f t="shared" ref="AR32:BI32" si="207">AR10/AR5</f>
         <v>0.10422753629702881</v>
       </c>
-      <c r="AO32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AS32" s="10">
+        <f t="shared" si="207"/>
         <v>0.11718969029774032</v>
       </c>
-      <c r="AP32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AT32" s="10">
+        <f t="shared" si="207"/>
         <v>0.11828336532168517</v>
       </c>
-      <c r="AQ32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AU32" s="10">
+        <f t="shared" si="207"/>
         <v>0.12717438970910686</v>
       </c>
-      <c r="AR32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AV32" s="10">
+        <f t="shared" si="207"/>
         <v>0.12382400048091993</v>
       </c>
-      <c r="AS32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AW32" s="10">
+        <f t="shared" si="207"/>
         <v>6.7299534439366607E-2</v>
       </c>
-      <c r="AT32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AX32" s="10">
+        <f t="shared" si="207"/>
         <v>5.7011272742343237E-2</v>
       </c>
-      <c r="AU32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AY32" s="10">
+        <f t="shared" si="207"/>
         <v>6.9283686161993263E-2</v>
       </c>
-      <c r="AV32" s="10">
-        <f t="shared" si="213"/>
+      <c r="AZ32" s="10">
+        <f t="shared" si="207"/>
         <v>8.2177815219569517E-2</v>
       </c>
-      <c r="AW32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BA32" s="10">
+        <f t="shared" si="207"/>
         <v>7.7194081265168718E-2</v>
       </c>
-      <c r="AX32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BB32" s="10">
+        <f t="shared" si="207"/>
         <v>6.8824172086293947E-2</v>
       </c>
-      <c r="AY32" s="10">
-        <f t="shared" si="213"/>
-        <v>6.5189747038517099E-2</v>
-      </c>
-      <c r="AZ32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BC32" s="10">
+        <f t="shared" si="207"/>
+        <v>6.5737790895548209E-2</v>
+      </c>
+      <c r="BD32" s="10">
+        <f t="shared" si="207"/>
         <v>0.06</v>
       </c>
-      <c r="BA32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BE32" s="10">
+        <f t="shared" si="207"/>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="BF32" s="10">
+        <f t="shared" si="207"/>
         <v>0.06</v>
       </c>
-      <c r="BB32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BG32" s="10">
+        <f t="shared" si="207"/>
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="BH32" s="10">
+        <f t="shared" si="207"/>
         <v>0.06</v>
       </c>
-      <c r="BC32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BI32" s="10">
+        <f t="shared" si="207"/>
         <v>0.06</v>
       </c>
-      <c r="BD32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BJ32" s="10">
+        <f t="shared" ref="BJ32:BM32" si="208">BJ10/BJ5</f>
+        <v>6.0000000000000005E-2</v>
+      </c>
+      <c r="BK32" s="10">
+        <f t="shared" si="208"/>
         <v>0.06</v>
       </c>
-      <c r="BE32" s="10">
-        <f t="shared" si="213"/>
+      <c r="BL32" s="10">
+        <f t="shared" si="208"/>
         <v>0.06</v>
       </c>
-      <c r="BF32" s="10">
-        <f t="shared" ref="BF32:BI32" si="214">BF10/BF5</f>
+      <c r="BM32" s="10">
+        <f t="shared" si="208"/>
         <v>0.06</v>
       </c>
-      <c r="BG32" s="10">
-        <f t="shared" si="214"/>
-        <v>0.06</v>
-      </c>
-      <c r="BH32" s="10">
-        <f t="shared" si="214"/>
-        <v>0.06</v>
-      </c>
-      <c r="BI32" s="10">
-        <f t="shared" si="214"/>
-        <v>0.06</v>
-      </c>
-      <c r="BK32" t="s">
+      <c r="BO32" t="s">
         <v>64</v>
       </c>
-      <c r="BL32" s="4">
+      <c r="BP32" s="4">
         <f>Main!D8</f>
-        <v>48579</v>
+        <v>57381</v>
       </c>
     </row>
-    <row r="33" spans="2:64" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>57</v>
       </c>
@@ -8321,484 +8438,492 @@
         <v>0.34213836477987414</v>
       </c>
       <c r="H33" s="10">
-        <f t="shared" ref="H33:V33" si="215">H11/D11-1</f>
+        <f t="shared" ref="H33:V33" si="209">H11/D11-1</f>
         <v>0.27116704805491998</v>
       </c>
       <c r="I33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>8.4375000000000089E-2</v>
       </c>
       <c r="J33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>6.9923371647509613E-2</v>
       </c>
       <c r="K33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>9.9343955014058016E-2</v>
       </c>
       <c r="L33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.14311431143114306</v>
       </c>
       <c r="M33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.29490874159462055</v>
       </c>
       <c r="N33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.26410026857654434</v>
       </c>
       <c r="O33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.23785166240409206</v>
       </c>
       <c r="P33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.24409448818897639</v>
       </c>
       <c r="Q33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.23738872403560829</v>
       </c>
       <c r="R33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.39376770538243622</v>
       </c>
       <c r="S33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.36845730027548207</v>
       </c>
       <c r="T33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.36582278481012653</v>
       </c>
       <c r="U33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.29076738609112707</v>
       </c>
       <c r="V33" s="10">
-        <f t="shared" si="215"/>
+        <f t="shared" si="209"/>
         <v>0.28302845528455278</v>
       </c>
       <c r="W33" s="10">
-        <f t="shared" ref="W33" si="216">W11/S11-1</f>
+        <f t="shared" ref="W33" si="210">W11/S11-1</f>
         <v>0.30548565676899853</v>
       </c>
       <c r="X33" s="10">
-        <f t="shared" ref="X33" si="217">X11/T11-1</f>
+        <f t="shared" ref="X33" si="211">X11/T11-1</f>
         <v>0.34522706209453191</v>
       </c>
       <c r="Y33" s="10">
-        <f t="shared" ref="Y33" si="218">Y11/U11-1</f>
+        <f t="shared" ref="Y33" si="212">Y11/U11-1</f>
         <v>0.42173711100789602</v>
       </c>
       <c r="Z33" s="10">
-        <f t="shared" ref="Z33" si="219">Z11/V11-1</f>
+        <f t="shared" ref="Z33" si="213">Z11/V11-1</f>
         <v>0.32000000000000006</v>
       </c>
       <c r="AA33" s="10">
-        <f t="shared" ref="AA33" si="220">AA11/W11-1</f>
+        <f t="shared" ref="AA33" si="214">AA11/W11-1</f>
         <v>0.17309175019275247</v>
       </c>
       <c r="AB33" s="10">
-        <f t="shared" ref="AB33" si="221">AB11/X11-1</f>
+        <f t="shared" ref="AB33" si="215">AB11/X11-1</f>
         <v>0.10299689975887016</v>
       </c>
       <c r="AC33" s="10">
-        <f t="shared" ref="AC33" si="222">AC11/Y11-1</f>
+        <f t="shared" ref="AC33" si="216">AC11/Y11-1</f>
         <v>-0.16334531198954594</v>
       </c>
       <c r="AD33" s="10">
-        <f t="shared" ref="AD33" si="223">AD11/Z11-1</f>
+        <f t="shared" ref="AD33" si="217">AD11/Z11-1</f>
         <v>-9.6909690969096962E-2</v>
       </c>
       <c r="AE33" s="10">
-        <f t="shared" ref="AE33" si="224">AE11/AA11-1</f>
+        <f t="shared" ref="AE33" si="218">AE11/AA11-1</f>
         <v>-9.8915543871179734E-2</v>
       </c>
       <c r="AF33" s="10">
-        <f t="shared" ref="AF33" si="225">AF11/AB11-1</f>
+        <f t="shared" ref="AF33" si="219">AF11/AB11-1</f>
         <v>-5.0281074328544673E-2</v>
       </c>
       <c r="AG33" s="10">
-        <f t="shared" ref="AG33" si="226">AG11/AC11-1</f>
+        <f t="shared" ref="AG33" si="220">AG11/AC11-1</f>
         <v>5.9351815696993437E-2</v>
       </c>
       <c r="AH33" s="10">
-        <f t="shared" ref="AH33" si="227">AH11/AD11-1</f>
+        <f t="shared" ref="AH33" si="221">AH11/AD11-1</f>
         <v>-4.8837209302325602E-2</v>
       </c>
       <c r="AI33" s="10">
-        <f t="shared" ref="AI33" si="228">AI11/AE11-1</f>
+        <f t="shared" ref="AI33" si="222">AI11/AE11-1</f>
         <v>-4.1575492341356712E-2</v>
       </c>
       <c r="AJ33" s="10">
-        <f t="shared" ref="AJ33" si="229">AJ11/AF11-1</f>
+        <f t="shared" ref="AJ33" si="223">AJ11/AF11-1</f>
         <v>-2.4991779020059224E-2</v>
       </c>
       <c r="AK33" s="10">
-        <f t="shared" ref="AK33" si="230">AK11/AG11-1</f>
+        <f t="shared" ref="AK33" si="224">AK11/AG11-1</f>
         <v>5.9712495392554299E-2</v>
       </c>
       <c r="AL33" s="10">
-        <f t="shared" ref="AL33" si="231">AL11/AH11-1</f>
-        <v>5.0000000000000044E-2</v>
-      </c>
+        <f t="shared" ref="AL33" si="225">AL11/AH11-1</f>
+        <v>-5.5536150890674096E-2</v>
+      </c>
+      <c r="AM33" s="10"/>
       <c r="AN33" s="10"/>
-      <c r="AO33" s="10">
-        <f t="shared" ref="AO33:BE33" si="232">AO11/AN11-1</f>
+      <c r="AO33" s="10"/>
+      <c r="AP33" s="10"/>
+      <c r="AR33" s="10"/>
+      <c r="AS33" s="10">
+        <f t="shared" ref="AS33:BI33" si="226">AS11/AR11-1</f>
         <v>0.12564432989690721</v>
       </c>
-      <c r="AP33" s="10">
-        <f t="shared" si="232"/>
+      <c r="AT33" s="10">
+        <f t="shared" si="226"/>
         <v>0.39210074413279905</v>
       </c>
-      <c r="AQ33" s="10">
-        <f t="shared" si="232"/>
+      <c r="AU33" s="10">
+        <f t="shared" si="226"/>
         <v>0.51027960526315796</v>
       </c>
-      <c r="AR33" s="10">
-        <f t="shared" si="232"/>
+      <c r="AV33" s="10">
+        <f t="shared" si="226"/>
         <v>0.18050639803974944</v>
       </c>
-      <c r="AS33" s="10">
-        <f t="shared" si="232"/>
+      <c r="AW33" s="10">
+        <f t="shared" si="226"/>
         <v>0.19995387453874547</v>
       </c>
-      <c r="AT33" s="10">
-        <f t="shared" si="232"/>
+      <c r="AX33" s="10">
+        <f t="shared" si="226"/>
         <v>0.28156832596578907</v>
       </c>
-      <c r="AU33" s="10">
-        <f t="shared" si="232"/>
+      <c r="AY33" s="10">
+        <f t="shared" si="226"/>
         <v>0.32318536292741462</v>
       </c>
-      <c r="AV33" s="10">
-        <f t="shared" si="232"/>
+      <c r="AZ33" s="10">
+        <f t="shared" si="226"/>
         <v>0.34772753031848569</v>
       </c>
-      <c r="AW33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BA33" s="10">
+        <f t="shared" si="226"/>
         <v>-6.3072912286603611E-3</v>
       </c>
-      <c r="AX33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BB33" s="10">
+        <f t="shared" si="226"/>
         <v>-3.8676371022342559E-2</v>
       </c>
-      <c r="AY33" s="10">
-        <f t="shared" si="232"/>
-        <v>1.0137336033101407E-2</v>
-      </c>
-      <c r="AZ33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BC33" s="10">
+        <f t="shared" si="226"/>
+        <v>-1.6462716788449683E-2</v>
+      </c>
+      <c r="BD33" s="10">
+        <f t="shared" si="226"/>
         <v>3.0000000000000027E-2</v>
       </c>
-      <c r="BA33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BE33" s="10">
+        <f t="shared" si="226"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BB33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BF33" s="10">
+        <f t="shared" si="226"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BC33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BG33" s="10">
+        <f t="shared" si="226"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="BD33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BH33" s="10">
+        <f t="shared" si="226"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BE33" s="10">
-        <f t="shared" si="232"/>
+      <c r="BI33" s="10">
+        <f t="shared" si="226"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BF33" s="10">
-        <f t="shared" ref="BF33" si="233">BF11/BE11-1</f>
+      <c r="BJ33" s="10">
+        <f t="shared" ref="BJ33" si="227">BJ11/BI11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BG33" s="10">
-        <f t="shared" ref="BG33" si="234">BG11/BF11-1</f>
+      <c r="BK33" s="10">
+        <f t="shared" ref="BK33" si="228">BK11/BJ11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BH33" s="10">
-        <f t="shared" ref="BH33" si="235">BH11/BG11-1</f>
+      <c r="BL33" s="10">
+        <f t="shared" ref="BL33" si="229">BL11/BK11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BI33" s="10">
-        <f t="shared" ref="BI33" si="236">BI11/BH11-1</f>
+      <c r="BM33" s="10">
+        <f t="shared" ref="BM33" si="230">BM11/BL11-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="BK33" t="s">
+      <c r="BO33" t="s">
         <v>65</v>
       </c>
-      <c r="BL33" s="4">
-        <f>BL31+BL32</f>
-        <v>2049552.7734789902</v>
+      <c r="BP33" s="4">
+        <f>BP31+BP32</f>
+        <v>2161259.5934383585</v>
       </c>
     </row>
-    <row r="34" spans="2:64" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>47</v>
       </c>
       <c r="C34" s="10">
-        <f t="shared" ref="C34:V34" si="237">C19/C18</f>
+        <f t="shared" ref="C34:V34" si="231">C19/C18</f>
         <v>0.2402938090241343</v>
       </c>
       <c r="D34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.70120120120120122</v>
       </c>
       <c r="E34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.18354430379746836</v>
       </c>
       <c r="F34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>8.5470085470085479E-3</v>
       </c>
       <c r="G34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.14979123173277661</v>
       </c>
       <c r="H34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>2.8406909788867563E-2</v>
       </c>
       <c r="I34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.14985250737463127</v>
       </c>
       <c r="J34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>9.7611940298507463E-2</v>
       </c>
       <c r="K34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.18995682799363781</v>
       </c>
       <c r="L34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>8.8958116995500172E-2</v>
       </c>
       <c r="M34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.18768996960486323</v>
       </c>
       <c r="N34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.19393042190969653</v>
       </c>
       <c r="O34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.21992314513745195</v>
       </c>
       <c r="P34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.1581739270213792</v>
       </c>
       <c r="Q34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>8.3565868703186955E-2</v>
       </c>
       <c r="R34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>7.2891178364455897E-2</v>
       </c>
       <c r="S34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.20997273081417997</v>
       </c>
       <c r="T34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.1005327773917072</v>
       </c>
       <c r="U34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>0.26767091541135574</v>
       </c>
       <c r="V34" s="10">
-        <f t="shared" si="237"/>
+        <f t="shared" si="231"/>
         <v>4.0980313378867012E-2</v>
       </c>
       <c r="W34" s="10">
-        <f t="shared" ref="W34:AE34" si="238">W19/W18</f>
+        <f t="shared" ref="W34:AE34" si="232">W19/W18</f>
         <v>0.27008547008547007</v>
       </c>
       <c r="X34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>0.24010554089709762</v>
       </c>
       <c r="Y34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>2.34375E-2</v>
       </c>
       <c r="Z34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>1.2754677754677755</v>
       </c>
       <c r="AA34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>0.23015294974508377</v>
       </c>
       <c r="AB34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>0.10630702102340341</v>
       </c>
       <c r="AC34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>0.18918697185987365</v>
       </c>
       <c r="AD34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>0.22373228116323249</v>
       </c>
       <c r="AE34" s="10">
-        <f t="shared" si="238"/>
+        <f t="shared" si="232"/>
         <v>0.1900177154740815</v>
       </c>
       <c r="AF34" s="10">
-        <f t="shared" ref="AF34:AH34" si="239">AF19/AF18</f>
+        <f t="shared" ref="AF34:AH34" si="233">AF19/AF18</f>
         <v>0.11590685470646113</v>
       </c>
       <c r="AG34" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="233"/>
         <v>0.15002494871652713</v>
       </c>
       <c r="AH34" s="10">
-        <f t="shared" si="239"/>
+        <f t="shared" si="233"/>
         <v>0.10403150029084075</v>
       </c>
       <c r="AI34" s="10">
-        <f t="shared" ref="AI34:AL34" si="240">AI19/AI18</f>
+        <f t="shared" ref="AI34:AL34" si="234">AI19/AI18</f>
         <v>0.21001891231145348</v>
       </c>
       <c r="AJ34" s="10">
-        <f t="shared" si="240"/>
+        <f t="shared" si="234"/>
         <v>0.1283981397132857</v>
       </c>
       <c r="AK34" s="10">
-        <f t="shared" si="240"/>
+        <f t="shared" si="234"/>
         <v>0.2452964146254881</v>
       </c>
       <c r="AL34" s="10">
-        <f t="shared" si="240"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AN34" s="10">
-        <f t="shared" ref="AN34:BE34" si="241">AN19/AN18</f>
+        <f t="shared" si="234"/>
+        <v>0.18590490509302762</v>
+      </c>
+      <c r="AM34" s="10"/>
+      <c r="AN34" s="10"/>
+      <c r="AO34" s="10"/>
+      <c r="AP34" s="10"/>
+      <c r="AR34" s="10">
+        <f t="shared" ref="AR34:BI34" si="235">AR19/AR18</f>
         <v>-1.5045045045045045</v>
       </c>
-      <c r="AO34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AS34" s="10">
+        <f t="shared" si="235"/>
         <v>0.60586734693877553</v>
       </c>
-      <c r="AP34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AT34" s="10">
+        <f t="shared" si="235"/>
         <v>0.36613566289825283</v>
       </c>
-      <c r="AQ34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AU34" s="10">
+        <f t="shared" si="235"/>
         <v>0.20225899658523772</v>
       </c>
-      <c r="AR34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AV34" s="10">
+        <f t="shared" si="235"/>
         <v>0.106207264008525</v>
       </c>
-      <c r="AS34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AW34" s="10">
+        <f t="shared" si="235"/>
         <v>0.16980322003577816</v>
       </c>
-      <c r="AT34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AX34" s="10">
+        <f t="shared" si="235"/>
         <v>0.1184134337000579</v>
       </c>
-      <c r="AU34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AY34" s="10">
+        <f t="shared" si="235"/>
         <v>0.12557993237398757</v>
       </c>
-      <c r="AV34" s="10">
-        <f t="shared" si="241"/>
+      <c r="AZ34" s="10">
+        <f t="shared" si="235"/>
         <v>0.54194743935309975</v>
       </c>
-      <c r="AW34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BA34" s="10">
+        <f t="shared" si="235"/>
         <v>0.18957850733551668</v>
       </c>
-      <c r="AX34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BB34" s="10">
+        <f t="shared" si="235"/>
         <v>0.13503075174162707</v>
       </c>
-      <c r="AY34" s="10">
-        <f t="shared" si="241"/>
-        <v>0.18449972538295703</v>
-      </c>
-      <c r="AZ34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BC34" s="10">
+        <f t="shared" si="235"/>
+        <v>0.19614432078593375</v>
+      </c>
+      <c r="BD34" s="10">
+        <f t="shared" si="235"/>
         <v>0.15</v>
       </c>
-      <c r="BA34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BE34" s="10">
+        <f t="shared" si="235"/>
+        <v>0.14999999999999997</v>
+      </c>
+      <c r="BF34" s="10">
+        <f t="shared" si="235"/>
         <v>0.15</v>
       </c>
-      <c r="BB34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BG34" s="10">
+        <f t="shared" si="235"/>
         <v>0.15</v>
       </c>
-      <c r="BC34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BH34" s="10">
+        <f t="shared" si="235"/>
         <v>0.15</v>
       </c>
-      <c r="BD34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BI34" s="10">
+        <f t="shared" si="235"/>
         <v>0.15</v>
       </c>
-      <c r="BE34" s="10">
-        <f t="shared" si="241"/>
+      <c r="BJ34" s="10">
+        <f t="shared" ref="BJ34:BM34" si="236">BJ19/BJ18</f>
         <v>0.15</v>
       </c>
-      <c r="BF34" s="10">
-        <f t="shared" ref="BF34:BI34" si="242">BF19/BF18</f>
+      <c r="BK34" s="10">
+        <f t="shared" si="236"/>
         <v>0.15</v>
       </c>
-      <c r="BG34" s="10">
-        <f t="shared" si="242"/>
+      <c r="BL34" s="10">
+        <f t="shared" si="236"/>
         <v>0.15</v>
       </c>
-      <c r="BH34" s="10">
-        <f t="shared" si="242"/>
+      <c r="BM34" s="10">
+        <f t="shared" si="236"/>
         <v>0.15</v>
       </c>
-      <c r="BI34" s="10">
-        <f t="shared" si="242"/>
-        <v>0.15</v>
-      </c>
-      <c r="BK34" t="s">
+      <c r="BO34" t="s">
         <v>66</v>
       </c>
-      <c r="BL34" s="3">
-        <f>BL33/BE22</f>
-        <v>192.01356318896291</v>
+      <c r="BP34" s="3">
+        <f>BP33/BI22</f>
+        <v>204.81990081864657</v>
       </c>
     </row>
-    <row r="35" spans="2:64" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:68" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>58</v>
       </c>
       <c r="C35" s="10">
-        <f t="shared" ref="C35:F35" si="243">C21/C5</f>
+        <f t="shared" ref="C35:F35" si="237">C21/C5</f>
         <v>2.027216217729742E-2</v>
       </c>
       <c r="D35" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="237"/>
         <v>5.1903570017125542E-3</v>
       </c>
       <c r="E35" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="237"/>
         <v>5.8522311631309439E-3</v>
       </c>
       <c r="F35" s="10">
-        <f t="shared" si="243"/>
+        <f t="shared" si="237"/>
         <v>3.0701536731014178E-2</v>
       </c>
       <c r="G35" s="10">
@@ -8806,240 +8931,244 @@
         <v>3.1914893617021274E-2</v>
       </c>
       <c r="H35" s="10">
-        <f t="shared" ref="H35:V35" si="244">H21/H5</f>
+        <f t="shared" ref="H35:V35" si="238">H21/H5</f>
         <v>4.791438187800174E-2</v>
       </c>
       <c r="I35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>5.0958003393665158E-2</v>
       </c>
       <c r="J35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>4.1819211693353411E-2</v>
       </c>
       <c r="K35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>5.9648241206030149E-2</v>
       </c>
       <c r="L35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>4.1401173427544007E-2</v>
       </c>
       <c r="M35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>3.0493991226189964E-2</v>
       </c>
       <c r="N35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>3.7375481775449755E-2</v>
       </c>
       <c r="O35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>3.3597518952446587E-2</v>
       </c>
       <c r="P35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>5.896841821126507E-2</v>
       </c>
       <c r="Q35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>6.5848458058141351E-2</v>
       </c>
       <c r="R35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>5.7520608498267692E-2</v>
       </c>
       <c r="S35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>7.470650030409702E-2</v>
       </c>
       <c r="T35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>6.8783162362928904E-2</v>
       </c>
       <c r="U35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>2.8480669963541854E-2</v>
       </c>
       <c r="V35" s="10">
-        <f t="shared" si="244"/>
+        <f t="shared" si="238"/>
         <v>0.1042339824760574</v>
       </c>
       <c r="W35" s="10">
-        <f t="shared" ref="W35:AE35" si="245">W21/W5</f>
+        <f t="shared" ref="W35:AE35" si="239">W21/W5</f>
         <v>-3.3011576380062517E-2</v>
       </c>
       <c r="X35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>-1.6727980599501788E-2</v>
       </c>
       <c r="Y35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>2.2596203019645794E-2</v>
       </c>
       <c r="Z35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>1.8632208251789495E-3</v>
       </c>
       <c r="AA35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>2.4906170008951147E-2</v>
       </c>
       <c r="AB35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>5.0229567728060844E-2</v>
       </c>
       <c r="AC35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>6.9043841686293975E-2</v>
       </c>
       <c r="AD35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>6.2508457822676972E-2</v>
       </c>
       <c r="AE35" s="10">
-        <f t="shared" si="245"/>
+        <f t="shared" si="239"/>
         <v>7.2784743882271671E-2</v>
       </c>
       <c r="AF35" s="10">
-        <f t="shared" ref="AF35:AH35" si="246">AF21/AF5</f>
+        <f t="shared" ref="AF35:AH35" si="240">AF21/AF5</f>
         <v>9.1129026808220201E-2</v>
       </c>
       <c r="AG35" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="240"/>
         <v>9.6477148989469838E-2</v>
       </c>
       <c r="AH35" s="10">
-        <f t="shared" si="246"/>
+        <f t="shared" si="240"/>
         <v>0.10652210956803272</v>
       </c>
       <c r="AI35" s="10">
-        <f t="shared" ref="AI35:AL35" si="247">AI21/AI5</f>
+        <f t="shared" ref="AI35:AL35" si="241">AI21/AI5</f>
         <v>0.1100233190078822</v>
       </c>
       <c r="AJ35" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="241"/>
         <v>0.10831117100571251</v>
       </c>
       <c r="AK35" s="10">
-        <f t="shared" si="247"/>
+        <f t="shared" si="241"/>
         <v>0.11759514677885763</v>
       </c>
       <c r="AL35" s="10">
-        <f t="shared" si="247"/>
-        <v>0.10164672370844936</v>
-      </c>
-      <c r="AN35" s="10">
-        <f t="shared" ref="AN35:BE35" si="248">AN21/AN5</f>
+        <f t="shared" si="241"/>
+        <v>9.9312982107542205E-2</v>
+      </c>
+      <c r="AM35" s="10"/>
+      <c r="AN35" s="10"/>
+      <c r="AO35" s="10"/>
+      <c r="AP35" s="10"/>
+      <c r="AR35" s="10">
+        <f t="shared" ref="AR35:BI35" si="242">AR21/AR5</f>
         <v>-2.7082303231896437E-3</v>
       </c>
-      <c r="AO35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AS35" s="10">
+        <f t="shared" si="242"/>
         <v>5.5697811337681999E-3</v>
       </c>
-      <c r="AP35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AT35" s="10">
+        <f t="shared" si="242"/>
         <v>1.7435490157147373E-2</v>
       </c>
-      <c r="AQ35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AU35" s="10">
+        <f t="shared" si="242"/>
         <v>1.7052162864178651E-2</v>
       </c>
-      <c r="AR35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AV35" s="10">
+        <f t="shared" si="242"/>
         <v>4.3252736305590261E-2</v>
       </c>
-      <c r="AS35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AW35" s="10">
+        <f t="shared" si="242"/>
         <v>4.1308703060722513E-2</v>
       </c>
-      <c r="AT35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AX35" s="10">
+        <f t="shared" si="242"/>
         <v>5.5252496995316841E-2</v>
       </c>
-      <c r="AU35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AY35" s="10">
+        <f t="shared" si="242"/>
         <v>7.1014128755145567E-2</v>
       </c>
-      <c r="AV35" s="10">
-        <f t="shared" si="248"/>
+      <c r="AZ35" s="10">
+        <f t="shared" si="242"/>
         <v>-5.2958950004183018E-3</v>
       </c>
-      <c r="AW35" s="10">
-        <f t="shared" si="248"/>
+      <c r="BA35" s="10">
+        <f t="shared" si="242"/>
         <v>5.2932835755978319E-2</v>
       </c>
-      <c r="AX35" s="10">
-        <f t="shared" si="248"/>
+      <c r="BB35" s="10">
+        <f t="shared" si="242"/>
         <v>9.2871171971866534E-2</v>
       </c>
-      <c r="AY35" s="10">
-        <f t="shared" si="248"/>
-        <v>0.10908738765712016</v>
-      </c>
-      <c r="AZ35" s="10">
-        <f t="shared" si="248"/>
-        <v>0.10375939714948236</v>
-      </c>
-      <c r="BA35" s="10">
-        <f t="shared" si="248"/>
-        <v>0.11345757791221037</v>
-      </c>
-      <c r="BB35" s="10">
-        <f t="shared" si="248"/>
-        <v>0.1234991021590255</v>
-      </c>
       <c r="BC35" s="10">
-        <f t="shared" si="248"/>
-        <v>0.12407941173713076</v>
+        <f t="shared" si="242"/>
+        <v>0.10833784334183261</v>
       </c>
       <c r="BD35" s="10">
-        <f t="shared" si="248"/>
-        <v>0.12522186644222519</v>
+        <f t="shared" si="242"/>
+        <v>0.10519154918216117</v>
       </c>
       <c r="BE35" s="10">
-        <f t="shared" si="248"/>
-        <v>0.1254826983565655</v>
+        <f t="shared" si="242"/>
+        <v>0.11491736644617059</v>
       </c>
       <c r="BF35" s="10">
-        <f>BJ21/BF5</f>
-        <v>0.12953451209226577</v>
+        <f t="shared" si="242"/>
+        <v>0.12495719276436335</v>
       </c>
       <c r="BG35" s="10">
-        <f t="shared" ref="BG35:BI35" si="249">BG21/BG5</f>
-        <v>0.12666761621297809</v>
+        <f t="shared" si="242"/>
+        <v>0.12553156867034945</v>
       </c>
       <c r="BH35" s="10">
-        <f t="shared" si="249"/>
-        <v>0.12682728647211533</v>
+        <f t="shared" si="242"/>
+        <v>0.12664590439900936</v>
       </c>
       <c r="BI35" s="10">
-        <f t="shared" si="249"/>
-        <v>0.12699486995289644</v>
-      </c>
-      <c r="BK35" t="s">
+        <f t="shared" si="242"/>
+        <v>0.12688508568670559</v>
+      </c>
+      <c r="BJ35" s="10">
+        <f>BN21/BJ5</f>
+        <v>0.13081807441163329</v>
+      </c>
+      <c r="BK35" s="10">
+        <f t="shared" ref="BK35:BM35" si="243">BK21/BK5</f>
+        <v>0.12799648771300878</v>
+      </c>
+      <c r="BL35" s="10">
+        <f t="shared" si="243"/>
+        <v>0.12812137630019702</v>
+      </c>
+      <c r="BM35" s="10">
+        <f t="shared" si="243"/>
+        <v>0.12825326686343105</v>
+      </c>
+      <c r="BO35" t="s">
         <v>67</v>
       </c>
-      <c r="BL35" s="3">
+      <c r="BP35" s="3">
         <f>Main!D3</f>
-        <v>250.9</v>
+        <v>205.61</v>
       </c>
     </row>
-    <row r="36" spans="2:64" x14ac:dyDescent="0.3">
-      <c r="BK36" s="1" t="s">
+    <row r="36" spans="2:68" x14ac:dyDescent="0.3">
+      <c r="BO36" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="BL36" s="13">
-        <f>BL34/BL35-1</f>
-        <v>-0.2347008242767521</v>
+      <c r="BP36" s="13">
+        <f>BP34/BP35-1</f>
+        <v>-3.8427079488032589E-3</v>
       </c>
     </row>
-    <row r="37" spans="2:64" x14ac:dyDescent="0.3">
-      <c r="BK37" t="s">
+    <row r="37" spans="2:68" x14ac:dyDescent="0.3">
+      <c r="BO37" t="s">
         <v>69</v>
       </c>
-      <c r="BL37" s="5" t="s">
-        <v>87</v>
+      <c r="BP37" s="5" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
